--- a/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
@@ -137,7 +137,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AveragesTable" displayName="AveragesTable" ref="A1:EC11" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AveragesTable_Croatia_HN" displayName="AveragesTable_Croatia_HN" ref="A1:EC11" headerRowCount="1">
   <autoFilter ref="A1:EC11"/>
   <tableColumns count="133">
     <tableColumn id="1" name="team_name"/>

--- a/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" t="n">
         <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2275,52 +2275,52 @@
         <v>1.71</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG4" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="AI4" t="n">
-        <v>107</v>
+        <v>107.43</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>3.33</v>
+        <v>3.29</v>
       </c>
       <c r="AL4" t="n">
-        <v>4.33</v>
+        <v>4.14</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AN4" t="n">
-        <v>58.83</v>
+        <v>59</v>
       </c>
       <c r="AO4" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AQ4" t="n">
-        <v>11.5</v>
+        <v>11.57</v>
       </c>
       <c r="AR4" t="n">
-        <v>11.17</v>
+        <v>10.43</v>
       </c>
       <c r="AS4" t="n">
-        <v>8.33</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="AT4" t="n">
-        <v>2</v>
+        <v>2.29</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="AV4" t="n">
         <v>0</v>
@@ -2332,82 +2332,82 @@
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>40.67</v>
+        <v>40.43</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="BA4" t="n">
-        <v>11.17</v>
+        <v>11</v>
       </c>
       <c r="BB4" t="n">
-        <v>7.83</v>
+        <v>7.71</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.33</v>
+        <v>3.29</v>
       </c>
       <c r="BD4" t="n">
-        <v>19.83</v>
+        <v>22.29</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.54</v>
+        <v>2.71</v>
       </c>
       <c r="BH4" t="n">
-        <v>10.85</v>
+        <v>10.29</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.54</v>
+        <v>2.71</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.77</v>
+        <v>0.86</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="BP4" t="n">
-        <v>5.38</v>
+        <v>5.07</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.38</v>
+        <v>5.14</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
       </c>
       <c r="BS4" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BT4" t="n">
-        <v>46.15</v>
+        <v>50</v>
       </c>
       <c r="BU4" t="n">
-        <v>23.08</v>
+        <v>28.57</v>
       </c>
       <c r="BV4" t="n">
-        <v>7.69</v>
+        <v>14.29</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>61.54</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BY4" t="n">
         <v>4.88</v>
@@ -2416,25 +2416,25 @@
         <v>5.66</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.1</v>
+        <v>4.07</v>
       </c>
       <c r="CB4" t="n">
-        <v>4.3</v>
+        <v>4.23</v>
       </c>
       <c r="CC4" t="n">
-        <v>6.78</v>
+        <v>6.46</v>
       </c>
       <c r="CD4" t="n">
-        <v>9.84</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="CE4" t="n">
         <v>1.36</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="CH4" t="n">
         <v>1.43</v>
@@ -2443,19 +2443,19 @@
         <v>1.79</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CK4" t="n">
         <v>1.6</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CM4" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="CO4" t="n">
         <v>1.28</v>
@@ -2479,10 +2479,10 @@
         <v>1.49</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="CX4" t="n">
         <v>1.74</v>
@@ -2500,85 +2500,85 @@
         <v>1.29</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="DG4" t="n">
         <v>2.07</v>
       </c>
       <c r="DH4" t="n">
-        <v>109.62</v>
+        <v>109.64</v>
       </c>
       <c r="DI4" t="n">
         <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.61</v>
+        <v>2.64</v>
       </c>
       <c r="DK4" t="n">
-        <v>3.77</v>
+        <v>3.72</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DM4" t="n">
-        <v>62.92</v>
+        <v>62.72</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="DP4" t="n">
-        <v>12.69</v>
+        <v>12.64</v>
       </c>
       <c r="DQ4" t="n">
-        <v>11.54</v>
+        <v>11.14</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.15</v>
+        <v>8.07</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>40.31</v>
+        <v>40.21</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.46</v>
+        <v>10.43</v>
       </c>
       <c r="DY4" t="n">
         <v>7</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.46</v>
+        <v>3.43</v>
       </c>
       <c r="EA4" t="n">
-        <v>19.85</v>
+        <v>21.07</v>
       </c>
       <c r="EB4" t="n">
         <v>1.36</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="5">
@@ -4603,61 +4603,61 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D10" t="n">
         <v>7</v>
       </c>
       <c r="E10" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F10" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="G10" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="H10" t="n">
-        <v>116.5</v>
+        <v>117.86</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>3.17</v>
+        <v>3</v>
       </c>
       <c r="K10" t="n">
-        <v>4</v>
+        <v>3.43</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="M10" t="n">
-        <v>57.33</v>
+        <v>57.43</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="O10" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="P10" t="n">
-        <v>13.33</v>
+        <v>12.43</v>
       </c>
       <c r="Q10" t="n">
-        <v>12.17</v>
+        <v>12.14</v>
       </c>
       <c r="R10" t="n">
-        <v>8.33</v>
+        <v>8.43</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>1.5</v>
+        <v>1.86</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -4669,28 +4669,28 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>50.33</v>
+        <v>51.86</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="Z10" t="n">
-        <v>14.5</v>
+        <v>14.29</v>
       </c>
       <c r="AA10" t="n">
-        <v>10.17</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="AB10" t="n">
-        <v>4.33</v>
+        <v>4.57</v>
       </c>
       <c r="AC10" t="n">
-        <v>25.5</v>
+        <v>26.14</v>
       </c>
       <c r="AD10" t="n">
         <v>1.64</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -4774,70 +4774,70 @@
         <v>2.29</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="BH10" t="n">
-        <v>7.54</v>
+        <v>7.21</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.62</v>
+        <v>0.71</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="BL10" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.77</v>
+        <v>3.57</v>
       </c>
       <c r="BQ10" t="n">
-        <v>3.77</v>
+        <v>3.64</v>
       </c>
       <c r="BR10" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS10" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BT10" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BU10" t="n">
-        <v>23.08</v>
+        <v>28.57</v>
       </c>
       <c r="BV10" t="n">
-        <v>7.69</v>
+        <v>14.29</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="BZ10" t="n">
-        <v>2.92</v>
+        <v>2.78</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.44</v>
+        <v>3.46</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.61</v>
+        <v>3.59</v>
       </c>
       <c r="CC10" t="n">
         <v>4.85</v>
@@ -4849,28 +4849,28 @@
         <v>1.37</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="CG10" t="n">
         <v>2.93</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CI10" t="n">
         <v>1.88</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="CM10" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CN10" t="n">
         <v>1.6</v>
@@ -4882,7 +4882,7 @@
         <v>1.95</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.37</v>
+        <v>3.35</v>
       </c>
       <c r="CR10" t="n">
         <v>1.41</v>
@@ -4897,10 +4897,10 @@
         <v>1.4</v>
       </c>
       <c r="CV10" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CX10" t="n">
         <v>1.74</v>
@@ -4915,55 +4915,55 @@
         <v>1.61</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.53</v>
+        <v>3.5</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF10" t="n">
         <v>2.08</v>
       </c>
       <c r="DG10" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="DH10" t="n">
-        <v>108.62</v>
+        <v>109.86</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ10" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="DK10" t="n">
-        <v>3.39</v>
+        <v>3.14</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.39</v>
+        <v>0.36</v>
       </c>
       <c r="DM10" t="n">
-        <v>50.92</v>
+        <v>51.43</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.61</v>
+        <v>0.57</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="DP10" t="n">
-        <v>14.54</v>
+        <v>14</v>
       </c>
       <c r="DQ10" t="n">
         <v>11.92</v>
       </c>
       <c r="DR10" t="n">
-        <v>8.85</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="DS10" t="n">
         <v>0</v>
@@ -4975,28 +4975,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.39</v>
+        <v>0.36</v>
       </c>
       <c r="DX10" t="n">
-        <v>11</v>
+        <v>11.14</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.46</v>
+        <v>7.42</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.54</v>
+        <v>3.72</v>
       </c>
       <c r="EA10" t="n">
-        <v>21.46</v>
+        <v>22.07</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="11">

--- a/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
@@ -1379,61 +1379,61 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
         <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="H2" t="n">
-        <v>123.17</v>
+        <v>122.57</v>
       </c>
       <c r="I2" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="J2" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="K2" t="n">
-        <v>6.67</v>
+        <v>6.43</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="M2" t="n">
-        <v>70.83</v>
+        <v>71.14</v>
       </c>
       <c r="N2" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="O2" t="n">
-        <v>3.67</v>
+        <v>3.71</v>
       </c>
       <c r="P2" t="n">
-        <v>12</v>
+        <v>11.86</v>
       </c>
       <c r="Q2" t="n">
-        <v>10.5</v>
+        <v>10.86</v>
       </c>
       <c r="R2" t="n">
-        <v>6.5</v>
+        <v>6.29</v>
       </c>
       <c r="S2" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="T2" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -1445,28 +1445,28 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>60.33</v>
+        <v>59</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="Z2" t="n">
-        <v>16.83</v>
+        <v>16.29</v>
       </c>
       <c r="AA2" t="n">
-        <v>9.83</v>
+        <v>9.43</v>
       </c>
       <c r="AB2" t="n">
-        <v>7</v>
+        <v>6.86</v>
       </c>
       <c r="AC2" t="n">
-        <v>20.67</v>
+        <v>21.29</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -1550,58 +1550,58 @@
         <v>1.86</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.85</v>
+        <v>2.93</v>
       </c>
       <c r="BH2" t="n">
-        <v>11.08</v>
+        <v>11.14</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.85</v>
+        <v>2.93</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.77</v>
+        <v>0.86</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.69</v>
+        <v>5.07</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.38</v>
+        <v>6.07</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BT2" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BU2" t="n">
-        <v>15.38</v>
+        <v>21.43</v>
       </c>
       <c r="BV2" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BY2" t="n">
         <v>1.26</v>
@@ -1613,7 +1613,7 @@
         <v>4.67</v>
       </c>
       <c r="CB2" t="n">
-        <v>5.21</v>
+        <v>5.22</v>
       </c>
       <c r="CC2" t="n">
         <v>1.56</v>
@@ -1640,10 +1640,10 @@
         <v>2.03</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CM2" t="n">
         <v>2.18</v>
@@ -1655,10 +1655,10 @@
         <v>1.21</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="CR2" t="n">
         <v>1.39</v>
@@ -1670,10 +1670,10 @@
         <v>2.97</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CW2" t="n">
         <v>2.07</v>
@@ -1682,94 +1682,94 @@
         <v>1.62</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="DB2" t="n">
         <v>1.23</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="DG2" t="n">
-        <v>4.15</v>
+        <v>3.92</v>
       </c>
       <c r="DH2" t="n">
-        <v>125.7</v>
+        <v>125.22</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="DK2" t="n">
-        <v>7.46</v>
+        <v>7.29</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="DM2" t="n">
-        <v>74.31</v>
+        <v>74.22</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="DO2" t="n">
-        <v>3.31</v>
+        <v>3.36</v>
       </c>
       <c r="DP2" t="n">
-        <v>13</v>
+        <v>12.86</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.77</v>
+        <v>12.78</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.39</v>
+        <v>6.29</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>58.07</v>
+        <v>57.57</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX2" t="n">
-        <v>16.69</v>
+        <v>16.43</v>
       </c>
       <c r="DY2" t="n">
-        <v>10.77</v>
+        <v>10.5</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5.92</v>
+        <v>5.93</v>
       </c>
       <c r="EA2" t="n">
-        <v>22.62</v>
+        <v>22.79</v>
       </c>
       <c r="EB2" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="EC2" t="n">
         <v>2</v>
@@ -1782,94 +1782,94 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
         <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="F3" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="G3" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H3" t="n">
-        <v>105.29</v>
+        <v>104.62</v>
       </c>
       <c r="I3" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="J3" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="K3" t="n">
-        <v>4.29</v>
+        <v>4</v>
       </c>
       <c r="L3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="M3" t="n">
-        <v>54</v>
+        <v>50.88</v>
       </c>
       <c r="N3" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="O3" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="P3" t="n">
-        <v>11.29</v>
+        <v>10.88</v>
       </c>
       <c r="Q3" t="n">
-        <v>13.71</v>
+        <v>13.62</v>
       </c>
       <c r="R3" t="n">
-        <v>8.859999999999999</v>
+        <v>9.25</v>
       </c>
       <c r="S3" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="T3" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="U3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>53.43</v>
+        <v>52.12</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z3" t="n">
-        <v>11.43</v>
+        <v>11.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>7.29</v>
+        <v>7.12</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.14</v>
+        <v>4.38</v>
       </c>
       <c r="AC3" t="n">
-        <v>22.43</v>
+        <v>22.25</v>
       </c>
       <c r="AD3" t="n">
         <v>1.41</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -1953,70 +1953,70 @@
         <v>2.17</v>
       </c>
       <c r="BG3" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="BH3" t="n">
-        <v>8.85</v>
+        <v>8.5</v>
       </c>
       <c r="BI3" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.15</v>
+        <v>3.93</v>
       </c>
       <c r="BQ3" t="n">
-        <v>3.69</v>
+        <v>3.64</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>84.62</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BT3" t="n">
-        <v>61.54</v>
+        <v>57.14</v>
       </c>
       <c r="BU3" t="n">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="BV3" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>76.92</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BY3" t="n">
-        <v>2.65</v>
+        <v>2.61</v>
       </c>
       <c r="BZ3" t="n">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.55</v>
+        <v>3.53</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.74</v>
+        <v>3.7</v>
       </c>
       <c r="CC3" t="n">
         <v>6.36</v>
@@ -2031,22 +2031,22 @@
         <v>2.87</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="CH3" t="n">
         <v>1.37</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="CK3" t="n">
         <v>1.72</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="CM3" t="n">
         <v>2.01</v>
@@ -2061,10 +2061,10 @@
         <v>2.05</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.58</v>
+        <v>3.59</v>
       </c>
       <c r="CR3" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CS3" t="n">
         <v>3.03</v>
@@ -2073,13 +2073,13 @@
         <v>2.82</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CX3" t="n">
         <v>1.77</v>
@@ -2088,7 +2088,7 @@
         <v>2.24</v>
       </c>
       <c r="CZ3" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="DA3" t="n">
         <v>1.57</v>
@@ -2100,82 +2100,82 @@
         <v>2.13</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.82</v>
+        <v>3.81</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="DG3" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="DH3" t="n">
-        <v>101.62</v>
+        <v>101.5</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.69</v>
+        <v>2.72</v>
       </c>
       <c r="DK3" t="n">
-        <v>5</v>
+        <v>4.78</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DM3" t="n">
-        <v>55.38</v>
+        <v>53.5</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="DP3" t="n">
-        <v>11</v>
+        <v>10.79</v>
       </c>
       <c r="DQ3" t="n">
-        <v>12.69</v>
+        <v>12.71</v>
       </c>
       <c r="DR3" t="n">
-        <v>9.08</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>49.39</v>
+        <v>48.93</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX3" t="n">
-        <v>12.54</v>
+        <v>12.5</v>
       </c>
       <c r="DY3" t="n">
-        <v>8.31</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4.23</v>
+        <v>4.36</v>
       </c>
       <c r="EA3" t="n">
-        <v>20.69</v>
+        <v>20.72</v>
       </c>
       <c r="EB3" t="n">
         <v>1.49</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="4">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" t="n">
         <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
         <v>0.14</v>
@@ -2678,139 +2678,139 @@
         <v>1</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.33</v>
+        <v>2.71</v>
       </c>
       <c r="AI5" t="n">
-        <v>104.17</v>
+        <v>103.43</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>-0.14</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AL5" t="n">
-        <v>5.83</v>
+        <v>6.14</v>
       </c>
       <c r="AM5" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AN5" t="n">
-        <v>63.33</v>
+        <v>62.43</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.5</v>
+        <v>3.43</v>
       </c>
       <c r="AQ5" t="n">
-        <v>12.33</v>
+        <v>11.57</v>
       </c>
       <c r="AR5" t="n">
-        <v>14.33</v>
+        <v>15</v>
       </c>
       <c r="AS5" t="n">
-        <v>8.17</v>
+        <v>7.43</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.5</v>
+        <v>1.14</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>56.33</v>
+        <v>58.14</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>14.5</v>
+        <v>13.71</v>
       </c>
       <c r="BB5" t="n">
-        <v>9.83</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.67</v>
+        <v>4.43</v>
       </c>
       <c r="BD5" t="n">
-        <v>19.33</v>
+        <v>20.14</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.31</v>
+        <v>2.5</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.31</v>
+        <v>9.43</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.31</v>
+        <v>2.5</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.46</v>
+        <v>0.64</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.77</v>
+        <v>0.86</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.08</v>
+        <v>4.21</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.08</v>
+        <v>5.07</v>
       </c>
       <c r="BR5" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS5" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT5" t="n">
-        <v>38.46</v>
+        <v>42.86</v>
       </c>
       <c r="BU5" t="n">
-        <v>15.38</v>
+        <v>21.43</v>
       </c>
       <c r="BV5" t="n">
-        <v>0</v>
+        <v>7.14</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BY5" t="n">
         <v>1.78</v>
@@ -2819,28 +2819,28 @@
         <v>1.8</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.65</v>
+        <v>3.59</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.62</v>
+        <v>3.56</v>
       </c>
       <c r="CC5" t="n">
-        <v>1.91</v>
+        <v>2.03</v>
       </c>
       <c r="CD5" t="n">
-        <v>1.99</v>
+        <v>2.13</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.91</v>
+        <v>2.95</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.72</v>
+        <v>2.69</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CI5" t="n">
         <v>1.74</v>
@@ -2849,13 +2849,13 @@
         <v>2.01</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="CM5" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CN5" t="n">
         <v>1.6</v>
@@ -2864,19 +2864,19 @@
         <v>1.32</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.63</v>
+        <v>3.71</v>
       </c>
       <c r="CR5" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CS5" t="n">
         <v>3.15</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="CU5" t="n">
         <v>1.36</v>
@@ -2885,103 +2885,103 @@
         <v>1.79</v>
       </c>
       <c r="CW5" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CY5" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CZ5" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.07</v>
+        <v>3.21</v>
       </c>
       <c r="DH5" t="n">
-        <v>115.23</v>
+        <v>114.07</v>
       </c>
       <c r="DI5" t="n">
-        <v>0</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.54</v>
+        <v>5.71</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="DM5" t="n">
-        <v>63.53</v>
+        <v>63.07</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.46</v>
+        <v>0.42</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="DP5" t="n">
-        <v>12</v>
+        <v>11.64</v>
       </c>
       <c r="DQ5" t="n">
-        <v>14.85</v>
+        <v>15.14</v>
       </c>
       <c r="DR5" t="n">
-        <v>6.69</v>
+        <v>6.43</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>57.69</v>
+        <v>58.5</v>
       </c>
       <c r="DW5" t="n">
         <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>15.54</v>
+        <v>15.07</v>
       </c>
       <c r="DY5" t="n">
-        <v>10.15</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="DZ5" t="n">
-        <v>5.39</v>
+        <v>5.21</v>
       </c>
       <c r="EA5" t="n">
-        <v>20.77</v>
+        <v>21.07</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C6" t="n">
         <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E6" t="n">
         <v>0.29</v>
@@ -3084,49 +3084,49 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AI6" t="n">
-        <v>104.5</v>
+        <v>105.43</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AL6" t="n">
-        <v>3.5</v>
+        <v>3.29</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="AN6" t="n">
-        <v>50.33</v>
+        <v>51.43</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.5</v>
+        <v>0.71</v>
       </c>
       <c r="AP6" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ6" t="n">
-        <v>10.67</v>
+        <v>11</v>
       </c>
       <c r="AR6" t="n">
-        <v>11.33</v>
+        <v>10.86</v>
       </c>
       <c r="AS6" t="n">
-        <v>11.67</v>
+        <v>10.43</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AV6" t="n">
         <v>0</v>
@@ -3138,73 +3138,73 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>46.83</v>
+        <v>48.29</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>6.67</v>
+        <v>7.71</v>
       </c>
       <c r="BB6" t="n">
-        <v>4.17</v>
+        <v>4.86</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.5</v>
+        <v>2.86</v>
       </c>
       <c r="BD6" t="n">
-        <v>24.5</v>
+        <v>24.14</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.97</v>
+        <v>1.07</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="BH6" t="n">
-        <v>10.38</v>
+        <v>9.93</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.46</v>
+        <v>4.21</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.08</v>
+        <v>4.93</v>
       </c>
       <c r="BR6" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS6" t="n">
-        <v>76.92</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT6" t="n">
-        <v>61.54</v>
+        <v>57.14</v>
       </c>
       <c r="BU6" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BV6" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>61.54</v>
+        <v>57.14</v>
       </c>
       <c r="BY6" t="n">
         <v>2.63</v>
@@ -3222,16 +3222,16 @@
         <v>2.68</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.57</v>
+        <v>3.54</v>
       </c>
       <c r="CC6" t="n">
-        <v>4.26</v>
+        <v>4.07</v>
       </c>
       <c r="CD6" t="n">
-        <v>4.78</v>
+        <v>4.55</v>
       </c>
       <c r="CE6" t="n">
         <v>1.4</v>
@@ -3243,22 +3243,22 @@
         <v>2.78</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CJ6" t="n">
         <v>1.86</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CL6" t="n">
         <v>2.37</v>
       </c>
       <c r="CM6" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CN6" t="n">
         <v>1.58</v>
@@ -3270,7 +3270,7 @@
         <v>2.04</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.43</v>
+        <v>3.46</v>
       </c>
       <c r="CR6" t="n">
         <v>1.43</v>
@@ -3279,28 +3279,28 @@
         <v>3.08</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="CU6" t="n">
         <v>1.38</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CW6" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="CX6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CY6" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="CZ6" t="n">
         <v>1.94</v>
       </c>
-      <c r="CX6" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="CY6" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="CZ6" t="n">
-        <v>1.93</v>
-      </c>
       <c r="DA6" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="DB6" t="n">
         <v>1.34</v>
@@ -3309,49 +3309,49 @@
         <v>2.08</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.67</v>
+        <v>3.68</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="DH6" t="n">
-        <v>103.39</v>
+        <v>103.93</v>
       </c>
       <c r="DI6" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ6" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="DK6" t="n">
-        <v>3.84</v>
+        <v>3.72</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="DM6" t="n">
-        <v>54.23</v>
+        <v>54.5</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.46</v>
+        <v>0.57</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="DP6" t="n">
-        <v>10.54</v>
+        <v>10.72</v>
       </c>
       <c r="DQ6" t="n">
-        <v>11.23</v>
+        <v>11</v>
       </c>
       <c r="DR6" t="n">
-        <v>10.77</v>
+        <v>10.22</v>
       </c>
       <c r="DS6" t="n">
         <v>0</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>47.84</v>
+        <v>48.5</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>9.699999999999999</v>
+        <v>10</v>
       </c>
       <c r="DY6" t="n">
-        <v>6.31</v>
+        <v>6.5</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="EA6" t="n">
-        <v>22.23</v>
+        <v>22.22</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="7">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C7" t="n">
         <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3484,139 +3484,139 @@
         <v>2.43</v>
       </c>
       <c r="AF7" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>116</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>67.70999999999999</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>15.29</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>10.57</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>53.29</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>13.14</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>9.710000000000001</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>19.14</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>9.710000000000001</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="BK7" t="n">
         <v>0.5</v>
       </c>
-      <c r="AG7" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>109</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>5.83</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>62</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>15.33</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>51.33</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>11.33</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>8.67</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>18.17</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>9.77</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>0.46</v>
-      </c>
       <c r="BL7" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.77</v>
+        <v>3.93</v>
       </c>
       <c r="BQ7" t="n">
-        <v>6</v>
+        <v>5.79</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT7" t="n">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="BU7" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BV7" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BY7" t="n">
         <v>3.25</v>
@@ -3625,25 +3625,25 @@
         <v>3.29</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.57</v>
+        <v>3.56</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.68</v>
+        <v>3.64</v>
       </c>
       <c r="CC7" t="n">
-        <v>4.31</v>
+        <v>4.2</v>
       </c>
       <c r="CD7" t="n">
-        <v>4.77</v>
+        <v>4.58</v>
       </c>
       <c r="CE7" t="n">
         <v>1.37</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="CH7" t="n">
         <v>1.41</v>
@@ -3655,37 +3655,37 @@
         <v>1.8</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CL7" t="n">
         <v>2.16</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CO7" t="n">
         <v>1.26</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="CR7" t="n">
         <v>1.39</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CV7" t="n">
         <v>1.97</v>
@@ -3694,100 +3694,100 @@
         <v>1.84</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="DB7" t="n">
         <v>1.3</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.37</v>
+        <v>3.39</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="DG7" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="DH7" t="n">
-        <v>107.08</v>
+        <v>110.72</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.84</v>
+        <v>4.93</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="DM7" t="n">
-        <v>60.31</v>
+        <v>63.28</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="DP7" t="n">
-        <v>15.77</v>
+        <v>15.72</v>
       </c>
       <c r="DQ7" t="n">
-        <v>12.38</v>
+        <v>12.28</v>
       </c>
       <c r="DR7" t="n">
-        <v>6.46</v>
+        <v>6.29</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.16</v>
+        <v>0.22</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.16</v>
+        <v>0.22</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>51.08</v>
+        <v>52.08</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX7" t="n">
-        <v>11.38</v>
+        <v>12.28</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.7</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.69</v>
+        <v>4</v>
       </c>
       <c r="EA7" t="n">
-        <v>20.46</v>
+        <v>20.78</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="8">
@@ -3797,10 +3797,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
         <v>8</v>
@@ -3809,49 +3809,49 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="G8" t="n">
-        <v>4</v>
+        <v>3.33</v>
       </c>
       <c r="H8" t="n">
-        <v>113.6</v>
+        <v>112.33</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="J8" t="n">
-        <v>1.4</v>
+        <v>1.83</v>
       </c>
       <c r="K8" t="n">
-        <v>7.4</v>
+        <v>6.67</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="M8" t="n">
-        <v>82</v>
+        <v>76.67</v>
       </c>
       <c r="N8" t="n">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="O8" t="n">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="P8" t="n">
-        <v>14.6</v>
+        <v>14.17</v>
       </c>
       <c r="Q8" t="n">
-        <v>10.8</v>
+        <v>11.5</v>
       </c>
       <c r="R8" t="n">
-        <v>7.8</v>
+        <v>8.17</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="T8" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -3863,28 +3863,28 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>55</v>
+        <v>51.67</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="Z8" t="n">
-        <v>14.6</v>
+        <v>13.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>22.2</v>
+        <v>22.17</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AF8" t="n">
         <v>0.12</v>
@@ -3968,70 +3968,70 @@
         <v>2.25</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="BH8" t="n">
-        <v>10.15</v>
+        <v>10.07</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BO8" t="n">
         <v>1</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.62</v>
+        <v>4.71</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.46</v>
+        <v>5.29</v>
       </c>
       <c r="BR8" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BS8" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT8" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BU8" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BV8" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW8" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX8" t="n">
-        <v>38.46</v>
+        <v>42.86</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.91</v>
+        <v>2.79</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.79</v>
+        <v>2.7</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.47</v>
+        <v>3.46</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.65</v>
+        <v>3.62</v>
       </c>
       <c r="CC8" t="n">
         <v>3.76</v>
@@ -4058,106 +4058,106 @@
         <v>1.81</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="CR8" t="n">
         <v>1.4</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CV8" t="n">
         <v>1.97</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="DB8" t="n">
         <v>1.3</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.41</v>
+        <v>3.43</v>
       </c>
       <c r="DE8" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.39</v>
+        <v>2.22</v>
       </c>
       <c r="DH8" t="n">
-        <v>105.61</v>
+        <v>105.64</v>
       </c>
       <c r="DI8" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.85</v>
+        <v>4.72</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.77</v>
+        <v>0.72</v>
       </c>
       <c r="DM8" t="n">
-        <v>63.85</v>
+        <v>62.86</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.39</v>
+        <v>2.43</v>
       </c>
       <c r="DP8" t="n">
-        <v>15</v>
+        <v>14.79</v>
       </c>
       <c r="DQ8" t="n">
-        <v>13.08</v>
+        <v>13.21</v>
       </c>
       <c r="DR8" t="n">
-        <v>8.300000000000001</v>
+        <v>8.43</v>
       </c>
       <c r="DS8" t="n">
         <v>0</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>51.31</v>
+        <v>50.14</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.23</v>
+        <v>0.29</v>
       </c>
       <c r="DX8" t="n">
-        <v>12.93</v>
+        <v>12.57</v>
       </c>
       <c r="DY8" t="n">
-        <v>9.84</v>
+        <v>9.5</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="EA8" t="n">
-        <v>22.15</v>
+        <v>22.14</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -4200,61 +4200,61 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D9" t="n">
         <v>7</v>
       </c>
       <c r="E9" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="F9" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="G9" t="n">
-        <v>3.17</v>
+        <v>2.71</v>
       </c>
       <c r="H9" t="n">
-        <v>109</v>
+        <v>106.57</v>
       </c>
       <c r="I9" t="n">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2.67</v>
+        <v>2.29</v>
       </c>
       <c r="K9" t="n">
-        <v>5.83</v>
+        <v>5.43</v>
       </c>
       <c r="L9" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="M9" t="n">
-        <v>65.5</v>
+        <v>64.43000000000001</v>
       </c>
       <c r="N9" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="P9" t="n">
+        <v>12.71</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>15.43</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7.71</v>
+      </c>
+      <c r="S9" t="n">
         <v>1</v>
       </c>
-      <c r="O9" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="P9" t="n">
-        <v>11.67</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>16.83</v>
-      </c>
-      <c r="R9" t="n">
-        <v>7.17</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.17</v>
-      </c>
       <c r="T9" t="n">
-        <v>1.33</v>
+        <v>1.86</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -4266,28 +4266,28 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>53</v>
+        <v>49.86</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>16.33</v>
+        <v>15.86</v>
       </c>
       <c r="AA9" t="n">
-        <v>11.83</v>
+        <v>11.29</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.5</v>
+        <v>4.57</v>
       </c>
       <c r="AC9" t="n">
-        <v>24.33</v>
+        <v>23.71</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.67</v>
+        <v>2.29</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -4371,70 +4371,70 @@
         <v>3.43</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.62</v>
+        <v>2.79</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.46</v>
+        <v>10.5</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.62</v>
+        <v>2.79</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.77</v>
+        <v>0.86</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="BP9" t="n">
-        <v>5.08</v>
+        <v>5.14</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.38</v>
+        <v>5.36</v>
       </c>
       <c r="BR9" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS9" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BT9" t="n">
-        <v>46.15</v>
+        <v>50</v>
       </c>
       <c r="BU9" t="n">
-        <v>30.77</v>
+        <v>35.71</v>
       </c>
       <c r="BV9" t="n">
-        <v>15.38</v>
+        <v>21.43</v>
       </c>
       <c r="BW9" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX9" t="n">
-        <v>61.54</v>
+        <v>57.14</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.24</v>
+        <v>2.29</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.46</v>
+        <v>3.41</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.58</v>
+        <v>3.53</v>
       </c>
       <c r="CC9" t="n">
         <v>3.05</v>
@@ -4446,49 +4446,49 @@
         <v>1.41</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.92</v>
+        <v>2.95</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CK9" t="n">
         <v>1.59</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="CM9" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.49</v>
+        <v>3.58</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CS9" t="n">
         <v>3.16</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="CU9" t="n">
         <v>1.36</v>
@@ -4497,103 +4497,103 @@
         <v>1.81</v>
       </c>
       <c r="CW9" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="CY9" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="CZ9" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="DB9" t="n">
         <v>1.36</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.15</v>
+        <v>0.22</v>
       </c>
       <c r="DF9" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="DG9" t="n">
-        <v>3.15</v>
+        <v>2.92</v>
       </c>
       <c r="DH9" t="n">
-        <v>110.46</v>
+        <v>109.14</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>3.23</v>
+        <v>3</v>
       </c>
       <c r="DK9" t="n">
-        <v>6.23</v>
+        <v>6</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.85</v>
+        <v>0.78</v>
       </c>
       <c r="DM9" t="n">
-        <v>62.85</v>
+        <v>62.5</v>
       </c>
       <c r="DN9" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="DO9" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="DP9" t="n">
-        <v>11.62</v>
+        <v>12.14</v>
       </c>
       <c r="DQ9" t="n">
-        <v>14.69</v>
+        <v>14.14</v>
       </c>
       <c r="DR9" t="n">
-        <v>7.08</v>
+        <v>7.36</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>52</v>
+        <v>50.5</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX9" t="n">
-        <v>16.08</v>
+        <v>15.86</v>
       </c>
       <c r="DY9" t="n">
-        <v>12.08</v>
+        <v>11.79</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4</v>
+        <v>4.07</v>
       </c>
       <c r="EA9" t="n">
-        <v>23.46</v>
+        <v>23.21</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="EC9" t="n">
-        <v>3.08</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="10">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C11" t="n">
         <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E11" t="n">
         <v>0.29</v>
@@ -5096,130 +5096,130 @@
         <v>1.57</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AI11" t="n">
-        <v>91.83</v>
+        <v>92.14</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AK11" t="n">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="AL11" t="n">
-        <v>3.67</v>
+        <v>4.14</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.67</v>
+        <v>1.14</v>
       </c>
       <c r="AN11" t="n">
-        <v>42.5</v>
+        <v>44.43</v>
       </c>
       <c r="AO11" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.5</v>
+        <v>2.14</v>
       </c>
       <c r="AQ11" t="n">
-        <v>13.33</v>
+        <v>13.29</v>
       </c>
       <c r="AR11" t="n">
-        <v>11.83</v>
+        <v>11.71</v>
       </c>
       <c r="AS11" t="n">
-        <v>6.33</v>
+        <v>6</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AU11" t="n">
         <v>1</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>43.67</v>
+        <v>44.43</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BA11" t="n">
-        <v>10.33</v>
+        <v>10.14</v>
       </c>
       <c r="BB11" t="n">
-        <v>6.83</v>
+        <v>6.86</v>
       </c>
       <c r="BC11" t="n">
-        <v>3.5</v>
+        <v>3.29</v>
       </c>
       <c r="BD11" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.67</v>
+        <v>2.43</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.23</v>
+        <v>2.36</v>
       </c>
       <c r="BH11" t="n">
-        <v>9</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.23</v>
+        <v>2.36</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.62</v>
+        <v>0.71</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="BP11" t="n">
-        <v>3.85</v>
+        <v>4.29</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.15</v>
+        <v>4.93</v>
       </c>
       <c r="BR11" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS11" t="n">
-        <v>61.54</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BT11" t="n">
-        <v>46.15</v>
+        <v>50</v>
       </c>
       <c r="BU11" t="n">
-        <v>30.77</v>
+        <v>35.71</v>
       </c>
       <c r="BV11" t="n">
         <v>0</v>
@@ -5228,7 +5228,7 @@
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BY11" t="n">
         <v>3.13</v>
@@ -5237,169 +5237,169 @@
         <v>3.39</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.32</v>
+        <v>3.41</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.35</v>
+        <v>3.49</v>
       </c>
       <c r="CC11" t="n">
-        <v>3.16</v>
+        <v>4.05</v>
       </c>
       <c r="CD11" t="n">
-        <v>3.63</v>
+        <v>4.42</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CF11" t="n">
-        <v>3.05</v>
+        <v>3.01</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.59</v>
+        <v>2.64</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CJ11" t="n">
         <v>1.93</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="CM11" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CP11" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.72</v>
+        <v>3.64</v>
       </c>
       <c r="CR11" t="n">
         <v>1.46</v>
       </c>
       <c r="CS11" t="n">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="CT11" t="n">
         <v>2.7</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="CV11" t="n">
         <v>1.84</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="CZ11" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.94</v>
+        <v>3.84</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="DG11" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="DH11" t="n">
+        <v>102</v>
+      </c>
+      <c r="DI11" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="DJ11" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="DK11" t="n">
+        <v>4</v>
+      </c>
+      <c r="DL11" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="DM11" t="n">
+        <v>51</v>
+      </c>
+      <c r="DN11" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="DO11" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="DP11" t="n">
+        <v>12.58</v>
+      </c>
+      <c r="DQ11" t="n">
+        <v>12.28</v>
+      </c>
+      <c r="DR11" t="n">
+        <v>7.71</v>
+      </c>
+      <c r="DS11" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="DT11" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="DU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV11" t="n">
+        <v>45.57</v>
+      </c>
+      <c r="DW11" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="DX11" t="n">
+        <v>12.28</v>
+      </c>
+      <c r="DY11" t="n">
+        <v>8.779999999999999</v>
+      </c>
+      <c r="DZ11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="EA11" t="n">
+        <v>20.72</v>
+      </c>
+      <c r="EB11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="EC11" t="n">
         <v>2</v>
-      </c>
-      <c r="DH11" t="n">
-        <v>102.62</v>
-      </c>
-      <c r="DI11" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="DJ11" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="DK11" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="DL11" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="DM11" t="n">
-        <v>50.61</v>
-      </c>
-      <c r="DN11" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="DO11" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="DP11" t="n">
-        <v>12.54</v>
-      </c>
-      <c r="DQ11" t="n">
-        <v>12.38</v>
-      </c>
-      <c r="DR11" t="n">
-        <v>8</v>
-      </c>
-      <c r="DS11" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="DT11" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="DU11" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV11" t="n">
-        <v>45.31</v>
-      </c>
-      <c r="DW11" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="DX11" t="n">
-        <v>12.54</v>
-      </c>
-      <c r="DY11" t="n">
-        <v>8.92</v>
-      </c>
-      <c r="DZ11" t="n">
-        <v>3.61</v>
-      </c>
-      <c r="EA11" t="n">
-        <v>20.54</v>
-      </c>
-      <c r="EB11" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="EC11" t="n">
-        <v>2.08</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
@@ -1824,7 +1824,7 @@
         <v>1.62</v>
       </c>
       <c r="P3" t="n">
-        <v>10.88</v>
+        <v>11</v>
       </c>
       <c r="Q3" t="n">
         <v>13.62</v>
@@ -1863,7 +1863,7 @@
         <v>4.38</v>
       </c>
       <c r="AC3" t="n">
-        <v>22.25</v>
+        <v>22.12</v>
       </c>
       <c r="AD3" t="n">
         <v>1.41</v>
@@ -2136,7 +2136,7 @@
         <v>2.07</v>
       </c>
       <c r="DP3" t="n">
-        <v>10.79</v>
+        <v>10.86</v>
       </c>
       <c r="DQ3" t="n">
         <v>12.71</v>
@@ -2169,7 +2169,7 @@
         <v>4.36</v>
       </c>
       <c r="EA3" t="n">
-        <v>20.72</v>
+        <v>20.64</v>
       </c>
       <c r="EB3" t="n">
         <v>1.49</v>
@@ -3117,7 +3117,7 @@
         <v>11</v>
       </c>
       <c r="AR6" t="n">
-        <v>10.86</v>
+        <v>11</v>
       </c>
       <c r="AS6" t="n">
         <v>10.43</v>
@@ -3153,7 +3153,7 @@
         <v>2.86</v>
       </c>
       <c r="BD6" t="n">
-        <v>24.14</v>
+        <v>24</v>
       </c>
       <c r="BE6" t="n">
         <v>1.07</v>
@@ -3348,7 +3348,7 @@
         <v>10.72</v>
       </c>
       <c r="DQ6" t="n">
-        <v>11</v>
+        <v>11.07</v>
       </c>
       <c r="DR6" t="n">
         <v>10.22</v>
@@ -3378,7 +3378,7 @@
         <v>3.5</v>
       </c>
       <c r="EA6" t="n">
-        <v>22.22</v>
+        <v>22.14</v>
       </c>
       <c r="EB6" t="n">
         <v>1.28</v>

--- a/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
         <v>7</v>
@@ -2197,82 +2197,82 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="G4" t="n">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>111.86</v>
+        <v>114.25</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="K4" t="n">
-        <v>3.29</v>
+        <v>3.38</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>66.43000000000001</v>
+        <v>67.75</v>
       </c>
       <c r="N4" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="O4" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="P4" t="n">
-        <v>13.71</v>
+        <v>13.12</v>
       </c>
       <c r="Q4" t="n">
-        <v>11.86</v>
+        <v>13</v>
       </c>
       <c r="R4" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="S4" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="T4" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="U4" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V4" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>40</v>
+        <v>41.38</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z4" t="n">
-        <v>9.859999999999999</v>
+        <v>10.12</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.29</v>
+        <v>6.62</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.57</v>
+        <v>3.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>19.86</v>
+        <v>20</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AF4" t="n">
         <v>0.14</v>
@@ -2356,70 +2356,70 @@
         <v>2.57</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.71</v>
+        <v>2.8</v>
       </c>
       <c r="BH4" t="n">
-        <v>10.29</v>
+        <v>10.53</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.71</v>
+        <v>2.8</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="BP4" t="n">
-        <v>5.07</v>
+        <v>5.13</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.14</v>
+        <v>5.33</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
       </c>
       <c r="BS4" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BT4" t="n">
-        <v>50</v>
+        <v>53.33</v>
       </c>
       <c r="BU4" t="n">
-        <v>28.57</v>
+        <v>33.33</v>
       </c>
       <c r="BV4" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>64.29000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BY4" t="n">
-        <v>4.88</v>
+        <v>4.66</v>
       </c>
       <c r="BZ4" t="n">
-        <v>5.66</v>
+        <v>5.35</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.07</v>
+        <v>4.01</v>
       </c>
       <c r="CB4" t="n">
-        <v>4.23</v>
+        <v>4.16</v>
       </c>
       <c r="CC4" t="n">
         <v>6.46</v>
@@ -2431,31 +2431,31 @@
         <v>1.36</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="CH4" t="n">
         <v>1.43</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="CK4" t="n">
         <v>1.6</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CM4" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CO4" t="n">
         <v>1.28</v>
@@ -2470,115 +2470,115 @@
         <v>1.4</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="CT4" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="DB4" t="n">
         <v>1.29</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.34</v>
+        <v>3.33</v>
       </c>
       <c r="DE4" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="DH4" t="n">
-        <v>109.64</v>
+        <v>111.07</v>
       </c>
       <c r="DI4" t="n">
         <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.64</v>
+        <v>2.47</v>
       </c>
       <c r="DK4" t="n">
-        <v>3.72</v>
+        <v>3.73</v>
       </c>
       <c r="DL4" t="n">
         <v>0.14</v>
       </c>
       <c r="DM4" t="n">
-        <v>62.72</v>
+        <v>63.67</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="DP4" t="n">
-        <v>12.64</v>
+        <v>12.4</v>
       </c>
       <c r="DQ4" t="n">
-        <v>11.14</v>
+        <v>11.8</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.07</v>
+        <v>7.8</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>40.21</v>
+        <v>40.94</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.43</v>
+        <v>10.53</v>
       </c>
       <c r="DY4" t="n">
-        <v>7</v>
+        <v>7.13</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.43</v>
+        <v>3.4</v>
       </c>
       <c r="EA4" t="n">
         <v>21.07</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8" t="n">
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -3887,52 +3887,52 @@
         <v>1.67</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.38</v>
+        <v>1.67</v>
       </c>
       <c r="AI8" t="n">
-        <v>100.62</v>
+        <v>103.56</v>
       </c>
       <c r="AJ8" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="AL8" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="AN8" t="n">
-        <v>52.5</v>
+        <v>55.22</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.88</v>
+        <v>2.33</v>
       </c>
       <c r="AQ8" t="n">
-        <v>15.25</v>
+        <v>15.89</v>
       </c>
       <c r="AR8" t="n">
-        <v>14.5</v>
+        <v>13.89</v>
       </c>
       <c r="AS8" t="n">
-        <v>8.619999999999999</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AV8" t="n">
         <v>0</v>
@@ -3947,79 +3947,79 @@
         <v>49</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="BA8" t="n">
-        <v>11.88</v>
+        <v>12.56</v>
       </c>
       <c r="BB8" t="n">
-        <v>9.119999999999999</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.75</v>
+        <v>3.44</v>
       </c>
       <c r="BD8" t="n">
-        <v>22.12</v>
+        <v>22.22</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.14</v>
+        <v>2.27</v>
       </c>
       <c r="BH8" t="n">
-        <v>10.07</v>
+        <v>10.33</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.14</v>
+        <v>2.27</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.71</v>
+        <v>0.8</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="BO8" t="n">
         <v>1</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.71</v>
+        <v>4.8</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.29</v>
+        <v>5.47</v>
       </c>
       <c r="BR8" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BS8" t="n">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="BT8" t="n">
-        <v>35.71</v>
+        <v>40</v>
       </c>
       <c r="BU8" t="n">
-        <v>14.29</v>
+        <v>20</v>
       </c>
       <c r="BV8" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW8" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX8" t="n">
-        <v>42.86</v>
+        <v>46.67</v>
       </c>
       <c r="BY8" t="n">
         <v>2.79</v>
@@ -4028,40 +4028,40 @@
         <v>2.7</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.46</v>
+        <v>3.45</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.62</v>
+        <v>3.59</v>
       </c>
       <c r="CC8" t="n">
-        <v>3.76</v>
+        <v>3.59</v>
       </c>
       <c r="CD8" t="n">
-        <v>4.19</v>
+        <v>4</v>
       </c>
       <c r="CE8" t="n">
         <v>1.38</v>
       </c>
       <c r="CF8" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="CG8" t="n">
         <v>2.8</v>
       </c>
-      <c r="CG8" t="n">
-        <v>2.81</v>
-      </c>
       <c r="CH8" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CM8" t="n">
         <v>2.19</v>
@@ -4076,13 +4076,13 @@
         <v>1.95</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.17</v>
+        <v>3.18</v>
       </c>
       <c r="CR8" t="n">
         <v>1.4</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="CT8" t="n">
         <v>2.95</v>
@@ -4091,73 +4091,73 @@
         <v>1.4</v>
       </c>
       <c r="CV8" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="DB8" t="n">
         <v>1.3</v>
       </c>
       <c r="DC8" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.43</v>
+        <v>3.42</v>
       </c>
       <c r="DE8" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.22</v>
+        <v>2.33</v>
       </c>
       <c r="DH8" t="n">
-        <v>105.64</v>
+        <v>107.07</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.72</v>
+        <v>5.07</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.72</v>
+        <v>0.8</v>
       </c>
       <c r="DM8" t="n">
-        <v>62.86</v>
+        <v>63.8</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.43</v>
+        <v>2.67</v>
       </c>
       <c r="DP8" t="n">
-        <v>14.79</v>
+        <v>15.2</v>
       </c>
       <c r="DQ8" t="n">
-        <v>13.21</v>
+        <v>12.93</v>
       </c>
       <c r="DR8" t="n">
-        <v>8.43</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="DS8" t="n">
         <v>0</v>
@@ -4169,25 +4169,25 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>50.14</v>
+        <v>50.07</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="DX8" t="n">
-        <v>12.57</v>
+        <v>12.94</v>
       </c>
       <c r="DY8" t="n">
-        <v>9.5</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.07</v>
+        <v>3.46</v>
       </c>
       <c r="EA8" t="n">
-        <v>22.14</v>
+        <v>22.2</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="EC8" t="n">
         <v>2</v>

--- a/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
@@ -2588,94 +2588,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
         <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F5" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>3.71</v>
+        <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>124.71</v>
+        <v>124.5</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="K5" t="n">
-        <v>5.29</v>
+        <v>5.5</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>63.71</v>
+        <v>67.12</v>
       </c>
       <c r="N5" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="O5" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="P5" t="n">
-        <v>11.71</v>
+        <v>12.12</v>
       </c>
       <c r="Q5" t="n">
-        <v>15.29</v>
+        <v>15.25</v>
       </c>
       <c r="R5" t="n">
-        <v>5.43</v>
+        <v>5.25</v>
       </c>
       <c r="S5" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="T5" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="U5" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="V5" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>58.86</v>
+        <v>60</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>16.43</v>
+        <v>15.88</v>
       </c>
       <c r="AA5" t="n">
-        <v>10.43</v>
+        <v>10.12</v>
       </c>
       <c r="AB5" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="AC5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="AE5" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AF5" t="n">
         <v>0.14</v>
@@ -2759,70 +2759,70 @@
         <v>1.86</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.43</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="BO5" t="n">
         <v>1.07</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.21</v>
+        <v>4.13</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.07</v>
+        <v>5.27</v>
       </c>
       <c r="BR5" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS5" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BT5" t="n">
-        <v>42.86</v>
+        <v>40</v>
       </c>
       <c r="BU5" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BV5" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>21.43</v>
+        <v>26.67</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="CA5" t="n">
         <v>3.59</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.56</v>
+        <v>3.57</v>
       </c>
       <c r="CC5" t="n">
         <v>2.03</v>
@@ -2834,7 +2834,7 @@
         <v>1.42</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="CG5" t="n">
         <v>2.69</v>
@@ -2843,40 +2843,40 @@
         <v>1.35</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CJ5" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CL5" t="n">
         <v>2.34</v>
       </c>
       <c r="CM5" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="CO5" t="n">
         <v>1.32</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.71</v>
+        <v>3.7</v>
       </c>
       <c r="CR5" t="n">
         <v>1.44</v>
       </c>
       <c r="CS5" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="CU5" t="n">
         <v>1.36</v>
@@ -2885,103 +2885,103 @@
         <v>1.79</v>
       </c>
       <c r="CW5" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CY5" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="CZ5" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="DB5" t="n">
         <v>1.37</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.9</v>
+        <v>3.88</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF5" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.21</v>
+        <v>3.4</v>
       </c>
       <c r="DH5" t="n">
-        <v>114.07</v>
+        <v>114.67</v>
       </c>
       <c r="DI5" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.71</v>
+        <v>5.8</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="DM5" t="n">
-        <v>63.07</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.64</v>
+        <v>11.86</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15.14</v>
+        <v>15.13</v>
       </c>
       <c r="DR5" t="n">
-        <v>6.43</v>
+        <v>6.27</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>58.5</v>
+        <v>59.13</v>
       </c>
       <c r="DW5" t="n">
         <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>15.07</v>
+        <v>14.87</v>
       </c>
       <c r="DY5" t="n">
-        <v>9.859999999999999</v>
+        <v>9.73</v>
       </c>
       <c r="DZ5" t="n">
-        <v>5.21</v>
+        <v>5.13</v>
       </c>
       <c r="EA5" t="n">
-        <v>21.07</v>
+        <v>21.67</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="6">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
         <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="F6" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="G6" t="n">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>102.43</v>
+        <v>103.5</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="J6" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="K6" t="n">
-        <v>4.14</v>
+        <v>4.12</v>
       </c>
       <c r="L6" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="M6" t="n">
-        <v>57.57</v>
+        <v>57</v>
       </c>
       <c r="N6" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="O6" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="P6" t="n">
-        <v>10.43</v>
+        <v>10.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>11.14</v>
+        <v>11.12</v>
       </c>
       <c r="R6" t="n">
-        <v>10</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="S6" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="T6" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -3057,28 +3057,28 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>48.71</v>
+        <v>49.5</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>12.29</v>
+        <v>12</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.140000000000001</v>
+        <v>8</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.14</v>
+        <v>4</v>
       </c>
       <c r="AC6" t="n">
-        <v>20.29</v>
+        <v>20.62</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3162,49 +3162,49 @@
         <v>1.57</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.93</v>
+        <v>9.67</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BN6" t="n">
         <v>1.07</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.21</v>
+        <v>4</v>
       </c>
       <c r="BQ6" t="n">
         <v>4.93</v>
       </c>
       <c r="BR6" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS6" t="n">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="BT6" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BU6" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BV6" t="n">
         <v>0</v>
@@ -3213,19 +3213,19 @@
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.63</v>
+        <v>2.57</v>
       </c>
       <c r="BZ6" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.4</v>
+        <v>3.37</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="CC6" t="n">
         <v>4.07</v>
@@ -3237,10 +3237,10 @@
         <v>1.4</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="CH6" t="n">
         <v>1.37</v>
@@ -3249,13 +3249,13 @@
         <v>1.82</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CK6" t="n">
         <v>1.75</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CM6" t="n">
         <v>1.97</v>
@@ -3264,37 +3264,37 @@
         <v>1.58</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CP6" t="n">
         <v>2.04</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.46</v>
+        <v>3.47</v>
       </c>
       <c r="CR6" t="n">
         <v>1.43</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.08</v>
+        <v>3.09</v>
       </c>
       <c r="CT6" t="n">
         <v>2.83</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CZ6" t="n">
         <v>1.94</v>
@@ -3306,52 +3306,52 @@
         <v>1.34</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="DD6" t="n">
         <v>3.68</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="DH6" t="n">
-        <v>103.93</v>
+        <v>104.4</v>
       </c>
       <c r="DI6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DJ6" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="DK6" t="n">
-        <v>3.72</v>
+        <v>3.73</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DM6" t="n">
-        <v>54.5</v>
+        <v>54.4</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="DP6" t="n">
-        <v>10.72</v>
+        <v>10.6</v>
       </c>
       <c r="DQ6" t="n">
-        <v>11.07</v>
+        <v>11.06</v>
       </c>
       <c r="DR6" t="n">
-        <v>10.22</v>
+        <v>10.14</v>
       </c>
       <c r="DS6" t="n">
         <v>0</v>
@@ -3363,7 +3363,7 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>48.5</v>
+        <v>48.94</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
@@ -3372,19 +3372,19 @@
         <v>10</v>
       </c>
       <c r="DY6" t="n">
-        <v>6.5</v>
+        <v>6.53</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.5</v>
+        <v>3.47</v>
       </c>
       <c r="EA6" t="n">
-        <v>22.14</v>
+        <v>22.2</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="7">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
         <v>7</v>
@@ -3406,82 +3406,82 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="G7" t="n">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="H7" t="n">
-        <v>105.43</v>
+        <v>107.5</v>
       </c>
       <c r="I7" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="J7" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="K7" t="n">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="L7" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="M7" t="n">
-        <v>58.86</v>
+        <v>60.12</v>
       </c>
       <c r="N7" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="O7" t="n">
-        <v>0.86</v>
+        <v>1.12</v>
       </c>
       <c r="P7" t="n">
-        <v>16.14</v>
+        <v>16</v>
       </c>
       <c r="Q7" t="n">
-        <v>14</v>
+        <v>14.25</v>
       </c>
       <c r="R7" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="S7" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="T7" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="U7" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="V7" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>50.86</v>
+        <v>52.5</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>11.43</v>
+        <v>11.62</v>
       </c>
       <c r="AA7" t="n">
-        <v>6.86</v>
+        <v>7.12</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.57</v>
+        <v>4.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>22.43</v>
+        <v>21.38</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="AF7" t="n">
         <v>0.43</v>
@@ -3565,70 +3565,70 @@
         <v>1.71</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.57</v>
+        <v>2.53</v>
       </c>
       <c r="BH7" t="n">
-        <v>9.710000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.57</v>
+        <v>2.53</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="BP7" t="n">
         <v>3.93</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.79</v>
+        <v>5.87</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BT7" t="n">
-        <v>42.86</v>
+        <v>40</v>
       </c>
       <c r="BU7" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BV7" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BY7" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="BZ7" t="n">
         <v>3.29</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.56</v>
+        <v>3.54</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.64</v>
+        <v>3.62</v>
       </c>
       <c r="CC7" t="n">
         <v>4.2</v>
@@ -3640,16 +3640,16 @@
         <v>1.37</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CJ7" t="n">
         <v>1.8</v>
@@ -3658,7 +3658,7 @@
         <v>1.59</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="CM7" t="n">
         <v>2.19</v>
@@ -3670,118 +3670,118 @@
         <v>1.26</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="CR7" t="n">
         <v>1.39</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="CU7" t="n">
         <v>1.41</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CW7" t="n">
         <v>1.84</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="DB7" t="n">
         <v>1.3</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.39</v>
+        <v>3.42</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="DG7" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="DH7" t="n">
-        <v>110.72</v>
+        <v>111.47</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.93</v>
+        <v>5</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DM7" t="n">
-        <v>63.28</v>
+        <v>63.66</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="DP7" t="n">
-        <v>15.72</v>
+        <v>15.67</v>
       </c>
       <c r="DQ7" t="n">
-        <v>12.28</v>
+        <v>12.53</v>
       </c>
       <c r="DR7" t="n">
-        <v>6.29</v>
+        <v>6.4</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>52.08</v>
+        <v>52.87</v>
       </c>
       <c r="DW7" t="n">
         <v>0.14</v>
       </c>
       <c r="DX7" t="n">
-        <v>12.28</v>
+        <v>12.33</v>
       </c>
       <c r="DY7" t="n">
-        <v>8.279999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="DZ7" t="n">
         <v>4</v>
       </c>
       <c r="EA7" t="n">
-        <v>20.78</v>
+        <v>20.33</v>
       </c>
       <c r="EB7" t="n">
         <v>1.52</v>
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
         <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E9" t="n">
         <v>0.43</v>
@@ -4290,139 +4290,139 @@
         <v>2.29</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="AI9" t="n">
-        <v>111.71</v>
+        <v>112.5</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>3.71</v>
+        <v>3.75</v>
       </c>
       <c r="AL9" t="n">
-        <v>6.57</v>
+        <v>6.38</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AN9" t="n">
-        <v>60.57</v>
+        <v>58.88</v>
       </c>
       <c r="AO9" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AP9" t="n">
-        <v>3.43</v>
+        <v>3.12</v>
       </c>
       <c r="AQ9" t="n">
-        <v>11.57</v>
+        <v>12.12</v>
       </c>
       <c r="AR9" t="n">
-        <v>12.86</v>
+        <v>13.12</v>
       </c>
       <c r="AS9" t="n">
-        <v>7</v>
+        <v>7.75</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>51.14</v>
+        <v>49.25</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA9" t="n">
-        <v>15.86</v>
+        <v>15.12</v>
       </c>
       <c r="BB9" t="n">
-        <v>12.29</v>
+        <v>11.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.57</v>
+        <v>3.62</v>
       </c>
       <c r="BD9" t="n">
-        <v>22.71</v>
+        <v>22.62</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="BF9" t="n">
-        <v>3.43</v>
+        <v>3.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.79</v>
+        <v>2.73</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.5</v>
+        <v>10.53</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.79</v>
+        <v>2.73</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="BP9" t="n">
-        <v>5.14</v>
+        <v>5.07</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.36</v>
+        <v>5.47</v>
       </c>
       <c r="BR9" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BS9" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BT9" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BU9" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BV9" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BW9" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX9" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BY9" t="n">
         <v>2.29</v>
@@ -4434,13 +4434,13 @@
         <v>3.41</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.53</v>
+        <v>3.51</v>
       </c>
       <c r="CC9" t="n">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="CD9" t="n">
-        <v>3.33</v>
+        <v>3.2</v>
       </c>
       <c r="CE9" t="n">
         <v>1.41</v>
@@ -4455,22 +4455,22 @@
         <v>1.36</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CK9" t="n">
         <v>1.59</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="CM9" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="CO9" t="n">
         <v>1.33</v>
@@ -4479,7 +4479,7 @@
         <v>2.05</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.58</v>
+        <v>3.57</v>
       </c>
       <c r="CR9" t="n">
         <v>1.44</v>
@@ -4494,22 +4494,22 @@
         <v>1.36</v>
       </c>
       <c r="CV9" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CW9" t="n">
         <v>2</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="CY9" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="CZ9" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="DB9" t="n">
         <v>1.36</v>
@@ -4518,82 +4518,82 @@
         <v>2.16</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.85</v>
+        <v>3.84</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.22</v>
+        <v>0.26</v>
       </c>
       <c r="DF9" t="n">
         <v>2</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="DH9" t="n">
-        <v>109.14</v>
+        <v>109.73</v>
       </c>
       <c r="DI9" t="n">
         <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>3</v>
+        <v>3.07</v>
       </c>
       <c r="DK9" t="n">
-        <v>6</v>
+        <v>5.94</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.78</v>
+        <v>0.73</v>
       </c>
       <c r="DM9" t="n">
-        <v>62.5</v>
+        <v>61.47</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="DO9" t="n">
-        <v>3.07</v>
+        <v>2.93</v>
       </c>
       <c r="DP9" t="n">
-        <v>12.14</v>
+        <v>12.4</v>
       </c>
       <c r="DQ9" t="n">
-        <v>14.14</v>
+        <v>14.2</v>
       </c>
       <c r="DR9" t="n">
-        <v>7.36</v>
+        <v>7.73</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>50.5</v>
+        <v>49.53</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DX9" t="n">
-        <v>15.86</v>
+        <v>15.47</v>
       </c>
       <c r="DY9" t="n">
-        <v>11.79</v>
+        <v>11.4</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.07</v>
+        <v>4.06</v>
       </c>
       <c r="EA9" t="n">
-        <v>23.21</v>
+        <v>23.13</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="10">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
         <v>7</v>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E10" t="n">
         <v>0.14</v>
@@ -4696,136 +4696,136 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AI10" t="n">
-        <v>101.86</v>
+        <v>104.12</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.86</v>
+        <v>2.75</v>
       </c>
       <c r="AL10" t="n">
-        <v>2.86</v>
+        <v>2.75</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AN10" t="n">
-        <v>45.43</v>
+        <v>46.62</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AP10" t="n">
         <v>1</v>
       </c>
       <c r="AQ10" t="n">
-        <v>15.57</v>
+        <v>15</v>
       </c>
       <c r="AR10" t="n">
-        <v>11.71</v>
+        <v>11.25</v>
       </c>
       <c r="AS10" t="n">
-        <v>9.289999999999999</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="AT10" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>44.14</v>
+        <v>44.25</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="BA10" t="n">
-        <v>8</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="BB10" t="n">
-        <v>5.14</v>
+        <v>6.38</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.86</v>
+        <v>2.75</v>
       </c>
       <c r="BD10" t="n">
-        <v>18</v>
+        <v>18.75</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="BG10" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="BH10" t="n">
-        <v>7.21</v>
+        <v>7.13</v>
       </c>
       <c r="BI10" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="BL10" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.57</v>
+        <v>3.4</v>
       </c>
       <c r="BQ10" t="n">
-        <v>3.64</v>
+        <v>3.73</v>
       </c>
       <c r="BR10" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS10" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BT10" t="n">
-        <v>71.43000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BU10" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BV10" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BY10" t="n">
         <v>2.55</v>
@@ -4834,28 +4834,28 @@
         <v>2.78</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.46</v>
+        <v>3.43</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.59</v>
+        <v>3.54</v>
       </c>
       <c r="CC10" t="n">
-        <v>4.85</v>
+        <v>4.62</v>
       </c>
       <c r="CD10" t="n">
-        <v>5.31</v>
+        <v>5</v>
       </c>
       <c r="CE10" t="n">
         <v>1.37</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.93</v>
+        <v>2.91</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CI10" t="n">
         <v>1.88</v>
@@ -4864,10 +4864,10 @@
         <v>1.83</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CM10" t="n">
         <v>2</v>
@@ -4876,28 +4876,28 @@
         <v>1.6</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.35</v>
+        <v>3.37</v>
       </c>
       <c r="CR10" t="n">
         <v>1.41</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="CU10" t="n">
         <v>1.4</v>
       </c>
       <c r="CV10" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CW10" t="n">
         <v>1.87</v>
@@ -4915,88 +4915,88 @@
         <v>1.61</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="DE10" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DF10" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="DH10" t="n">
-        <v>109.86</v>
+        <v>110.53</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.93</v>
+        <v>2.87</v>
       </c>
       <c r="DK10" t="n">
-        <v>3.14</v>
+        <v>3.07</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="DM10" t="n">
-        <v>51.43</v>
+        <v>51.66</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="DP10" t="n">
-        <v>14</v>
+        <v>13.8</v>
       </c>
       <c r="DQ10" t="n">
-        <v>11.92</v>
+        <v>11.67</v>
       </c>
       <c r="DR10" t="n">
-        <v>8.859999999999999</v>
+        <v>8.67</v>
       </c>
       <c r="DS10" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DT10" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>48</v>
+        <v>47.8</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="DX10" t="n">
-        <v>11.14</v>
+        <v>11.53</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.42</v>
+        <v>7.93</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.72</v>
+        <v>3.6</v>
       </c>
       <c r="EA10" t="n">
-        <v>22.07</v>
+        <v>22.2</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="11">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
         <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E11" t="n">
         <v>0.29</v>
@@ -5096,130 +5096,130 @@
         <v>1.57</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AH11" t="n">
         <v>2</v>
       </c>
       <c r="AI11" t="n">
-        <v>92.14</v>
+        <v>90.38</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AL11" t="n">
-        <v>4.14</v>
+        <v>4.12</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AN11" t="n">
-        <v>44.43</v>
+        <v>44.12</v>
       </c>
       <c r="AO11" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AQ11" t="n">
-        <v>13.29</v>
+        <v>13.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>11.71</v>
+        <v>12.12</v>
       </c>
       <c r="AS11" t="n">
-        <v>6</v>
+        <v>6.88</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AU11" t="n">
         <v>1</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>44.43</v>
+        <v>42.88</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="BA11" t="n">
-        <v>10.14</v>
+        <v>10.12</v>
       </c>
       <c r="BB11" t="n">
-        <v>6.86</v>
+        <v>7</v>
       </c>
       <c r="BC11" t="n">
-        <v>3.29</v>
+        <v>3.12</v>
       </c>
       <c r="BD11" t="n">
-        <v>20</v>
+        <v>19.12</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.210000000000001</v>
+        <v>9.33</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BN11" t="n">
         <v>1</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.29</v>
+        <v>4.2</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.93</v>
+        <v>5.13</v>
       </c>
       <c r="BR11" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BS11" t="n">
-        <v>64.29000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BT11" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BU11" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BV11" t="n">
         <v>0</v>
@@ -5228,7 +5228,7 @@
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BY11" t="n">
         <v>3.13</v>
@@ -5237,16 +5237,16 @@
         <v>3.39</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.41</v>
+        <v>3.42</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.49</v>
+        <v>3.5</v>
       </c>
       <c r="CC11" t="n">
-        <v>4.05</v>
+        <v>4.36</v>
       </c>
       <c r="CD11" t="n">
-        <v>4.42</v>
+        <v>4.7</v>
       </c>
       <c r="CE11" t="n">
         <v>1.42</v>
@@ -5255,28 +5255,28 @@
         <v>3.01</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="CH11" t="n">
         <v>1.35</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="CM11" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CO11" t="n">
         <v>1.33</v>
@@ -5285,37 +5285,37 @@
         <v>2.07</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.64</v>
+        <v>3.63</v>
       </c>
       <c r="CR11" t="n">
         <v>1.46</v>
       </c>
       <c r="CS11" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="CT11" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="CU11" t="n">
         <v>1.35</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CW11" t="n">
         <v>1.98</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="CZ11" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="DB11" t="n">
         <v>1.36</v>
@@ -5324,79 +5324,79 @@
         <v>2.15</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.84</v>
+        <v>3.83</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="DG11" t="n">
         <v>1.93</v>
       </c>
       <c r="DH11" t="n">
-        <v>102</v>
+        <v>100.4</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.21</v>
+        <v>2.26</v>
       </c>
       <c r="DK11" t="n">
         <v>4</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="DM11" t="n">
-        <v>51</v>
+        <v>50.4</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="DP11" t="n">
-        <v>12.58</v>
+        <v>12.73</v>
       </c>
       <c r="DQ11" t="n">
-        <v>12.28</v>
+        <v>12.47</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.71</v>
+        <v>8.07</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>45.57</v>
+        <v>44.67</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="DX11" t="n">
-        <v>12.28</v>
+        <v>12.13</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.779999999999999</v>
+        <v>8.73</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="EA11" t="n">
-        <v>20.72</v>
+        <v>20.2</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="EC11" t="n">
         <v>2</v>

--- a/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="n">
         <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
         <v>0.29</v>
@@ -1472,136 +1472,136 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.57</v>
+        <v>1.88</v>
       </c>
       <c r="AH2" t="n">
-        <v>5.14</v>
+        <v>4.62</v>
       </c>
       <c r="AI2" t="n">
-        <v>127.86</v>
+        <v>121.5</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.86</v>
+        <v>2.25</v>
       </c>
       <c r="AL2" t="n">
-        <v>8.140000000000001</v>
+        <v>7.62</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AN2" t="n">
-        <v>77.29000000000001</v>
+        <v>76.62</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="AP2" t="n">
         <v>3</v>
       </c>
       <c r="AQ2" t="n">
-        <v>13.86</v>
+        <v>14</v>
       </c>
       <c r="AR2" t="n">
-        <v>14.71</v>
+        <v>14.25</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.29</v>
+        <v>6.12</v>
       </c>
       <c r="AT2" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>56.14</v>
+        <v>55.38</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="BA2" t="n">
-        <v>16.57</v>
+        <v>16</v>
       </c>
       <c r="BB2" t="n">
-        <v>11.57</v>
+        <v>11.38</v>
       </c>
       <c r="BC2" t="n">
-        <v>5</v>
+        <v>4.62</v>
       </c>
       <c r="BD2" t="n">
-        <v>24.29</v>
+        <v>24.12</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.96</v>
+        <v>1.89</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.93</v>
+        <v>2.87</v>
       </c>
       <c r="BH2" t="n">
-        <v>11.14</v>
+        <v>10.87</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.93</v>
+        <v>2.87</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="BP2" t="n">
-        <v>5.07</v>
+        <v>4.93</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.07</v>
+        <v>5.93</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BT2" t="n">
-        <v>71.43000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BU2" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BV2" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BY2" t="n">
         <v>1.26</v>
@@ -1610,34 +1610,34 @@
         <v>1.27</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.67</v>
+        <v>4.65</v>
       </c>
       <c r="CB2" t="n">
-        <v>5.22</v>
+        <v>5.17</v>
       </c>
       <c r="CC2" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CD2" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="CE2" t="n">
         <v>1.3</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.22</v>
+        <v>3.23</v>
       </c>
       <c r="CH2" t="n">
         <v>1.51</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CJ2" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="CK2" t="n">
         <v>1.59</v>
@@ -1646,7 +1646,7 @@
         <v>2.14</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="CN2" t="n">
         <v>1.74</v>
@@ -1658,7 +1658,7 @@
         <v>1.72</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.79</v>
+        <v>2.76</v>
       </c>
       <c r="CR2" t="n">
         <v>1.39</v>
@@ -1673,106 +1673,106 @@
         <v>1.54</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="CW2" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="DB2" t="n">
         <v>1.23</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="DE2" t="n">
         <v>0.14</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.57</v>
+        <v>1.74</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.92</v>
+        <v>3.73</v>
       </c>
       <c r="DH2" t="n">
-        <v>125.22</v>
+        <v>122</v>
       </c>
       <c r="DI2" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.14</v>
+        <v>2.33</v>
       </c>
       <c r="DK2" t="n">
-        <v>7.29</v>
+        <v>7.06</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DM2" t="n">
-        <v>74.22</v>
+        <v>74.06</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="DO2" t="n">
-        <v>3.36</v>
+        <v>3.33</v>
       </c>
       <c r="DP2" t="n">
-        <v>12.86</v>
+        <v>13</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.78</v>
+        <v>12.67</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.29</v>
+        <v>6.2</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>57.57</v>
+        <v>57.07</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="DX2" t="n">
-        <v>16.43</v>
+        <v>16.14</v>
       </c>
       <c r="DY2" t="n">
-        <v>10.5</v>
+        <v>10.47</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5.93</v>
+        <v>5.67</v>
       </c>
       <c r="EA2" t="n">
-        <v>22.79</v>
+        <v>22.8</v>
       </c>
       <c r="EB2" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="EC2" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="3">
@@ -1782,94 +1782,94 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
         <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="F3" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="G3" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="H3" t="n">
-        <v>104.62</v>
+        <v>102.44</v>
       </c>
       <c r="I3" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="J3" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>3.89</v>
       </c>
       <c r="L3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="M3" t="n">
-        <v>50.88</v>
+        <v>52</v>
       </c>
       <c r="N3" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="O3" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="P3" t="n">
         <v>11</v>
       </c>
       <c r="Q3" t="n">
-        <v>13.62</v>
+        <v>13.78</v>
       </c>
       <c r="R3" t="n">
-        <v>9.25</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="T3" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="U3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>52.12</v>
+        <v>51.89</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z3" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AA3" t="n">
-        <v>7.12</v>
+        <v>6.89</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.38</v>
+        <v>4.11</v>
       </c>
       <c r="AC3" t="n">
-        <v>22.12</v>
+        <v>22.11</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -1953,70 +1953,70 @@
         <v>2.17</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="BH3" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.93</v>
+        <v>3.87</v>
       </c>
       <c r="BQ3" t="n">
-        <v>3.64</v>
+        <v>3.67</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BT3" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BU3" t="n">
-        <v>42.86</v>
+        <v>40</v>
       </c>
       <c r="BV3" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>71.43000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BY3" t="n">
-        <v>2.61</v>
+        <v>3.03</v>
       </c>
       <c r="BZ3" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.53</v>
+        <v>3.58</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="CC3" t="n">
         <v>6.36</v>
@@ -2025,43 +2025,43 @@
         <v>6.48</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.87</v>
+        <v>2.84</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.78</v>
+        <v>2.81</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CO3" t="n">
         <v>1.32</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.59</v>
+        <v>3.52</v>
       </c>
       <c r="CR3" t="n">
         <v>1.43</v>
@@ -2076,73 +2076,73 @@
         <v>1.39</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.24</v>
+        <v>2.21</v>
       </c>
       <c r="CZ3" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.81</v>
+        <v>3.73</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="DG3" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="DH3" t="n">
-        <v>101.5</v>
+        <v>100.4</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="DK3" t="n">
-        <v>4.78</v>
+        <v>4.67</v>
       </c>
       <c r="DL3" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DM3" t="n">
-        <v>53.5</v>
+        <v>54</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="DP3" t="n">
-        <v>10.86</v>
+        <v>10.87</v>
       </c>
       <c r="DQ3" t="n">
-        <v>12.71</v>
+        <v>12.87</v>
       </c>
       <c r="DR3" t="n">
-        <v>9.279999999999999</v>
+        <v>9</v>
       </c>
       <c r="DS3" t="n">
         <v>0.07000000000000001</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>48.93</v>
+        <v>49</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX3" t="n">
-        <v>12.5</v>
+        <v>12.13</v>
       </c>
       <c r="DY3" t="n">
-        <v>8.140000000000001</v>
+        <v>7.93</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4.36</v>
+        <v>4.2</v>
       </c>
       <c r="EA3" t="n">
-        <v>20.64</v>
+        <v>20.73</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="4">
@@ -3460,7 +3460,7 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>52.5</v>
+        <v>52.38</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
@@ -3766,7 +3766,7 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>52.87</v>
+        <v>52.8</v>
       </c>
       <c r="DW7" t="n">
         <v>0.14</v>
@@ -4347,7 +4347,7 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>49.25</v>
+        <v>49.38</v>
       </c>
       <c r="AZ9" t="n">
         <v>0.12</v>
@@ -4572,7 +4572,7 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>49.53</v>
+        <v>49.6</v>
       </c>
       <c r="DW9" t="n">
         <v>0.06</v>

--- a/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" t="n">
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
         <v>0.22</v>
@@ -1875,22 +1875,22 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AI3" t="n">
-        <v>97.33</v>
+        <v>98.14</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="AL3" t="n">
-        <v>5.83</v>
+        <v>5.29</v>
       </c>
       <c r="AM3" t="n">
         <v>0</v>
@@ -1899,25 +1899,25 @@
         <v>57</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.67</v>
+        <v>2.57</v>
       </c>
       <c r="AQ3" t="n">
-        <v>10.67</v>
+        <v>11.43</v>
       </c>
       <c r="AR3" t="n">
-        <v>11.5</v>
+        <v>12.29</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.33</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
@@ -1929,82 +1929,82 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>44.67</v>
+        <v>44.57</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BA3" t="n">
-        <v>13.83</v>
+        <v>13.71</v>
       </c>
       <c r="BB3" t="n">
-        <v>9.5</v>
+        <v>9.43</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.33</v>
+        <v>4.29</v>
       </c>
       <c r="BD3" t="n">
-        <v>18.67</v>
+        <v>18.71</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="BH3" t="n">
-        <v>8.4</v>
+        <v>8.25</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.87</v>
+        <v>3.75</v>
       </c>
       <c r="BQ3" t="n">
-        <v>3.67</v>
+        <v>3.69</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BT3" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BU3" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BV3" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>66.67</v>
+        <v>68.75</v>
       </c>
       <c r="BY3" t="n">
         <v>3.03</v>
@@ -2013,40 +2013,40 @@
         <v>3.25</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.58</v>
+        <v>3.57</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.75</v>
+        <v>3.71</v>
       </c>
       <c r="CC3" t="n">
-        <v>6.36</v>
+        <v>5.98</v>
       </c>
       <c r="CD3" t="n">
-        <v>6.48</v>
+        <v>6.12</v>
       </c>
       <c r="CE3" t="n">
         <v>1.4</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="CH3" t="n">
         <v>1.38</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CK3" t="n">
         <v>1.71</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="CM3" t="n">
         <v>2.03</v>
@@ -2055,19 +2055,19 @@
         <v>1.62</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.52</v>
+        <v>3.51</v>
       </c>
       <c r="CR3" t="n">
         <v>1.43</v>
       </c>
       <c r="CS3" t="n">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="CT3" t="n">
         <v>2.82</v>
@@ -2076,22 +2076,22 @@
         <v>1.39</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CX3" t="n">
         <v>1.75</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="DB3" t="n">
         <v>1.34</v>
@@ -2100,82 +2100,82 @@
         <v>2.1</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.73</v>
+        <v>3.72</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="DG3" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="DH3" t="n">
-        <v>100.4</v>
+        <v>100.56</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.73</v>
+        <v>2.63</v>
       </c>
       <c r="DK3" t="n">
-        <v>4.67</v>
+        <v>4.5</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DM3" t="n">
-        <v>54</v>
+        <v>54.19</v>
       </c>
       <c r="DN3" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DO3" t="n">
         <v>1.93</v>
       </c>
       <c r="DP3" t="n">
-        <v>10.87</v>
+        <v>11.19</v>
       </c>
       <c r="DQ3" t="n">
-        <v>12.87</v>
+        <v>13.13</v>
       </c>
       <c r="DR3" t="n">
-        <v>9</v>
+        <v>8.82</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>49</v>
+        <v>48.69</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX3" t="n">
-        <v>12.13</v>
+        <v>12.19</v>
       </c>
       <c r="DY3" t="n">
-        <v>7.93</v>
+        <v>8</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4.2</v>
+        <v>4.19</v>
       </c>
       <c r="EA3" t="n">
-        <v>20.73</v>
+        <v>20.62</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.54</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="4">
@@ -4603,61 +4603,61 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D10" t="n">
         <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="F10" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="G10" t="n">
-        <v>1.86</v>
+        <v>2.12</v>
       </c>
       <c r="H10" t="n">
-        <v>117.86</v>
+        <v>122.38</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="K10" t="n">
-        <v>3.43</v>
+        <v>3.5</v>
       </c>
       <c r="L10" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="M10" t="n">
-        <v>57.43</v>
+        <v>60</v>
       </c>
       <c r="N10" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="O10" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="P10" t="n">
-        <v>12.43</v>
+        <v>13</v>
       </c>
       <c r="Q10" t="n">
-        <v>12.14</v>
+        <v>12.62</v>
       </c>
       <c r="R10" t="n">
-        <v>8.43</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -4669,28 +4669,28 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>51.86</v>
+        <v>52.38</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="Z10" t="n">
-        <v>14.29</v>
+        <v>14.12</v>
       </c>
       <c r="AA10" t="n">
-        <v>9.710000000000001</v>
+        <v>9.25</v>
       </c>
       <c r="AB10" t="n">
-        <v>4.57</v>
+        <v>4.88</v>
       </c>
       <c r="AC10" t="n">
-        <v>26.14</v>
+        <v>26.25</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -4774,70 +4774,70 @@
         <v>2.25</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="BH10" t="n">
-        <v>7.13</v>
+        <v>7.06</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BL10" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.4</v>
+        <v>3.31</v>
       </c>
       <c r="BQ10" t="n">
-        <v>3.73</v>
+        <v>3.75</v>
       </c>
       <c r="BR10" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS10" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BT10" t="n">
-        <v>66.67</v>
+        <v>68.75</v>
       </c>
       <c r="BU10" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BV10" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.55</v>
+        <v>2.47</v>
       </c>
       <c r="BZ10" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.43</v>
+        <v>3.42</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.54</v>
+        <v>3.52</v>
       </c>
       <c r="CC10" t="n">
         <v>4.62</v>
@@ -4852,7 +4852,7 @@
         <v>2.86</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="CH10" t="n">
         <v>1.39</v>
@@ -4867,10 +4867,10 @@
         <v>1.74</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="CM10" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CN10" t="n">
         <v>1.6</v>
@@ -4891,7 +4891,7 @@
         <v>3</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="CU10" t="n">
         <v>1.4</v>
@@ -4900,70 +4900,70 @@
         <v>1.95</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CY10" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="DB10" t="n">
         <v>1.32</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.52</v>
+        <v>3.53</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="DF10" t="n">
         <v>2</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="DH10" t="n">
-        <v>110.53</v>
+        <v>113.25</v>
       </c>
       <c r="DI10" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.87</v>
+        <v>2.82</v>
       </c>
       <c r="DK10" t="n">
-        <v>3.07</v>
+        <v>3.12</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="DM10" t="n">
-        <v>51.66</v>
+        <v>53.31</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="DP10" t="n">
-        <v>13.8</v>
+        <v>14</v>
       </c>
       <c r="DQ10" t="n">
-        <v>11.67</v>
+        <v>11.93</v>
       </c>
       <c r="DR10" t="n">
-        <v>8.67</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="DS10" t="n">
         <v>0.06</v>
@@ -4975,28 +4975,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>47.8</v>
+        <v>48.32</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="DX10" t="n">
-        <v>11.53</v>
+        <v>11.62</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.93</v>
+        <v>7.82</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.6</v>
+        <v>3.82</v>
       </c>
       <c r="EA10" t="n">
-        <v>22.2</v>
+        <v>22.5</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="11">

--- a/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
@@ -1379,61 +1379,61 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
         <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="F2" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>2.71</v>
+        <v>2.88</v>
       </c>
       <c r="H2" t="n">
-        <v>122.57</v>
+        <v>126.62</v>
       </c>
       <c r="I2" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="J2" t="n">
-        <v>2.43</v>
+        <v>2.88</v>
       </c>
       <c r="K2" t="n">
-        <v>6.43</v>
+        <v>6.62</v>
       </c>
       <c r="L2" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="M2" t="n">
-        <v>71.14</v>
+        <v>74.38</v>
       </c>
       <c r="N2" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="O2" t="n">
-        <v>3.71</v>
+        <v>3.62</v>
       </c>
       <c r="P2" t="n">
-        <v>11.86</v>
+        <v>11.88</v>
       </c>
       <c r="Q2" t="n">
-        <v>10.86</v>
+        <v>12.88</v>
       </c>
       <c r="R2" t="n">
-        <v>6.29</v>
+        <v>5.62</v>
       </c>
       <c r="S2" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="T2" t="n">
-        <v>2.57</v>
+        <v>2.38</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -1445,28 +1445,28 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>59</v>
+        <v>59.12</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z2" t="n">
-        <v>16.29</v>
+        <v>15.88</v>
       </c>
       <c r="AA2" t="n">
-        <v>9.43</v>
+        <v>9.25</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.86</v>
+        <v>6.62</v>
       </c>
       <c r="AC2" t="n">
-        <v>21.29</v>
+        <v>22.25</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.14</v>
+        <v>2.62</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -1550,70 +1550,70 @@
         <v>2</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.87</v>
+        <v>2.81</v>
       </c>
       <c r="BH2" t="n">
-        <v>10.87</v>
+        <v>10.81</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.87</v>
+        <v>2.81</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.93</v>
+        <v>4.94</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.93</v>
+        <v>5.81</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BT2" t="n">
-        <v>66.67</v>
+        <v>62.5</v>
       </c>
       <c r="BU2" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BV2" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.65</v>
+        <v>4.57</v>
       </c>
       <c r="CB2" t="n">
-        <v>5.17</v>
+        <v>5.07</v>
       </c>
       <c r="CC2" t="n">
         <v>1.55</v>
@@ -1622,157 +1622,157 @@
         <v>1.65</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.23</v>
+        <v>3.21</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CI2" t="n">
         <v>1.77</v>
       </c>
       <c r="CJ2" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CL2" t="n">
         <v>2.14</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="CN2" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="CP2" t="n">
         <v>1.74</v>
       </c>
-      <c r="CO2" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="CP2" t="n">
-        <v>1.72</v>
-      </c>
       <c r="CQ2" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="CR2" t="n">
         <v>1.39</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.53</v>
+        <v>2.57</v>
       </c>
       <c r="CT2" t="n">
         <v>2.97</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CV2" t="n">
         <v>1.82</v>
       </c>
       <c r="CW2" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CY2" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.74</v>
+        <v>1.94</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.73</v>
+        <v>3.75</v>
       </c>
       <c r="DH2" t="n">
-        <v>122</v>
+        <v>124.06</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.33</v>
+        <v>2.56</v>
       </c>
       <c r="DK2" t="n">
-        <v>7.06</v>
+        <v>7.12</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="DM2" t="n">
-        <v>74.06</v>
+        <v>75.5</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DO2" t="n">
-        <v>3.33</v>
+        <v>3.31</v>
       </c>
       <c r="DP2" t="n">
-        <v>13</v>
+        <v>12.94</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.67</v>
+        <v>13.57</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.2</v>
+        <v>5.87</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>57.07</v>
+        <v>57.25</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DX2" t="n">
-        <v>16.14</v>
+        <v>15.94</v>
       </c>
       <c r="DY2" t="n">
-        <v>10.47</v>
+        <v>10.32</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5.67</v>
+        <v>5.62</v>
       </c>
       <c r="EA2" t="n">
-        <v>22.8</v>
+        <v>23.18</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.07</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="3">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" t="n">
         <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2275,52 +2275,52 @@
         <v>1.5</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>107.43</v>
+        <v>103.62</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AK4" t="n">
-        <v>3.29</v>
+        <v>3.25</v>
       </c>
       <c r="AL4" t="n">
-        <v>4.14</v>
+        <v>4</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AN4" t="n">
-        <v>59</v>
+        <v>56.25</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>11.57</v>
+        <v>12.12</v>
       </c>
       <c r="AR4" t="n">
-        <v>10.43</v>
+        <v>10.12</v>
       </c>
       <c r="AS4" t="n">
-        <v>8.140000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="AV4" t="n">
         <v>0</v>
@@ -2332,82 +2332,82 @@
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>40.43</v>
+        <v>39.38</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="BA4" t="n">
-        <v>11</v>
+        <v>10.25</v>
       </c>
       <c r="BB4" t="n">
-        <v>7.71</v>
+        <v>7.25</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.29</v>
+        <v>3</v>
       </c>
       <c r="BD4" t="n">
-        <v>22.29</v>
+        <v>21.12</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="BH4" t="n">
-        <v>10.53</v>
+        <v>10.81</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL4" t="n">
         <v>1</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="BP4" t="n">
-        <v>5.13</v>
+        <v>5.19</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.33</v>
+        <v>5.56</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
       </c>
       <c r="BS4" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BT4" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BU4" t="n">
-        <v>33.33</v>
+        <v>37.5</v>
       </c>
       <c r="BV4" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>66.67</v>
+        <v>68.75</v>
       </c>
       <c r="BY4" t="n">
         <v>4.66</v>
@@ -2416,70 +2416,70 @@
         <v>5.35</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.01</v>
+        <v>4.08</v>
       </c>
       <c r="CB4" t="n">
-        <v>4.16</v>
+        <v>4.27</v>
       </c>
       <c r="CC4" t="n">
-        <v>6.46</v>
+        <v>6.65</v>
       </c>
       <c r="CD4" t="n">
-        <v>9.050000000000001</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="CE4" t="n">
         <v>1.36</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.94</v>
+        <v>2.97</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="CM4" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CO4" t="n">
         <v>1.28</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.17</v>
+        <v>3.14</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.71</v>
+        <v>2.67</v>
       </c>
       <c r="CT4" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CW4" t="n">
         <v>2</v>
@@ -2500,52 +2500,52 @@
         <v>1.29</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.33</v>
+        <v>3.28</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="DH4" t="n">
-        <v>111.07</v>
+        <v>108.94</v>
       </c>
       <c r="DI4" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="DK4" t="n">
-        <v>3.73</v>
+        <v>3.69</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DM4" t="n">
-        <v>63.67</v>
+        <v>62</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="DP4" t="n">
-        <v>12.4</v>
+        <v>12.62</v>
       </c>
       <c r="DQ4" t="n">
-        <v>11.8</v>
+        <v>11.56</v>
       </c>
       <c r="DR4" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="DS4" t="n">
         <v>0.06</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>40.94</v>
+        <v>40.38</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.53</v>
+        <v>10.18</v>
       </c>
       <c r="DY4" t="n">
-        <v>7.13</v>
+        <v>6.94</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="EA4" t="n">
-        <v>21.07</v>
+        <v>20.56</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="EC4" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" t="n">
         <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
         <v>0.12</v>
@@ -2678,139 +2678,139 @@
         <v>1.25</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.14</v>
+        <v>1.88</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.71</v>
+        <v>2.38</v>
       </c>
       <c r="AI5" t="n">
-        <v>103.43</v>
+        <v>101.88</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.86</v>
+        <v>2.88</v>
       </c>
       <c r="AL5" t="n">
-        <v>6.14</v>
+        <v>5.62</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AN5" t="n">
-        <v>62.43</v>
+        <v>58.5</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.43</v>
+        <v>3.25</v>
       </c>
       <c r="AQ5" t="n">
-        <v>11.57</v>
+        <v>13.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>15</v>
+        <v>14.62</v>
       </c>
       <c r="AS5" t="n">
-        <v>7.43</v>
+        <v>7.75</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>58.14</v>
+        <v>55.88</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>13.71</v>
+        <v>12.5</v>
       </c>
       <c r="BB5" t="n">
-        <v>9.289999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.43</v>
+        <v>4</v>
       </c>
       <c r="BD5" t="n">
-        <v>20.14</v>
+        <v>19.75</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.86</v>
+        <v>2.88</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.529999999999999</v>
+        <v>9.56</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.13</v>
+        <v>4.19</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.27</v>
+        <v>5.19</v>
       </c>
       <c r="BR5" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS5" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BT5" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BU5" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BV5" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>26.67</v>
+        <v>31.25</v>
       </c>
       <c r="BY5" t="n">
         <v>1.74</v>
@@ -2819,25 +2819,25 @@
         <v>1.77</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.59</v>
+        <v>3.58</v>
       </c>
       <c r="CB5" t="n">
         <v>3.57</v>
       </c>
       <c r="CC5" t="n">
-        <v>2.03</v>
+        <v>2.4</v>
       </c>
       <c r="CD5" t="n">
-        <v>2.13</v>
+        <v>2.5</v>
       </c>
       <c r="CE5" t="n">
         <v>1.42</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="CH5" t="n">
         <v>1.35</v>
@@ -2846,37 +2846,37 @@
         <v>1.73</v>
       </c>
       <c r="CJ5" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CO5" t="n">
         <v>1.32</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.7</v>
+        <v>3.69</v>
       </c>
       <c r="CR5" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CS5" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="CU5" t="n">
         <v>1.36</v>
@@ -2885,103 +2885,103 @@
         <v>1.79</v>
       </c>
       <c r="CW5" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="CY5" t="n">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.88</v>
+        <v>3.86</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.07</v>
+        <v>1.44</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.4</v>
+        <v>3.19</v>
       </c>
       <c r="DH5" t="n">
-        <v>114.67</v>
+        <v>113.19</v>
       </c>
       <c r="DI5" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.53</v>
+        <v>2.06</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.8</v>
+        <v>5.56</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="DM5" t="n">
-        <v>64.93000000000001</v>
+        <v>62.81</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.46</v>
+        <v>0.62</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.86</v>
+        <v>12.81</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15.13</v>
+        <v>14.93</v>
       </c>
       <c r="DR5" t="n">
-        <v>6.27</v>
+        <v>6.5</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>59.13</v>
+        <v>57.94</v>
       </c>
       <c r="DW5" t="n">
         <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>14.87</v>
+        <v>14.19</v>
       </c>
       <c r="DY5" t="n">
-        <v>9.73</v>
+        <v>9.31</v>
       </c>
       <c r="DZ5" t="n">
-        <v>5.13</v>
+        <v>4.88</v>
       </c>
       <c r="EA5" t="n">
-        <v>21.67</v>
+        <v>21.38</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.53</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" t="n">
         <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E6" t="n">
         <v>0.25</v>
@@ -3084,49 +3084,49 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AI6" t="n">
-        <v>105.43</v>
+        <v>108.62</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL6" t="n">
-        <v>3.29</v>
+        <v>3.25</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AN6" t="n">
-        <v>51.43</v>
+        <v>55.38</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>11</v>
+        <v>11.38</v>
       </c>
       <c r="AR6" t="n">
-        <v>11</v>
+        <v>11.62</v>
       </c>
       <c r="AS6" t="n">
-        <v>10.43</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.71</v>
+        <v>1.25</v>
       </c>
       <c r="AV6" t="n">
         <v>0</v>
@@ -3138,82 +3138,82 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>48.29</v>
+        <v>48.38</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>7.71</v>
+        <v>8.25</v>
       </c>
       <c r="BB6" t="n">
-        <v>4.86</v>
+        <v>5</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.86</v>
+        <v>3.25</v>
       </c>
       <c r="BD6" t="n">
-        <v>24</v>
+        <v>23.38</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.67</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.33</v>
+        <v>0.44</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="BP6" t="n">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.93</v>
+        <v>4.69</v>
       </c>
       <c r="BR6" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS6" t="n">
-        <v>73.33</v>
+        <v>75</v>
       </c>
       <c r="BT6" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BU6" t="n">
-        <v>6.67</v>
+        <v>12.5</v>
       </c>
       <c r="BV6" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="BW6" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="BX6" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BY6" t="n">
         <v>2.57</v>
@@ -3222,52 +3222,52 @@
         <v>2.7</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.37</v>
+        <v>3.36</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.5</v>
+        <v>3.47</v>
       </c>
       <c r="CC6" t="n">
-        <v>4.07</v>
+        <v>3.92</v>
       </c>
       <c r="CD6" t="n">
-        <v>4.55</v>
+        <v>4.38</v>
       </c>
       <c r="CE6" t="n">
         <v>1.4</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="CH6" t="n">
         <v>1.37</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CJ6" t="n">
         <v>1.85</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="CM6" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CO6" t="n">
         <v>1.32</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CQ6" t="n">
         <v>3.47</v>
@@ -3276,10 +3276,10 @@
         <v>1.43</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="CU6" t="n">
         <v>1.37</v>
@@ -3291,67 +3291,67 @@
         <v>1.92</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
       <c r="CZ6" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="DB6" t="n">
         <v>1.34</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="DD6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="DE6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="DF6" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="DG6" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="DH6" t="n">
+        <v>106.06</v>
+      </c>
+      <c r="DI6" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="DJ6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DK6" t="n">
         <v>3.68</v>
       </c>
-      <c r="DE6" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="DF6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="DG6" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="DH6" t="n">
-        <v>104.4</v>
-      </c>
-      <c r="DI6" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="DJ6" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="DK6" t="n">
-        <v>3.73</v>
-      </c>
       <c r="DL6" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="DM6" t="n">
-        <v>54.4</v>
+        <v>56.19</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="DP6" t="n">
-        <v>10.6</v>
+        <v>10.82</v>
       </c>
       <c r="DQ6" t="n">
-        <v>11.06</v>
+        <v>11.37</v>
       </c>
       <c r="DR6" t="n">
-        <v>10.14</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="DS6" t="n">
         <v>0</v>
@@ -3369,22 +3369,22 @@
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>10</v>
+        <v>10.12</v>
       </c>
       <c r="DY6" t="n">
-        <v>6.53</v>
+        <v>6.5</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.47</v>
+        <v>3.62</v>
       </c>
       <c r="EA6" t="n">
-        <v>22.2</v>
+        <v>22</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="7">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" t="n">
         <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3484,139 +3484,139 @@
         <v>2.38</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AH7" t="n">
-        <v>3.29</v>
+        <v>3.12</v>
       </c>
       <c r="AI7" t="n">
-        <v>116</v>
+        <v>115.25</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AL7" t="n">
-        <v>5.86</v>
+        <v>5.62</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AN7" t="n">
-        <v>67.70999999999999</v>
+        <v>66.62</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AP7" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>15.29</v>
+        <v>15.12</v>
       </c>
       <c r="AR7" t="n">
-        <v>10.57</v>
+        <v>11.12</v>
       </c>
       <c r="AS7" t="n">
-        <v>6.57</v>
+        <v>6.62</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>53.29</v>
+        <v>53.75</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="BA7" t="n">
-        <v>13.14</v>
+        <v>12.38</v>
       </c>
       <c r="BB7" t="n">
-        <v>9.710000000000001</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="BC7" t="n">
-        <v>3.43</v>
+        <v>3.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>19.14</v>
+        <v>19.38</v>
       </c>
       <c r="BE7" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>9.69</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="BN7" t="n">
         <v>1.56</v>
       </c>
-      <c r="BF7" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>1.4</v>
-      </c>
       <c r="BO7" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.93</v>
+        <v>3.94</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.87</v>
+        <v>5.75</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BT7" t="n">
-        <v>40</v>
+        <v>43.75</v>
       </c>
       <c r="BU7" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BV7" t="n">
-        <v>6.67</v>
+        <v>12.5</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="BX7" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BY7" t="n">
         <v>3.22</v>
@@ -3625,31 +3625,31 @@
         <v>3.29</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.54</v>
+        <v>3.53</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.62</v>
+        <v>3.57</v>
       </c>
       <c r="CC7" t="n">
-        <v>4.2</v>
+        <v>4.06</v>
       </c>
       <c r="CD7" t="n">
-        <v>4.58</v>
+        <v>4.44</v>
       </c>
       <c r="CE7" t="n">
         <v>1.37</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="CH7" t="n">
         <v>1.4</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CJ7" t="n">
         <v>1.8</v>
@@ -3658,10 +3658,10 @@
         <v>1.59</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="CN7" t="n">
         <v>1.74</v>
@@ -3673,19 +3673,19 @@
         <v>1.95</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.24</v>
+        <v>3.26</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CV7" t="n">
         <v>1.96</v>
@@ -3694,100 +3694,100 @@
         <v>1.84</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.42</v>
+        <v>3.45</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="DG7" t="n">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="DH7" t="n">
-        <v>111.47</v>
+        <v>111.38</v>
       </c>
       <c r="DI7" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.27</v>
+        <v>2.32</v>
       </c>
       <c r="DK7" t="n">
-        <v>5</v>
+        <v>4.94</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DM7" t="n">
-        <v>63.66</v>
+        <v>63.37</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="DP7" t="n">
-        <v>15.67</v>
+        <v>15.56</v>
       </c>
       <c r="DQ7" t="n">
-        <v>12.53</v>
+        <v>12.68</v>
       </c>
       <c r="DR7" t="n">
-        <v>6.4</v>
+        <v>6.44</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>52.8</v>
+        <v>53.06</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DX7" t="n">
-        <v>12.33</v>
+        <v>12</v>
       </c>
       <c r="DY7" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="DZ7" t="n">
         <v>4</v>
       </c>
       <c r="EA7" t="n">
-        <v>20.33</v>
+        <v>20.38</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="8">
@@ -3797,10 +3797,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D8" t="n">
         <v>9</v>
@@ -3809,49 +3809,49 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="G8" t="n">
-        <v>3.33</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
-        <v>112.33</v>
+        <v>114</v>
       </c>
       <c r="I8" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="J8" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="K8" t="n">
-        <v>6.67</v>
+        <v>6.57</v>
       </c>
       <c r="L8" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="M8" t="n">
-        <v>76.67</v>
+        <v>77.56999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="O8" t="n">
-        <v>3.17</v>
+        <v>3.43</v>
       </c>
       <c r="P8" t="n">
-        <v>14.17</v>
+        <v>14.43</v>
       </c>
       <c r="Q8" t="n">
-        <v>11.5</v>
+        <v>11.86</v>
       </c>
       <c r="R8" t="n">
-        <v>8.17</v>
+        <v>7</v>
       </c>
       <c r="S8" t="n">
-        <v>0.83</v>
+        <v>1.43</v>
       </c>
       <c r="T8" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -3863,28 +3863,28 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>51.67</v>
+        <v>51.57</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="Z8" t="n">
-        <v>13.5</v>
+        <v>13.43</v>
       </c>
       <c r="AA8" t="n">
-        <v>10</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.5</v>
+        <v>3.57</v>
       </c>
       <c r="AC8" t="n">
-        <v>22.17</v>
+        <v>21.71</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AF8" t="n">
         <v>0.11</v>
@@ -3968,70 +3968,70 @@
         <v>2.22</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="BH8" t="n">
-        <v>10.33</v>
+        <v>10.25</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.47</v>
+        <v>0.62</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.47</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="BO8" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.47</v>
+        <v>5.19</v>
       </c>
       <c r="BR8" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BS8" t="n">
-        <v>73.33</v>
+        <v>75</v>
       </c>
       <c r="BT8" t="n">
-        <v>40</v>
+        <v>43.75</v>
       </c>
       <c r="BU8" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BV8" t="n">
-        <v>6.67</v>
+        <v>12.5</v>
       </c>
       <c r="BW8" t="n">
-        <v>6.67</v>
+        <v>12.5</v>
       </c>
       <c r="BX8" t="n">
-        <v>46.67</v>
+        <v>50</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.79</v>
+        <v>2.72</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.45</v>
+        <v>3.43</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.59</v>
+        <v>3.55</v>
       </c>
       <c r="CC8" t="n">
         <v>3.59</v>
@@ -4061,7 +4061,7 @@
         <v>1.6</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="CM8" t="n">
         <v>2.19</v>
@@ -4070,22 +4070,22 @@
         <v>1.73</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="CR8" t="n">
         <v>1.4</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="CU8" t="n">
         <v>1.4</v>
@@ -4094,70 +4094,70 @@
         <v>1.98</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CX8" t="n">
         <v>1.63</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CZ8" t="n">
         <v>2.19</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.42</v>
+        <v>3.45</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="DH8" t="n">
-        <v>107.07</v>
+        <v>108.13</v>
       </c>
       <c r="DI8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.07</v>
+        <v>5.12</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="DM8" t="n">
-        <v>63.8</v>
+        <v>65</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.67</v>
+        <v>2.81</v>
       </c>
       <c r="DP8" t="n">
-        <v>15.2</v>
+        <v>15.25</v>
       </c>
       <c r="DQ8" t="n">
-        <v>12.93</v>
+        <v>13</v>
       </c>
       <c r="DR8" t="n">
-        <v>8.539999999999999</v>
+        <v>8</v>
       </c>
       <c r="DS8" t="n">
         <v>0</v>
@@ -4169,25 +4169,25 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>50.07</v>
+        <v>50.12</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DX8" t="n">
         <v>12.94</v>
       </c>
       <c r="DY8" t="n">
-        <v>9.470000000000001</v>
+        <v>9.44</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.46</v>
+        <v>3.5</v>
       </c>
       <c r="EA8" t="n">
-        <v>22.2</v>
+        <v>22</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="EC8" t="n">
         <v>2</v>
@@ -4200,94 +4200,94 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
         <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="F9" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="G9" t="n">
-        <v>2.71</v>
+        <v>3.12</v>
       </c>
       <c r="H9" t="n">
-        <v>106.57</v>
+        <v>111.75</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="K9" t="n">
-        <v>5.43</v>
+        <v>6.25</v>
       </c>
       <c r="L9" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="M9" t="n">
-        <v>64.43000000000001</v>
+        <v>67.25</v>
       </c>
       <c r="N9" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="O9" t="n">
-        <v>2.71</v>
+        <v>3.12</v>
       </c>
       <c r="P9" t="n">
-        <v>12.71</v>
+        <v>12.12</v>
       </c>
       <c r="Q9" t="n">
-        <v>15.43</v>
+        <v>15.38</v>
       </c>
       <c r="R9" t="n">
-        <v>7.71</v>
+        <v>6.88</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
       </c>
       <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>52.12</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>16.38</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>24.75</v>
+      </c>
+      <c r="AD9" t="n">
         <v>1.86</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>49.86</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>15.86</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>11.29</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>4.57</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>23.71</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.78</v>
-      </c>
       <c r="AE9" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="AF9" t="n">
         <v>0.12</v>
@@ -4371,70 +4371,70 @@
         <v>3.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.73</v>
+        <v>2.81</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.53</v>
+        <v>10.81</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.73</v>
+        <v>2.81</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.73</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="BP9" t="n">
-        <v>5.07</v>
+        <v>5.12</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.47</v>
+        <v>5.69</v>
       </c>
       <c r="BR9" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BS9" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BT9" t="n">
-        <v>46.67</v>
+        <v>50</v>
       </c>
       <c r="BU9" t="n">
-        <v>33.33</v>
+        <v>37.5</v>
       </c>
       <c r="BV9" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BW9" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX9" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.29</v>
+        <v>2.17</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.41</v>
+        <v>3.51</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.51</v>
+        <v>3.67</v>
       </c>
       <c r="CC9" t="n">
         <v>2.94</v>
@@ -4443,58 +4443,58 @@
         <v>3.2</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.95</v>
+        <v>2.92</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CI9" t="n">
         <v>1.77</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CL9" t="n">
         <v>2.17</v>
       </c>
       <c r="CM9" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.57</v>
+        <v>3.51</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CS9" t="n">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="CV9" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CW9" t="n">
         <v>2</v>
@@ -4512,88 +4512,88 @@
         <v>1.6</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.84</v>
+        <v>3.76</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DF9" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="DG9" t="n">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="DH9" t="n">
-        <v>109.73</v>
+        <v>112.12</v>
       </c>
       <c r="DI9" t="n">
         <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>3.07</v>
+        <v>2.94</v>
       </c>
       <c r="DK9" t="n">
-        <v>5.94</v>
+        <v>6.32</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="DM9" t="n">
-        <v>61.47</v>
+        <v>63.06</v>
       </c>
       <c r="DN9" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.93</v>
+        <v>3.12</v>
       </c>
       <c r="DP9" t="n">
-        <v>12.4</v>
+        <v>12.12</v>
       </c>
       <c r="DQ9" t="n">
-        <v>14.2</v>
+        <v>14.25</v>
       </c>
       <c r="DR9" t="n">
-        <v>7.73</v>
+        <v>7.32</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>49.6</v>
+        <v>50.75</v>
       </c>
       <c r="DW9" t="n">
         <v>0.06</v>
       </c>
       <c r="DX9" t="n">
-        <v>15.47</v>
+        <v>15.75</v>
       </c>
       <c r="DY9" t="n">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.06</v>
+        <v>4.25</v>
       </c>
       <c r="EA9" t="n">
-        <v>23.13</v>
+        <v>23.68</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.94</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="10">
@@ -5006,94 +5006,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D11" t="n">
         <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="F11" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="G11" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="H11" t="n">
-        <v>111.86</v>
+        <v>108.62</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>3.86</v>
+        <v>3.88</v>
       </c>
       <c r="L11" t="n">
-        <v>0.14</v>
+        <v>0.38</v>
       </c>
       <c r="M11" t="n">
-        <v>57.57</v>
+        <v>56.62</v>
       </c>
       <c r="N11" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="O11" t="n">
         <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>11.86</v>
+        <v>12.38</v>
       </c>
       <c r="Q11" t="n">
-        <v>12.86</v>
+        <v>12.88</v>
       </c>
       <c r="R11" t="n">
-        <v>9.43</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="T11" t="n">
-        <v>1.29</v>
+        <v>1.62</v>
       </c>
       <c r="U11" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="V11" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>46.71</v>
+        <v>46.25</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z11" t="n">
-        <v>14.43</v>
+        <v>13.88</v>
       </c>
       <c r="AA11" t="n">
-        <v>10.71</v>
+        <v>10</v>
       </c>
       <c r="AB11" t="n">
-        <v>3.71</v>
+        <v>3.88</v>
       </c>
       <c r="AC11" t="n">
-        <v>21.43</v>
+        <v>21.38</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.57</v>
+        <v>1.88</v>
       </c>
       <c r="AF11" t="n">
         <v>0.12</v>
@@ -5177,70 +5177,70 @@
         <v>2.38</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.33</v>
+        <v>2.56</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.33</v>
+        <v>9.25</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.33</v>
+        <v>2.56</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.67</v>
+        <v>0.88</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BN11" t="n">
-        <v>1</v>
+        <v>1.19</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.2</v>
+        <v>4.19</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.13</v>
+        <v>5.06</v>
       </c>
       <c r="BR11" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BS11" t="n">
-        <v>66.67</v>
+        <v>68.75</v>
       </c>
       <c r="BT11" t="n">
-        <v>46.67</v>
+        <v>50</v>
       </c>
       <c r="BU11" t="n">
-        <v>33.33</v>
+        <v>37.5</v>
       </c>
       <c r="BV11" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="BW11" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="BX11" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BY11" t="n">
-        <v>3.13</v>
+        <v>3.01</v>
       </c>
       <c r="BZ11" t="n">
-        <v>3.39</v>
+        <v>3.27</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.42</v>
+        <v>3.41</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.5</v>
+        <v>3.47</v>
       </c>
       <c r="CC11" t="n">
         <v>4.36</v>
@@ -5264,31 +5264,31 @@
         <v>1.79</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CL11" t="n">
         <v>2.34</v>
       </c>
       <c r="CM11" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CP11" t="n">
         <v>2.07</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.63</v>
+        <v>3.64</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CS11" t="n">
         <v>3.2</v>
@@ -5300,22 +5300,22 @@
         <v>1.35</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CW11" t="n">
         <v>1.98</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CZ11" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="DB11" t="n">
         <v>1.36</v>
@@ -5324,34 +5324,34 @@
         <v>2.15</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.83</v>
+        <v>3.84</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="DG11" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="DH11" t="n">
-        <v>100.4</v>
+        <v>99.5</v>
       </c>
       <c r="DI11" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="DK11" t="n">
         <v>4</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.6</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DM11" t="n">
-        <v>50.4</v>
+        <v>50.37</v>
       </c>
       <c r="DN11" t="n">
         <v>1</v>
@@ -5360,46 +5360,46 @@
         <v>2.06</v>
       </c>
       <c r="DP11" t="n">
-        <v>12.73</v>
+        <v>12.94</v>
       </c>
       <c r="DQ11" t="n">
-        <v>12.47</v>
+        <v>12.5</v>
       </c>
       <c r="DR11" t="n">
-        <v>8.07</v>
+        <v>7.63</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>44.67</v>
+        <v>44.56</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DX11" t="n">
-        <v>12.13</v>
+        <v>12</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.73</v>
+        <v>8.5</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="EA11" t="n">
-        <v>20.2</v>
+        <v>20.25</v>
       </c>
       <c r="EB11" t="n">
         <v>1.37</v>
       </c>
       <c r="EC11" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
@@ -1445,7 +1445,7 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>59.12</v>
+        <v>59</v>
       </c>
       <c r="Y2" t="n">
         <v>0.12</v>
@@ -1751,7 +1751,7 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>57.25</v>
+        <v>57.19</v>
       </c>
       <c r="DW2" t="n">
         <v>0.18</v>
@@ -2735,7 +2735,7 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>55.88</v>
+        <v>56</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
@@ -2960,7 +2960,7 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>57.94</v>
+        <v>58</v>
       </c>
       <c r="DW5" t="n">
         <v>0</v>
@@ -3523,7 +3523,7 @@
         <v>11.12</v>
       </c>
       <c r="AS7" t="n">
-        <v>6.62</v>
+        <v>6.5</v>
       </c>
       <c r="AT7" t="n">
         <v>2</v>
@@ -3541,7 +3541,7 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>53.75</v>
+        <v>54</v>
       </c>
       <c r="AZ7" t="n">
         <v>0.25</v>
@@ -3754,7 +3754,7 @@
         <v>12.68</v>
       </c>
       <c r="DR7" t="n">
-        <v>6.44</v>
+        <v>6.38</v>
       </c>
       <c r="DS7" t="n">
         <v>0.25</v>
@@ -3766,7 +3766,7 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>53.06</v>
+        <v>53.19</v>
       </c>
       <c r="DW7" t="n">
         <v>0.12</v>
@@ -5072,7 +5072,7 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>46.25</v>
+        <v>46</v>
       </c>
       <c r="Y11" t="n">
         <v>0.12</v>
@@ -5378,7 +5378,7 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>44.56</v>
+        <v>44.44</v>
       </c>
       <c r="DW11" t="n">
         <v>0.18</v>

--- a/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" t="n">
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" t="n">
         <v>0.25</v>
@@ -1469,79 +1469,79 @@
         <v>2.62</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AH2" t="n">
-        <v>4.62</v>
+        <v>4.33</v>
       </c>
       <c r="AI2" t="n">
-        <v>121.5</v>
+        <v>119.33</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="AL2" t="n">
-        <v>7.62</v>
+        <v>7.11</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AN2" t="n">
-        <v>76.62</v>
+        <v>76</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.38</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP2" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="AQ2" t="n">
-        <v>14</v>
+        <v>14.44</v>
       </c>
       <c r="AR2" t="n">
-        <v>14.25</v>
+        <v>14.33</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.12</v>
+        <v>6</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.5</v>
+        <v>1.89</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>55.38</v>
+        <v>55.11</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="BA2" t="n">
-        <v>16</v>
+        <v>15.89</v>
       </c>
       <c r="BB2" t="n">
-        <v>11.38</v>
+        <v>11.11</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.62</v>
+        <v>4.78</v>
       </c>
       <c r="BD2" t="n">
-        <v>24.12</v>
+        <v>24.11</v>
       </c>
       <c r="BE2" t="n">
         <v>1.89</v>
@@ -1550,58 +1550,58 @@
         <v>2</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.81</v>
+        <v>3.06</v>
       </c>
       <c r="BH2" t="n">
-        <v>10.81</v>
+        <v>10.53</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.81</v>
+        <v>3.06</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.38</v>
+        <v>0.59</v>
       </c>
       <c r="BL2" t="n">
         <v>0.88</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.12</v>
+        <v>1.35</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.94</v>
+        <v>4.71</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.81</v>
+        <v>5.76</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BT2" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BU2" t="n">
-        <v>18.75</v>
+        <v>23.53</v>
       </c>
       <c r="BV2" t="n">
-        <v>6.25</v>
+        <v>11.76</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>5.88</v>
       </c>
       <c r="BX2" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BY2" t="n">
         <v>1.31</v>
@@ -1610,22 +1610,22 @@
         <v>1.33</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.57</v>
+        <v>4.52</v>
       </c>
       <c r="CB2" t="n">
-        <v>5.07</v>
+        <v>4.99</v>
       </c>
       <c r="CC2" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="CD2" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CE2" t="n">
         <v>1.31</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="CG2" t="n">
         <v>3.21</v>
@@ -1634,19 +1634,19 @@
         <v>1.5</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CJ2" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CK2" t="n">
         <v>1.58</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CN2" t="n">
         <v>1.75</v>
@@ -1661,85 +1661,85 @@
         <v>2.82</v>
       </c>
       <c r="CR2" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CS2" t="n">
         <v>2.57</v>
       </c>
       <c r="CT2" t="n">
-        <v>2.97</v>
+        <v>3.02</v>
       </c>
       <c r="CU2" t="n">
         <v>1.53</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="CW2" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="DB2" t="n">
         <v>1.24</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="DH2" t="n">
-        <v>124.06</v>
+        <v>122.76</v>
       </c>
       <c r="DI2" t="n">
         <v>0.12</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="DK2" t="n">
-        <v>7.12</v>
+        <v>6.88</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DM2" t="n">
-        <v>75.5</v>
+        <v>75.23999999999999</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="DO2" t="n">
-        <v>3.31</v>
+        <v>3.18</v>
       </c>
       <c r="DP2" t="n">
-        <v>12.94</v>
+        <v>13.24</v>
       </c>
       <c r="DQ2" t="n">
-        <v>13.57</v>
+        <v>13.65</v>
       </c>
       <c r="DR2" t="n">
-        <v>5.87</v>
+        <v>5.82</v>
       </c>
       <c r="DS2" t="n">
         <v>0.12</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>57.19</v>
+        <v>56.94</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX2" t="n">
-        <v>15.94</v>
+        <v>15.89</v>
       </c>
       <c r="DY2" t="n">
-        <v>10.32</v>
+        <v>10.23</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5.62</v>
+        <v>5.65</v>
       </c>
       <c r="EA2" t="n">
-        <v>23.18</v>
+        <v>23.23</v>
       </c>
       <c r="EB2" t="n">
         <v>1.95</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" t="n">
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
         <v>0.22</v>
@@ -1875,136 +1875,136 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AI3" t="n">
-        <v>98.14</v>
+        <v>98.12</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AL3" t="n">
-        <v>5.29</v>
+        <v>5</v>
       </c>
       <c r="AM3" t="n">
         <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>57</v>
+        <v>55.38</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>11.43</v>
+        <v>12.12</v>
       </c>
       <c r="AR3" t="n">
-        <v>12.29</v>
+        <v>13</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.859999999999999</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AU3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>43.25</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>8.35</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BO3" t="n">
         <v>1.29</v>
       </c>
-      <c r="AV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>44.57</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>13.71</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>9.43</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>4.29</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>18.71</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>2</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>1.31</v>
-      </c>
       <c r="BP3" t="n">
-        <v>3.75</v>
+        <v>3.71</v>
       </c>
       <c r="BQ3" t="n">
-        <v>3.69</v>
+        <v>3.88</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BT3" t="n">
-        <v>56.25</v>
+        <v>52.94</v>
       </c>
       <c r="BU3" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BV3" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>68.75</v>
+        <v>70.59</v>
       </c>
       <c r="BY3" t="n">
         <v>3.03</v>
@@ -2013,16 +2013,16 @@
         <v>3.25</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.57</v>
+        <v>3.56</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.71</v>
+        <v>3.68</v>
       </c>
       <c r="CC3" t="n">
-        <v>5.98</v>
+        <v>5.63</v>
       </c>
       <c r="CD3" t="n">
-        <v>6.12</v>
+        <v>5.72</v>
       </c>
       <c r="CE3" t="n">
         <v>1.4</v>
@@ -2037,22 +2037,22 @@
         <v>1.38</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.42</v>
+        <v>2.39</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CO3" t="n">
         <v>1.31</v>
@@ -2061,7 +2061,7 @@
         <v>2.02</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.51</v>
+        <v>3.5</v>
       </c>
       <c r="CR3" t="n">
         <v>1.43</v>
@@ -2070,28 +2070,28 @@
         <v>3.04</v>
       </c>
       <c r="CT3" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="CU3" t="n">
         <v>1.39</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.22</v>
+        <v>2.19</v>
       </c>
       <c r="CZ3" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="DB3" t="n">
         <v>1.34</v>
@@ -2106,43 +2106,43 @@
         <v>0.12</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="DG3" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="DH3" t="n">
-        <v>100.56</v>
+        <v>100.41</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="DK3" t="n">
-        <v>4.5</v>
+        <v>4.41</v>
       </c>
       <c r="DL3" t="n">
         <v>0.06</v>
       </c>
       <c r="DM3" t="n">
-        <v>54.19</v>
+        <v>53.59</v>
       </c>
       <c r="DN3" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="DP3" t="n">
-        <v>11.19</v>
+        <v>11.53</v>
       </c>
       <c r="DQ3" t="n">
-        <v>13.13</v>
+        <v>13.41</v>
       </c>
       <c r="DR3" t="n">
-        <v>8.82</v>
+        <v>8.83</v>
       </c>
       <c r="DS3" t="n">
         <v>0.06</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>48.69</v>
+        <v>47.82</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="DX3" t="n">
-        <v>12.19</v>
+        <v>11.71</v>
       </c>
       <c r="DY3" t="n">
-        <v>8</v>
+        <v>7.65</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4.19</v>
+        <v>4.06</v>
       </c>
       <c r="EA3" t="n">
-        <v>20.62</v>
+        <v>20.41</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="4">
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
         <v>8</v>
@@ -2197,82 +2197,82 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>114.25</v>
+        <v>115.89</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="K4" t="n">
-        <v>3.38</v>
+        <v>3.44</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>67.75</v>
+        <v>68.67</v>
       </c>
       <c r="N4" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="O4" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="P4" t="n">
-        <v>13.12</v>
+        <v>13.44</v>
       </c>
       <c r="Q4" t="n">
-        <v>13</v>
+        <v>12.44</v>
       </c>
       <c r="R4" t="n">
-        <v>7.5</v>
+        <v>7.67</v>
       </c>
       <c r="S4" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="T4" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="U4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>41.38</v>
+        <v>42.67</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z4" t="n">
-        <v>10.12</v>
+        <v>10.44</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.62</v>
+        <v>6.67</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.5</v>
+        <v>3.78</v>
       </c>
       <c r="AC4" t="n">
-        <v>20</v>
+        <v>20.56</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AF4" t="n">
         <v>0.12</v>
@@ -2356,70 +2356,70 @@
         <v>2.62</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="BH4" t="n">
-        <v>10.81</v>
+        <v>10.65</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BL4" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="BP4" t="n">
-        <v>5.19</v>
+        <v>5.24</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.56</v>
+        <v>5.35</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
       </c>
       <c r="BS4" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BT4" t="n">
-        <v>56.25</v>
+        <v>52.94</v>
       </c>
       <c r="BU4" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BV4" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>68.75</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BY4" t="n">
-        <v>4.66</v>
+        <v>4.46</v>
       </c>
       <c r="BZ4" t="n">
-        <v>5.35</v>
+        <v>5.11</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.08</v>
+        <v>4.03</v>
       </c>
       <c r="CB4" t="n">
-        <v>4.27</v>
+        <v>4.22</v>
       </c>
       <c r="CC4" t="n">
         <v>6.65</v>
@@ -2431,58 +2431,58 @@
         <v>1.36</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CM4" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CO4" t="n">
         <v>1.28</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.14</v>
+        <v>3.17</v>
       </c>
       <c r="CR4" t="n">
         <v>1.39</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="CT4" t="n">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="CU4" t="n">
         <v>1.49</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="CW4" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="CX4" t="n">
         <v>1.72</v>
@@ -2491,7 +2491,7 @@
         <v>2.14</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="DA4" t="n">
         <v>1.65</v>
@@ -2509,43 +2509,43 @@
         <v>0.06</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="DH4" t="n">
-        <v>108.94</v>
+        <v>110.12</v>
       </c>
       <c r="DI4" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="DK4" t="n">
-        <v>3.69</v>
+        <v>3.7</v>
       </c>
       <c r="DL4" t="n">
         <v>0.12</v>
       </c>
       <c r="DM4" t="n">
-        <v>62</v>
+        <v>62.83</v>
       </c>
       <c r="DN4" t="n">
         <v>0.88</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="DP4" t="n">
-        <v>12.62</v>
+        <v>12.82</v>
       </c>
       <c r="DQ4" t="n">
-        <v>11.56</v>
+        <v>11.35</v>
       </c>
       <c r="DR4" t="n">
-        <v>8</v>
+        <v>8.06</v>
       </c>
       <c r="DS4" t="n">
         <v>0.06</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>40.38</v>
+        <v>41.12</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.18</v>
+        <v>10.35</v>
       </c>
       <c r="DY4" t="n">
         <v>6.94</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.25</v>
+        <v>3.41</v>
       </c>
       <c r="EA4" t="n">
-        <v>20.56</v>
+        <v>20.82</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" t="n">
         <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
         <v>0.12</v>
@@ -2678,139 +2678,139 @@
         <v>1.25</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="AI5" t="n">
-        <v>101.88</v>
+        <v>100.22</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="AL5" t="n">
-        <v>5.62</v>
+        <v>5.56</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AN5" t="n">
-        <v>58.5</v>
+        <v>58.44</v>
       </c>
       <c r="AO5" t="n">
         <v>1</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="AQ5" t="n">
-        <v>13.5</v>
+        <v>13.22</v>
       </c>
       <c r="AR5" t="n">
-        <v>14.62</v>
+        <v>14.67</v>
       </c>
       <c r="AS5" t="n">
-        <v>7.75</v>
+        <v>7.22</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>56</v>
+        <v>55.56</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>12.5</v>
+        <v>13.22</v>
       </c>
       <c r="BB5" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="BC5" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>19.78</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="BP5" t="n">
         <v>4</v>
       </c>
-      <c r="BD5" t="n">
-        <v>19.75</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>9.56</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>4.19</v>
-      </c>
       <c r="BQ5" t="n">
-        <v>5.19</v>
+        <v>5.18</v>
       </c>
       <c r="BR5" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS5" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BT5" t="n">
-        <v>37.5</v>
+        <v>41.18</v>
       </c>
       <c r="BU5" t="n">
-        <v>18.75</v>
+        <v>23.53</v>
       </c>
       <c r="BV5" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>31.25</v>
+        <v>35.29</v>
       </c>
       <c r="BY5" t="n">
         <v>1.74</v>
@@ -2819,46 +2819,46 @@
         <v>1.77</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.58</v>
+        <v>3.56</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.57</v>
+        <v>3.55</v>
       </c>
       <c r="CC5" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="CD5" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="CH5" t="n">
         <v>1.35</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CJ5" t="n">
         <v>2.01</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CO5" t="n">
         <v>1.32</v>
@@ -2882,22 +2882,22 @@
         <v>1.36</v>
       </c>
       <c r="CV5" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CW5" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CY5" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="DB5" t="n">
         <v>1.36</v>
@@ -2906,19 +2906,19 @@
         <v>2.16</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.86</v>
+        <v>3.85</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.19</v>
+        <v>3.24</v>
       </c>
       <c r="DH5" t="n">
-        <v>113.19</v>
+        <v>111.65</v>
       </c>
       <c r="DI5" t="n">
         <v>-0.06</v>
@@ -2927,58 +2927,58 @@
         <v>2.06</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.56</v>
+        <v>5.53</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="DM5" t="n">
-        <v>62.81</v>
+        <v>62.52</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="DP5" t="n">
-        <v>12.81</v>
+        <v>12.7</v>
       </c>
       <c r="DQ5" t="n">
-        <v>14.93</v>
+        <v>14.94</v>
       </c>
       <c r="DR5" t="n">
-        <v>6.5</v>
+        <v>6.29</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>58</v>
+        <v>57.65</v>
       </c>
       <c r="DW5" t="n">
         <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>14.19</v>
+        <v>14.47</v>
       </c>
       <c r="DY5" t="n">
-        <v>9.31</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4.88</v>
+        <v>4.94</v>
       </c>
       <c r="EA5" t="n">
-        <v>21.38</v>
+        <v>21.3</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="EC5" t="n">
         <v>2.06</v>
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" t="n">
         <v>8</v>
@@ -3406,82 +3406,82 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="G7" t="n">
-        <v>3.12</v>
+        <v>2.89</v>
       </c>
       <c r="H7" t="n">
-        <v>107.5</v>
+        <v>109.33</v>
       </c>
       <c r="I7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J7" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="K7" t="n">
-        <v>4.25</v>
+        <v>3.89</v>
       </c>
       <c r="L7" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="M7" t="n">
-        <v>60.12</v>
+        <v>60.11</v>
       </c>
       <c r="N7" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="P7" t="n">
-        <v>16</v>
+        <v>15.89</v>
       </c>
       <c r="Q7" t="n">
-        <v>14.25</v>
+        <v>13.89</v>
       </c>
       <c r="R7" t="n">
-        <v>6.25</v>
+        <v>6.56</v>
       </c>
       <c r="S7" t="n">
-        <v>1.12</v>
+        <v>1.33</v>
       </c>
       <c r="T7" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="U7" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="V7" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>52.38</v>
+        <v>51.89</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>11.62</v>
+        <v>11</v>
       </c>
       <c r="AA7" t="n">
-        <v>7.12</v>
+        <v>6.78</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.5</v>
+        <v>4.22</v>
       </c>
       <c r="AC7" t="n">
-        <v>21.38</v>
+        <v>22</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="AF7" t="n">
         <v>0.5</v>
@@ -3565,70 +3565,70 @@
         <v>1.88</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.75</v>
+        <v>2.82</v>
       </c>
       <c r="BH7" t="n">
-        <v>9.69</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.75</v>
+        <v>2.82</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="BL7" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.94</v>
+        <v>3.76</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.75</v>
+        <v>5.71</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BT7" t="n">
-        <v>43.75</v>
+        <v>47.06</v>
       </c>
       <c r="BU7" t="n">
-        <v>25</v>
+        <v>29.41</v>
       </c>
       <c r="BV7" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW7" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX7" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BY7" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="BZ7" t="n">
-        <v>3.29</v>
+        <v>3.28</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.53</v>
+        <v>3.51</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.57</v>
+        <v>3.55</v>
       </c>
       <c r="CC7" t="n">
         <v>4.06</v>
@@ -3640,10 +3640,10 @@
         <v>1.37</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="CH7" t="n">
         <v>1.4</v>
@@ -3652,10 +3652,10 @@
         <v>1.9</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CL7" t="n">
         <v>2.15</v>
@@ -3664,25 +3664,25 @@
         <v>2.2</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.26</v>
+        <v>3.29</v>
       </c>
       <c r="CR7" t="n">
         <v>1.4</v>
       </c>
       <c r="CS7" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="CT7" t="n">
         <v>2.95</v>
-      </c>
-      <c r="CT7" t="n">
-        <v>2.96</v>
       </c>
       <c r="CU7" t="n">
         <v>1.4</v>
@@ -3694,100 +3694,100 @@
         <v>1.84</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="DB7" t="n">
         <v>1.31</v>
       </c>
       <c r="DC7" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.45</v>
+        <v>3.47</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="DG7" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="DH7" t="n">
-        <v>111.38</v>
+        <v>112.12</v>
       </c>
       <c r="DI7" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.32</v>
+        <v>2.41</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.94</v>
+        <v>4.7</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DM7" t="n">
-        <v>63.37</v>
+        <v>63.17</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.76</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="DP7" t="n">
-        <v>15.56</v>
+        <v>15.53</v>
       </c>
       <c r="DQ7" t="n">
-        <v>12.68</v>
+        <v>12.59</v>
       </c>
       <c r="DR7" t="n">
-        <v>6.38</v>
+        <v>6.53</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>53.19</v>
+        <v>52.88</v>
       </c>
       <c r="DW7" t="n">
         <v>0.12</v>
       </c>
       <c r="DX7" t="n">
-        <v>12</v>
+        <v>11.65</v>
       </c>
       <c r="DY7" t="n">
-        <v>8</v>
+        <v>7.77</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="EA7" t="n">
-        <v>20.38</v>
+        <v>20.77</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.13</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="8">
@@ -3797,10 +3797,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
         <v>9</v>
@@ -3809,49 +3809,49 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.71</v>
+        <v>0.88</v>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>3.38</v>
       </c>
       <c r="H8" t="n">
-        <v>114</v>
+        <v>120.75</v>
       </c>
       <c r="I8" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="J8" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>6.57</v>
+        <v>6.62</v>
       </c>
       <c r="L8" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="M8" t="n">
-        <v>77.56999999999999</v>
+        <v>83.75</v>
       </c>
       <c r="N8" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="O8" t="n">
-        <v>3.43</v>
+        <v>3.12</v>
       </c>
       <c r="P8" t="n">
-        <v>14.43</v>
+        <v>14.88</v>
       </c>
       <c r="Q8" t="n">
-        <v>11.86</v>
+        <v>12.5</v>
       </c>
       <c r="R8" t="n">
-        <v>7</v>
+        <v>6.38</v>
       </c>
       <c r="S8" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="T8" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -3863,28 +3863,28 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>51.57</v>
+        <v>53.38</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z8" t="n">
-        <v>13.43</v>
+        <v>13.75</v>
       </c>
       <c r="AA8" t="n">
-        <v>9.859999999999999</v>
+        <v>10</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.57</v>
+        <v>3.75</v>
       </c>
       <c r="AC8" t="n">
-        <v>21.71</v>
+        <v>22.62</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AF8" t="n">
         <v>0.11</v>
@@ -3968,70 +3968,70 @@
         <v>2.22</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="BH8" t="n">
-        <v>10.25</v>
+        <v>10.24</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="BO8" t="n">
         <v>1.12</v>
       </c>
       <c r="BP8" t="n">
-        <v>5</v>
+        <v>4.88</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.19</v>
+        <v>5.29</v>
       </c>
       <c r="BR8" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BS8" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BT8" t="n">
-        <v>43.75</v>
+        <v>41.18</v>
       </c>
       <c r="BU8" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BV8" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW8" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BX8" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.72</v>
+        <v>2.65</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="CA8" t="n">
         <v>3.43</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.55</v>
+        <v>3.53</v>
       </c>
       <c r="CC8" t="n">
         <v>3.59</v>
@@ -4040,16 +4040,16 @@
         <v>4</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="CG8" t="n">
         <v>2.8</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CI8" t="n">
         <v>1.92</v>
@@ -4061,13 +4061,13 @@
         <v>1.6</v>
       </c>
       <c r="CL8" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="CM8" t="n">
         <v>2.2</v>
       </c>
-      <c r="CM8" t="n">
-        <v>2.19</v>
-      </c>
       <c r="CN8" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CO8" t="n">
         <v>1.3</v>
@@ -4076,13 +4076,13 @@
         <v>1.96</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="CR8" t="n">
         <v>1.4</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.97</v>
+        <v>2.98</v>
       </c>
       <c r="CT8" t="n">
         <v>2.94</v>
@@ -4091,19 +4091,19 @@
         <v>1.4</v>
       </c>
       <c r="CV8" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="DA8" t="n">
         <v>1.74</v>
@@ -4115,49 +4115,49 @@
         <v>2.01</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.45</v>
+        <v>3.46</v>
       </c>
       <c r="DE8" t="n">
         <v>0.06</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.25</v>
+        <v>2.47</v>
       </c>
       <c r="DH8" t="n">
-        <v>108.13</v>
+        <v>111.65</v>
       </c>
       <c r="DI8" t="n">
         <v>-0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.12</v>
+        <v>5.23</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="DM8" t="n">
-        <v>65</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.81</v>
+        <v>2.7</v>
       </c>
       <c r="DP8" t="n">
-        <v>15.25</v>
+        <v>15.41</v>
       </c>
       <c r="DQ8" t="n">
-        <v>13</v>
+        <v>13.24</v>
       </c>
       <c r="DR8" t="n">
-        <v>8</v>
+        <v>7.65</v>
       </c>
       <c r="DS8" t="n">
         <v>0</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>50.12</v>
+        <v>51.06</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DX8" t="n">
-        <v>12.94</v>
+        <v>13.12</v>
       </c>
       <c r="DY8" t="n">
-        <v>9.44</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.5</v>
+        <v>3.59</v>
       </c>
       <c r="EA8" t="n">
-        <v>22</v>
+        <v>22.41</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="EC8" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="9">
@@ -4603,61 +4603,61 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" t="n">
         <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="F10" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="G10" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="H10" t="n">
-        <v>122.38</v>
+        <v>118.67</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>2.88</v>
+        <v>2.67</v>
       </c>
       <c r="K10" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="L10" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="M10" t="n">
-        <v>60</v>
+        <v>59.56</v>
       </c>
       <c r="N10" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="O10" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="P10" t="n">
-        <v>13</v>
+        <v>13.22</v>
       </c>
       <c r="Q10" t="n">
-        <v>12.62</v>
+        <v>13.22</v>
       </c>
       <c r="R10" t="n">
-        <v>8.880000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>1.44</v>
       </c>
       <c r="T10" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -4669,28 +4669,28 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>52.38</v>
+        <v>51.78</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="Z10" t="n">
-        <v>14.12</v>
+        <v>13.67</v>
       </c>
       <c r="AA10" t="n">
-        <v>9.25</v>
+        <v>8.67</v>
       </c>
       <c r="AB10" t="n">
-        <v>4.88</v>
+        <v>5</v>
       </c>
       <c r="AC10" t="n">
-        <v>26.25</v>
+        <v>25.78</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -4774,70 +4774,70 @@
         <v>2.25</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.94</v>
+        <v>3.18</v>
       </c>
       <c r="BH10" t="n">
-        <v>7.06</v>
+        <v>7</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.94</v>
+        <v>3.18</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.62</v>
+        <v>0.82</v>
       </c>
       <c r="BL10" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.31</v>
+        <v>1.53</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.31</v>
+        <v>3.18</v>
       </c>
       <c r="BQ10" t="n">
-        <v>3.75</v>
+        <v>3.82</v>
       </c>
       <c r="BR10" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS10" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BT10" t="n">
-        <v>68.75</v>
+        <v>70.59</v>
       </c>
       <c r="BU10" t="n">
-        <v>25</v>
+        <v>29.41</v>
       </c>
       <c r="BV10" t="n">
-        <v>12.5</v>
+        <v>17.65</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>5.88</v>
       </c>
       <c r="BX10" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.47</v>
+        <v>2.71</v>
       </c>
       <c r="BZ10" t="n">
-        <v>2.7</v>
+        <v>2.91</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.42</v>
+        <v>3.44</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.52</v>
+        <v>3.53</v>
       </c>
       <c r="CC10" t="n">
         <v>4.62</v>
@@ -4849,19 +4849,19 @@
         <v>1.37</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CK10" t="n">
         <v>1.74</v>
@@ -4870,7 +4870,7 @@
         <v>2.37</v>
       </c>
       <c r="CM10" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CN10" t="n">
         <v>1.6</v>
@@ -4879,28 +4879,28 @@
         <v>1.28</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.37</v>
+        <v>3.34</v>
       </c>
       <c r="CR10" t="n">
         <v>1.41</v>
       </c>
       <c r="CS10" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.89</v>
+        <v>2.92</v>
       </c>
       <c r="CU10" t="n">
         <v>1.4</v>
       </c>
       <c r="CV10" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CX10" t="n">
         <v>1.75</v>
@@ -4912,58 +4912,58 @@
         <v>2</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.53</v>
+        <v>3.49</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="DF10" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="DG10" t="n">
         <v>2</v>
       </c>
-      <c r="DG10" t="n">
-        <v>1.94</v>
-      </c>
       <c r="DH10" t="n">
-        <v>113.25</v>
+        <v>111.82</v>
       </c>
       <c r="DI10" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.82</v>
+        <v>2.71</v>
       </c>
       <c r="DK10" t="n">
         <v>3.12</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.32</v>
+        <v>0.29</v>
       </c>
       <c r="DM10" t="n">
-        <v>53.31</v>
+        <v>53.47</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="DP10" t="n">
-        <v>14</v>
+        <v>14.06</v>
       </c>
       <c r="DQ10" t="n">
-        <v>11.93</v>
+        <v>12.29</v>
       </c>
       <c r="DR10" t="n">
-        <v>8.880000000000001</v>
+        <v>8.77</v>
       </c>
       <c r="DS10" t="n">
         <v>0.06</v>
@@ -4975,28 +4975,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>48.32</v>
+        <v>48.24</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.32</v>
+        <v>0.29</v>
       </c>
       <c r="DX10" t="n">
-        <v>11.62</v>
+        <v>11.53</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.82</v>
+        <v>7.59</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.82</v>
+        <v>3.94</v>
       </c>
       <c r="EA10" t="n">
-        <v>22.5</v>
+        <v>22.47</v>
       </c>
       <c r="EB10" t="n">
         <v>1.4</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="11">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" t="n">
         <v>8</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
         <v>0.25</v>
@@ -5096,139 +5096,139 @@
         <v>1.88</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AH11" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AI11" t="n">
-        <v>90.38</v>
+        <v>94.56</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="AL11" t="n">
-        <v>4.12</v>
+        <v>4.11</v>
       </c>
       <c r="AM11" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AN11" t="n">
-        <v>44.12</v>
+        <v>46.11</v>
       </c>
       <c r="AO11" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.12</v>
+        <v>2.33</v>
       </c>
       <c r="AQ11" t="n">
-        <v>13.5</v>
+        <v>12.89</v>
       </c>
       <c r="AR11" t="n">
-        <v>12.12</v>
+        <v>12.56</v>
       </c>
       <c r="AS11" t="n">
-        <v>6.88</v>
+        <v>7.33</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AU11" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>42.88</v>
+        <v>43.33</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="BA11" t="n">
-        <v>10.12</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="BB11" t="n">
-        <v>7</v>
+        <v>6.78</v>
       </c>
       <c r="BC11" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="BD11" t="n">
-        <v>19.12</v>
+        <v>19.22</v>
       </c>
       <c r="BE11" t="n">
         <v>1.18</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.25</v>
+        <v>9.18</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.88</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.19</v>
+        <v>4.29</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.06</v>
+        <v>4.88</v>
       </c>
       <c r="BR11" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BS11" t="n">
-        <v>68.75</v>
+        <v>70.59</v>
       </c>
       <c r="BT11" t="n">
-        <v>50</v>
+        <v>47.06</v>
       </c>
       <c r="BU11" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BV11" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW11" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX11" t="n">
-        <v>62.5</v>
+        <v>58.82</v>
       </c>
       <c r="BY11" t="n">
         <v>3.01</v>
@@ -5240,43 +5240,43 @@
         <v>3.41</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.47</v>
+        <v>3.46</v>
       </c>
       <c r="CC11" t="n">
-        <v>4.36</v>
+        <v>4.11</v>
       </c>
       <c r="CD11" t="n">
-        <v>4.7</v>
+        <v>4.43</v>
       </c>
       <c r="CE11" t="n">
         <v>1.42</v>
       </c>
       <c r="CF11" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="CH11" t="n">
         <v>1.35</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CK11" t="n">
         <v>1.73</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="CM11" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CO11" t="n">
         <v>1.32</v>
@@ -5285,31 +5285,31 @@
         <v>2.07</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.64</v>
+        <v>3.63</v>
       </c>
       <c r="CR11" t="n">
         <v>1.45</v>
       </c>
       <c r="CS11" t="n">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="CT11" t="n">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="CX11" t="n">
         <v>1.76</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CZ11" t="n">
         <v>1.99</v>
@@ -5330,76 +5330,76 @@
         <v>0.18</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="DG11" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="DH11" t="n">
-        <v>99.5</v>
+        <v>101.18</v>
       </c>
       <c r="DI11" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="DK11" t="n">
         <v>4</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="DM11" t="n">
-        <v>50.37</v>
+        <v>51.06</v>
       </c>
       <c r="DN11" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DO11" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="DP11" t="n">
+        <v>12.65</v>
+      </c>
+      <c r="DQ11" t="n">
+        <v>12.71</v>
+      </c>
+      <c r="DR11" t="n">
+        <v>7.82</v>
+      </c>
+      <c r="DS11" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="DT11" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="DU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV11" t="n">
+        <v>44.59</v>
+      </c>
+      <c r="DW11" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="DX11" t="n">
+        <v>11.77</v>
+      </c>
+      <c r="DY11" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="DZ11" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="EA11" t="n">
+        <v>20.24</v>
+      </c>
+      <c r="EB11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="EC11" t="n">
         <v>2.06</v>
-      </c>
-      <c r="DP11" t="n">
-        <v>12.94</v>
-      </c>
-      <c r="DQ11" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="DR11" t="n">
-        <v>7.63</v>
-      </c>
-      <c r="DS11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="DT11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="DU11" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV11" t="n">
-        <v>44.44</v>
-      </c>
-      <c r="DW11" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="DX11" t="n">
-        <v>12</v>
-      </c>
-      <c r="DY11" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="DZ11" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="EA11" t="n">
-        <v>20.25</v>
-      </c>
-      <c r="EB11" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="EC11" t="n">
-        <v>2.13</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
@@ -1541,7 +1541,7 @@
         <v>4.78</v>
       </c>
       <c r="BD2" t="n">
-        <v>24.11</v>
+        <v>24.33</v>
       </c>
       <c r="BE2" t="n">
         <v>1.89</v>
@@ -1766,7 +1766,7 @@
         <v>5.65</v>
       </c>
       <c r="EA2" t="n">
-        <v>23.23</v>
+        <v>23.35</v>
       </c>
       <c r="EB2" t="n">
         <v>1.95</v>
@@ -3878,7 +3878,7 @@
         <v>3.75</v>
       </c>
       <c r="AC8" t="n">
-        <v>22.62</v>
+        <v>22.5</v>
       </c>
       <c r="AD8" t="n">
         <v>1.74</v>
@@ -4184,7 +4184,7 @@
         <v>3.59</v>
       </c>
       <c r="EA8" t="n">
-        <v>22.41</v>
+        <v>22.35</v>
       </c>
       <c r="EB8" t="n">
         <v>1.58</v>

--- a/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
@@ -1502,7 +1502,7 @@
         <v>2.78</v>
       </c>
       <c r="AQ2" t="n">
-        <v>14.44</v>
+        <v>14.33</v>
       </c>
       <c r="AR2" t="n">
         <v>14.33</v>
@@ -1733,7 +1733,7 @@
         <v>3.18</v>
       </c>
       <c r="DP2" t="n">
-        <v>13.24</v>
+        <v>13.18</v>
       </c>
       <c r="DQ2" t="n">
         <v>13.65</v>

--- a/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
@@ -1379,61 +1379,61 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
         <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="G2" t="n">
-        <v>2.88</v>
+        <v>2.56</v>
       </c>
       <c r="H2" t="n">
-        <v>126.62</v>
+        <v>128.89</v>
       </c>
       <c r="I2" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="J2" t="n">
-        <v>2.88</v>
+        <v>2.67</v>
       </c>
       <c r="K2" t="n">
-        <v>6.62</v>
+        <v>5.89</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="M2" t="n">
-        <v>74.38</v>
+        <v>74.67</v>
       </c>
       <c r="N2" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="O2" t="n">
-        <v>3.62</v>
+        <v>3.22</v>
       </c>
       <c r="P2" t="n">
-        <v>11.88</v>
+        <v>11.56</v>
       </c>
       <c r="Q2" t="n">
-        <v>12.88</v>
+        <v>13</v>
       </c>
       <c r="R2" t="n">
-        <v>5.62</v>
+        <v>5.78</v>
       </c>
       <c r="S2" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="T2" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -1445,28 +1445,28 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>59</v>
+        <v>57.78</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z2" t="n">
-        <v>15.88</v>
+        <v>15.44</v>
       </c>
       <c r="AA2" t="n">
-        <v>9.25</v>
+        <v>9</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.62</v>
+        <v>6.44</v>
       </c>
       <c r="AC2" t="n">
-        <v>22.25</v>
+        <v>22.67</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.01</v>
+        <v>1.97</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="AF2" t="n">
         <v>0.11</v>
@@ -1550,70 +1550,70 @@
         <v>2</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="BH2" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.71</v>
+        <v>4.44</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.76</v>
+        <v>5.5</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BT2" t="n">
-        <v>64.70999999999999</v>
+        <v>61.11</v>
       </c>
       <c r="BU2" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BV2" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW2" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX2" t="n">
-        <v>58.82</v>
+        <v>55.56</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="BZ2" t="n">
         <v>1.33</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.52</v>
+        <v>4.58</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.99</v>
+        <v>5.02</v>
       </c>
       <c r="CC2" t="n">
         <v>1.57</v>
@@ -1643,52 +1643,52 @@
         <v>1.58</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CO2" t="n">
         <v>1.22</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="CR2" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="CT2" t="n">
-        <v>3.02</v>
+        <v>3.06</v>
       </c>
       <c r="CU2" t="n">
         <v>1.53</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CW2" t="n">
         <v>2.02</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="CY2" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="DB2" t="n">
         <v>1.24</v>
@@ -1700,79 +1700,79 @@
         <v>2.87</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.65</v>
+        <v>3.44</v>
       </c>
       <c r="DH2" t="n">
-        <v>122.76</v>
+        <v>124.11</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="DK2" t="n">
-        <v>6.88</v>
+        <v>6.5</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="DM2" t="n">
-        <v>75.23999999999999</v>
+        <v>75.33</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="DO2" t="n">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="DP2" t="n">
-        <v>13.18</v>
+        <v>12.94</v>
       </c>
       <c r="DQ2" t="n">
-        <v>13.65</v>
+        <v>13.66</v>
       </c>
       <c r="DR2" t="n">
-        <v>5.82</v>
+        <v>5.89</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>56.94</v>
+        <v>56.44</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DX2" t="n">
-        <v>15.89</v>
+        <v>15.66</v>
       </c>
       <c r="DY2" t="n">
-        <v>10.23</v>
+        <v>10.06</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5.65</v>
+        <v>5.61</v>
       </c>
       <c r="EA2" t="n">
-        <v>23.35</v>
+        <v>23.5</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.29</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="3">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" t="n">
         <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
         <v>0.25</v>
@@ -3084,136 +3084,136 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AI6" t="n">
-        <v>108.62</v>
+        <v>107.11</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="AL6" t="n">
-        <v>3.25</v>
+        <v>3.44</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AN6" t="n">
-        <v>55.38</v>
+        <v>55.56</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AP6" t="n">
         <v>2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>11.38</v>
+        <v>11</v>
       </c>
       <c r="AR6" t="n">
-        <v>11.62</v>
+        <v>12.11</v>
       </c>
       <c r="AS6" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>22.89</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="BH6" t="n">
         <v>9.880000000000001</v>
       </c>
-      <c r="AT6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>48.38</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>23.38</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>9.619999999999999</v>
-      </c>
       <c r="BI6" t="n">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.44</v>
+        <v>0.53</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.25</v>
+        <v>4.41</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.69</v>
+        <v>4.82</v>
       </c>
       <c r="BR6" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS6" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BT6" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BU6" t="n">
-        <v>12.5</v>
+        <v>17.65</v>
       </c>
       <c r="BV6" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW6" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX6" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BY6" t="n">
         <v>2.57</v>
@@ -3222,22 +3222,22 @@
         <v>2.7</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.36</v>
+        <v>3.33</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.47</v>
+        <v>3.44</v>
       </c>
       <c r="CC6" t="n">
-        <v>3.92</v>
+        <v>3.83</v>
       </c>
       <c r="CD6" t="n">
-        <v>4.38</v>
+        <v>4.27</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.89</v>
+        <v>2.92</v>
       </c>
       <c r="CG6" t="n">
         <v>2.76</v>
@@ -3246,7 +3246,7 @@
         <v>1.37</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CJ6" t="n">
         <v>1.85</v>
@@ -3255,22 +3255,22 @@
         <v>1.74</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.34</v>
+        <v>2.37</v>
       </c>
       <c r="CM6" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CO6" t="n">
         <v>1.32</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.47</v>
+        <v>3.51</v>
       </c>
       <c r="CR6" t="n">
         <v>1.43</v>
@@ -3291,67 +3291,67 @@
         <v>1.92</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="CY6" t="n">
         <v>2.24</v>
       </c>
       <c r="CZ6" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="DA6" t="n">
         <v>1.58</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.7</v>
+        <v>3.74</v>
       </c>
       <c r="DE6" t="n">
         <v>0.12</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="DH6" t="n">
-        <v>106.06</v>
+        <v>105.41</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DJ6" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="DK6" t="n">
-        <v>3.68</v>
+        <v>3.76</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="DM6" t="n">
-        <v>56.19</v>
+        <v>56.24</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="DP6" t="n">
-        <v>10.82</v>
+        <v>10.65</v>
       </c>
       <c r="DQ6" t="n">
-        <v>11.37</v>
+        <v>11.64</v>
       </c>
       <c r="DR6" t="n">
-        <v>9.880000000000001</v>
+        <v>9.65</v>
       </c>
       <c r="DS6" t="n">
         <v>0</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>48.94</v>
+        <v>48.71</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>10.12</v>
+        <v>10.35</v>
       </c>
       <c r="DY6" t="n">
-        <v>6.5</v>
+        <v>6.71</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.62</v>
+        <v>3.65</v>
       </c>
       <c r="EA6" t="n">
-        <v>22</v>
+        <v>21.82</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="7">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" t="n">
         <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3484,139 +3484,139 @@
         <v>2.56</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AH7" t="n">
-        <v>3.12</v>
+        <v>2.89</v>
       </c>
       <c r="AI7" t="n">
-        <v>115.25</v>
+        <v>115.78</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="AL7" t="n">
-        <v>5.62</v>
+        <v>5.11</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AN7" t="n">
-        <v>66.62</v>
+        <v>65</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AP7" t="n">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="AQ7" t="n">
-        <v>15.12</v>
+        <v>15</v>
       </c>
       <c r="AR7" t="n">
-        <v>11.12</v>
+        <v>10.89</v>
       </c>
       <c r="AS7" t="n">
-        <v>6.5</v>
+        <v>6.67</v>
       </c>
       <c r="AT7" t="n">
         <v>2</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>54</v>
+        <v>53.78</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="BA7" t="n">
-        <v>12.38</v>
+        <v>11.67</v>
       </c>
       <c r="BB7" t="n">
-        <v>8.880000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="BC7" t="n">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="BD7" t="n">
-        <v>19.38</v>
+        <v>20.33</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="BH7" t="n">
-        <v>9.470000000000001</v>
+        <v>9</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="BL7" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.76</v>
+        <v>3.56</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.71</v>
+        <v>5.44</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BT7" t="n">
-        <v>47.06</v>
+        <v>44.44</v>
       </c>
       <c r="BU7" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BV7" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW7" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX7" t="n">
-        <v>82.34999999999999</v>
+        <v>77.78</v>
       </c>
       <c r="BY7" t="n">
         <v>3.21</v>
@@ -3625,85 +3625,85 @@
         <v>3.28</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.51</v>
+        <v>3.63</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.55</v>
+        <v>3.66</v>
       </c>
       <c r="CC7" t="n">
-        <v>4.06</v>
+        <v>4.71</v>
       </c>
       <c r="CD7" t="n">
-        <v>4.44</v>
+        <v>5</v>
       </c>
       <c r="CE7" t="n">
         <v>1.37</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="CH7" t="n">
         <v>1.4</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CO7" t="n">
         <v>1.27</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.29</v>
+        <v>3.25</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CS7" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="CT7" t="n">
         <v>2.97</v>
       </c>
-      <c r="CT7" t="n">
-        <v>2.95</v>
-      </c>
       <c r="CU7" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="DB7" t="n">
         <v>1.31</v>
@@ -3715,79 +3715,79 @@
         <v>3.47</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="DG7" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="DH7" t="n">
-        <v>112.12</v>
+        <v>112.56</v>
       </c>
       <c r="DI7" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DM7" t="n">
-        <v>63.17</v>
+        <v>62.56</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.76</v>
+        <v>0.84</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="DP7" t="n">
-        <v>15.53</v>
+        <v>15.44</v>
       </c>
       <c r="DQ7" t="n">
-        <v>12.59</v>
+        <v>12.39</v>
       </c>
       <c r="DR7" t="n">
-        <v>6.53</v>
+        <v>6.61</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>52.88</v>
+        <v>52.84</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX7" t="n">
-        <v>11.65</v>
+        <v>11.34</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.77</v>
+        <v>7.56</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.88</v>
+        <v>3.77</v>
       </c>
       <c r="EA7" t="n">
-        <v>20.77</v>
+        <v>21.16</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="8">
@@ -3797,10 +3797,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" t="n">
         <v>9</v>
@@ -3809,49 +3809,49 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>3.38</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
-        <v>120.75</v>
+        <v>124.33</v>
       </c>
       <c r="I8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="K8" t="n">
-        <v>6.62</v>
+        <v>6.22</v>
       </c>
       <c r="L8" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="M8" t="n">
-        <v>83.75</v>
+        <v>86.22</v>
       </c>
       <c r="N8" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="O8" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="P8" t="n">
-        <v>14.88</v>
+        <v>14.78</v>
       </c>
       <c r="Q8" t="n">
-        <v>12.5</v>
+        <v>13.44</v>
       </c>
       <c r="R8" t="n">
-        <v>6.38</v>
+        <v>6.22</v>
       </c>
       <c r="S8" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="T8" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -3863,28 +3863,28 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>53.38</v>
+        <v>52.89</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z8" t="n">
-        <v>13.75</v>
+        <v>13.56</v>
       </c>
       <c r="AA8" t="n">
-        <v>10</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.75</v>
+        <v>3.67</v>
       </c>
       <c r="AC8" t="n">
-        <v>22.5</v>
+        <v>23</v>
       </c>
       <c r="AD8" t="n">
         <v>1.74</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AF8" t="n">
         <v>0.11</v>
@@ -3968,70 +3968,70 @@
         <v>2.22</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.47</v>
+        <v>2.33</v>
       </c>
       <c r="BH8" t="n">
-        <v>10.24</v>
+        <v>10.17</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.47</v>
+        <v>2.33</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.88</v>
+        <v>5.06</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.29</v>
+        <v>5.06</v>
       </c>
       <c r="BR8" t="n">
-        <v>82.34999999999999</v>
+        <v>77.78</v>
       </c>
       <c r="BS8" t="n">
-        <v>76.47</v>
+        <v>72.22</v>
       </c>
       <c r="BT8" t="n">
-        <v>41.18</v>
+        <v>38.89</v>
       </c>
       <c r="BU8" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BV8" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW8" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BX8" t="n">
-        <v>52.94</v>
+        <v>50</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.43</v>
+        <v>3.4</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.53</v>
+        <v>3.5</v>
       </c>
       <c r="CC8" t="n">
         <v>3.59</v>
@@ -4040,13 +4040,13 @@
         <v>4</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="CH8" t="n">
         <v>1.39</v>
@@ -4058,13 +4058,13 @@
         <v>1.8</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CN8" t="n">
         <v>1.74</v>
@@ -4082,16 +4082,16 @@
         <v>1.4</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CV8" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CW8" t="n">
         <v>1.83</v>
@@ -4112,52 +4112,52 @@
         <v>1.31</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.46</v>
+        <v>3.49</v>
       </c>
       <c r="DE8" t="n">
         <v>0.06</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.47</v>
+        <v>2.34</v>
       </c>
       <c r="DH8" t="n">
-        <v>111.65</v>
+        <v>113.94</v>
       </c>
       <c r="DI8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.23</v>
+        <v>5.11</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="DM8" t="n">
-        <v>68.65000000000001</v>
+        <v>70.72</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.82</v>
+        <v>0.84</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="DP8" t="n">
-        <v>15.41</v>
+        <v>15.34</v>
       </c>
       <c r="DQ8" t="n">
-        <v>13.24</v>
+        <v>13.66</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.65</v>
+        <v>7.5</v>
       </c>
       <c r="DS8" t="n">
         <v>0</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>51.06</v>
+        <v>50.94</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DX8" t="n">
-        <v>13.12</v>
+        <v>13.06</v>
       </c>
       <c r="DY8" t="n">
-        <v>9.529999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.59</v>
+        <v>3.56</v>
       </c>
       <c r="EA8" t="n">
-        <v>22.35</v>
+        <v>22.61</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="9">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10" t="n">
         <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
         <v>0.33</v>
@@ -4696,136 +4696,136 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AI10" t="n">
-        <v>104.12</v>
+        <v>104.78</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="AL10" t="n">
-        <v>2.75</v>
+        <v>3.11</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AN10" t="n">
-        <v>46.62</v>
+        <v>47.78</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AP10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>15.67</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>11.56</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>9.109999999999999</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AU10" t="n">
         <v>1</v>
       </c>
-      <c r="AQ10" t="n">
-        <v>15</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>8.880000000000001</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AV10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>44.25</v>
+        <v>45</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="BA10" t="n">
-        <v>9.119999999999999</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="BB10" t="n">
-        <v>6.38</v>
+        <v>6.11</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="BD10" t="n">
-        <v>18.75</v>
+        <v>19.11</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="BH10" t="n">
-        <v>7</v>
+        <v>7.11</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BL10" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.18</v>
+        <v>3.44</v>
       </c>
       <c r="BQ10" t="n">
-        <v>3.82</v>
+        <v>3.67</v>
       </c>
       <c r="BR10" t="n">
-        <v>94.12</v>
+        <v>88.89</v>
       </c>
       <c r="BS10" t="n">
-        <v>94.12</v>
+        <v>88.89</v>
       </c>
       <c r="BT10" t="n">
-        <v>70.59</v>
+        <v>66.67</v>
       </c>
       <c r="BU10" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BV10" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BW10" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX10" t="n">
-        <v>82.34999999999999</v>
+        <v>77.78</v>
       </c>
       <c r="BY10" t="n">
         <v>2.71</v>
@@ -4834,52 +4834,52 @@
         <v>2.91</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.44</v>
+        <v>3.42</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.53</v>
+        <v>3.5</v>
       </c>
       <c r="CC10" t="n">
-        <v>4.62</v>
+        <v>4.43</v>
       </c>
       <c r="CD10" t="n">
-        <v>5</v>
+        <v>4.81</v>
       </c>
       <c r="CE10" t="n">
         <v>1.37</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CI10" t="n">
         <v>1.89</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="CM10" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CO10" t="n">
         <v>1.28</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CQ10" t="n">
         <v>3.34</v>
@@ -4888,10 +4888,10 @@
         <v>1.41</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="CU10" t="n">
         <v>1.4</v>
@@ -4903,67 +4903,67 @@
         <v>1.85</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CY10" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.49</v>
+        <v>3.53</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF10" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="DG10" t="n">
         <v>1.94</v>
       </c>
-      <c r="DG10" t="n">
-        <v>2</v>
-      </c>
       <c r="DH10" t="n">
-        <v>111.82</v>
+        <v>111.72</v>
       </c>
       <c r="DI10" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="DK10" t="n">
-        <v>3.12</v>
+        <v>3.28</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="DM10" t="n">
-        <v>53.47</v>
+        <v>53.67</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.12</v>
+        <v>1.33</v>
       </c>
       <c r="DP10" t="n">
-        <v>14.06</v>
+        <v>14.44</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.29</v>
+        <v>12.39</v>
       </c>
       <c r="DR10" t="n">
-        <v>8.77</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="DS10" t="n">
         <v>0.06</v>
@@ -4975,28 +4975,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>48.24</v>
+        <v>48.39</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DX10" t="n">
-        <v>11.53</v>
+        <v>11.28</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.59</v>
+        <v>7.39</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.94</v>
+        <v>3.89</v>
       </c>
       <c r="EA10" t="n">
-        <v>22.47</v>
+        <v>22.44</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="11">
@@ -5006,94 +5006,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11" t="n">
         <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="F11" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="G11" t="n">
-        <v>1.88</v>
+        <v>2.11</v>
       </c>
       <c r="H11" t="n">
-        <v>108.62</v>
+        <v>111.44</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="M11" t="n">
+        <v>58.22</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="P11" t="n">
+        <v>12.67</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>12.33</v>
+      </c>
+      <c r="R11" t="n">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>47</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>14.67</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>10.22</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AE11" t="n">
         <v>2</v>
-      </c>
-      <c r="K11" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="M11" t="n">
-        <v>56.62</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O11" t="n">
-        <v>2</v>
-      </c>
-      <c r="P11" t="n">
-        <v>12.38</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>12.88</v>
-      </c>
-      <c r="R11" t="n">
-        <v>8.380000000000001</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>46</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>13.88</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>21.38</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.88</v>
       </c>
       <c r="AF11" t="n">
         <v>0.11</v>
@@ -5177,70 +5177,70 @@
         <v>2.22</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.53</v>
+        <v>2.61</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.18</v>
+        <v>9.44</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.53</v>
+        <v>2.61</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.29</v>
+        <v>0.39</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.29</v>
+        <v>4.44</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.88</v>
+        <v>5</v>
       </c>
       <c r="BR11" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BS11" t="n">
-        <v>70.59</v>
+        <v>72.22</v>
       </c>
       <c r="BT11" t="n">
-        <v>47.06</v>
+        <v>50</v>
       </c>
       <c r="BU11" t="n">
-        <v>35.29</v>
+        <v>38.89</v>
       </c>
       <c r="BV11" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW11" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX11" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BY11" t="n">
-        <v>3.01</v>
+        <v>2.9</v>
       </c>
       <c r="BZ11" t="n">
-        <v>3.27</v>
+        <v>3.18</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.41</v>
+        <v>3.38</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.46</v>
+        <v>3.43</v>
       </c>
       <c r="CC11" t="n">
         <v>4.11</v>
@@ -5252,13 +5252,13 @@
         <v>1.42</v>
       </c>
       <c r="CF11" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="CG11" t="n">
         <v>2.64</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CI11" t="n">
         <v>1.8</v>
@@ -5270,22 +5270,22 @@
         <v>1.73</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CP11" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.63</v>
+        <v>3.66</v>
       </c>
       <c r="CR11" t="n">
         <v>1.45</v>
@@ -5300,106 +5300,106 @@
         <v>1.36</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CZ11" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="DA11" t="n">
         <v>1.6</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.84</v>
+        <v>3.87</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="DG11" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="DH11" t="n">
-        <v>101.18</v>
+        <v>103</v>
       </c>
       <c r="DI11" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="DK11" t="n">
-        <v>4</v>
+        <v>4.28</v>
       </c>
       <c r="DL11" t="n">
         <v>0.88</v>
       </c>
       <c r="DM11" t="n">
-        <v>51.06</v>
+        <v>52.16</v>
       </c>
       <c r="DN11" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.17</v>
+        <v>2.33</v>
       </c>
       <c r="DP11" t="n">
-        <v>12.65</v>
+        <v>12.78</v>
       </c>
       <c r="DQ11" t="n">
-        <v>12.71</v>
+        <v>12.44</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.82</v>
+        <v>7.78</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>44.59</v>
+        <v>45.16</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DX11" t="n">
-        <v>11.77</v>
+        <v>12.28</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.47</v>
+        <v>3.78</v>
       </c>
       <c r="EA11" t="n">
-        <v>20.24</v>
+        <v>20.11</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
@@ -1421,7 +1421,7 @@
         <v>3.22</v>
       </c>
       <c r="P2" t="n">
-        <v>11.56</v>
+        <v>11.44</v>
       </c>
       <c r="Q2" t="n">
         <v>13</v>
@@ -1733,7 +1733,7 @@
         <v>3</v>
       </c>
       <c r="DP2" t="n">
-        <v>12.94</v>
+        <v>12.88</v>
       </c>
       <c r="DQ2" t="n">
         <v>13.66</v>
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" t="n">
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E3" t="n">
         <v>0.22</v>
@@ -1875,49 +1875,49 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AI3" t="n">
-        <v>98.12</v>
+        <v>96.78</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AL3" t="n">
-        <v>5</v>
+        <v>4.89</v>
       </c>
       <c r="AM3" t="n">
         <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>55.38</v>
+        <v>53.89</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="AQ3" t="n">
-        <v>12.12</v>
+        <v>11.67</v>
       </c>
       <c r="AR3" t="n">
-        <v>13</v>
+        <v>12.89</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.880000000000001</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
@@ -1929,82 +1929,82 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>43.25</v>
+        <v>43.22</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="BA3" t="n">
-        <v>12.5</v>
+        <v>11.89</v>
       </c>
       <c r="BB3" t="n">
-        <v>8.5</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="BC3" t="n">
-        <v>4</v>
+        <v>3.78</v>
       </c>
       <c r="BD3" t="n">
-        <v>18.5</v>
+        <v>19.22</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.76</v>
+        <v>2.67</v>
       </c>
       <c r="BH3" t="n">
-        <v>8.35</v>
+        <v>8.67</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.76</v>
+        <v>2.67</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.71</v>
+        <v>3.89</v>
       </c>
       <c r="BQ3" t="n">
-        <v>3.88</v>
+        <v>4.06</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>82.34999999999999</v>
+        <v>77.78</v>
       </c>
       <c r="BT3" t="n">
-        <v>52.94</v>
+        <v>50</v>
       </c>
       <c r="BU3" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BV3" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>70.59</v>
+        <v>66.67</v>
       </c>
       <c r="BY3" t="n">
         <v>3.03</v>
@@ -2013,46 +2013,46 @@
         <v>3.25</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.56</v>
+        <v>3.58</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="CC3" t="n">
-        <v>5.63</v>
+        <v>5.72</v>
       </c>
       <c r="CD3" t="n">
-        <v>5.72</v>
+        <v>5.85</v>
       </c>
       <c r="CE3" t="n">
         <v>1.4</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="CH3" t="n">
         <v>1.38</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CJ3" t="n">
         <v>1.92</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CO3" t="n">
         <v>1.31</v>
@@ -2061,16 +2061,16 @@
         <v>2.02</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="CR3" t="n">
         <v>1.43</v>
       </c>
       <c r="CS3" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="CT3" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="CU3" t="n">
         <v>1.39</v>
@@ -2082,67 +2082,67 @@
         <v>1.93</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="DB3" t="n">
         <v>1.34</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.72</v>
+        <v>3.69</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="DG3" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="DH3" t="n">
-        <v>100.41</v>
+        <v>99.61</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.65</v>
+        <v>2.61</v>
       </c>
       <c r="DK3" t="n">
-        <v>4.41</v>
+        <v>4.39</v>
       </c>
       <c r="DL3" t="n">
         <v>0.06</v>
       </c>
       <c r="DM3" t="n">
-        <v>53.59</v>
+        <v>52.94</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="DP3" t="n">
-        <v>11.53</v>
+        <v>11.34</v>
       </c>
       <c r="DQ3" t="n">
-        <v>13.41</v>
+        <v>13.34</v>
       </c>
       <c r="DR3" t="n">
-        <v>8.83</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="DS3" t="n">
         <v>0.06</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>47.82</v>
+        <v>47.56</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DX3" t="n">
-        <v>11.71</v>
+        <v>11.44</v>
       </c>
       <c r="DY3" t="n">
-        <v>7.65</v>
+        <v>7.5</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4.06</v>
+        <v>3.94</v>
       </c>
       <c r="EA3" t="n">
-        <v>20.41</v>
+        <v>20.67</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4" t="n">
         <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2275,52 +2275,52 @@
         <v>1.67</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG4" t="n">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="AI4" t="n">
-        <v>103.62</v>
+        <v>101.33</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK4" t="n">
-        <v>3.25</v>
+        <v>3.67</v>
       </c>
       <c r="AL4" t="n">
-        <v>4</v>
+        <v>3.89</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AN4" t="n">
-        <v>56.25</v>
+        <v>55</v>
       </c>
       <c r="AO4" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AQ4" t="n">
-        <v>12.12</v>
+        <v>12.22</v>
       </c>
       <c r="AR4" t="n">
-        <v>10.12</v>
+        <v>10.33</v>
       </c>
       <c r="AS4" t="n">
-        <v>8.5</v>
+        <v>8.44</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="AV4" t="n">
         <v>0</v>
@@ -2332,82 +2332,82 @@
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>39.38</v>
+        <v>38.44</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="BA4" t="n">
-        <v>10.25</v>
+        <v>9.44</v>
       </c>
       <c r="BB4" t="n">
-        <v>7.25</v>
+        <v>6.67</v>
       </c>
       <c r="BC4" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="BD4" t="n">
-        <v>21.12</v>
+        <v>20.78</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.62</v>
+        <v>2.89</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="BH4" t="n">
-        <v>10.65</v>
+        <v>10.33</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BL4" t="n">
         <v>1.06</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.41</v>
+        <v>0.44</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="BP4" t="n">
-        <v>5.24</v>
+        <v>5.11</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.35</v>
+        <v>5.17</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
       </c>
       <c r="BS4" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT4" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BU4" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BV4" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BY4" t="n">
         <v>4.46</v>
@@ -2416,34 +2416,34 @@
         <v>5.11</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.03</v>
+        <v>4.12</v>
       </c>
       <c r="CB4" t="n">
-        <v>4.22</v>
+        <v>4.28</v>
       </c>
       <c r="CC4" t="n">
-        <v>6.65</v>
+        <v>6.71</v>
       </c>
       <c r="CD4" t="n">
-        <v>9.380000000000001</v>
+        <v>9.52</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.73</v>
+        <v>2.71</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CK4" t="n">
         <v>1.6</v>
@@ -2458,13 +2458,13 @@
         <v>1.54</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.17</v>
+        <v>3.13</v>
       </c>
       <c r="CR4" t="n">
         <v>1.39</v>
@@ -2479,70 +2479,70 @@
         <v>1.49</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CW4" t="n">
         <v>1.98</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.28</v>
+        <v>3.24</v>
       </c>
       <c r="DE4" t="n">
         <v>0.06</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.47</v>
+        <v>1.61</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="DH4" t="n">
-        <v>110.12</v>
+        <v>108.61</v>
       </c>
       <c r="DI4" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.53</v>
+        <v>2.78</v>
       </c>
       <c r="DK4" t="n">
-        <v>3.7</v>
+        <v>3.66</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="DM4" t="n">
-        <v>62.83</v>
+        <v>61.84</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.88</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="DP4" t="n">
-        <v>12.82</v>
+        <v>12.83</v>
       </c>
       <c r="DQ4" t="n">
-        <v>11.35</v>
+        <v>11.38</v>
       </c>
       <c r="DR4" t="n">
         <v>8.06</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>41.12</v>
+        <v>40.56</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.24</v>
+        <v>0.28</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.35</v>
+        <v>9.94</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.94</v>
+        <v>6.67</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.41</v>
+        <v>3.28</v>
       </c>
       <c r="EA4" t="n">
-        <v>20.82</v>
+        <v>20.67</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="5">
@@ -2588,94 +2588,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
         <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="G5" t="n">
-        <v>4</v>
+        <v>3.67</v>
       </c>
       <c r="H5" t="n">
-        <v>124.5</v>
+        <v>122.78</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="K5" t="n">
-        <v>5.5</v>
+        <v>5.11</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>67.12</v>
+        <v>67</v>
       </c>
       <c r="N5" t="n">
-        <v>0.25</v>
+        <v>0.44</v>
       </c>
       <c r="O5" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="P5" t="n">
-        <v>12.12</v>
+        <v>12.11</v>
       </c>
       <c r="Q5" t="n">
-        <v>15.25</v>
+        <v>15</v>
       </c>
       <c r="R5" t="n">
-        <v>5.25</v>
+        <v>5.11</v>
       </c>
       <c r="S5" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="T5" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="U5" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="V5" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="Z5" t="n">
-        <v>15.88</v>
+        <v>15.89</v>
       </c>
       <c r="AA5" t="n">
-        <v>10.12</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="AC5" t="n">
-        <v>23</v>
+        <v>22.78</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AF5" t="n">
         <v>0.11</v>
@@ -2759,70 +2759,70 @@
         <v>2.78</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.35</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="BO5" t="n">
         <v>1.06</v>
       </c>
       <c r="BP5" t="n">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.18</v>
+        <v>5</v>
       </c>
       <c r="BR5" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS5" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BT5" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BU5" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BV5" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>35.29</v>
+        <v>38.89</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.56</v>
+        <v>3.67</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="CC5" t="n">
         <v>2.38</v>
@@ -2834,13 +2834,13 @@
         <v>1.41</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.96</v>
+        <v>2.93</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CI5" t="n">
         <v>1.74</v>
@@ -2864,10 +2864,10 @@
         <v>1.32</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.69</v>
+        <v>3.63</v>
       </c>
       <c r="CR5" t="n">
         <v>1.43</v>
@@ -2888,100 +2888,100 @@
         <v>2.02</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CY5" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="DB5" t="n">
         <v>1.36</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.85</v>
+        <v>3.78</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.24</v>
+        <v>3.12</v>
       </c>
       <c r="DH5" t="n">
-        <v>111.65</v>
+        <v>111.5</v>
       </c>
       <c r="DI5" t="n">
         <v>-0.06</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.06</v>
+        <v>2.22</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.53</v>
+        <v>5.34</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="DM5" t="n">
-        <v>62.52</v>
+        <v>62.72</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.65</v>
+        <v>0.72</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.29</v>
+        <v>2.22</v>
       </c>
       <c r="DP5" t="n">
-        <v>12.7</v>
+        <v>12.66</v>
       </c>
       <c r="DQ5" t="n">
-        <v>14.94</v>
+        <v>14.84</v>
       </c>
       <c r="DR5" t="n">
-        <v>6.29</v>
+        <v>6.16</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>57.65</v>
+        <v>58.28</v>
       </c>
       <c r="DW5" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="DX5" t="n">
-        <v>14.47</v>
+        <v>14.56</v>
       </c>
       <c r="DY5" t="n">
-        <v>9.529999999999999</v>
+        <v>9.44</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4.94</v>
+        <v>5.11</v>
       </c>
       <c r="EA5" t="n">
-        <v>21.3</v>
+        <v>21.28</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="6">
@@ -3517,7 +3517,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ7" t="n">
-        <v>15</v>
+        <v>14.89</v>
       </c>
       <c r="AR7" t="n">
         <v>10.89</v>
@@ -3748,7 +3748,7 @@
         <v>1.61</v>
       </c>
       <c r="DP7" t="n">
-        <v>15.44</v>
+        <v>15.39</v>
       </c>
       <c r="DQ7" t="n">
         <v>12.39</v>
@@ -4200,94 +4200,94 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" t="n">
         <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="F9" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="G9" t="n">
-        <v>3.12</v>
+        <v>3.22</v>
       </c>
       <c r="H9" t="n">
-        <v>111.75</v>
+        <v>116</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="K9" t="n">
-        <v>6.25</v>
+        <v>6.67</v>
       </c>
       <c r="L9" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="M9" t="n">
-        <v>67.25</v>
+        <v>71</v>
       </c>
       <c r="N9" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="O9" t="n">
-        <v>3.12</v>
+        <v>3.44</v>
       </c>
       <c r="P9" t="n">
-        <v>12.12</v>
+        <v>12.11</v>
       </c>
       <c r="Q9" t="n">
-        <v>15.38</v>
+        <v>14.56</v>
       </c>
       <c r="R9" t="n">
-        <v>6.88</v>
+        <v>6.67</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="T9" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="U9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>52.12</v>
+        <v>52.67</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>16.38</v>
+        <v>16.22</v>
       </c>
       <c r="AA9" t="n">
-        <v>11.5</v>
+        <v>11.44</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.88</v>
+        <v>4.78</v>
       </c>
       <c r="AC9" t="n">
-        <v>24.75</v>
+        <v>25.22</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="AF9" t="n">
         <v>0.12</v>
@@ -4371,70 +4371,70 @@
         <v>3.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.81</v>
+        <v>2.71</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.81</v>
+        <v>11</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.81</v>
+        <v>2.71</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BL9" t="n">
         <v>0.88</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="BP9" t="n">
-        <v>5.12</v>
+        <v>5.24</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.69</v>
+        <v>5.76</v>
       </c>
       <c r="BR9" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BS9" t="n">
-        <v>81.25</v>
+        <v>76.47</v>
       </c>
       <c r="BT9" t="n">
-        <v>50</v>
+        <v>47.06</v>
       </c>
       <c r="BU9" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BV9" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BW9" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX9" t="n">
-        <v>62.5</v>
+        <v>58.82</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.17</v>
+        <v>2.09</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.51</v>
+        <v>3.54</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.67</v>
+        <v>3.7</v>
       </c>
       <c r="CC9" t="n">
         <v>2.94</v>
@@ -4446,16 +4446,16 @@
         <v>1.4</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="CH9" t="n">
         <v>1.37</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CJ9" t="n">
         <v>1.97</v>
@@ -4464,136 +4464,136 @@
         <v>1.58</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CM9" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="CP9" t="n">
         <v>2.02</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.51</v>
+        <v>3.49</v>
       </c>
       <c r="CR9" t="n">
         <v>1.43</v>
       </c>
       <c r="CS9" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="CU9" t="n">
         <v>1.38</v>
       </c>
       <c r="CV9" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CW9" t="n">
         <v>2</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="CY9" t="n">
-        <v>2.22</v>
+        <v>2.19</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="DB9" t="n">
         <v>1.35</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.76</v>
+        <v>3.73</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DF9" t="n">
         <v>1.94</v>
       </c>
       <c r="DG9" t="n">
-        <v>3.18</v>
+        <v>3.23</v>
       </c>
       <c r="DH9" t="n">
-        <v>112.12</v>
+        <v>114.35</v>
       </c>
       <c r="DI9" t="n">
         <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="DK9" t="n">
-        <v>6.32</v>
+        <v>6.53</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="DM9" t="n">
-        <v>63.06</v>
+        <v>65.3</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="DO9" t="n">
-        <v>3.12</v>
+        <v>3.29</v>
       </c>
       <c r="DP9" t="n">
-        <v>12.12</v>
+        <v>12.11</v>
       </c>
       <c r="DQ9" t="n">
-        <v>14.25</v>
+        <v>13.88</v>
       </c>
       <c r="DR9" t="n">
-        <v>7.32</v>
+        <v>7.18</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>50.75</v>
+        <v>51.12</v>
       </c>
       <c r="DW9" t="n">
         <v>0.06</v>
       </c>
       <c r="DX9" t="n">
-        <v>15.75</v>
+        <v>15.7</v>
       </c>
       <c r="DY9" t="n">
-        <v>11.5</v>
+        <v>11.47</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.25</v>
+        <v>4.23</v>
       </c>
       <c r="EA9" t="n">
-        <v>23.68</v>
+        <v>24</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.81</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="10">
@@ -5048,7 +5048,7 @@
         <v>2.33</v>
       </c>
       <c r="P11" t="n">
-        <v>12.67</v>
+        <v>12.78</v>
       </c>
       <c r="Q11" t="n">
         <v>12.33</v>
@@ -5360,7 +5360,7 @@
         <v>2.33</v>
       </c>
       <c r="DP11" t="n">
-        <v>12.78</v>
+        <v>12.84</v>
       </c>
       <c r="DQ11" t="n">
         <v>12.44</v>

--- a/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
@@ -1403,7 +1403,7 @@
         <v>0.22</v>
       </c>
       <c r="J2" t="n">
-        <v>2.67</v>
+        <v>2.56</v>
       </c>
       <c r="K2" t="n">
         <v>5.89</v>
@@ -1415,13 +1415,13 @@
         <v>74.67</v>
       </c>
       <c r="N2" t="n">
-        <v>0.67</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="O2" t="n">
         <v>3.22</v>
       </c>
       <c r="P2" t="n">
-        <v>11.44</v>
+        <v>11.56</v>
       </c>
       <c r="Q2" t="n">
         <v>13</v>
@@ -1466,7 +1466,7 @@
         <v>1.97</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.44</v>
+        <v>2.33</v>
       </c>
       <c r="AF2" t="n">
         <v>0.11</v>
@@ -1715,7 +1715,7 @@
         <v>0.11</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="DK2" t="n">
         <v>6.5</v>
@@ -1727,13 +1727,13 @@
         <v>75.33</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DO2" t="n">
         <v>3</v>
       </c>
       <c r="DP2" t="n">
-        <v>12.88</v>
+        <v>12.94</v>
       </c>
       <c r="DQ2" t="n">
         <v>13.66</v>
@@ -1772,7 +1772,7 @@
         <v>1.93</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="3">
@@ -2278,7 +2278,7 @@
         <v>0.11</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.22</v>
+        <v>2.33</v>
       </c>
       <c r="AH4" t="n">
         <v>2.33</v>
@@ -2290,7 +2290,7 @@
         <v>0.11</v>
       </c>
       <c r="AK4" t="n">
-        <v>3.67</v>
+        <v>3.78</v>
       </c>
       <c r="AL4" t="n">
         <v>3.89</v>
@@ -2353,7 +2353,7 @@
         <v>1.2</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="BG4" t="n">
         <v>2.83</v>
@@ -2509,7 +2509,7 @@
         <v>0.06</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="DG4" t="n">
         <v>2.16</v>
@@ -2521,7 +2521,7 @@
         <v>0.06</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.78</v>
+        <v>2.83</v>
       </c>
       <c r="DK4" t="n">
         <v>3.66</v>
@@ -2578,7 +2578,7 @@
         <v>1.32</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="5">
@@ -3015,7 +3015,7 @@
         <v>-0.12</v>
       </c>
       <c r="J6" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
         <v>4.12</v>
@@ -3027,7 +3027,7 @@
         <v>57</v>
       </c>
       <c r="N6" t="n">
-        <v>0.38</v>
+        <v>0.5</v>
       </c>
       <c r="O6" t="n">
         <v>1.62</v>
@@ -3078,7 +3078,7 @@
         <v>1.45</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3327,7 +3327,7 @@
         <v>0.12</v>
       </c>
       <c r="DJ6" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="DK6" t="n">
         <v>3.76</v>
@@ -3339,7 +3339,7 @@
         <v>56.24</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.59</v>
+        <v>0.65</v>
       </c>
       <c r="DO6" t="n">
         <v>1.82</v>
@@ -3384,7 +3384,7 @@
         <v>1.32</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="7">
@@ -3517,7 +3517,7 @@
         <v>2.22</v>
       </c>
       <c r="AQ7" t="n">
-        <v>14.89</v>
+        <v>15</v>
       </c>
       <c r="AR7" t="n">
         <v>10.89</v>
@@ -3748,7 +3748,7 @@
         <v>1.61</v>
       </c>
       <c r="DP7" t="n">
-        <v>15.39</v>
+        <v>15.44</v>
       </c>
       <c r="DQ7" t="n">
         <v>12.39</v>
@@ -4648,7 +4648,7 @@
         <v>13.22</v>
       </c>
       <c r="Q10" t="n">
-        <v>13.22</v>
+        <v>13.11</v>
       </c>
       <c r="R10" t="n">
         <v>8.67</v>
@@ -4960,7 +4960,7 @@
         <v>14.44</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.39</v>
+        <v>12.34</v>
       </c>
       <c r="DR10" t="n">
         <v>8.890000000000001</v>

--- a/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
         <v>9</v>
       </c>
       <c r="E6" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="G6" t="n">
         <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>103.5</v>
+        <v>101.56</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="K6" t="n">
-        <v>4.12</v>
+        <v>4</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="M6" t="n">
-        <v>57</v>
+        <v>55.44</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="O6" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="P6" t="n">
-        <v>10.25</v>
+        <v>10.89</v>
       </c>
       <c r="Q6" t="n">
-        <v>11.12</v>
+        <v>11.44</v>
       </c>
       <c r="R6" t="n">
-        <v>9.880000000000001</v>
+        <v>10.56</v>
       </c>
       <c r="S6" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="T6" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -3057,28 +3057,28 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>49.5</v>
+        <v>49.11</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>12</v>
+        <v>11.89</v>
       </c>
       <c r="AA6" t="n">
-        <v>8</v>
+        <v>7.89</v>
       </c>
       <c r="AB6" t="n">
         <v>4</v>
       </c>
       <c r="AC6" t="n">
-        <v>20.62</v>
+        <v>21</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AE6" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3162,70 +3162,70 @@
         <v>1.78</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.880000000000001</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.41</v>
+        <v>4.33</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.82</v>
+        <v>4.78</v>
       </c>
       <c r="BR6" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS6" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BT6" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BU6" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BV6" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW6" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX6" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.57</v>
+        <v>2.65</v>
       </c>
       <c r="BZ6" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.33</v>
+        <v>3.32</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.44</v>
+        <v>3.42</v>
       </c>
       <c r="CC6" t="n">
         <v>3.83</v>
@@ -3237,10 +3237,10 @@
         <v>1.41</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="CH6" t="n">
         <v>1.37</v>
@@ -3249,13 +3249,13 @@
         <v>1.82</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CM6" t="n">
         <v>1.98</v>
@@ -3264,7 +3264,7 @@
         <v>1.58</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CP6" t="n">
         <v>2.06</v>
@@ -3276,10 +3276,10 @@
         <v>1.43</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="CU6" t="n">
         <v>1.37</v>
@@ -3306,52 +3306,52 @@
         <v>1.35</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="DD6" t="n">
         <v>3.74</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="DH6" t="n">
-        <v>105.41</v>
+        <v>104.34</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ6" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="DK6" t="n">
-        <v>3.76</v>
+        <v>3.72</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.41</v>
+        <v>0.38</v>
       </c>
       <c r="DM6" t="n">
-        <v>56.24</v>
+        <v>55.5</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="DP6" t="n">
-        <v>10.65</v>
+        <v>10.94</v>
       </c>
       <c r="DQ6" t="n">
-        <v>11.64</v>
+        <v>11.77</v>
       </c>
       <c r="DR6" t="n">
-        <v>9.65</v>
+        <v>10</v>
       </c>
       <c r="DS6" t="n">
         <v>0</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>48.71</v>
+        <v>48.56</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>10.35</v>
+        <v>10.39</v>
       </c>
       <c r="DY6" t="n">
-        <v>6.71</v>
+        <v>6.72</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.65</v>
+        <v>3.66</v>
       </c>
       <c r="EA6" t="n">
-        <v>21.82</v>
+        <v>21.94</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="7">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
         <v>9</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E9" t="n">
         <v>0.33</v>
@@ -4290,139 +4290,139 @@
         <v>2.11</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="AH9" t="n">
-        <v>3.25</v>
+        <v>3.11</v>
       </c>
       <c r="AI9" t="n">
-        <v>112.5</v>
+        <v>107.89</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>3.75</v>
+        <v>3.56</v>
       </c>
       <c r="AL9" t="n">
-        <v>6.38</v>
+        <v>6.11</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AN9" t="n">
-        <v>58.88</v>
+        <v>57.78</v>
       </c>
       <c r="AO9" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="AP9" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="AQ9" t="n">
-        <v>12.12</v>
+        <v>12.33</v>
       </c>
       <c r="AR9" t="n">
-        <v>13.12</v>
+        <v>13.33</v>
       </c>
       <c r="AS9" t="n">
-        <v>7.75</v>
+        <v>7.56</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>49.38</v>
+        <v>49.89</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA9" t="n">
-        <v>15.12</v>
+        <v>14.56</v>
       </c>
       <c r="BB9" t="n">
-        <v>11.5</v>
+        <v>11.11</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.62</v>
+        <v>3.44</v>
       </c>
       <c r="BD9" t="n">
-        <v>22.62</v>
+        <v>22.33</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="BF9" t="n">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="BH9" t="n">
-        <v>11</v>
+        <v>10.78</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="BP9" t="n">
-        <v>5.24</v>
+        <v>5.11</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.76</v>
+        <v>5.67</v>
       </c>
       <c r="BR9" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BS9" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BT9" t="n">
-        <v>47.06</v>
+        <v>50</v>
       </c>
       <c r="BU9" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BV9" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BW9" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX9" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BY9" t="n">
         <v>2.09</v>
@@ -4431,49 +4431,49 @@
         <v>2.06</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.54</v>
+        <v>3.51</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.7</v>
+        <v>3.67</v>
       </c>
       <c r="CC9" t="n">
-        <v>2.94</v>
+        <v>2.84</v>
       </c>
       <c r="CD9" t="n">
-        <v>3.2</v>
+        <v>3.09</v>
       </c>
       <c r="CE9" t="n">
         <v>1.4</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.91</v>
+        <v>2.89</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="CH9" t="n">
         <v>1.37</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="CM9" t="n">
         <v>1.95</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CP9" t="n">
         <v>2.02</v>
@@ -4482,13 +4482,13 @@
         <v>3.49</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CS9" t="n">
-        <v>3.09</v>
+        <v>3.07</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="CU9" t="n">
         <v>1.38</v>
@@ -4497,7 +4497,7 @@
         <v>1.82</v>
       </c>
       <c r="CW9" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CX9" t="n">
         <v>1.74</v>
@@ -4521,79 +4521,79 @@
         <v>3.73</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.23</v>
+        <v>0.28</v>
       </c>
       <c r="DF9" t="n">
         <v>1.94</v>
       </c>
       <c r="DG9" t="n">
-        <v>3.23</v>
+        <v>3.16</v>
       </c>
       <c r="DH9" t="n">
-        <v>114.35</v>
+        <v>111.94</v>
       </c>
       <c r="DI9" t="n">
         <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="DK9" t="n">
-        <v>6.53</v>
+        <v>6.39</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="DM9" t="n">
-        <v>65.3</v>
+        <v>64.39</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="DO9" t="n">
-        <v>3.29</v>
+        <v>3.22</v>
       </c>
       <c r="DP9" t="n">
-        <v>12.11</v>
+        <v>12.22</v>
       </c>
       <c r="DQ9" t="n">
-        <v>13.88</v>
+        <v>13.94</v>
       </c>
       <c r="DR9" t="n">
-        <v>7.18</v>
+        <v>7.11</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>51.12</v>
+        <v>51.28</v>
       </c>
       <c r="DW9" t="n">
         <v>0.06</v>
       </c>
       <c r="DX9" t="n">
-        <v>15.7</v>
+        <v>15.39</v>
       </c>
       <c r="DY9" t="n">
-        <v>11.47</v>
+        <v>11.27</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.23</v>
+        <v>4.11</v>
       </c>
       <c r="EA9" t="n">
-        <v>24</v>
+        <v>23.77</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="10">

--- a/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
@@ -4362,7 +4362,7 @@
         <v>3.44</v>
       </c>
       <c r="BD9" t="n">
-        <v>22.33</v>
+        <v>22.44</v>
       </c>
       <c r="BE9" t="n">
         <v>1.58</v>
@@ -4587,7 +4587,7 @@
         <v>4.11</v>
       </c>
       <c r="EA9" t="n">
-        <v>23.77</v>
+        <v>23.83</v>
       </c>
       <c r="EB9" t="n">
         <v>1.73</v>

--- a/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" t="n">
         <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" t="n">
         <v>0.22</v>
@@ -1469,82 +1469,82 @@
         <v>2.33</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AH2" t="n">
-        <v>4.33</v>
+        <v>3.9</v>
       </c>
       <c r="AI2" t="n">
-        <v>119.33</v>
+        <v>118.9</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="AL2" t="n">
-        <v>7.11</v>
+        <v>6.6</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AN2" t="n">
-        <v>76</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="AQ2" t="n">
-        <v>14.33</v>
+        <v>14.2</v>
       </c>
       <c r="AR2" t="n">
-        <v>14.33</v>
+        <v>14.3</v>
       </c>
       <c r="AS2" t="n">
         <v>6</v>
       </c>
       <c r="AT2" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>55.11</v>
+        <v>55.1</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="BA2" t="n">
-        <v>15.89</v>
+        <v>16</v>
       </c>
       <c r="BB2" t="n">
-        <v>11.11</v>
+        <v>11.1</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.78</v>
+        <v>4.9</v>
       </c>
       <c r="BD2" t="n">
-        <v>24.33</v>
+        <v>23.8</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="BF2" t="n">
         <v>2</v>
@@ -1553,55 +1553,55 @@
         <v>3</v>
       </c>
       <c r="BH2" t="n">
-        <v>10</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="BI2" t="n">
         <v>3</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.44</v>
+        <v>4.47</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.5</v>
+        <v>5.26</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BT2" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BU2" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BV2" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BW2" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX2" t="n">
-        <v>55.56</v>
+        <v>52.63</v>
       </c>
       <c r="BY2" t="n">
         <v>1.3</v>
@@ -1610,16 +1610,16 @@
         <v>1.33</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.58</v>
+        <v>4.55</v>
       </c>
       <c r="CB2" t="n">
-        <v>5.02</v>
+        <v>4.95</v>
       </c>
       <c r="CC2" t="n">
         <v>1.57</v>
       </c>
       <c r="CD2" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CE2" t="n">
         <v>1.31</v>
@@ -1628,25 +1628,25 @@
         <v>2.49</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CL2" t="n">
         <v>2.13</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="CN2" t="n">
         <v>1.76</v>
@@ -1655,34 +1655,34 @@
         <v>1.22</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="CR2" t="n">
         <v>1.37</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="CT2" t="n">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CW2" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CX2" t="n">
         <v>1.59</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CZ2" t="n">
         <v>2.23</v>
@@ -1697,49 +1697,49 @@
         <v>1.75</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="DE2" t="n">
         <v>0.16</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.44</v>
+        <v>3.27</v>
       </c>
       <c r="DH2" t="n">
-        <v>124.11</v>
+        <v>123.63</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="DK2" t="n">
-        <v>6.5</v>
+        <v>6.26</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="DM2" t="n">
-        <v>75.33</v>
+        <v>74.79000000000001</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="DO2" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="DP2" t="n">
-        <v>12.94</v>
+        <v>12.95</v>
       </c>
       <c r="DQ2" t="n">
-        <v>13.66</v>
+        <v>13.68</v>
       </c>
       <c r="DR2" t="n">
-        <v>5.89</v>
+        <v>5.9</v>
       </c>
       <c r="DS2" t="n">
         <v>0.11</v>
@@ -1751,22 +1751,22 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>56.44</v>
+        <v>56.37</v>
       </c>
       <c r="DW2" t="n">
         <v>0.16</v>
       </c>
       <c r="DX2" t="n">
-        <v>15.66</v>
+        <v>15.73</v>
       </c>
       <c r="DY2" t="n">
-        <v>10.06</v>
+        <v>10.11</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5.61</v>
+        <v>5.63</v>
       </c>
       <c r="EA2" t="n">
-        <v>23.5</v>
+        <v>23.26</v>
       </c>
       <c r="EB2" t="n">
         <v>1.93</v>
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" t="n">
         <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2275,139 +2275,139 @@
         <v>1.67</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AI4" t="n">
-        <v>101.33</v>
+        <v>100.7</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK4" t="n">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="AL4" t="n">
-        <v>3.89</v>
+        <v>3.8</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AN4" t="n">
-        <v>55</v>
+        <v>54.4</v>
       </c>
       <c r="AO4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>10.21</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="BL4" t="n">
         <v>1.11</v>
       </c>
-      <c r="AP4" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>12.22</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>10.33</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>8.44</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>38.44</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>9.44</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>6.67</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>20.78</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>3</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>10.33</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1.06</v>
-      </c>
       <c r="BM4" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="BP4" t="n">
-        <v>5.11</v>
+        <v>5.21</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.17</v>
+        <v>4.95</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
       </c>
       <c r="BS4" t="n">
-        <v>83.33</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BT4" t="n">
-        <v>55.56</v>
+        <v>57.89</v>
       </c>
       <c r="BU4" t="n">
-        <v>33.33</v>
+        <v>31.58</v>
       </c>
       <c r="BV4" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="BY4" t="n">
         <v>4.46</v>
@@ -2416,34 +2416,34 @@
         <v>5.11</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.12</v>
+        <v>4.09</v>
       </c>
       <c r="CB4" t="n">
-        <v>4.28</v>
+        <v>4.25</v>
       </c>
       <c r="CC4" t="n">
-        <v>6.71</v>
+        <v>6.46</v>
       </c>
       <c r="CD4" t="n">
-        <v>9.52</v>
+        <v>9.02</v>
       </c>
       <c r="CE4" t="n">
         <v>1.35</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.97</v>
+        <v>2.98</v>
       </c>
       <c r="CH4" t="n">
         <v>1.44</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CK4" t="n">
         <v>1.6</v>
@@ -2452,10 +2452,10 @@
         <v>2.18</v>
       </c>
       <c r="CM4" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CO4" t="n">
         <v>1.27</v>
@@ -2467,118 +2467,118 @@
         <v>3.13</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="CT4" t="n">
-        <v>3.03</v>
+        <v>3.05</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="DB4" t="n">
         <v>1.28</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.24</v>
+        <v>3.23</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.66</v>
+        <v>1.79</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.16</v>
+        <v>2.11</v>
       </c>
       <c r="DH4" t="n">
-        <v>108.61</v>
+        <v>107.9</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="DK4" t="n">
-        <v>3.66</v>
+        <v>3.63</v>
       </c>
       <c r="DL4" t="n">
         <v>0.16</v>
       </c>
       <c r="DM4" t="n">
-        <v>61.84</v>
+        <v>61.16</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="DP4" t="n">
-        <v>12.83</v>
+        <v>12.73</v>
       </c>
       <c r="DQ4" t="n">
-        <v>11.38</v>
+        <v>11.16</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.06</v>
+        <v>8.16</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>40.56</v>
+        <v>40.95</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DX4" t="n">
-        <v>9.94</v>
+        <v>9.84</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.67</v>
+        <v>6.63</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.28</v>
+        <v>3.21</v>
       </c>
       <c r="EA4" t="n">
-        <v>20.67</v>
+        <v>20.9</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="5">
@@ -2588,94 +2588,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
         <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="F5" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="G5" t="n">
-        <v>3.67</v>
+        <v>3.6</v>
       </c>
       <c r="H5" t="n">
-        <v>122.78</v>
+        <v>120.2</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="K5" t="n">
-        <v>5.11</v>
+        <v>5.2</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="M5" t="n">
-        <v>67</v>
+        <v>66.8</v>
       </c>
       <c r="N5" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="O5" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="P5" t="n">
-        <v>12.11</v>
+        <v>11.7</v>
       </c>
       <c r="Q5" t="n">
-        <v>15</v>
+        <v>15.2</v>
       </c>
       <c r="R5" t="n">
-        <v>5.11</v>
+        <v>5.1</v>
       </c>
       <c r="S5" t="n">
-        <v>0.78</v>
+        <v>0.9</v>
       </c>
       <c r="T5" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="U5" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="V5" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>61</v>
+        <v>61.2</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="Z5" t="n">
-        <v>15.89</v>
+        <v>16.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.890000000000001</v>
+        <v>10.4</v>
       </c>
       <c r="AB5" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="AC5" t="n">
-        <v>22.78</v>
+        <v>23.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="AF5" t="n">
         <v>0.11</v>
@@ -2759,70 +2759,70 @@
         <v>2.78</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.109999999999999</v>
+        <v>9.26</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.44</v>
+        <v>0.53</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.94</v>
+        <v>4.11</v>
       </c>
       <c r="BQ5" t="n">
         <v>5</v>
       </c>
       <c r="BR5" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS5" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BT5" t="n">
-        <v>44.44</v>
+        <v>47.37</v>
       </c>
       <c r="BU5" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BV5" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>38.89</v>
+        <v>42.11</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="BZ5" t="n">
         <v>1.72</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.67</v>
+        <v>3.69</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.65</v>
+        <v>3.64</v>
       </c>
       <c r="CC5" t="n">
         <v>2.38</v>
@@ -2846,10 +2846,10 @@
         <v>1.74</v>
       </c>
       <c r="CJ5" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CL5" t="n">
         <v>2.31</v>
@@ -2861,22 +2861,22 @@
         <v>1.64</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.63</v>
+        <v>3.62</v>
       </c>
       <c r="CR5" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CS5" t="n">
-        <v>3.13</v>
+        <v>3.14</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="CU5" t="n">
         <v>1.36</v>
@@ -2912,76 +2912,76 @@
         <v>0.16</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="DH5" t="n">
-        <v>111.5</v>
+        <v>110.74</v>
       </c>
       <c r="DI5" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.34</v>
+        <v>5.37</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.34</v>
+        <v>0.37</v>
       </c>
       <c r="DM5" t="n">
-        <v>62.72</v>
+        <v>62.84</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="DP5" t="n">
-        <v>12.66</v>
+        <v>12.42</v>
       </c>
       <c r="DQ5" t="n">
-        <v>14.84</v>
+        <v>14.95</v>
       </c>
       <c r="DR5" t="n">
-        <v>6.16</v>
+        <v>6.1</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>58.28</v>
+        <v>58.53</v>
       </c>
       <c r="DW5" t="n">
         <v>0.11</v>
       </c>
       <c r="DX5" t="n">
-        <v>14.56</v>
+        <v>14.95</v>
       </c>
       <c r="DY5" t="n">
-        <v>9.44</v>
+        <v>9.74</v>
       </c>
       <c r="DZ5" t="n">
-        <v>5.11</v>
+        <v>5.21</v>
       </c>
       <c r="EA5" t="n">
-        <v>21.28</v>
+        <v>21.69</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.11</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" t="n">
         <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
         <v>0.33</v>
@@ -3081,52 +3081,52 @@
         <v>1.89</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AG6" t="n">
         <v>1</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>107.11</v>
+        <v>104.8</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AL6" t="n">
-        <v>3.44</v>
+        <v>3.7</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="AN6" t="n">
-        <v>55.56</v>
+        <v>54.9</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AP6" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>11</v>
+        <v>11.6</v>
       </c>
       <c r="AR6" t="n">
-        <v>12.11</v>
+        <v>11.7</v>
       </c>
       <c r="AS6" t="n">
-        <v>9.44</v>
+        <v>10.1</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AV6" t="n">
         <v>0</v>
@@ -3138,82 +3138,82 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>48</v>
+        <v>46.9</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>8.890000000000001</v>
+        <v>9</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.56</v>
+        <v>5.6</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.33</v>
+        <v>3.4</v>
       </c>
       <c r="BD6" t="n">
-        <v>22.89</v>
+        <v>22.9</v>
       </c>
       <c r="BE6" t="n">
         <v>1.21</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.720000000000001</v>
+        <v>9.84</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.78</v>
+        <v>0.84</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.33</v>
+        <v>4.47</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.78</v>
+        <v>4.79</v>
       </c>
       <c r="BR6" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS6" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BT6" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BU6" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BV6" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BW6" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX6" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="BY6" t="n">
         <v>2.65</v>
@@ -3222,16 +3222,16 @@
         <v>2.78</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.32</v>
+        <v>3.35</v>
       </c>
       <c r="CB6" t="n">
         <v>3.42</v>
       </c>
       <c r="CC6" t="n">
-        <v>3.83</v>
+        <v>3.99</v>
       </c>
       <c r="CD6" t="n">
-        <v>4.27</v>
+        <v>4.38</v>
       </c>
       <c r="CE6" t="n">
         <v>1.41</v>
@@ -3240,7 +3240,7 @@
         <v>2.9</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="CH6" t="n">
         <v>1.37</v>
@@ -3252,22 +3252,22 @@
         <v>1.86</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CL6" t="n">
         <v>2.38</v>
       </c>
       <c r="CM6" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CO6" t="n">
         <v>1.33</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CQ6" t="n">
         <v>3.51</v>
@@ -3276,16 +3276,16 @@
         <v>1.43</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.08</v>
+        <v>3.09</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="CU6" t="n">
         <v>1.37</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CW6" t="n">
         <v>1.92</v>
@@ -3312,16 +3312,16 @@
         <v>3.74</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="DH6" t="n">
-        <v>104.34</v>
+        <v>103.27</v>
       </c>
       <c r="DI6" t="n">
         <v>0.11</v>
@@ -3330,28 +3330,28 @@
         <v>1.84</v>
       </c>
       <c r="DK6" t="n">
-        <v>3.72</v>
+        <v>3.84</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.38</v>
+        <v>0.42</v>
       </c>
       <c r="DM6" t="n">
-        <v>55.5</v>
+        <v>55.16</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="DP6" t="n">
-        <v>10.94</v>
+        <v>11.26</v>
       </c>
       <c r="DQ6" t="n">
-        <v>11.77</v>
+        <v>11.58</v>
       </c>
       <c r="DR6" t="n">
-        <v>10</v>
+        <v>10.32</v>
       </c>
       <c r="DS6" t="n">
         <v>0</v>
@@ -3363,25 +3363,25 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>48.56</v>
+        <v>47.95</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>10.39</v>
+        <v>10.37</v>
       </c>
       <c r="DY6" t="n">
-        <v>6.72</v>
+        <v>6.68</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.66</v>
+        <v>3.68</v>
       </c>
       <c r="EA6" t="n">
-        <v>21.94</v>
+        <v>22</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="EC6" t="n">
         <v>1.84</v>
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7" t="n">
         <v>9</v>
@@ -3406,82 +3406,82 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="G7" t="n">
-        <v>2.89</v>
+        <v>2.6</v>
       </c>
       <c r="H7" t="n">
-        <v>109.33</v>
+        <v>107.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J7" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="K7" t="n">
-        <v>3.89</v>
+        <v>4</v>
       </c>
       <c r="L7" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="M7" t="n">
-        <v>60.11</v>
+        <v>60.2</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="P7" t="n">
-        <v>15.89</v>
+        <v>15.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>13.89</v>
+        <v>13.5</v>
       </c>
       <c r="R7" t="n">
-        <v>6.56</v>
+        <v>7</v>
       </c>
       <c r="S7" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T7" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="U7" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="V7" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>51.89</v>
+        <v>51.9</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>11</v>
+        <v>10.7</v>
       </c>
       <c r="AA7" t="n">
-        <v>6.78</v>
+        <v>6.7</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.22</v>
+        <v>4</v>
       </c>
       <c r="AC7" t="n">
-        <v>22</v>
+        <v>23.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AF7" t="n">
         <v>0.44</v>
@@ -3565,64 +3565,64 @@
         <v>1.89</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="BH7" t="n">
-        <v>9</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.56</v>
+        <v>3.74</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.44</v>
+        <v>5.21</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BT7" t="n">
-        <v>44.44</v>
+        <v>47.37</v>
       </c>
       <c r="BU7" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BV7" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BW7" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX7" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BY7" t="n">
-        <v>3.21</v>
+        <v>3.06</v>
       </c>
       <c r="BZ7" t="n">
-        <v>3.28</v>
+        <v>3.14</v>
       </c>
       <c r="CA7" t="n">
         <v>3.63</v>
@@ -3640,19 +3640,19 @@
         <v>1.37</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CK7" t="n">
         <v>1.57</v>
@@ -3667,28 +3667,28 @@
         <v>1.76</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="CR7" t="n">
         <v>1.39</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.97</v>
+        <v>2.98</v>
       </c>
       <c r="CU7" t="n">
         <v>1.41</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CW7" t="n">
         <v>1.85</v>
@@ -3709,85 +3709,85 @@
         <v>1.31</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.47</v>
+        <v>3.45</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.89</v>
+        <v>2.74</v>
       </c>
       <c r="DH7" t="n">
-        <v>112.56</v>
+        <v>111.26</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.39</v>
+        <v>2.31</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.5</v>
+        <v>4.53</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DM7" t="n">
-        <v>62.56</v>
+        <v>62.47</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.84</v>
+        <v>0.79</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.61</v>
+        <v>1.79</v>
       </c>
       <c r="DP7" t="n">
-        <v>15.44</v>
+        <v>15.05</v>
       </c>
       <c r="DQ7" t="n">
-        <v>12.39</v>
+        <v>12.26</v>
       </c>
       <c r="DR7" t="n">
-        <v>6.61</v>
+        <v>6.84</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.22</v>
+        <v>0.26</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.22</v>
+        <v>0.26</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>52.84</v>
+        <v>52.79</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX7" t="n">
-        <v>11.34</v>
+        <v>11.16</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.56</v>
+        <v>7.47</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.77</v>
+        <v>3.68</v>
       </c>
       <c r="EA7" t="n">
-        <v>21.16</v>
+        <v>21.84</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="8">
@@ -3797,10 +3797,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D8" t="n">
         <v>9</v>
@@ -3812,46 +3812,46 @@
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="H8" t="n">
-        <v>124.33</v>
+        <v>123.5</v>
       </c>
       <c r="I8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J8" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>6.22</v>
+        <v>6</v>
       </c>
       <c r="L8" t="n">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="M8" t="n">
-        <v>86.22</v>
+        <v>83.7</v>
       </c>
       <c r="N8" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="P8" t="n">
-        <v>14.78</v>
+        <v>14.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>13.44</v>
+        <v>13.4</v>
       </c>
       <c r="R8" t="n">
-        <v>6.22</v>
+        <v>6.5</v>
       </c>
       <c r="S8" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="T8" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -3863,28 +3863,28 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>52.89</v>
+        <v>52.1</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z8" t="n">
-        <v>13.56</v>
+        <v>13</v>
       </c>
       <c r="AA8" t="n">
-        <v>9.890000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.67</v>
+        <v>3.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>23</v>
+        <v>22.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AE8" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AF8" t="n">
         <v>0.11</v>
@@ -3968,70 +3968,70 @@
         <v>2.22</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="BH8" t="n">
-        <v>10.17</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.61</v>
+        <v>0.68</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="BP8" t="n">
-        <v>5.06</v>
+        <v>5.05</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.06</v>
+        <v>4.84</v>
       </c>
       <c r="BR8" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BS8" t="n">
-        <v>72.22</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="BT8" t="n">
-        <v>38.89</v>
+        <v>42.11</v>
       </c>
       <c r="BU8" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BV8" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BW8" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BX8" t="n">
-        <v>50</v>
+        <v>47.37</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.62</v>
+        <v>2.84</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.4</v>
+        <v>3.43</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.5</v>
+        <v>3.51</v>
       </c>
       <c r="CC8" t="n">
         <v>3.59</v>
@@ -4043,10 +4043,10 @@
         <v>1.38</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="CH8" t="n">
         <v>1.39</v>
@@ -4058,37 +4058,37 @@
         <v>1.8</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.21</v>
+        <v>3.19</v>
       </c>
       <c r="CR8" t="n">
         <v>1.4</v>
       </c>
       <c r="CS8" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CV8" t="n">
         <v>1.98</v>
@@ -4112,52 +4112,52 @@
         <v>1.31</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.49</v>
+        <v>3.48</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.34</v>
+        <v>2.26</v>
       </c>
       <c r="DH8" t="n">
-        <v>113.94</v>
+        <v>114.05</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.34</v>
+        <v>2.27</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.11</v>
+        <v>5.05</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.78</v>
+        <v>0.84</v>
       </c>
       <c r="DM8" t="n">
-        <v>70.72</v>
+        <v>70.20999999999999</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.84</v>
+        <v>0.79</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="DP8" t="n">
-        <v>15.34</v>
+        <v>15.26</v>
       </c>
       <c r="DQ8" t="n">
-        <v>13.66</v>
+        <v>13.63</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.5</v>
+        <v>7.58</v>
       </c>
       <c r="DS8" t="n">
         <v>0</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>50.94</v>
+        <v>50.63</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DX8" t="n">
-        <v>13.06</v>
+        <v>12.79</v>
       </c>
       <c r="DY8" t="n">
-        <v>9.5</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.56</v>
+        <v>3.42</v>
       </c>
       <c r="EA8" t="n">
-        <v>22.61</v>
+        <v>22.21</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="9">
@@ -4200,94 +4200,94 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D9" t="n">
         <v>9</v>
       </c>
       <c r="E9" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="F9" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="G9" t="n">
-        <v>3.22</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>116</v>
+        <v>116.4</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2.11</v>
+        <v>2.4</v>
       </c>
       <c r="K9" t="n">
-        <v>6.67</v>
+        <v>6.4</v>
       </c>
       <c r="L9" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>71</v>
+        <v>70.8</v>
       </c>
       <c r="N9" t="n">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="O9" t="n">
-        <v>3.44</v>
+        <v>3.4</v>
       </c>
       <c r="P9" t="n">
-        <v>12.11</v>
+        <v>12.7</v>
       </c>
       <c r="Q9" t="n">
-        <v>14.56</v>
+        <v>14.4</v>
       </c>
       <c r="R9" t="n">
-        <v>6.67</v>
+        <v>7.3</v>
       </c>
       <c r="S9" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>52.67</v>
+        <v>52.1</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="Z9" t="n">
-        <v>16.22</v>
+        <v>16.1</v>
       </c>
       <c r="AA9" t="n">
-        <v>11.44</v>
+        <v>11.4</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.78</v>
+        <v>4.7</v>
       </c>
       <c r="AC9" t="n">
-        <v>25.22</v>
+        <v>24.9</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AF9" t="n">
         <v>0.22</v>
@@ -4371,67 +4371,67 @@
         <v>3.33</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.72</v>
+        <v>2.79</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.78</v>
+        <v>10.58</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.72</v>
+        <v>2.79</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.83</v>
+        <v>0.89</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="BP9" t="n">
-        <v>5.11</v>
+        <v>5.05</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.67</v>
+        <v>5.53</v>
       </c>
       <c r="BR9" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BS9" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BT9" t="n">
-        <v>50</v>
+        <v>52.63</v>
       </c>
       <c r="BU9" t="n">
-        <v>33.33</v>
+        <v>36.84</v>
       </c>
       <c r="BV9" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BW9" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX9" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.06</v>
+        <v>2.01</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.51</v>
+        <v>3.52</v>
       </c>
       <c r="CB9" t="n">
         <v>3.67</v>
@@ -4464,22 +4464,22 @@
         <v>1.6</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="CM9" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CN9" t="n">
         <v>1.56</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="CP9" t="n">
         <v>2.02</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.49</v>
+        <v>3.48</v>
       </c>
       <c r="CR9" t="n">
         <v>1.42</v>
@@ -4521,46 +4521,46 @@
         <v>3.73</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="DG9" t="n">
-        <v>3.16</v>
+        <v>3.05</v>
       </c>
       <c r="DH9" t="n">
-        <v>111.94</v>
+        <v>112.37</v>
       </c>
       <c r="DI9" t="n">
         <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.84</v>
+        <v>2.95</v>
       </c>
       <c r="DK9" t="n">
-        <v>6.39</v>
+        <v>6.26</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.78</v>
+        <v>0.84</v>
       </c>
       <c r="DM9" t="n">
-        <v>64.39</v>
+        <v>64.63</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.84</v>
+        <v>0.89</v>
       </c>
       <c r="DO9" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="DP9" t="n">
-        <v>12.22</v>
+        <v>12.52</v>
       </c>
       <c r="DQ9" t="n">
-        <v>13.94</v>
+        <v>13.89</v>
       </c>
       <c r="DR9" t="n">
-        <v>7.11</v>
+        <v>7.42</v>
       </c>
       <c r="DS9" t="n">
         <v>0.16</v>
@@ -4572,28 +4572,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>51.28</v>
+        <v>51.05</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="DX9" t="n">
-        <v>15.39</v>
+        <v>15.37</v>
       </c>
       <c r="DY9" t="n">
-        <v>11.27</v>
+        <v>11.26</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.11</v>
+        <v>4.1</v>
       </c>
       <c r="EA9" t="n">
-        <v>23.83</v>
+        <v>23.73</v>
       </c>
       <c r="EB9" t="n">
         <v>1.73</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="10">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
         <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
         <v>0.33</v>
@@ -4693,139 +4693,139 @@
         <v>2.11</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AI10" t="n">
-        <v>104.78</v>
+        <v>105.2</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="AL10" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AN10" t="n">
-        <v>47.78</v>
+        <v>48.4</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AQ10" t="n">
-        <v>15.67</v>
+        <v>15.4</v>
       </c>
       <c r="AR10" t="n">
-        <v>11.56</v>
+        <v>12.2</v>
       </c>
       <c r="AS10" t="n">
-        <v>9.109999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AU10" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>45</v>
+        <v>45.8</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="BA10" t="n">
-        <v>8.890000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB10" t="n">
-        <v>6.11</v>
+        <v>6.7</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.78</v>
+        <v>3.1</v>
       </c>
       <c r="BD10" t="n">
-        <v>19.11</v>
+        <v>18.8</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="BG10" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BH10" t="n">
         <v>7.11</v>
       </c>
       <c r="BI10" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BL10" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.44</v>
+        <v>3.47</v>
       </c>
       <c r="BQ10" t="n">
-        <v>3.67</v>
+        <v>3.63</v>
       </c>
       <c r="BR10" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BS10" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BT10" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="BU10" t="n">
-        <v>27.78</v>
+        <v>31.58</v>
       </c>
       <c r="BV10" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BW10" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX10" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BY10" t="n">
         <v>2.71</v>
@@ -4834,16 +4834,16 @@
         <v>2.91</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.42</v>
+        <v>3.43</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.5</v>
+        <v>3.51</v>
       </c>
       <c r="CC10" t="n">
-        <v>4.43</v>
+        <v>4.48</v>
       </c>
       <c r="CD10" t="n">
-        <v>4.81</v>
+        <v>4.92</v>
       </c>
       <c r="CE10" t="n">
         <v>1.37</v>
@@ -4852,13 +4852,13 @@
         <v>2.85</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="CH10" t="n">
         <v>1.39</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CJ10" t="n">
         <v>1.83</v>
@@ -4873,13 +4873,13 @@
         <v>2.02</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CO10" t="n">
         <v>1.28</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CQ10" t="n">
         <v>3.34</v>
@@ -4891,16 +4891,16 @@
         <v>3</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="CU10" t="n">
         <v>1.4</v>
       </c>
       <c r="CV10" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CX10" t="n">
         <v>1.74</v>
@@ -4924,79 +4924,79 @@
         <v>3.53</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="DH10" t="n">
-        <v>111.72</v>
+        <v>111.58</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="DK10" t="n">
-        <v>3.28</v>
+        <v>3.26</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DM10" t="n">
-        <v>53.67</v>
+        <v>53.69</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="DP10" t="n">
-        <v>14.44</v>
+        <v>14.37</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.34</v>
+        <v>12.63</v>
       </c>
       <c r="DR10" t="n">
-        <v>8.890000000000001</v>
+        <v>8.74</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>48.39</v>
+        <v>48.63</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DX10" t="n">
-        <v>11.28</v>
+        <v>11.63</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.39</v>
+        <v>7.63</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.89</v>
+        <v>4</v>
       </c>
       <c r="EA10" t="n">
-        <v>22.44</v>
+        <v>22.11</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="11">

--- a/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
@@ -1782,94 +1782,94 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
         <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="F3" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="G3" t="n">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="H3" t="n">
-        <v>102.44</v>
+        <v>100.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="J3" t="n">
-        <v>2.89</v>
+        <v>2.7</v>
       </c>
       <c r="K3" t="n">
-        <v>3.89</v>
+        <v>4.2</v>
       </c>
       <c r="L3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="M3" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="N3" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="O3" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="P3" t="n">
-        <v>11</v>
+        <v>10.7</v>
       </c>
       <c r="Q3" t="n">
-        <v>13.78</v>
+        <v>13.8</v>
       </c>
       <c r="R3" t="n">
-        <v>8.779999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="S3" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="T3" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="U3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>51.89</v>
+        <v>51.9</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z3" t="n">
-        <v>11</v>
+        <v>11.2</v>
       </c>
       <c r="AA3" t="n">
-        <v>6.89</v>
+        <v>7</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.11</v>
+        <v>4.2</v>
       </c>
       <c r="AC3" t="n">
-        <v>22.11</v>
+        <v>22</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -1953,70 +1953,70 @@
         <v>1.89</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="BH3" t="n">
-        <v>8.67</v>
+        <v>8.74</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="BP3" t="n">
         <v>3.89</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.06</v>
+        <v>4.16</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BT3" t="n">
-        <v>50</v>
+        <v>52.63</v>
       </c>
       <c r="BU3" t="n">
-        <v>33.33</v>
+        <v>31.58</v>
       </c>
       <c r="BV3" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="BY3" t="n">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="BZ3" t="n">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.58</v>
+        <v>3.55</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.7</v>
+        <v>3.68</v>
       </c>
       <c r="CC3" t="n">
         <v>5.72</v>
@@ -2028,10 +2028,10 @@
         <v>1.4</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="CH3" t="n">
         <v>1.38</v>
@@ -2046,7 +2046,7 @@
         <v>1.69</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="CM3" t="n">
         <v>2.06</v>
@@ -2058,10 +2058,10 @@
         <v>1.31</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.48</v>
+        <v>3.49</v>
       </c>
       <c r="CR3" t="n">
         <v>1.43</v>
@@ -2100,82 +2100,82 @@
         <v>2.09</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.69</v>
+        <v>3.71</v>
       </c>
       <c r="DE3" t="n">
         <v>0.11</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="DG3" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="DH3" t="n">
-        <v>99.61</v>
+        <v>98.58</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.61</v>
+        <v>2.52</v>
       </c>
       <c r="DK3" t="n">
-        <v>4.39</v>
+        <v>4.53</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DM3" t="n">
-        <v>52.94</v>
+        <v>52.37</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="DP3" t="n">
-        <v>11.34</v>
+        <v>11.16</v>
       </c>
       <c r="DQ3" t="n">
-        <v>13.34</v>
+        <v>13.37</v>
       </c>
       <c r="DR3" t="n">
-        <v>8.779999999999999</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>47.56</v>
+        <v>47.79</v>
       </c>
       <c r="DW3" t="n">
         <v>0.16</v>
       </c>
       <c r="DX3" t="n">
-        <v>11.44</v>
+        <v>11.53</v>
       </c>
       <c r="DY3" t="n">
-        <v>7.5</v>
+        <v>7.53</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.94</v>
+        <v>4</v>
       </c>
       <c r="EA3" t="n">
-        <v>20.67</v>
+        <v>20.68</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.34</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="4">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C11" t="n">
         <v>9</v>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
         <v>0.22</v>
@@ -5096,139 +5096,139 @@
         <v>2</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AI11" t="n">
-        <v>94.56</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="AL11" t="n">
-        <v>4.11</v>
+        <v>4</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AN11" t="n">
-        <v>46.11</v>
+        <v>45.1</v>
       </c>
       <c r="AO11" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AQ11" t="n">
-        <v>12.89</v>
+        <v>13</v>
       </c>
       <c r="AR11" t="n">
-        <v>12.56</v>
+        <v>12.1</v>
       </c>
       <c r="AS11" t="n">
-        <v>7.33</v>
+        <v>7.5</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>43.33</v>
+        <v>43.8</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="BA11" t="n">
-        <v>9.890000000000001</v>
+        <v>10.1</v>
       </c>
       <c r="BB11" t="n">
-        <v>6.78</v>
+        <v>6.9</v>
       </c>
       <c r="BC11" t="n">
-        <v>3.11</v>
+        <v>3.2</v>
       </c>
       <c r="BD11" t="n">
-        <v>19.22</v>
+        <v>19.3</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.44</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.44</v>
+        <v>4.42</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5</v>
+        <v>5.05</v>
       </c>
       <c r="BR11" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BS11" t="n">
-        <v>72.22</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="BT11" t="n">
-        <v>50</v>
+        <v>52.63</v>
       </c>
       <c r="BU11" t="n">
-        <v>38.89</v>
+        <v>36.84</v>
       </c>
       <c r="BV11" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BW11" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX11" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BY11" t="n">
         <v>2.9</v>
@@ -5237,25 +5237,25 @@
         <v>3.18</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.38</v>
+        <v>3.36</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.43</v>
+        <v>3.41</v>
       </c>
       <c r="CC11" t="n">
-        <v>4.11</v>
+        <v>3.94</v>
       </c>
       <c r="CD11" t="n">
-        <v>4.43</v>
+        <v>4.28</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CF11" t="n">
         <v>3.02</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="CH11" t="n">
         <v>1.34</v>
@@ -5264,13 +5264,13 @@
         <v>1.8</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CK11" t="n">
         <v>1.73</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="CM11" t="n">
         <v>2</v>
@@ -5300,10 +5300,10 @@
         <v>1.36</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CX11" t="n">
         <v>1.77</v>
@@ -5324,79 +5324,79 @@
         <v>2.17</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.87</v>
+        <v>3.88</v>
       </c>
       <c r="DE11" t="n">
         <v>0.16</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="DG11" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="DH11" t="n">
-        <v>103</v>
+        <v>101.52</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.28</v>
+        <v>4.21</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="DM11" t="n">
-        <v>52.16</v>
+        <v>51.31</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.33</v>
+        <v>2.26</v>
       </c>
       <c r="DP11" t="n">
-        <v>12.84</v>
+        <v>12.9</v>
       </c>
       <c r="DQ11" t="n">
-        <v>12.44</v>
+        <v>12.21</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.78</v>
+        <v>7.84</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>45.16</v>
+        <v>45.32</v>
       </c>
       <c r="DW11" t="n">
         <v>0.16</v>
       </c>
       <c r="DX11" t="n">
-        <v>12.28</v>
+        <v>12.26</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.5</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.78</v>
+        <v>3.79</v>
       </c>
       <c r="EA11" t="n">
         <v>20.11</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="EC11" t="n">
         <v>2.11</v>

--- a/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6" t="n">
         <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="F6" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="H6" t="n">
-        <v>101.56</v>
+        <v>105.5</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="J6" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="K6" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L6" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="M6" t="n">
-        <v>55.44</v>
+        <v>57.9</v>
       </c>
       <c r="N6" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="O6" t="n">
-        <v>1.56</v>
+        <v>1.8</v>
       </c>
       <c r="P6" t="n">
-        <v>10.89</v>
+        <v>10.7</v>
       </c>
       <c r="Q6" t="n">
-        <v>11.44</v>
+        <v>11.9</v>
       </c>
       <c r="R6" t="n">
-        <v>10.56</v>
+        <v>10.2</v>
       </c>
       <c r="S6" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T6" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -3057,28 +3057,28 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>49.11</v>
+        <v>50.8</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>11.89</v>
+        <v>11.8</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.89</v>
+        <v>8.1</v>
       </c>
       <c r="AB6" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="AC6" t="n">
-        <v>21</v>
+        <v>21.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AF6" t="n">
         <v>0.1</v>
@@ -3162,70 +3162,70 @@
         <v>1.8</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.84</v>
+        <v>9.85</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.47</v>
+        <v>4.5</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.79</v>
+        <v>4.8</v>
       </c>
       <c r="BR6" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS6" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BT6" t="n">
-        <v>63.16</v>
+        <v>60</v>
       </c>
       <c r="BU6" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BV6" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BW6" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX6" t="n">
-        <v>68.42</v>
+        <v>70</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="BZ6" t="n">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.42</v>
+        <v>3.41</v>
       </c>
       <c r="CC6" t="n">
         <v>3.99</v>
@@ -3255,7 +3255,7 @@
         <v>1.75</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CM6" t="n">
         <v>1.99</v>
@@ -3264,10 +3264,10 @@
         <v>1.59</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CQ6" t="n">
         <v>3.51</v>
@@ -3285,19 +3285,19 @@
         <v>1.37</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CW6" t="n">
         <v>1.92</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CZ6" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="DA6" t="n">
         <v>1.58</v>
@@ -3306,52 +3306,52 @@
         <v>1.35</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="DD6" t="n">
         <v>3.74</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="DH6" t="n">
-        <v>103.27</v>
+        <v>105.15</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ6" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="DK6" t="n">
-        <v>3.84</v>
+        <v>3.9</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.42</v>
+        <v>0.45</v>
       </c>
       <c r="DM6" t="n">
-        <v>55.16</v>
+        <v>56.4</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="DP6" t="n">
-        <v>11.26</v>
+        <v>11.15</v>
       </c>
       <c r="DQ6" t="n">
-        <v>11.58</v>
+        <v>11.8</v>
       </c>
       <c r="DR6" t="n">
-        <v>10.32</v>
+        <v>10.15</v>
       </c>
       <c r="DS6" t="n">
         <v>0</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>47.95</v>
+        <v>48.85</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>10.37</v>
+        <v>10.4</v>
       </c>
       <c r="DY6" t="n">
-        <v>6.68</v>
+        <v>6.85</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.68</v>
+        <v>3.55</v>
       </c>
       <c r="EA6" t="n">
-        <v>22</v>
+        <v>22.05</v>
       </c>
       <c r="EB6" t="n">
         <v>1.32</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="7">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" t="n">
         <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3484,139 +3484,139 @@
         <v>2.4</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="AI7" t="n">
-        <v>115.78</v>
+        <v>113.6</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="AL7" t="n">
-        <v>5.11</v>
+        <v>5.1</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AN7" t="n">
-        <v>65</v>
+        <v>62.9</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="AP7" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ7" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="AR7" t="n">
-        <v>10.89</v>
+        <v>10.7</v>
       </c>
       <c r="AS7" t="n">
-        <v>6.67</v>
+        <v>7.2</v>
       </c>
       <c r="AT7" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>53.78</v>
+        <v>51.8</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="BA7" t="n">
-        <v>11.67</v>
+        <v>11.3</v>
       </c>
       <c r="BB7" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="BC7" t="n">
-        <v>3.33</v>
+        <v>3.3</v>
       </c>
       <c r="BD7" t="n">
-        <v>20.33</v>
+        <v>20.3</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.949999999999999</v>
+        <v>9</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="BL7" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.74</v>
+        <v>3.8</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.21</v>
+        <v>5.2</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BT7" t="n">
-        <v>47.37</v>
+        <v>45</v>
       </c>
       <c r="BU7" t="n">
-        <v>26.32</v>
+        <v>25</v>
       </c>
       <c r="BV7" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BW7" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX7" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BY7" t="n">
         <v>3.06</v>
@@ -3625,16 +3625,16 @@
         <v>3.14</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.63</v>
+        <v>3.6</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.66</v>
+        <v>3.64</v>
       </c>
       <c r="CC7" t="n">
-        <v>4.71</v>
+        <v>4.55</v>
       </c>
       <c r="CD7" t="n">
-        <v>5</v>
+        <v>4.85</v>
       </c>
       <c r="CE7" t="n">
         <v>1.37</v>
@@ -3643,10 +3643,10 @@
         <v>2.79</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CI7" t="n">
         <v>1.9</v>
@@ -3655,31 +3655,31 @@
         <v>1.81</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CL7" t="n">
         <v>2.13</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.24</v>
+        <v>3.26</v>
       </c>
       <c r="CR7" t="n">
         <v>1.39</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="CT7" t="n">
         <v>2.98</v>
@@ -3688,106 +3688,106 @@
         <v>1.41</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CY7" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="DB7" t="n">
         <v>1.31</v>
       </c>
       <c r="DC7" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.45</v>
+        <v>3.46</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="DH7" t="n">
-        <v>111.26</v>
+        <v>110.4</v>
       </c>
       <c r="DI7" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.53</v>
+        <v>4.55</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DM7" t="n">
-        <v>62.47</v>
+        <v>61.55</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.79</v>
+        <v>0.85</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="DP7" t="n">
-        <v>15.05</v>
+        <v>15.1</v>
       </c>
       <c r="DQ7" t="n">
-        <v>12.26</v>
+        <v>12.1</v>
       </c>
       <c r="DR7" t="n">
-        <v>6.84</v>
+        <v>7.1</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>52.79</v>
+        <v>51.85</v>
       </c>
       <c r="DW7" t="n">
         <v>0.1</v>
       </c>
       <c r="DX7" t="n">
-        <v>11.16</v>
+        <v>11</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.47</v>
+        <v>7.35</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.68</v>
+        <v>3.65</v>
       </c>
       <c r="EA7" t="n">
-        <v>21.84</v>
+        <v>21.75</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="8">

--- a/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
@@ -1782,94 +1782,94 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
         <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="G3" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="H3" t="n">
-        <v>100.2</v>
+        <v>98</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="J3" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="K3" t="n">
-        <v>4.2</v>
+        <v>3.91</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="M3" t="n">
-        <v>51</v>
+        <v>48.82</v>
       </c>
       <c r="N3" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="O3" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="P3" t="n">
-        <v>10.7</v>
+        <v>11.36</v>
       </c>
       <c r="Q3" t="n">
-        <v>13.8</v>
+        <v>13.18</v>
       </c>
       <c r="R3" t="n">
-        <v>8.5</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="S3" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="T3" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>51.9</v>
+        <v>49.55</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z3" t="n">
-        <v>11.2</v>
+        <v>10.73</v>
       </c>
       <c r="AA3" t="n">
-        <v>7</v>
+        <v>6.73</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AC3" t="n">
-        <v>22</v>
+        <v>21.91</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -1953,70 +1953,70 @@
         <v>1.89</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="BH3" t="n">
-        <v>8.74</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.89</v>
+        <v>3.9</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.16</v>
+        <v>4.25</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>78.95</v>
+        <v>75</v>
       </c>
       <c r="BT3" t="n">
-        <v>52.63</v>
+        <v>50</v>
       </c>
       <c r="BU3" t="n">
-        <v>31.58</v>
+        <v>30</v>
       </c>
       <c r="BV3" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>68.42</v>
+        <v>65</v>
       </c>
       <c r="BY3" t="n">
-        <v>3.02</v>
+        <v>3.06</v>
       </c>
       <c r="BZ3" t="n">
-        <v>3.18</v>
+        <v>3.22</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.55</v>
+        <v>3.53</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.68</v>
+        <v>3.65</v>
       </c>
       <c r="CC3" t="n">
         <v>5.72</v>
@@ -2031,7 +2031,7 @@
         <v>2.86</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="CH3" t="n">
         <v>1.38</v>
@@ -2061,13 +2061,13 @@
         <v>2.03</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.49</v>
+        <v>3.48</v>
       </c>
       <c r="CR3" t="n">
         <v>1.43</v>
       </c>
       <c r="CS3" t="n">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="CT3" t="n">
         <v>2.84</v>
@@ -2097,52 +2097,52 @@
         <v>1.34</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.71</v>
+        <v>3.72</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="DG3" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="DH3" t="n">
-        <v>98.58</v>
+        <v>97.45</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="DK3" t="n">
-        <v>4.53</v>
+        <v>4.35</v>
       </c>
       <c r="DL3" t="n">
         <v>0.05</v>
       </c>
       <c r="DM3" t="n">
-        <v>52.37</v>
+        <v>51.1</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="DP3" t="n">
-        <v>11.16</v>
+        <v>11.5</v>
       </c>
       <c r="DQ3" t="n">
-        <v>13.37</v>
+        <v>13.05</v>
       </c>
       <c r="DR3" t="n">
-        <v>8.630000000000001</v>
+        <v>8.65</v>
       </c>
       <c r="DS3" t="n">
         <v>0.05</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>47.79</v>
+        <v>46.7</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DX3" t="n">
-        <v>11.53</v>
+        <v>11.25</v>
       </c>
       <c r="DY3" t="n">
-        <v>7.53</v>
+        <v>7.35</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="EA3" t="n">
-        <v>20.68</v>
+        <v>20.7</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="4">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C5" t="n">
         <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
         <v>0.2</v>
@@ -2678,139 +2678,139 @@
         <v>1.7</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="AI5" t="n">
-        <v>100.22</v>
+        <v>103.8</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="AL5" t="n">
-        <v>5.56</v>
+        <v>5.9</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AN5" t="n">
-        <v>58.44</v>
+        <v>60.5</v>
       </c>
       <c r="AO5" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AP5" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AQ5" t="n">
-        <v>13.22</v>
+        <v>12.6</v>
       </c>
       <c r="AR5" t="n">
-        <v>14.67</v>
+        <v>15</v>
       </c>
       <c r="AS5" t="n">
-        <v>7.22</v>
+        <v>7</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>55.56</v>
+        <v>57.4</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>13.22</v>
+        <v>14</v>
       </c>
       <c r="BB5" t="n">
-        <v>9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.22</v>
+        <v>4.3</v>
       </c>
       <c r="BD5" t="n">
-        <v>19.78</v>
+        <v>20.9</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.26</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.11</v>
+        <v>4.1</v>
       </c>
       <c r="BQ5" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>95</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>85</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>45</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>20</v>
+      </c>
+      <c r="BV5" t="n">
         <v>5</v>
       </c>
-      <c r="BR5" t="n">
-        <v>94.73999999999999</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>89.47</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>47.37</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>21.05</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>5.26</v>
-      </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>42.11</v>
+        <v>40</v>
       </c>
       <c r="BY5" t="n">
         <v>1.66</v>
@@ -2819,22 +2819,22 @@
         <v>1.72</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.69</v>
+        <v>3.66</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.64</v>
+        <v>3.61</v>
       </c>
       <c r="CC5" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="CD5" t="n">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="CE5" t="n">
         <v>1.41</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="CG5" t="n">
         <v>2.74</v>
@@ -2852,7 +2852,7 @@
         <v>1.69</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CM5" t="n">
         <v>2.06</v>
@@ -2867,13 +2867,13 @@
         <v>2.06</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.62</v>
+        <v>3.61</v>
       </c>
       <c r="CR5" t="n">
         <v>1.44</v>
       </c>
       <c r="CS5" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="CT5" t="n">
         <v>2.81</v>
@@ -2882,10 +2882,10 @@
         <v>1.36</v>
       </c>
       <c r="CV5" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CW5" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CX5" t="n">
         <v>1.71</v>
@@ -2906,82 +2906,82 @@
         <v>2.13</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.78</v>
+        <v>3.79</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.11</v>
+        <v>3.2</v>
       </c>
       <c r="DH5" t="n">
-        <v>110.74</v>
+        <v>112</v>
       </c>
       <c r="DI5" t="n">
         <v>-0.05</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.37</v>
+        <v>5.55</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="DM5" t="n">
-        <v>62.84</v>
+        <v>63.65</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.26</v>
+        <v>2.35</v>
       </c>
       <c r="DP5" t="n">
-        <v>12.42</v>
+        <v>12.15</v>
       </c>
       <c r="DQ5" t="n">
-        <v>14.95</v>
+        <v>15.1</v>
       </c>
       <c r="DR5" t="n">
-        <v>6.1</v>
+        <v>6.05</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>58.53</v>
+        <v>59.3</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX5" t="n">
-        <v>14.95</v>
+        <v>15.25</v>
       </c>
       <c r="DY5" t="n">
-        <v>9.74</v>
+        <v>10.05</v>
       </c>
       <c r="DZ5" t="n">
-        <v>5.21</v>
+        <v>5.2</v>
       </c>
       <c r="EA5" t="n">
-        <v>21.69</v>
+        <v>22.15</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="6">
@@ -3797,10 +3797,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D8" t="n">
         <v>9</v>
@@ -3809,49 +3809,49 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="G8" t="n">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="H8" t="n">
-        <v>123.5</v>
+        <v>118.27</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="K8" t="n">
-        <v>6</v>
+        <v>5.73</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="M8" t="n">
-        <v>83.7</v>
+        <v>80.64</v>
       </c>
       <c r="N8" t="n">
         <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P8" t="n">
-        <v>14.7</v>
+        <v>14.73</v>
       </c>
       <c r="Q8" t="n">
-        <v>13.4</v>
+        <v>13.64</v>
       </c>
       <c r="R8" t="n">
-        <v>6.5</v>
+        <v>7.27</v>
       </c>
       <c r="S8" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -3863,28 +3863,28 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>52.1</v>
+        <v>50.27</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z8" t="n">
-        <v>13</v>
+        <v>12.64</v>
       </c>
       <c r="AA8" t="n">
-        <v>9.6</v>
+        <v>9.27</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.4</v>
+        <v>3.36</v>
       </c>
       <c r="AC8" t="n">
-        <v>22.2</v>
+        <v>22.18</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.9</v>
+        <v>2.09</v>
       </c>
       <c r="AF8" t="n">
         <v>0.11</v>
@@ -3968,70 +3968,70 @@
         <v>2.22</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="BH8" t="n">
         <v>9.949999999999999</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.42</v>
+        <v>0.45</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="BP8" t="n">
         <v>5.05</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.84</v>
+        <v>4.85</v>
       </c>
       <c r="BR8" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BS8" t="n">
-        <v>73.68000000000001</v>
+        <v>70</v>
       </c>
       <c r="BT8" t="n">
-        <v>42.11</v>
+        <v>40</v>
       </c>
       <c r="BU8" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BV8" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BW8" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BX8" t="n">
-        <v>47.37</v>
+        <v>45</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.43</v>
+        <v>3.41</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.51</v>
+        <v>3.49</v>
       </c>
       <c r="CC8" t="n">
         <v>3.59</v>
@@ -4043,22 +4043,22 @@
         <v>1.38</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="CH8" t="n">
         <v>1.39</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CJ8" t="n">
         <v>1.8</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CL8" t="n">
         <v>2.16</v>
@@ -4076,88 +4076,88 @@
         <v>1.95</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.19</v>
+        <v>3.23</v>
       </c>
       <c r="CR8" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CV8" t="n">
         <v>1.98</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="DB8" t="n">
         <v>1.31</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.48</v>
+        <v>3.51</v>
       </c>
       <c r="DE8" t="n">
         <v>0.05</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="DH8" t="n">
-        <v>114.05</v>
+        <v>111.65</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.27</v>
+        <v>2.35</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.05</v>
+        <v>4.95</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="DM8" t="n">
-        <v>70.20999999999999</v>
+        <v>69.2</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="DP8" t="n">
-        <v>15.26</v>
+        <v>15.25</v>
       </c>
       <c r="DQ8" t="n">
-        <v>13.63</v>
+        <v>13.75</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.58</v>
+        <v>7.95</v>
       </c>
       <c r="DS8" t="n">
         <v>0</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>50.63</v>
+        <v>49.7</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DX8" t="n">
-        <v>12.79</v>
+        <v>12.6</v>
       </c>
       <c r="DY8" t="n">
-        <v>9.369999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="EA8" t="n">
-        <v>22.21</v>
+        <v>22.2</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="9">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
         <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
         <v>0.3</v>
@@ -4290,31 +4290,31 @@
         <v>2.2</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="AH9" t="n">
-        <v>3.11</v>
+        <v>3.2</v>
       </c>
       <c r="AI9" t="n">
-        <v>107.89</v>
+        <v>107.9</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>3.56</v>
+        <v>3.3</v>
       </c>
       <c r="AL9" t="n">
-        <v>6.11</v>
+        <v>6.2</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AN9" t="n">
-        <v>57.78</v>
+        <v>59.7</v>
       </c>
       <c r="AO9" t="n">
         <v>1</v>
@@ -4323,106 +4323,106 @@
         <v>3</v>
       </c>
       <c r="AQ9" t="n">
-        <v>12.33</v>
+        <v>12.7</v>
       </c>
       <c r="AR9" t="n">
-        <v>13.33</v>
+        <v>13.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>7.56</v>
+        <v>7.2</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>49.89</v>
+        <v>51.7</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA9" t="n">
-        <v>14.56</v>
+        <v>14.6</v>
       </c>
       <c r="BB9" t="n">
-        <v>11.11</v>
+        <v>11.3</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="BD9" t="n">
-        <v>22.44</v>
+        <v>22.4</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="BF9" t="n">
-        <v>3.33</v>
+        <v>3.1</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.79</v>
+        <v>2.7</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.58</v>
+        <v>10.55</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.79</v>
+        <v>2.7</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="BP9" t="n">
         <v>5.05</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.53</v>
+        <v>5.5</v>
       </c>
       <c r="BR9" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BS9" t="n">
-        <v>78.95</v>
+        <v>75</v>
       </c>
       <c r="BT9" t="n">
-        <v>52.63</v>
+        <v>50</v>
       </c>
       <c r="BU9" t="n">
-        <v>36.84</v>
+        <v>35</v>
       </c>
       <c r="BV9" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BW9" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX9" t="n">
-        <v>63.16</v>
+        <v>60</v>
       </c>
       <c r="BY9" t="n">
         <v>2.04</v>
@@ -4431,25 +4431,25 @@
         <v>2.01</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.67</v>
+        <v>3.63</v>
       </c>
       <c r="CC9" t="n">
-        <v>2.84</v>
+        <v>2.77</v>
       </c>
       <c r="CD9" t="n">
-        <v>3.09</v>
+        <v>3.05</v>
       </c>
       <c r="CE9" t="n">
         <v>1.4</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="CH9" t="n">
         <v>1.37</v>
@@ -4467,10 +4467,10 @@
         <v>2.19</v>
       </c>
       <c r="CM9" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CO9" t="n">
         <v>1.31</v>
@@ -4479,16 +4479,16 @@
         <v>2.02</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.48</v>
+        <v>3.51</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CS9" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="CU9" t="n">
         <v>1.38</v>
@@ -4500,100 +4500,100 @@
         <v>1.99</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="CY9" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="DB9" t="n">
         <v>1.35</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.73</v>
+        <v>3.75</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="DG9" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="DH9" t="n">
-        <v>112.37</v>
+        <v>112.15</v>
       </c>
       <c r="DI9" t="n">
         <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="DK9" t="n">
-        <v>6.26</v>
+        <v>6.3</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="DM9" t="n">
-        <v>64.63</v>
+        <v>65.25</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="DO9" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="DP9" t="n">
-        <v>12.52</v>
+        <v>12.7</v>
       </c>
       <c r="DQ9" t="n">
-        <v>13.89</v>
+        <v>13.95</v>
       </c>
       <c r="DR9" t="n">
-        <v>7.42</v>
+        <v>7.25</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>51.05</v>
+        <v>51.9</v>
       </c>
       <c r="DW9" t="n">
         <v>0.1</v>
       </c>
       <c r="DX9" t="n">
-        <v>15.37</v>
+        <v>15.35</v>
       </c>
       <c r="DY9" t="n">
-        <v>11.26</v>
+        <v>11.35</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="EA9" t="n">
-        <v>23.73</v>
+        <v>23.65</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.74</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="10">
@@ -4603,61 +4603,61 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
         <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="F10" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>2.22</v>
+        <v>1.9</v>
       </c>
       <c r="H10" t="n">
-        <v>118.67</v>
+        <v>118</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="K10" t="n">
-        <v>3.44</v>
+        <v>4.2</v>
       </c>
       <c r="L10" t="n">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="M10" t="n">
-        <v>59.56</v>
+        <v>63.3</v>
       </c>
       <c r="N10" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="O10" t="n">
-        <v>1.22</v>
+        <v>1</v>
       </c>
       <c r="P10" t="n">
-        <v>13.22</v>
+        <v>13.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>13.11</v>
+        <v>12.9</v>
       </c>
       <c r="R10" t="n">
-        <v>8.67</v>
+        <v>8</v>
       </c>
       <c r="S10" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="T10" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -4669,28 +4669,28 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>51.78</v>
+        <v>53.7</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="Z10" t="n">
-        <v>13.67</v>
+        <v>14.8</v>
       </c>
       <c r="AA10" t="n">
-        <v>8.67</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AB10" t="n">
         <v>5</v>
       </c>
       <c r="AC10" t="n">
-        <v>25.78</v>
+        <v>25.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AF10" t="n">
         <v>0.1</v>
@@ -4774,70 +4774,70 @@
         <v>2.1</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BH10" t="n">
-        <v>7.11</v>
+        <v>7.55</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.79</v>
+        <v>0.85</v>
       </c>
       <c r="BL10" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.47</v>
+        <v>3.25</v>
       </c>
       <c r="BQ10" t="n">
-        <v>3.63</v>
+        <v>3.4</v>
       </c>
       <c r="BR10" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BS10" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BT10" t="n">
-        <v>68.42</v>
+        <v>65</v>
       </c>
       <c r="BU10" t="n">
-        <v>31.58</v>
+        <v>30</v>
       </c>
       <c r="BV10" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BW10" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX10" t="n">
-        <v>78.95</v>
+        <v>75</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.71</v>
+        <v>2.66</v>
       </c>
       <c r="BZ10" t="n">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.43</v>
+        <v>3.41</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.51</v>
+        <v>3.48</v>
       </c>
       <c r="CC10" t="n">
         <v>4.48</v>
@@ -4852,7 +4852,7 @@
         <v>2.85</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="CH10" t="n">
         <v>1.39</v>
@@ -4873,28 +4873,28 @@
         <v>2.02</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CO10" t="n">
         <v>1.28</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="CR10" t="n">
         <v>1.41</v>
       </c>
       <c r="CS10" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CV10" t="n">
         <v>1.95</v>
@@ -4906,64 +4906,64 @@
         <v>1.74</v>
       </c>
       <c r="CY10" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="DB10" t="n">
         <v>1.32</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.53</v>
+        <v>3.55</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="DH10" t="n">
-        <v>111.58</v>
+        <v>111.6</v>
       </c>
       <c r="DI10" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="DK10" t="n">
-        <v>3.26</v>
+        <v>3.65</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.31</v>
+        <v>0.25</v>
       </c>
       <c r="DM10" t="n">
-        <v>53.69</v>
+        <v>55.85</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="DP10" t="n">
-        <v>14.37</v>
+        <v>14.5</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.63</v>
+        <v>12.55</v>
       </c>
       <c r="DR10" t="n">
-        <v>8.74</v>
+        <v>8.4</v>
       </c>
       <c r="DS10" t="n">
         <v>0.05</v>
@@ -4975,28 +4975,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>48.63</v>
+        <v>49.75</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DX10" t="n">
-        <v>11.63</v>
+        <v>12.3</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.63</v>
+        <v>8.25</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="EA10" t="n">
-        <v>22.11</v>
+        <v>22.3</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="11">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C11" t="n">
         <v>9</v>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E11" t="n">
         <v>0.22</v>
@@ -5096,139 +5096,139 @@
         <v>2</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG11" t="n">
         <v>1</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AI11" t="n">
-        <v>92.59999999999999</v>
+        <v>90.73</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="AL11" t="n">
-        <v>4</v>
+        <v>4.09</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AN11" t="n">
-        <v>45.1</v>
+        <v>44.27</v>
       </c>
       <c r="AO11" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AQ11" t="n">
-        <v>13</v>
+        <v>12.91</v>
       </c>
       <c r="AR11" t="n">
-        <v>12.1</v>
+        <v>12.45</v>
       </c>
       <c r="AS11" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AU11" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>43.8</v>
+        <v>42.45</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="BA11" t="n">
-        <v>10.1</v>
+        <v>9.91</v>
       </c>
       <c r="BB11" t="n">
-        <v>6.9</v>
+        <v>6.55</v>
       </c>
       <c r="BC11" t="n">
-        <v>3.2</v>
+        <v>3.36</v>
       </c>
       <c r="BD11" t="n">
-        <v>19.3</v>
+        <v>18.64</v>
       </c>
       <c r="BE11" t="n">
         <v>1.19</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.470000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.74</v>
+        <v>0.8</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.42</v>
+        <v>4.15</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.05</v>
+        <v>4.75</v>
       </c>
       <c r="BR11" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BS11" t="n">
-        <v>73.68000000000001</v>
+        <v>75</v>
       </c>
       <c r="BT11" t="n">
-        <v>52.63</v>
+        <v>50</v>
       </c>
       <c r="BU11" t="n">
-        <v>36.84</v>
+        <v>35</v>
       </c>
       <c r="BV11" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BW11" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX11" t="n">
-        <v>63.16</v>
+        <v>60</v>
       </c>
       <c r="BY11" t="n">
         <v>2.9</v>
@@ -5237,16 +5237,16 @@
         <v>3.18</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.36</v>
+        <v>3.35</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.41</v>
+        <v>3.39</v>
       </c>
       <c r="CC11" t="n">
-        <v>3.94</v>
+        <v>3.86</v>
       </c>
       <c r="CD11" t="n">
-        <v>4.28</v>
+        <v>4.16</v>
       </c>
       <c r="CE11" t="n">
         <v>1.43</v>
@@ -5267,10 +5267,10 @@
         <v>1.92</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CM11" t="n">
         <v>2</v>
@@ -5282,7 +5282,7 @@
         <v>1.33</v>
       </c>
       <c r="CP11" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CQ11" t="n">
         <v>3.66</v>
@@ -5291,10 +5291,10 @@
         <v>1.45</v>
       </c>
       <c r="CS11" t="n">
-        <v>3.17</v>
+        <v>3.18</v>
       </c>
       <c r="CT11" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="CU11" t="n">
         <v>1.36</v>
@@ -5312,7 +5312,7 @@
         <v>2.21</v>
       </c>
       <c r="CZ11" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="DA11" t="n">
         <v>1.6</v>
@@ -5327,79 +5327,79 @@
         <v>3.88</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="DG11" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="DH11" t="n">
-        <v>101.52</v>
+        <v>100.05</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.21</v>
+        <v>4.25</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.84</v>
+        <v>0.75</v>
       </c>
       <c r="DM11" t="n">
-        <v>51.31</v>
+        <v>50.55</v>
       </c>
       <c r="DN11" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="DP11" t="n">
-        <v>12.9</v>
+        <v>12.85</v>
       </c>
       <c r="DQ11" t="n">
-        <v>12.21</v>
+        <v>12.4</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.84</v>
+        <v>8.1</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>45.32</v>
+        <v>44.5</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="DX11" t="n">
-        <v>12.26</v>
+        <v>12.05</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.470000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.79</v>
+        <v>3.85</v>
       </c>
       <c r="EA11" t="n">
-        <v>20.11</v>
+        <v>19.7</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
@@ -645,7 +645,7 @@
     <col width="9.6" customWidth="1" min="73" max="73"/>
     <col width="9.6" customWidth="1" min="74" max="74"/>
     <col width="9.6" customWidth="1" min="75" max="75"/>
-    <col width="8.4" customWidth="1" min="76" max="76"/>
+    <col width="7.199999999999999" customWidth="1" min="76" max="76"/>
     <col width="18" customWidth="1" min="77" max="77"/>
     <col width="27.6" customWidth="1" min="78" max="78"/>
     <col width="18" customWidth="1" min="79" max="79"/>
@@ -1379,61 +1379,61 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
         <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="F2" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="G2" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="H2" t="n">
-        <v>128.89</v>
+        <v>128.8</v>
       </c>
       <c r="I2" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="J2" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="K2" t="n">
-        <v>5.89</v>
+        <v>6.1</v>
       </c>
       <c r="L2" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="M2" t="n">
-        <v>74.67</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="O2" t="n">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="P2" t="n">
-        <v>11.56</v>
+        <v>11.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>13</v>
+        <v>12.8</v>
       </c>
       <c r="R2" t="n">
-        <v>5.78</v>
+        <v>5.4</v>
       </c>
       <c r="S2" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="T2" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -1445,28 +1445,28 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>57.78</v>
+        <v>58.3</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z2" t="n">
-        <v>15.44</v>
+        <v>16.6</v>
       </c>
       <c r="AA2" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.44</v>
+        <v>6.8</v>
       </c>
       <c r="AC2" t="n">
-        <v>22.67</v>
+        <v>22.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.97</v>
+        <v>2.07</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AF2" t="n">
         <v>0.1</v>
@@ -1550,70 +1550,70 @@
         <v>2</v>
       </c>
       <c r="BG2" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.789999999999999</v>
+        <v>9.75</v>
       </c>
       <c r="BI2" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.84</v>
+        <v>0.9</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.47</v>
+        <v>4.55</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.26</v>
+        <v>5.15</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BT2" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BU2" t="n">
-        <v>21.05</v>
+        <v>25</v>
       </c>
       <c r="BV2" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BW2" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX2" t="n">
-        <v>52.63</v>
+        <v>55</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.55</v>
+        <v>4.73</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.95</v>
+        <v>5.1</v>
       </c>
       <c r="CC2" t="n">
         <v>1.57</v>
@@ -1622,157 +1622,157 @@
         <v>1.67</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.2</v>
+        <v>3.23</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CJ2" t="n">
         <v>1.98</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="CR2" t="n">
         <v>1.37</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="CT2" t="n">
         <v>3.07</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CW2" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CX2" t="n">
         <v>1.59</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="DH2" t="n">
-        <v>123.63</v>
+        <v>123.85</v>
       </c>
       <c r="DI2" t="n">
         <v>0.1</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="DK2" t="n">
-        <v>6.26</v>
+        <v>6.35</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.42</v>
+        <v>0.45</v>
       </c>
       <c r="DM2" t="n">
-        <v>74.79000000000001</v>
+        <v>75.25</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="DP2" t="n">
-        <v>12.95</v>
+        <v>12.75</v>
       </c>
       <c r="DQ2" t="n">
-        <v>13.68</v>
+        <v>13.55</v>
       </c>
       <c r="DR2" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>56.37</v>
+        <v>56.7</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DX2" t="n">
-        <v>15.73</v>
+        <v>16.3</v>
       </c>
       <c r="DY2" t="n">
-        <v>10.11</v>
+        <v>10.45</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5.63</v>
+        <v>5.85</v>
       </c>
       <c r="EA2" t="n">
-        <v>23.26</v>
+        <v>23.3</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="3">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4" t="n">
         <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2275,139 +2275,139 @@
         <v>1.67</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AI4" t="n">
-        <v>100.7</v>
+        <v>101.09</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK4" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="AL4" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AN4" t="n">
-        <v>54.4</v>
+        <v>53.18</v>
       </c>
       <c r="AO4" t="n">
         <v>1</v>
       </c>
       <c r="AP4" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>9.91</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>39.18</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>21.73</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>10.15</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="BN4" t="n">
         <v>1.6</v>
       </c>
-      <c r="AQ4" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>39.4</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>10.21</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>1.53</v>
-      </c>
       <c r="BO4" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="BP4" t="n">
-        <v>5.21</v>
+        <v>5.25</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.95</v>
+        <v>4.85</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
       </c>
       <c r="BS4" t="n">
-        <v>84.20999999999999</v>
+        <v>85</v>
       </c>
       <c r="BT4" t="n">
-        <v>57.89</v>
+        <v>60</v>
       </c>
       <c r="BU4" t="n">
-        <v>31.58</v>
+        <v>35</v>
       </c>
       <c r="BV4" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>68.42</v>
+        <v>70</v>
       </c>
       <c r="BY4" t="n">
         <v>4.46</v>
@@ -2416,28 +2416,28 @@
         <v>5.11</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.09</v>
+        <v>4.3</v>
       </c>
       <c r="CB4" t="n">
-        <v>4.25</v>
+        <v>4.42</v>
       </c>
       <c r="CC4" t="n">
-        <v>6.46</v>
+        <v>6.78</v>
       </c>
       <c r="CD4" t="n">
-        <v>9.02</v>
+        <v>9.49</v>
       </c>
       <c r="CE4" t="n">
         <v>1.35</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.98</v>
+        <v>3.03</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CI4" t="n">
         <v>1.81</v>
@@ -2446,106 +2446,106 @@
         <v>1.93</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="CM4" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.13</v>
+        <v>3.08</v>
       </c>
       <c r="CR4" t="n">
         <v>1.38</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="CT4" t="n">
         <v>3.05</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="CV4" t="n">
         <v>1.88</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CX4" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="CY4" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="CZ4" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="DA4" t="n">
         <v>1.7</v>
       </c>
-      <c r="CY4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="CZ4" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="DA4" t="n">
-        <v>1.68</v>
-      </c>
       <c r="DB4" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.23</v>
+        <v>3.18</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="DH4" t="n">
-        <v>107.9</v>
+        <v>107.75</v>
       </c>
       <c r="DI4" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="DK4" t="n">
-        <v>3.63</v>
+        <v>3.5</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DM4" t="n">
-        <v>61.16</v>
+        <v>60.15</v>
       </c>
       <c r="DN4" t="n">
         <v>0.9</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="DP4" t="n">
-        <v>12.73</v>
+        <v>12.65</v>
       </c>
       <c r="DQ4" t="n">
-        <v>11.16</v>
+        <v>11.05</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.16</v>
+        <v>8.4</v>
       </c>
       <c r="DS4" t="n">
         <v>0.1</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>40.95</v>
+        <v>40.75</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DX4" t="n">
-        <v>9.84</v>
+        <v>9.65</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.63</v>
+        <v>6.5</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.21</v>
+        <v>3.15</v>
       </c>
       <c r="EA4" t="n">
-        <v>20.9</v>
+        <v>21.2</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.42</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="5">
@@ -2744,16 +2744,16 @@
         <v>14</v>
       </c>
       <c r="BB5" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BD5" t="n">
         <v>20.9</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="BF5" t="n">
         <v>2.6</v>
@@ -2969,16 +2969,16 @@
         <v>15.25</v>
       </c>
       <c r="DY5" t="n">
-        <v>10.05</v>
+        <v>10</v>
       </c>
       <c r="DZ5" t="n">
-        <v>5.2</v>
+        <v>5.25</v>
       </c>
       <c r="EA5" t="n">
         <v>22.15</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="EC5" t="n">
         <v>2.15</v>
@@ -3057,7 +3057,7 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>50.8</v>
+        <v>50.9</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -3363,7 +3363,7 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>48.85</v>
+        <v>48.9</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
@@ -3541,7 +3541,7 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>51.8</v>
+        <v>51.7</v>
       </c>
       <c r="AZ7" t="n">
         <v>0.2</v>
@@ -3766,7 +3766,7 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>51.85</v>
+        <v>51.8</v>
       </c>
       <c r="DW7" t="n">
         <v>0.1</v>
@@ -4669,7 +4669,7 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>53.7</v>
+        <v>53.6</v>
       </c>
       <c r="Y10" t="n">
         <v>0.3</v>
@@ -4975,7 +4975,7 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>49.75</v>
+        <v>49.7</v>
       </c>
       <c r="DW10" t="n">
         <v>0.25</v>
@@ -5153,7 +5153,7 @@
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>42.45</v>
+        <v>42.55</v>
       </c>
       <c r="AZ11" t="n">
         <v>0.27</v>
@@ -5378,7 +5378,7 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>44.5</v>
+        <v>44.55</v>
       </c>
       <c r="DW11" t="n">
         <v>0.2</v>

--- a/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
@@ -645,7 +645,7 @@
     <col width="9.6" customWidth="1" min="73" max="73"/>
     <col width="9.6" customWidth="1" min="74" max="74"/>
     <col width="9.6" customWidth="1" min="75" max="75"/>
-    <col width="7.199999999999999" customWidth="1" min="76" max="76"/>
+    <col width="8.4" customWidth="1" min="76" max="76"/>
     <col width="18" customWidth="1" min="77" max="77"/>
     <col width="27.6" customWidth="1" min="78" max="78"/>
     <col width="18" customWidth="1" min="79" max="79"/>
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3" t="n">
         <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3" t="n">
         <v>0.18</v>
@@ -1875,136 +1875,136 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.56</v>
+        <v>1.9</v>
       </c>
       <c r="AI3" t="n">
-        <v>96.78</v>
+        <v>97.8</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AL3" t="n">
-        <v>4.89</v>
+        <v>5.3</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AN3" t="n">
-        <v>53.89</v>
+        <v>54.8</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>11.67</v>
+        <v>11.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>12.89</v>
+        <v>12.9</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.779999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="BN3" t="n">
         <v>1.33</v>
       </c>
-      <c r="AU3" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>43.22</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>11.89</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>8.109999999999999</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>19.22</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>1.35</v>
-      </c>
       <c r="BO3" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.25</v>
+        <v>4.29</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>75</v>
+        <v>76.19</v>
       </c>
       <c r="BT3" t="n">
-        <v>50</v>
+        <v>52.38</v>
       </c>
       <c r="BU3" t="n">
-        <v>30</v>
+        <v>28.57</v>
       </c>
       <c r="BV3" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>65</v>
+        <v>61.9</v>
       </c>
       <c r="BY3" t="n">
         <v>3.06</v>
@@ -2013,46 +2013,46 @@
         <v>3.22</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.53</v>
+        <v>3.51</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.65</v>
+        <v>3.62</v>
       </c>
       <c r="CC3" t="n">
-        <v>5.72</v>
+        <v>5.47</v>
       </c>
       <c r="CD3" t="n">
-        <v>5.85</v>
+        <v>5.62</v>
       </c>
       <c r="CE3" t="n">
         <v>1.4</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CI3" t="n">
         <v>1.82</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CK3" t="n">
         <v>1.69</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CO3" t="n">
         <v>1.31</v>
@@ -2061,7 +2061,7 @@
         <v>2.03</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="CR3" t="n">
         <v>1.43</v>
@@ -2076,22 +2076,22 @@
         <v>1.39</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="DB3" t="n">
         <v>1.34</v>
@@ -2103,46 +2103,46 @@
         <v>3.72</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="DG3" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="DH3" t="n">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="DI3" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="DJ3" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="DK3" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="DL3" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="DM3" t="n">
+        <v>51.67</v>
+      </c>
+      <c r="DN3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="DO3" t="n">
         <v>1.95</v>
       </c>
-      <c r="DH3" t="n">
-        <v>97.45</v>
-      </c>
-      <c r="DI3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="DJ3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="DK3" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="DL3" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="DM3" t="n">
-        <v>51.1</v>
-      </c>
-      <c r="DN3" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="DO3" t="n">
-        <v>1.85</v>
-      </c>
       <c r="DP3" t="n">
-        <v>11.5</v>
+        <v>11.43</v>
       </c>
       <c r="DQ3" t="n">
         <v>13.05</v>
       </c>
       <c r="DR3" t="n">
-        <v>8.65</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="DS3" t="n">
         <v>0.05</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>46.7</v>
+        <v>47.62</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX3" t="n">
-        <v>11.25</v>
+        <v>11.67</v>
       </c>
       <c r="DY3" t="n">
-        <v>7.35</v>
+        <v>7.76</v>
       </c>
       <c r="DZ3" t="n">
         <v>3.9</v>
       </c>
       <c r="EA3" t="n">
-        <v>20.7</v>
+        <v>20.67</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="4">
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
         <v>11</v>
@@ -2197,82 +2197,82 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="H4" t="n">
-        <v>115.89</v>
+        <v>114.2</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="K4" t="n">
-        <v>3.44</v>
+        <v>3.8</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>68.67</v>
+        <v>70.2</v>
       </c>
       <c r="N4" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="O4" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="P4" t="n">
-        <v>13.44</v>
+        <v>12.6</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.44</v>
+        <v>12.3</v>
       </c>
       <c r="R4" t="n">
-        <v>7.67</v>
+        <v>7.4</v>
       </c>
       <c r="S4" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T4" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="U4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>42.67</v>
+        <v>42.1</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z4" t="n">
-        <v>10.44</v>
+        <v>12</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.67</v>
+        <v>7.3</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.78</v>
+        <v>4.7</v>
       </c>
       <c r="AC4" t="n">
-        <v>20.56</v>
+        <v>20.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AF4" t="n">
         <v>0.18</v>
@@ -2356,70 +2356,70 @@
         <v>2.91</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="BH4" t="n">
-        <v>10.15</v>
+        <v>10.24</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BL4" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.45</v>
+        <v>0.52</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BP4" t="n">
-        <v>5.25</v>
+        <v>5.19</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.85</v>
+        <v>5</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
       </c>
       <c r="BS4" t="n">
-        <v>85</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT4" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BU4" t="n">
-        <v>35</v>
+        <v>38.1</v>
       </c>
       <c r="BV4" t="n">
-        <v>10</v>
+        <v>14.29</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>70</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BY4" t="n">
-        <v>4.46</v>
+        <v>4.32</v>
       </c>
       <c r="BZ4" t="n">
-        <v>5.11</v>
+        <v>4.9</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="CB4" t="n">
-        <v>4.42</v>
+        <v>4.37</v>
       </c>
       <c r="CC4" t="n">
         <v>6.78</v>
@@ -2434,25 +2434,25 @@
         <v>2.67</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.03</v>
+        <v>3.01</v>
       </c>
       <c r="CH4" t="n">
         <v>1.45</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="CM4" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CN4" t="n">
         <v>1.57</v>
@@ -2470,19 +2470,19 @@
         <v>1.38</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="CT4" t="n">
         <v>3.05</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CX4" t="n">
         <v>1.68</v>
@@ -2506,79 +2506,79 @@
         <v>3.18</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="DG4" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="DH4" t="n">
-        <v>107.75</v>
+        <v>107.33</v>
       </c>
       <c r="DI4" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="DK4" t="n">
-        <v>3.5</v>
+        <v>3.67</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DM4" t="n">
-        <v>60.15</v>
+        <v>61.28</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="DP4" t="n">
-        <v>12.65</v>
+        <v>12.29</v>
       </c>
       <c r="DQ4" t="n">
         <v>11.05</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.4</v>
+        <v>8.24</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>40.75</v>
+        <v>40.57</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DX4" t="n">
-        <v>9.65</v>
+        <v>10.43</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.5</v>
+        <v>6.81</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.15</v>
+        <v>3.62</v>
       </c>
       <c r="EA4" t="n">
-        <v>21.2</v>
+        <v>20.95</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="5">
@@ -2588,94 +2588,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D5" t="n">
         <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="G5" t="n">
-        <v>3.6</v>
+        <v>3.36</v>
       </c>
       <c r="H5" t="n">
-        <v>120.2</v>
+        <v>118.36</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="K5" t="n">
-        <v>5.2</v>
+        <v>4.91</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="M5" t="n">
-        <v>66.8</v>
+        <v>65.55</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="O5" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="P5" t="n">
-        <v>11.7</v>
+        <v>12.09</v>
       </c>
       <c r="Q5" t="n">
-        <v>15.2</v>
+        <v>15.27</v>
       </c>
       <c r="R5" t="n">
-        <v>5.1</v>
+        <v>5.45</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="T5" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>61.2</v>
+        <v>60.36</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="Z5" t="n">
-        <v>16.5</v>
+        <v>15.82</v>
       </c>
       <c r="AA5" t="n">
-        <v>10.4</v>
+        <v>9.91</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.1</v>
+        <v>5.91</v>
       </c>
       <c r="AC5" t="n">
-        <v>23.4</v>
+        <v>22.36</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AF5" t="n">
         <v>0.1</v>
@@ -2759,70 +2759,70 @@
         <v>2.6</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.05</v>
+        <v>4.9</v>
       </c>
       <c r="BR5" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS5" t="n">
-        <v>85</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT5" t="n">
-        <v>45</v>
+        <v>42.86</v>
       </c>
       <c r="BU5" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BV5" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>40</v>
+        <v>38.1</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="CA5" t="n">
         <v>3.66</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.61</v>
+        <v>3.63</v>
       </c>
       <c r="CC5" t="n">
         <v>2.34</v>
@@ -2837,7 +2837,7 @@
         <v>2.92</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="CH5" t="n">
         <v>1.36</v>
@@ -2852,7 +2852,7 @@
         <v>1.69</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="CM5" t="n">
         <v>2.06</v>
@@ -2864,19 +2864,19 @@
         <v>1.31</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.61</v>
+        <v>3.6</v>
       </c>
       <c r="CR5" t="n">
         <v>1.44</v>
       </c>
       <c r="CS5" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="CU5" t="n">
         <v>1.36</v>
@@ -2900,88 +2900,88 @@
         <v>1.65</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="DC5" t="n">
         <v>2.13</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.79</v>
+        <v>3.77</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.2</v>
+        <v>3.09</v>
       </c>
       <c r="DH5" t="n">
-        <v>112</v>
+        <v>111.43</v>
       </c>
       <c r="DI5" t="n">
         <v>-0.05</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.55</v>
+        <v>5.38</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DM5" t="n">
-        <v>63.65</v>
+        <v>63.15</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.7</v>
+        <v>0.66</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="DP5" t="n">
-        <v>12.15</v>
+        <v>12.33</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15.1</v>
+        <v>15.14</v>
       </c>
       <c r="DR5" t="n">
-        <v>6.05</v>
+        <v>6.19</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>59.3</v>
+        <v>58.95</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX5" t="n">
-        <v>15.25</v>
+        <v>14.95</v>
       </c>
       <c r="DY5" t="n">
-        <v>10</v>
+        <v>9.76</v>
       </c>
       <c r="DZ5" t="n">
-        <v>5.25</v>
+        <v>5.19</v>
       </c>
       <c r="EA5" t="n">
-        <v>22.15</v>
+        <v>21.66</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6" t="n">
         <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E6" t="n">
         <v>0.3</v>
@@ -3081,139 +3081,139 @@
         <v>1.7</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG6" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AI6" t="n">
-        <v>104.8</v>
+        <v>110.64</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AL6" t="n">
-        <v>3.7</v>
+        <v>3.82</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AN6" t="n">
-        <v>54.9</v>
+        <v>59.27</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AQ6" t="n">
-        <v>11.6</v>
+        <v>11</v>
       </c>
       <c r="AR6" t="n">
-        <v>11.7</v>
+        <v>11.45</v>
       </c>
       <c r="AS6" t="n">
-        <v>10.1</v>
+        <v>9.73</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>46.9</v>
+        <v>48.36</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>9</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.6</v>
+        <v>5.91</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BD6" t="n">
-        <v>22.9</v>
+        <v>23.36</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.6</v>
+        <v>2.71</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.85</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.6</v>
+        <v>2.71</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.5</v>
+        <v>4.48</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.8</v>
+        <v>4.95</v>
       </c>
       <c r="BR6" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS6" t="n">
-        <v>80</v>
+        <v>80.95</v>
       </c>
       <c r="BT6" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BU6" t="n">
-        <v>15</v>
+        <v>19.05</v>
       </c>
       <c r="BV6" t="n">
-        <v>5</v>
+        <v>9.52</v>
       </c>
       <c r="BW6" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX6" t="n">
-        <v>70</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BY6" t="n">
         <v>2.6</v>
@@ -3228,16 +3228,16 @@
         <v>3.41</v>
       </c>
       <c r="CC6" t="n">
-        <v>3.99</v>
+        <v>3.84</v>
       </c>
       <c r="CD6" t="n">
-        <v>4.38</v>
+        <v>4.2</v>
       </c>
       <c r="CE6" t="n">
         <v>1.41</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="CG6" t="n">
         <v>2.75</v>
@@ -3246,16 +3246,16 @@
         <v>1.37</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CK6" t="n">
         <v>1.75</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CM6" t="n">
         <v>1.99</v>
@@ -3267,28 +3267,28 @@
         <v>1.32</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.51</v>
+        <v>3.5</v>
       </c>
       <c r="CR6" t="n">
         <v>1.43</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="CX6" t="n">
         <v>1.78</v>
@@ -3306,85 +3306,85 @@
         <v>1.35</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.74</v>
+        <v>3.71</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="DH6" t="n">
-        <v>105.15</v>
+        <v>108.19</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="DJ6" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="DK6" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="DM6" t="n">
-        <v>56.4</v>
+        <v>58.62</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="DO6" t="n">
         <v>2</v>
       </c>
       <c r="DP6" t="n">
-        <v>11.15</v>
+        <v>10.86</v>
       </c>
       <c r="DQ6" t="n">
-        <v>11.8</v>
+        <v>11.66</v>
       </c>
       <c r="DR6" t="n">
-        <v>10.15</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="DS6" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="DT6" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>48.9</v>
+        <v>49.57</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>10.4</v>
+        <v>10.52</v>
       </c>
       <c r="DY6" t="n">
-        <v>6.85</v>
+        <v>6.95</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.55</v>
+        <v>3.57</v>
       </c>
       <c r="EA6" t="n">
-        <v>22.05</v>
+        <v>22.33</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="7">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D7" t="n">
         <v>10</v>
@@ -3406,82 +3406,82 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="G7" t="n">
-        <v>2.6</v>
+        <v>2.36</v>
       </c>
       <c r="H7" t="n">
-        <v>107.2</v>
+        <v>104.09</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J7" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="K7" t="n">
-        <v>4</v>
+        <v>3.82</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="M7" t="n">
-        <v>60.2</v>
+        <v>57.91</v>
       </c>
       <c r="N7" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="O7" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="P7" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="Q7" t="n">
-        <v>13.5</v>
+        <v>13.09</v>
       </c>
       <c r="R7" t="n">
-        <v>7</v>
+        <v>7.55</v>
       </c>
       <c r="S7" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="T7" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>51.9</v>
+        <v>50.27</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>10.7</v>
+        <v>10.64</v>
       </c>
       <c r="AA7" t="n">
-        <v>6.7</v>
+        <v>6.36</v>
       </c>
       <c r="AB7" t="n">
-        <v>4</v>
+        <v>4.27</v>
       </c>
       <c r="AC7" t="n">
-        <v>23.2</v>
+        <v>22.55</v>
       </c>
       <c r="AD7" t="n">
         <v>1.4</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AF7" t="n">
         <v>0.4</v>
@@ -3565,70 +3565,70 @@
         <v>1.9</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="BH7" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BL7" t="n">
         <v>0.95</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.2</v>
+        <v>5.19</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BT7" t="n">
-        <v>45</v>
+        <v>47.62</v>
       </c>
       <c r="BU7" t="n">
-        <v>25</v>
+        <v>23.81</v>
       </c>
       <c r="BV7" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW7" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX7" t="n">
-        <v>80</v>
+        <v>76.19</v>
       </c>
       <c r="BY7" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="BZ7" t="n">
         <v>3.06</v>
       </c>
-      <c r="BZ7" t="n">
-        <v>3.14</v>
-      </c>
       <c r="CA7" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.64</v>
+        <v>3.61</v>
       </c>
       <c r="CC7" t="n">
         <v>4.55</v>
@@ -3640,16 +3640,16 @@
         <v>1.37</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.79</v>
+        <v>2.81</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="CH7" t="n">
         <v>1.4</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CJ7" t="n">
         <v>1.81</v>
@@ -3658,7 +3658,7 @@
         <v>1.58</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CM7" t="n">
         <v>2.21</v>
@@ -3670,10 +3670,10 @@
         <v>1.27</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.26</v>
+        <v>3.28</v>
       </c>
       <c r="CR7" t="n">
         <v>1.39</v>
@@ -3712,82 +3712,82 @@
         <v>2.01</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.46</v>
+        <v>3.48</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="DH7" t="n">
-        <v>110.4</v>
+        <v>108.62</v>
       </c>
       <c r="DI7" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.55</v>
+        <v>4.43</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DM7" t="n">
-        <v>61.55</v>
+        <v>60.29</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="DP7" t="n">
-        <v>15.1</v>
+        <v>15.05</v>
       </c>
       <c r="DQ7" t="n">
-        <v>12.1</v>
+        <v>11.95</v>
       </c>
       <c r="DR7" t="n">
-        <v>7.1</v>
+        <v>7.38</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>51.8</v>
+        <v>50.95</v>
       </c>
       <c r="DW7" t="n">
         <v>0.1</v>
       </c>
       <c r="DX7" t="n">
-        <v>11</v>
+        <v>10.95</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.35</v>
+        <v>7.14</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.65</v>
+        <v>3.81</v>
       </c>
       <c r="EA7" t="n">
-        <v>21.75</v>
+        <v>21.48</v>
       </c>
       <c r="EB7" t="n">
         <v>1.4</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="8">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C10" t="n">
         <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E10" t="n">
         <v>0.3</v>
@@ -4693,139 +4693,139 @@
         <v>2</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AI10" t="n">
-        <v>105.2</v>
+        <v>107.09</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="AL10" t="n">
-        <v>3.1</v>
+        <v>2.91</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AN10" t="n">
-        <v>48.4</v>
+        <v>49.45</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AQ10" t="n">
-        <v>15.4</v>
+        <v>15.36</v>
       </c>
       <c r="AR10" t="n">
-        <v>12.2</v>
+        <v>12.64</v>
       </c>
       <c r="AS10" t="n">
-        <v>8.800000000000001</v>
+        <v>8.82</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>45.8</v>
+        <v>46</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="BA10" t="n">
-        <v>9.800000000000001</v>
+        <v>10.09</v>
       </c>
       <c r="BB10" t="n">
-        <v>6.7</v>
+        <v>6.82</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.1</v>
+        <v>3.27</v>
       </c>
       <c r="BD10" t="n">
-        <v>18.8</v>
+        <v>18.82</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.1</v>
+        <v>2.27</v>
       </c>
       <c r="BG10" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="BH10" t="n">
-        <v>7.55</v>
+        <v>7.33</v>
       </c>
       <c r="BI10" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BL10" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.25</v>
+        <v>3.14</v>
       </c>
       <c r="BQ10" t="n">
-        <v>3.4</v>
+        <v>3.33</v>
       </c>
       <c r="BR10" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BS10" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BT10" t="n">
-        <v>65</v>
+        <v>61.9</v>
       </c>
       <c r="BU10" t="n">
-        <v>30</v>
+        <v>28.57</v>
       </c>
       <c r="BV10" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BW10" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX10" t="n">
-        <v>75</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BY10" t="n">
         <v>2.66</v>
@@ -4834,40 +4834,40 @@
         <v>2.88</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.41</v>
+        <v>3.43</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.48</v>
+        <v>3.51</v>
       </c>
       <c r="CC10" t="n">
-        <v>4.48</v>
+        <v>4.55</v>
       </c>
       <c r="CD10" t="n">
-        <v>4.92</v>
+        <v>5.14</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CF10" t="n">
         <v>2.85</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="CH10" t="n">
         <v>1.39</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CK10" t="n">
         <v>1.72</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="CM10" t="n">
         <v>2.02</v>
@@ -4891,22 +4891,22 @@
         <v>3.02</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="CU10" t="n">
         <v>1.39</v>
       </c>
       <c r="CV10" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CX10" t="n">
         <v>1.74</v>
       </c>
       <c r="CY10" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CZ10" t="n">
         <v>2.01</v>
@@ -4924,46 +4924,46 @@
         <v>3.55</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="DH10" t="n">
-        <v>111.6</v>
+        <v>112.29</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="DK10" t="n">
-        <v>3.65</v>
+        <v>3.52</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DM10" t="n">
-        <v>55.85</v>
+        <v>56.05</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="DP10" t="n">
-        <v>14.5</v>
+        <v>14.52</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.55</v>
+        <v>12.76</v>
       </c>
       <c r="DR10" t="n">
-        <v>8.4</v>
+        <v>8.43</v>
       </c>
       <c r="DS10" t="n">
         <v>0.05</v>
@@ -4975,28 +4975,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>49.7</v>
+        <v>49.62</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.3</v>
+        <v>12.33</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.25</v>
+        <v>8.24</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.05</v>
+        <v>4.09</v>
       </c>
       <c r="EA10" t="n">
-        <v>22.3</v>
+        <v>22.14</v>
       </c>
       <c r="EB10" t="n">
         <v>1.48</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="11">

--- a/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" t="n">
         <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" t="n">
         <v>0.2</v>
@@ -1469,139 +1469,139 @@
         <v>2.2</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AH2" t="n">
-        <v>3.9</v>
+        <v>4.09</v>
       </c>
       <c r="AI2" t="n">
-        <v>118.9</v>
+        <v>119.36</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AL2" t="n">
-        <v>6.6</v>
+        <v>6.64</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="AN2" t="n">
-        <v>74.90000000000001</v>
+        <v>75.55</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AQ2" t="n">
-        <v>14.2</v>
+        <v>13.91</v>
       </c>
       <c r="AR2" t="n">
-        <v>14.3</v>
+        <v>13.91</v>
       </c>
       <c r="AS2" t="n">
-        <v>6</v>
+        <v>6.18</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AU2" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>55.1</v>
+        <v>54.64</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="BA2" t="n">
-        <v>16</v>
+        <v>15.64</v>
       </c>
       <c r="BB2" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.9</v>
+        <v>4.64</v>
       </c>
       <c r="BD2" t="n">
-        <v>23.8</v>
+        <v>24.18</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="BF2" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.75</v>
+        <v>9.81</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.55</v>
+        <v>4.48</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.15</v>
+        <v>5.29</v>
       </c>
       <c r="BR2" t="n">
-        <v>100</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS2" t="n">
-        <v>95</v>
+        <v>90.48</v>
       </c>
       <c r="BT2" t="n">
-        <v>65</v>
+        <v>61.9</v>
       </c>
       <c r="BU2" t="n">
-        <v>25</v>
+        <v>23.81</v>
       </c>
       <c r="BV2" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW2" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX2" t="n">
-        <v>55</v>
+        <v>52.38</v>
       </c>
       <c r="BY2" t="n">
         <v>1.28</v>
@@ -1610,73 +1610,73 @@
         <v>1.31</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.73</v>
+        <v>4.66</v>
       </c>
       <c r="CB2" t="n">
-        <v>5.1</v>
+        <v>5.01</v>
       </c>
       <c r="CC2" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="CK2" t="n">
         <v>1.57</v>
       </c>
-      <c r="CD2" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="CE2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="CF2" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="CG2" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="CH2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="CI2" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="CJ2" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="CK2" t="n">
-        <v>1.56</v>
-      </c>
       <c r="CL2" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.78</v>
+        <v>2.83</v>
       </c>
       <c r="CR2" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="CT2" t="n">
-        <v>3.07</v>
+        <v>3.04</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CW2" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CX2" t="n">
         <v>1.59</v>
@@ -1691,88 +1691,88 @@
         <v>1.77</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.25</v>
+        <v>3.38</v>
       </c>
       <c r="DH2" t="n">
-        <v>123.85</v>
+        <v>123.86</v>
       </c>
       <c r="DI2" t="n">
         <v>0.1</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="DK2" t="n">
-        <v>6.35</v>
+        <v>6.38</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.45</v>
+        <v>0.47</v>
       </c>
       <c r="DM2" t="n">
-        <v>75.25</v>
+        <v>75.56999999999999</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="DO2" t="n">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="DP2" t="n">
-        <v>12.75</v>
+        <v>12.67</v>
       </c>
       <c r="DQ2" t="n">
-        <v>13.55</v>
+        <v>13.38</v>
       </c>
       <c r="DR2" t="n">
-        <v>5.7</v>
+        <v>5.81</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>56.7</v>
+        <v>56.38</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX2" t="n">
-        <v>16.3</v>
+        <v>16.1</v>
       </c>
       <c r="DY2" t="n">
-        <v>10.45</v>
+        <v>10.43</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5.85</v>
+        <v>5.67</v>
       </c>
       <c r="EA2" t="n">
-        <v>23.3</v>
+        <v>23.52</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="3">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C8" t="n">
         <v>11</v>
       </c>
       <c r="D8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -3887,49 +3887,49 @@
         <v>2.09</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG8" t="n">
         <v>2</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AI8" t="n">
-        <v>103.56</v>
+        <v>105</v>
       </c>
       <c r="AJ8" t="n">
-        <v>-0.11</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="AL8" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AN8" t="n">
-        <v>55.22</v>
+        <v>56.1</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="AP8" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AQ8" t="n">
-        <v>15.89</v>
+        <v>15.6</v>
       </c>
       <c r="AR8" t="n">
-        <v>13.89</v>
+        <v>13.2</v>
       </c>
       <c r="AS8" t="n">
-        <v>8.779999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AU8" t="n">
         <v>1</v>
@@ -3944,82 +3944,82 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>49</v>
+        <v>48.8</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="BA8" t="n">
-        <v>12.56</v>
+        <v>12.2</v>
       </c>
       <c r="BB8" t="n">
-        <v>9.109999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.44</v>
+        <v>3.6</v>
       </c>
       <c r="BD8" t="n">
-        <v>22.22</v>
+        <v>22.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.949999999999999</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="BP8" t="n">
-        <v>5.05</v>
+        <v>4.95</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.85</v>
+        <v>4.86</v>
       </c>
       <c r="BR8" t="n">
-        <v>80</v>
+        <v>80.95</v>
       </c>
       <c r="BS8" t="n">
-        <v>70</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT8" t="n">
-        <v>40</v>
+        <v>42.86</v>
       </c>
       <c r="BU8" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BV8" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW8" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BX8" t="n">
-        <v>45</v>
+        <v>47.62</v>
       </c>
       <c r="BY8" t="n">
         <v>2.83</v>
@@ -4028,40 +4028,40 @@
         <v>2.85</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.49</v>
+        <v>3.45</v>
       </c>
       <c r="CC8" t="n">
-        <v>3.59</v>
+        <v>3.55</v>
       </c>
       <c r="CD8" t="n">
-        <v>4</v>
+        <v>3.96</v>
       </c>
       <c r="CE8" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="CH8" t="n">
         <v>1.38</v>
-      </c>
-      <c r="CF8" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="CG8" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="CH8" t="n">
-        <v>1.39</v>
       </c>
       <c r="CI8" t="n">
         <v>1.91</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CM8" t="n">
         <v>2.22</v>
@@ -4070,22 +4070,22 @@
         <v>1.75</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="CR8" t="n">
         <v>1.41</v>
       </c>
       <c r="CS8" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="CU8" t="n">
         <v>1.39</v>
@@ -4109,55 +4109,55 @@
         <v>1.75</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.51</v>
+        <v>3.54</v>
       </c>
       <c r="DE8" t="n">
         <v>0.05</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="DH8" t="n">
-        <v>111.65</v>
+        <v>111.95</v>
       </c>
       <c r="DI8" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.35</v>
+        <v>2.43</v>
       </c>
       <c r="DK8" t="n">
         <v>4.95</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="DM8" t="n">
-        <v>69.2</v>
+        <v>68.95</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="DP8" t="n">
-        <v>15.25</v>
+        <v>15.14</v>
       </c>
       <c r="DQ8" t="n">
-        <v>13.75</v>
+        <v>13.43</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.95</v>
+        <v>7.76</v>
       </c>
       <c r="DS8" t="n">
         <v>0</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>49.7</v>
+        <v>49.57</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DX8" t="n">
-        <v>12.6</v>
+        <v>12.43</v>
       </c>
       <c r="DY8" t="n">
-        <v>9.199999999999999</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.4</v>
+        <v>3.47</v>
       </c>
       <c r="EA8" t="n">
-        <v>22.2</v>
+        <v>22.33</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.15</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="9">
@@ -4200,94 +4200,94 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D9" t="n">
         <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="F9" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="H9" t="n">
-        <v>116.4</v>
+        <v>117</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="K9" t="n">
-        <v>6.4</v>
+        <v>6.18</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="M9" t="n">
-        <v>70.8</v>
+        <v>69.18000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="O9" t="n">
-        <v>3.4</v>
+        <v>3.27</v>
       </c>
       <c r="P9" t="n">
-        <v>12.7</v>
+        <v>12.45</v>
       </c>
       <c r="Q9" t="n">
-        <v>14.4</v>
+        <v>14.18</v>
       </c>
       <c r="R9" t="n">
-        <v>7.3</v>
+        <v>7.27</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="T9" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>52.1</v>
+        <v>51.91</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z9" t="n">
-        <v>16.1</v>
+        <v>14.82</v>
       </c>
       <c r="AA9" t="n">
-        <v>11.4</v>
+        <v>10.55</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.7</v>
+        <v>4.27</v>
       </c>
       <c r="AC9" t="n">
-        <v>24.9</v>
+        <v>24.27</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.86</v>
+        <v>1.74</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AF9" t="n">
         <v>0.2</v>
@@ -4371,70 +4371,70 @@
         <v>3.1</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.7</v>
+        <v>2.57</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.55</v>
+        <v>10.57</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.7</v>
+        <v>2.57</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="BP9" t="n">
-        <v>5.05</v>
+        <v>4.95</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.5</v>
+        <v>5.62</v>
       </c>
       <c r="BR9" t="n">
-        <v>90</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS9" t="n">
-        <v>75</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT9" t="n">
-        <v>50</v>
+        <v>47.62</v>
       </c>
       <c r="BU9" t="n">
-        <v>35</v>
+        <v>33.33</v>
       </c>
       <c r="BV9" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BW9" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX9" t="n">
-        <v>60</v>
+        <v>57.14</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.01</v>
+        <v>2.14</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.5</v>
+        <v>3.49</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.63</v>
+        <v>3.61</v>
       </c>
       <c r="CC9" t="n">
         <v>2.77</v>
@@ -4458,13 +4458,13 @@
         <v>1.77</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="CM9" t="n">
         <v>1.97</v>
@@ -4479,13 +4479,13 @@
         <v>2.02</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.51</v>
+        <v>3.52</v>
       </c>
       <c r="CR9" t="n">
         <v>1.43</v>
       </c>
       <c r="CS9" t="n">
-        <v>3.08</v>
+        <v>3.09</v>
       </c>
       <c r="CT9" t="n">
         <v>2.84</v>
@@ -4494,10 +4494,10 @@
         <v>1.38</v>
       </c>
       <c r="CV9" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CX9" t="n">
         <v>1.72</v>
@@ -4521,79 +4521,79 @@
         <v>3.75</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="DG9" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="DH9" t="n">
-        <v>112.15</v>
+        <v>112.67</v>
       </c>
       <c r="DI9" t="n">
         <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.85</v>
+        <v>2.71</v>
       </c>
       <c r="DK9" t="n">
-        <v>6.3</v>
+        <v>6.19</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="DM9" t="n">
-        <v>65.25</v>
+        <v>64.67</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="DO9" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="DP9" t="n">
-        <v>12.7</v>
+        <v>12.57</v>
       </c>
       <c r="DQ9" t="n">
-        <v>13.95</v>
+        <v>13.86</v>
       </c>
       <c r="DR9" t="n">
-        <v>7.25</v>
+        <v>7.24</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>51.9</v>
+        <v>51.81</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX9" t="n">
-        <v>15.35</v>
+        <v>14.72</v>
       </c>
       <c r="DY9" t="n">
-        <v>11.35</v>
+        <v>10.91</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4</v>
+        <v>3.81</v>
       </c>
       <c r="EA9" t="n">
-        <v>23.65</v>
+        <v>23.38</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.65</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="10">
@@ -5006,94 +5006,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D11" t="n">
         <v>11</v>
       </c>
       <c r="E11" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="F11" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="G11" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="H11" t="n">
-        <v>111.44</v>
+        <v>112.9</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="K11" t="n">
-        <v>4.44</v>
+        <v>4.3</v>
       </c>
       <c r="L11" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="M11" t="n">
-        <v>58.22</v>
+        <v>57.9</v>
       </c>
       <c r="N11" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="O11" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="P11" t="n">
-        <v>12.78</v>
+        <v>12.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>12.33</v>
+        <v>12.5</v>
       </c>
       <c r="R11" t="n">
-        <v>8.220000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="S11" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T11" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="U11" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="V11" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>47</v>
+        <v>47.6</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z11" t="n">
-        <v>14.67</v>
+        <v>14.2</v>
       </c>
       <c r="AA11" t="n">
-        <v>10.22</v>
+        <v>9.9</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.44</v>
+        <v>4.3</v>
       </c>
       <c r="AC11" t="n">
-        <v>21</v>
+        <v>20.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AE11" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AF11" t="n">
         <v>0.09</v>
@@ -5177,70 +5177,70 @@
         <v>2.27</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.800000000000001</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.75</v>
+        <v>4.76</v>
       </c>
       <c r="BR11" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BS11" t="n">
-        <v>75</v>
+        <v>76.19</v>
       </c>
       <c r="BT11" t="n">
-        <v>50</v>
+        <v>52.38</v>
       </c>
       <c r="BU11" t="n">
-        <v>35</v>
+        <v>33.33</v>
       </c>
       <c r="BV11" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BW11" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX11" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="BZ11" t="n">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.35</v>
+        <v>3.33</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.39</v>
+        <v>3.36</v>
       </c>
       <c r="CC11" t="n">
         <v>3.86</v>
@@ -5255,7 +5255,7 @@
         <v>3.02</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="CH11" t="n">
         <v>1.34</v>
@@ -5267,13 +5267,13 @@
         <v>1.92</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="CM11" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CN11" t="n">
         <v>1.6</v>
@@ -5285,121 +5285,121 @@
         <v>2.09</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.66</v>
+        <v>3.63</v>
       </c>
       <c r="CR11" t="n">
         <v>1.45</v>
       </c>
       <c r="CS11" t="n">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="CT11" t="n">
         <v>2.76</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CZ11" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="DB11" t="n">
         <v>1.37</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.88</v>
+        <v>3.89</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="DG11" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="DH11" t="n">
-        <v>100.05</v>
+        <v>101.29</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.25</v>
+        <v>4.19</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="DM11" t="n">
-        <v>50.55</v>
+        <v>50.76</v>
       </c>
       <c r="DN11" t="n">
         <v>1.1</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="DP11" t="n">
-        <v>12.85</v>
+        <v>12.57</v>
       </c>
       <c r="DQ11" t="n">
-        <v>12.4</v>
+        <v>12.47</v>
       </c>
       <c r="DR11" t="n">
-        <v>8.1</v>
+        <v>7.95</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>44.55</v>
+        <v>44.95</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DX11" t="n">
-        <v>12.05</v>
+        <v>11.95</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.199999999999999</v>
+        <v>8.15</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.85</v>
+        <v>3.81</v>
       </c>
       <c r="EA11" t="n">
-        <v>19.7</v>
+        <v>19.57</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.15</v>
+        <v>2.24</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
@@ -1379,61 +1379,61 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
         <v>11</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="G2" t="n">
-        <v>2.6</v>
+        <v>2.82</v>
       </c>
       <c r="H2" t="n">
-        <v>128.8</v>
+        <v>123.91</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="J2" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="K2" t="n">
-        <v>6.1</v>
+        <v>6.36</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="M2" t="n">
-        <v>75.59999999999999</v>
+        <v>75.36</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="O2" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P2" t="n">
-        <v>11.3</v>
+        <v>11.36</v>
       </c>
       <c r="Q2" t="n">
-        <v>12.8</v>
+        <v>12.73</v>
       </c>
       <c r="R2" t="n">
-        <v>5.4</v>
+        <v>5.36</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="T2" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -1445,28 +1445,28 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>58.3</v>
+        <v>58.27</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z2" t="n">
-        <v>16.6</v>
+        <v>17</v>
       </c>
       <c r="AA2" t="n">
-        <v>9.800000000000001</v>
+        <v>10.18</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.8</v>
+        <v>6.82</v>
       </c>
       <c r="AC2" t="n">
-        <v>22.8</v>
+        <v>22.36</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AF2" t="n">
         <v>0.09</v>
@@ -1550,70 +1550,70 @@
         <v>1.91</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.81</v>
+        <v>9.91</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.86</v>
+        <v>0.95</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="BO2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>95.45</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>90.91</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>63.64</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>27.27</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>9.09</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>50</v>
+      </c>
+      <c r="BY2" t="n">
         <v>1.29</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>4.48</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>5.29</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>95.23999999999999</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>90.48</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>61.9</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>23.81</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>9.52</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>4.76</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>52.38</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>1.28</v>
       </c>
       <c r="BZ2" t="n">
         <v>1.31</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.66</v>
+        <v>4.67</v>
       </c>
       <c r="CB2" t="n">
-        <v>5.01</v>
+        <v>5.06</v>
       </c>
       <c r="CC2" t="n">
         <v>1.63</v>
@@ -1628,7 +1628,7 @@
         <v>2.49</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.21</v>
+        <v>3.22</v>
       </c>
       <c r="CH2" t="n">
         <v>1.49</v>
@@ -1637,13 +1637,13 @@
         <v>1.79</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CK2" t="n">
         <v>1.57</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CM2" t="n">
         <v>2.23</v>
@@ -1658,19 +1658,19 @@
         <v>1.74</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="CR2" t="n">
         <v>1.38</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.59</v>
+        <v>2.57</v>
       </c>
       <c r="CT2" t="n">
         <v>3.04</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CV2" t="n">
         <v>1.84</v>
@@ -1694,52 +1694,52 @@
         <v>1.24</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.38</v>
+        <v>3.45</v>
       </c>
       <c r="DH2" t="n">
-        <v>123.86</v>
+        <v>121.64</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="DK2" t="n">
-        <v>6.38</v>
+        <v>6.5</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="DM2" t="n">
-        <v>75.56999999999999</v>
+        <v>75.45999999999999</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="DP2" t="n">
-        <v>12.67</v>
+        <v>12.63</v>
       </c>
       <c r="DQ2" t="n">
-        <v>13.38</v>
+        <v>13.32</v>
       </c>
       <c r="DR2" t="n">
-        <v>5.81</v>
+        <v>5.77</v>
       </c>
       <c r="DS2" t="n">
         <v>0.09</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>56.38</v>
+        <v>56.46</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX2" t="n">
-        <v>16.1</v>
+        <v>16.32</v>
       </c>
       <c r="DY2" t="n">
-        <v>10.43</v>
+        <v>10.59</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5.67</v>
+        <v>5.73</v>
       </c>
       <c r="EA2" t="n">
-        <v>23.52</v>
+        <v>23.27</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6" t="n">
         <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
         <v>0.3</v>
@@ -3081,139 +3081,139 @@
         <v>1.7</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>110.64</v>
+        <v>106.58</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AK6" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AL6" t="n">
-        <v>3.82</v>
+        <v>3.75</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AN6" t="n">
-        <v>59.27</v>
+        <v>57.58</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ6" t="n">
-        <v>11</v>
+        <v>10.83</v>
       </c>
       <c r="AR6" t="n">
-        <v>11.45</v>
+        <v>11.58</v>
       </c>
       <c r="AS6" t="n">
-        <v>9.73</v>
+        <v>9.83</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.45</v>
+        <v>1.67</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>48.36</v>
+        <v>47.83</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>9.359999999999999</v>
+        <v>8.83</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.91</v>
+        <v>5.58</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="BD6" t="n">
-        <v>23.36</v>
+        <v>23.08</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="BF6" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.71</v>
+        <v>2.77</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.949999999999999</v>
+        <v>10.05</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.71</v>
+        <v>2.77</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.71</v>
+        <v>0.82</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.48</v>
+        <v>4.59</v>
       </c>
       <c r="BQ6" t="n">
         <v>4.95</v>
       </c>
       <c r="BR6" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS6" t="n">
-        <v>80.95</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT6" t="n">
-        <v>61.9</v>
+        <v>63.64</v>
       </c>
       <c r="BU6" t="n">
-        <v>19.05</v>
+        <v>22.73</v>
       </c>
       <c r="BV6" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BW6" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX6" t="n">
-        <v>71.43000000000001</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BY6" t="n">
         <v>2.6</v>
@@ -3222,25 +3222,25 @@
         <v>2.72</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.41</v>
+        <v>3.54</v>
       </c>
       <c r="CC6" t="n">
-        <v>3.84</v>
+        <v>4.1</v>
       </c>
       <c r="CD6" t="n">
-        <v>4.2</v>
+        <v>4.75</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.89</v>
+        <v>2.86</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="CH6" t="n">
         <v>1.37</v>
@@ -3249,46 +3249,46 @@
         <v>1.83</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CL6" t="n">
         <v>2.38</v>
       </c>
       <c r="CM6" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CO6" t="n">
         <v>1.32</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.5</v>
+        <v>3.46</v>
       </c>
       <c r="CR6" t="n">
         <v>1.43</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="CT6" t="n">
         <v>2.84</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CV6" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="CW6" t="n">
         <v>1.91</v>
-      </c>
-      <c r="CW6" t="n">
-        <v>1.9</v>
       </c>
       <c r="CX6" t="n">
         <v>1.78</v>
@@ -3303,88 +3303,88 @@
         <v>1.58</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.71</v>
+        <v>3.66</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="DH6" t="n">
-        <v>108.19</v>
+        <v>106.09</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ6" t="n">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="DK6" t="n">
-        <v>3.95</v>
+        <v>3.91</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="DM6" t="n">
-        <v>58.62</v>
+        <v>57.73</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="DO6" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="DP6" t="n">
-        <v>10.86</v>
+        <v>10.77</v>
       </c>
       <c r="DQ6" t="n">
-        <v>11.66</v>
+        <v>11.73</v>
       </c>
       <c r="DR6" t="n">
-        <v>9.949999999999999</v>
+        <v>10</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>49.57</v>
+        <v>49.23</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>10.52</v>
+        <v>10.18</v>
       </c>
       <c r="DY6" t="n">
-        <v>6.95</v>
+        <v>6.73</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.57</v>
+        <v>3.45</v>
       </c>
       <c r="EA6" t="n">
-        <v>22.33</v>
+        <v>22.23</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="7">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" t="n">
         <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3484,139 +3484,139 @@
         <v>2.27</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AH7" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>112.09</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>60.18</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>14.91</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>10.64</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>52</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>10.55</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="BC7" t="n">
         <v>3</v>
       </c>
-      <c r="AI7" t="n">
-        <v>113.6</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>62.9</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>51.7</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>3.3</v>
-      </c>
       <c r="BD7" t="n">
-        <v>20.3</v>
+        <v>20.73</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.76</v>
+        <v>2.73</v>
       </c>
       <c r="BH7" t="n">
-        <v>9.1</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.76</v>
+        <v>2.73</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BL7" t="n">
         <v>0.95</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.9</v>
+        <v>3.86</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.19</v>
+        <v>5</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BT7" t="n">
-        <v>47.62</v>
+        <v>45.45</v>
       </c>
       <c r="BU7" t="n">
-        <v>23.81</v>
+        <v>22.73</v>
       </c>
       <c r="BV7" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BW7" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX7" t="n">
-        <v>76.19</v>
+        <v>72.73</v>
       </c>
       <c r="BY7" t="n">
         <v>2.97</v>
@@ -3625,31 +3625,31 @@
         <v>3.06</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.58</v>
+        <v>3.56</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.61</v>
+        <v>3.59</v>
       </c>
       <c r="CC7" t="n">
-        <v>4.55</v>
+        <v>4.39</v>
       </c>
       <c r="CD7" t="n">
-        <v>4.85</v>
+        <v>4.67</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CF7" t="n">
         <v>2.81</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="CH7" t="n">
         <v>1.4</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CJ7" t="n">
         <v>1.81</v>
@@ -3661,10 +3661,10 @@
         <v>2.12</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CO7" t="n">
         <v>1.27</v>
@@ -3688,22 +3688,22 @@
         <v>1.41</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CX7" t="n">
         <v>1.6</v>
       </c>
       <c r="CY7" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="DB7" t="n">
         <v>1.31</v>
@@ -3712,82 +3712,82 @@
         <v>2.01</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.48</v>
+        <v>3.47</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.66</v>
+        <v>2.54</v>
       </c>
       <c r="DH7" t="n">
-        <v>108.62</v>
+        <v>108.09</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.43</v>
+        <v>4.32</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.19</v>
+        <v>0.22</v>
       </c>
       <c r="DM7" t="n">
-        <v>60.29</v>
+        <v>59.04</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="DP7" t="n">
-        <v>15.05</v>
+        <v>14.96</v>
       </c>
       <c r="DQ7" t="n">
-        <v>11.95</v>
+        <v>11.87</v>
       </c>
       <c r="DR7" t="n">
-        <v>7.38</v>
+        <v>7.23</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>50.95</v>
+        <v>51.14</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX7" t="n">
-        <v>10.95</v>
+        <v>10.6</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.14</v>
+        <v>6.95</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.81</v>
+        <v>3.64</v>
       </c>
       <c r="EA7" t="n">
-        <v>21.48</v>
+        <v>21.64</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="8">
@@ -4200,94 +4200,94 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D9" t="n">
         <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="F9" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="G9" t="n">
-        <v>2.91</v>
+        <v>3.17</v>
       </c>
       <c r="H9" t="n">
-        <v>117</v>
+        <v>116.92</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="K9" t="n">
-        <v>6.18</v>
+        <v>6.5</v>
       </c>
       <c r="L9" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="M9" t="n">
-        <v>69.18000000000001</v>
+        <v>69.83</v>
       </c>
       <c r="N9" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="O9" t="n">
-        <v>3.27</v>
+        <v>3.33</v>
       </c>
       <c r="P9" t="n">
-        <v>12.45</v>
+        <v>12.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>14.18</v>
+        <v>13.67</v>
       </c>
       <c r="R9" t="n">
-        <v>7.27</v>
+        <v>7.25</v>
       </c>
       <c r="S9" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="T9" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="U9" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="V9" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>51.91</v>
+        <v>52.08</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z9" t="n">
-        <v>14.82</v>
+        <v>15.75</v>
       </c>
       <c r="AA9" t="n">
-        <v>10.55</v>
+        <v>11.08</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.27</v>
+        <v>4.67</v>
       </c>
       <c r="AC9" t="n">
-        <v>24.27</v>
+        <v>23.83</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="AE9" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AF9" t="n">
         <v>0.2</v>
@@ -4371,70 +4371,70 @@
         <v>3.1</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.57</v>
+        <v>2.64</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.57</v>
+        <v>10.68</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.57</v>
+        <v>2.64</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.86</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.95</v>
+        <v>4.91</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.62</v>
+        <v>5.77</v>
       </c>
       <c r="BR9" t="n">
-        <v>85.70999999999999</v>
+        <v>86.36</v>
       </c>
       <c r="BS9" t="n">
-        <v>71.43000000000001</v>
+        <v>72.73</v>
       </c>
       <c r="BT9" t="n">
-        <v>47.62</v>
+        <v>50</v>
       </c>
       <c r="BU9" t="n">
-        <v>33.33</v>
+        <v>36.36</v>
       </c>
       <c r="BV9" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BW9" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX9" t="n">
-        <v>57.14</v>
+        <v>59.09</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.49</v>
+        <v>3.48</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.61</v>
+        <v>3.62</v>
       </c>
       <c r="CC9" t="n">
         <v>2.77</v>
@@ -4446,34 +4446,34 @@
         <v>1.4</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.91</v>
+        <v>2.93</v>
       </c>
       <c r="CG9" t="n">
         <v>2.73</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CK9" t="n">
         <v>1.61</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CM9" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CP9" t="n">
         <v>2.02</v>
@@ -4500,16 +4500,16 @@
         <v>1.98</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CY9" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="DB9" t="n">
         <v>1.35</v>
@@ -4521,79 +4521,79 @@
         <v>3.75</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="DG9" t="n">
-        <v>3.05</v>
+        <v>3.18</v>
       </c>
       <c r="DH9" t="n">
-        <v>112.67</v>
+        <v>112.82</v>
       </c>
       <c r="DI9" t="n">
         <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="DK9" t="n">
-        <v>6.19</v>
+        <v>6.36</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="DM9" t="n">
-        <v>64.67</v>
+        <v>65.23</v>
       </c>
       <c r="DN9" t="n">
         <v>0.86</v>
       </c>
       <c r="DO9" t="n">
-        <v>3.14</v>
+        <v>3.18</v>
       </c>
       <c r="DP9" t="n">
-        <v>12.57</v>
+        <v>12.59</v>
       </c>
       <c r="DQ9" t="n">
-        <v>13.86</v>
+        <v>13.59</v>
       </c>
       <c r="DR9" t="n">
-        <v>7.24</v>
+        <v>7.23</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>51.81</v>
+        <v>51.91</v>
       </c>
       <c r="DW9" t="n">
         <v>0.09</v>
       </c>
       <c r="DX9" t="n">
-        <v>14.72</v>
+        <v>15.23</v>
       </c>
       <c r="DY9" t="n">
-        <v>10.91</v>
+        <v>11.18</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3.81</v>
+        <v>4.05</v>
       </c>
       <c r="EA9" t="n">
-        <v>23.38</v>
+        <v>23.18</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="10">
@@ -4603,94 +4603,94 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D10" t="n">
         <v>11</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="G10" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="H10" t="n">
-        <v>118</v>
+        <v>116.91</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="K10" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="M10" t="n">
-        <v>63.3</v>
+        <v>61.45</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
       </c>
       <c r="P10" t="n">
-        <v>13.6</v>
+        <v>13.27</v>
       </c>
       <c r="Q10" t="n">
-        <v>12.9</v>
+        <v>13.18</v>
       </c>
       <c r="R10" t="n">
-        <v>8</v>
+        <v>8.09</v>
       </c>
       <c r="S10" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="T10" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>53.6</v>
+        <v>52.82</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="Z10" t="n">
-        <v>14.8</v>
+        <v>14.45</v>
       </c>
       <c r="AA10" t="n">
-        <v>9.800000000000001</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="AB10" t="n">
         <v>5</v>
       </c>
       <c r="AC10" t="n">
-        <v>25.8</v>
+        <v>25.27</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AE10" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AF10" t="n">
         <v>0.09</v>
@@ -4774,70 +4774,70 @@
         <v>2.27</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.95</v>
+        <v>2.91</v>
       </c>
       <c r="BH10" t="n">
-        <v>7.33</v>
+        <v>7.18</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.95</v>
+        <v>2.91</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="BL10" t="n">
         <v>1.05</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="BP10" t="n">
         <v>3.14</v>
       </c>
       <c r="BQ10" t="n">
-        <v>3.33</v>
+        <v>3.23</v>
       </c>
       <c r="BR10" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BS10" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BT10" t="n">
-        <v>61.9</v>
+        <v>59.09</v>
       </c>
       <c r="BU10" t="n">
-        <v>28.57</v>
+        <v>27.27</v>
       </c>
       <c r="BV10" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BW10" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX10" t="n">
-        <v>71.43000000000001</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="BZ10" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.43</v>
+        <v>3.42</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.51</v>
+        <v>3.49</v>
       </c>
       <c r="CC10" t="n">
         <v>4.55</v>
@@ -4849,16 +4849,16 @@
         <v>1.38</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="CH10" t="n">
         <v>1.39</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CJ10" t="n">
         <v>1.84</v>
@@ -4867,7 +4867,7 @@
         <v>1.72</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CM10" t="n">
         <v>2.02</v>
@@ -4876,19 +4876,19 @@
         <v>1.61</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CP10" t="n">
         <v>1.96</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="CR10" t="n">
         <v>1.41</v>
       </c>
       <c r="CS10" t="n">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="CT10" t="n">
         <v>2.9</v>
@@ -4897,10 +4897,10 @@
         <v>1.39</v>
       </c>
       <c r="CV10" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CX10" t="n">
         <v>1.74</v>
@@ -4909,7 +4909,7 @@
         <v>2.19</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="DA10" t="n">
         <v>1.61</v>
@@ -4918,85 +4918,85 @@
         <v>1.32</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.55</v>
+        <v>3.54</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="DH10" t="n">
-        <v>112.29</v>
+        <v>112</v>
       </c>
       <c r="DI10" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.57</v>
+        <v>2.46</v>
       </c>
       <c r="DK10" t="n">
-        <v>3.52</v>
+        <v>3.46</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DM10" t="n">
-        <v>56.05</v>
+        <v>55.45</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="DO10" t="n">
         <v>1.14</v>
       </c>
       <c r="DP10" t="n">
-        <v>14.52</v>
+        <v>14.31</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.76</v>
+        <v>12.91</v>
       </c>
       <c r="DR10" t="n">
-        <v>8.43</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>49.62</v>
+        <v>49.41</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.33</v>
+        <v>12.27</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.24</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.09</v>
+        <v>4.14</v>
       </c>
       <c r="EA10" t="n">
-        <v>22.14</v>
+        <v>22.04</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="11">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C11" t="n">
         <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E11" t="n">
         <v>0.3</v>
@@ -5096,139 +5096,139 @@
         <v>2.2</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG11" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AI11" t="n">
-        <v>90.73</v>
+        <v>90.42</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="AL11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>45.25</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>12.58</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>12.58</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>42.83</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>10.58</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>9.859999999999999</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BP11" t="n">
         <v>4.09</v>
       </c>
-      <c r="AM11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>44.27</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>12.91</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>12.45</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>8</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>42.55</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>9.91</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>18.64</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>9.710000000000001</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BQ11" t="n">
-        <v>4.76</v>
+        <v>4.95</v>
       </c>
       <c r="BR11" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BS11" t="n">
-        <v>76.19</v>
+        <v>77.27</v>
       </c>
       <c r="BT11" t="n">
-        <v>52.38</v>
+        <v>54.55</v>
       </c>
       <c r="BU11" t="n">
-        <v>33.33</v>
+        <v>36.36</v>
       </c>
       <c r="BV11" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BW11" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX11" t="n">
-        <v>61.9</v>
+        <v>63.64</v>
       </c>
       <c r="BY11" t="n">
         <v>2.83</v>
@@ -5240,13 +5240,13 @@
         <v>3.33</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.36</v>
+        <v>3.38</v>
       </c>
       <c r="CC11" t="n">
-        <v>3.86</v>
+        <v>3.9</v>
       </c>
       <c r="CD11" t="n">
-        <v>4.16</v>
+        <v>4.28</v>
       </c>
       <c r="CE11" t="n">
         <v>1.43</v>
@@ -5267,16 +5267,16 @@
         <v>1.92</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="CM11" t="n">
         <v>2.01</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CO11" t="n">
         <v>1.33</v>
@@ -5291,25 +5291,25 @@
         <v>1.45</v>
       </c>
       <c r="CS11" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="CT11" t="n">
         <v>2.76</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CX11" t="n">
         <v>1.76</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CZ11" t="n">
         <v>1.99</v>
@@ -5321,85 +5321,85 @@
         <v>1.37</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.89</v>
+        <v>3.88</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="DG11" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="DH11" t="n">
-        <v>101.29</v>
+        <v>100.64</v>
       </c>
       <c r="DI11" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.19</v>
+        <v>4.14</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="DM11" t="n">
-        <v>50.76</v>
+        <v>51</v>
       </c>
       <c r="DN11" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="DP11" t="n">
-        <v>12.57</v>
+        <v>12.41</v>
       </c>
       <c r="DQ11" t="n">
-        <v>12.47</v>
+        <v>12.54</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.95</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>44.95</v>
+        <v>45</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DX11" t="n">
-        <v>11.95</v>
+        <v>12.23</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.15</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.81</v>
+        <v>3.86</v>
       </c>
       <c r="EA11" t="n">
-        <v>19.57</v>
+        <v>19.45</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
@@ -1782,94 +1782,94 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
         <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F3" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="G3" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="H3" t="n">
-        <v>98</v>
+        <v>98.42</v>
       </c>
       <c r="I3" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="J3" t="n">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="K3" t="n">
-        <v>3.91</v>
+        <v>4</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="M3" t="n">
-        <v>48.82</v>
+        <v>49.42</v>
       </c>
       <c r="N3" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>1.45</v>
+        <v>1.67</v>
       </c>
       <c r="P3" t="n">
-        <v>11.36</v>
+        <v>11.67</v>
       </c>
       <c r="Q3" t="n">
-        <v>13.18</v>
+        <v>13.83</v>
       </c>
       <c r="R3" t="n">
-        <v>8.550000000000001</v>
+        <v>8.25</v>
       </c>
       <c r="S3" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="T3" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="U3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="V3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>49.55</v>
+        <v>49.08</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z3" t="n">
-        <v>10.73</v>
+        <v>11</v>
       </c>
       <c r="AA3" t="n">
-        <v>6.73</v>
+        <v>7.17</v>
       </c>
       <c r="AB3" t="n">
-        <v>4</v>
+        <v>3.83</v>
       </c>
       <c r="AC3" t="n">
-        <v>21.91</v>
+        <v>21.42</v>
       </c>
       <c r="AD3" t="n">
         <v>1.32</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -1953,70 +1953,70 @@
         <v>1.9</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="BH3" t="n">
-        <v>8.9</v>
+        <v>8.77</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="BP3" t="n">
         <v>4</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.29</v>
+        <v>4.18</v>
       </c>
       <c r="BR3" t="n">
-        <v>100</v>
+        <v>95.45</v>
       </c>
       <c r="BS3" t="n">
-        <v>76.19</v>
+        <v>72.73</v>
       </c>
       <c r="BT3" t="n">
-        <v>52.38</v>
+        <v>50</v>
       </c>
       <c r="BU3" t="n">
-        <v>28.57</v>
+        <v>27.27</v>
       </c>
       <c r="BV3" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>61.9</v>
+        <v>59.09</v>
       </c>
       <c r="BY3" t="n">
-        <v>3.06</v>
+        <v>2.96</v>
       </c>
       <c r="BZ3" t="n">
-        <v>3.22</v>
+        <v>3.11</v>
       </c>
       <c r="CA3" t="n">
         <v>3.51</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.62</v>
+        <v>3.61</v>
       </c>
       <c r="CC3" t="n">
         <v>5.47</v>
@@ -2028,28 +2028,28 @@
         <v>1.4</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="CH3" t="n">
         <v>1.37</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CN3" t="n">
         <v>1.65</v>
@@ -2061,31 +2061,31 @@
         <v>2.03</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="CR3" t="n">
         <v>1.43</v>
       </c>
       <c r="CS3" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="CT3" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="CU3" t="n">
         <v>1.39</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CZ3" t="n">
         <v>2.04</v>
@@ -2097,85 +2097,85 @@
         <v>1.34</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="DE3" t="n">
         <v>0.09</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="DH3" t="n">
-        <v>97.90000000000001</v>
+        <v>98.14</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.48</v>
+        <v>2.41</v>
       </c>
       <c r="DK3" t="n">
-        <v>4.57</v>
+        <v>4.59</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.09</v>
+        <v>0.14</v>
       </c>
       <c r="DM3" t="n">
-        <v>51.67</v>
+        <v>51.87</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="DP3" t="n">
-        <v>11.43</v>
+        <v>11.59</v>
       </c>
       <c r="DQ3" t="n">
-        <v>13.05</v>
+        <v>13.41</v>
       </c>
       <c r="DR3" t="n">
-        <v>8.380000000000001</v>
+        <v>8.23</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>47.62</v>
+        <v>47.45</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX3" t="n">
-        <v>11.67</v>
+        <v>11.77</v>
       </c>
       <c r="DY3" t="n">
-        <v>7.76</v>
+        <v>7.96</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.9</v>
+        <v>3.82</v>
       </c>
       <c r="EA3" t="n">
-        <v>20.67</v>
+        <v>20.46</v>
       </c>
       <c r="EB3" t="n">
         <v>1.39</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" t="n">
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2275,139 +2275,139 @@
         <v>1.7</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AH4" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AI4" t="n">
-        <v>101.09</v>
+        <v>103.33</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK4" t="n">
-        <v>3.55</v>
+        <v>3.33</v>
       </c>
       <c r="AL4" t="n">
-        <v>3.55</v>
+        <v>3.33</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AN4" t="n">
-        <v>53.18</v>
+        <v>54</v>
       </c>
       <c r="AO4" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ4" t="n">
-        <v>12</v>
+        <v>12.75</v>
       </c>
       <c r="AR4" t="n">
-        <v>9.91</v>
+        <v>10.33</v>
       </c>
       <c r="AS4" t="n">
-        <v>9</v>
+        <v>8.92</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>39.18</v>
+        <v>40.58</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BA4" t="n">
         <v>9</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.36</v>
+        <v>6.42</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="BD4" t="n">
-        <v>21.73</v>
+        <v>22.33</v>
       </c>
       <c r="BE4" t="n">
         <v>1.15</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.91</v>
+        <v>2.75</v>
       </c>
       <c r="BG4" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="BH4" t="n">
-        <v>10.24</v>
+        <v>10.05</v>
       </c>
       <c r="BI4" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="BL4" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="BP4" t="n">
-        <v>5.19</v>
+        <v>5.14</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5</v>
+        <v>4.86</v>
       </c>
       <c r="BR4" t="n">
-        <v>100</v>
+        <v>95.45</v>
       </c>
       <c r="BS4" t="n">
-        <v>85.70999999999999</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT4" t="n">
-        <v>61.9</v>
+        <v>59.09</v>
       </c>
       <c r="BU4" t="n">
-        <v>38.1</v>
+        <v>36.36</v>
       </c>
       <c r="BV4" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>71.43000000000001</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BY4" t="n">
         <v>4.32</v>
@@ -2416,16 +2416,16 @@
         <v>4.9</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.25</v>
+        <v>4.21</v>
       </c>
       <c r="CB4" t="n">
-        <v>4.37</v>
+        <v>4.33</v>
       </c>
       <c r="CC4" t="n">
-        <v>6.78</v>
+        <v>6.54</v>
       </c>
       <c r="CD4" t="n">
-        <v>9.49</v>
+        <v>9.06</v>
       </c>
       <c r="CE4" t="n">
         <v>1.35</v>
@@ -2434,16 +2434,16 @@
         <v>2.67</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CI4" t="n">
         <v>1.82</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CK4" t="n">
         <v>1.6</v>
@@ -2455,7 +2455,7 @@
         <v>1.97</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CO4" t="n">
         <v>1.26</v>
@@ -2470,7 +2470,7 @@
         <v>1.38</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="CT4" t="n">
         <v>3.05</v>
@@ -2479,16 +2479,16 @@
         <v>1.49</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CZ4" t="n">
         <v>2.11</v>
@@ -2500,52 +2500,52 @@
         <v>1.27</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="DE4" t="n">
         <v>0.09</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="DH4" t="n">
-        <v>107.33</v>
+        <v>108.27</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="DK4" t="n">
-        <v>3.67</v>
+        <v>3.54</v>
       </c>
       <c r="DL4" t="n">
         <v>0.14</v>
       </c>
       <c r="DM4" t="n">
-        <v>61.28</v>
+        <v>61.36</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="DP4" t="n">
-        <v>12.29</v>
+        <v>12.68</v>
       </c>
       <c r="DQ4" t="n">
-        <v>11.05</v>
+        <v>11.23</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.24</v>
+        <v>8.23</v>
       </c>
       <c r="DS4" t="n">
         <v>0.09</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>40.57</v>
+        <v>41.27</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.43</v>
+        <v>10.36</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.81</v>
+        <v>6.82</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.62</v>
+        <v>3.54</v>
       </c>
       <c r="EA4" t="n">
-        <v>20.95</v>
+        <v>21.32</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.33</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" t="n">
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E5" t="n">
         <v>0.27</v>
@@ -2678,64 +2678,64 @@
         <v>1.64</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.8</v>
+        <v>3.09</v>
       </c>
       <c r="AI5" t="n">
-        <v>103.8</v>
+        <v>108</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AL5" t="n">
-        <v>5.9</v>
+        <v>6.18</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AN5" t="n">
-        <v>60.5</v>
+        <v>64.09</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="AQ5" t="n">
-        <v>12.6</v>
+        <v>12.82</v>
       </c>
       <c r="AR5" t="n">
-        <v>15</v>
+        <v>14.73</v>
       </c>
       <c r="AS5" t="n">
-        <v>7</v>
+        <v>6.91</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>57.4</v>
+        <v>58</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
@@ -2744,73 +2744,73 @@
         <v>14</v>
       </c>
       <c r="BB5" t="n">
-        <v>9.6</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="BD5" t="n">
-        <v>20.9</v>
+        <v>20.91</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="BH5" t="n">
-        <v>9</v>
+        <v>9.18</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="BO5" t="n">
         <v>1.14</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.95</v>
+        <v>3.91</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.9</v>
+        <v>5.14</v>
       </c>
       <c r="BR5" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS5" t="n">
-        <v>85.70999999999999</v>
+        <v>86.36</v>
       </c>
       <c r="BT5" t="n">
-        <v>42.86</v>
+        <v>40.91</v>
       </c>
       <c r="BU5" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BV5" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>38.1</v>
+        <v>36.36</v>
       </c>
       <c r="BY5" t="n">
         <v>1.65</v>
@@ -2819,16 +2819,16 @@
         <v>1.7</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.66</v>
+        <v>3.65</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.63</v>
+        <v>3.61</v>
       </c>
       <c r="CC5" t="n">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="CD5" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="CE5" t="n">
         <v>1.41</v>
@@ -2843,40 +2843,40 @@
         <v>1.36</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CJ5" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CO5" t="n">
         <v>1.31</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.6</v>
+        <v>3.61</v>
       </c>
       <c r="CR5" t="n">
         <v>1.44</v>
       </c>
       <c r="CS5" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="CU5" t="n">
         <v>1.36</v>
@@ -2891,97 +2891,97 @@
         <v>1.71</v>
       </c>
       <c r="CY5" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CZ5" t="n">
         <v>2.06</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.77</v>
+        <v>3.8</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.09</v>
+        <v>3.22</v>
       </c>
       <c r="DH5" t="n">
-        <v>111.43</v>
+        <v>113.18</v>
       </c>
       <c r="DI5" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.38</v>
+        <v>5.54</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.33</v>
+        <v>0.36</v>
       </c>
       <c r="DM5" t="n">
-        <v>63.15</v>
+        <v>64.81999999999999</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.66</v>
+        <v>0.72</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="DP5" t="n">
-        <v>12.33</v>
+        <v>12.46</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15.14</v>
+        <v>15</v>
       </c>
       <c r="DR5" t="n">
-        <v>6.19</v>
+        <v>6.18</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.19</v>
+        <v>0.22</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.19</v>
+        <v>0.22</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>58.95</v>
+        <v>59.18</v>
       </c>
       <c r="DW5" t="n">
         <v>0.09</v>
       </c>
       <c r="DX5" t="n">
-        <v>14.95</v>
+        <v>14.91</v>
       </c>
       <c r="DY5" t="n">
-        <v>9.76</v>
+        <v>9.73</v>
       </c>
       <c r="DZ5" t="n">
-        <v>5.19</v>
+        <v>5.18</v>
       </c>
       <c r="EA5" t="n">
-        <v>21.66</v>
+        <v>21.64</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="6">
@@ -3797,10 +3797,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D8" t="n">
         <v>10</v>
@@ -3809,49 +3809,49 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="G8" t="n">
-        <v>2.64</v>
+        <v>2.75</v>
       </c>
       <c r="H8" t="n">
-        <v>118.27</v>
+        <v>116.5</v>
       </c>
       <c r="I8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="K8" t="n">
-        <v>5.73</v>
+        <v>5.58</v>
       </c>
       <c r="L8" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="M8" t="n">
-        <v>80.64</v>
+        <v>78.75</v>
       </c>
       <c r="N8" t="n">
         <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="P8" t="n">
-        <v>14.73</v>
+        <v>14.58</v>
       </c>
       <c r="Q8" t="n">
-        <v>13.64</v>
+        <v>13.75</v>
       </c>
       <c r="R8" t="n">
-        <v>7.27</v>
+        <v>7.25</v>
       </c>
       <c r="S8" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="T8" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -3863,28 +3863,28 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>50.27</v>
+        <v>49.08</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z8" t="n">
-        <v>12.64</v>
+        <v>12.17</v>
       </c>
       <c r="AA8" t="n">
-        <v>9.27</v>
+        <v>8.75</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.36</v>
+        <v>3.42</v>
       </c>
       <c r="AC8" t="n">
-        <v>22.18</v>
+        <v>21.42</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AF8" t="n">
         <v>0.1</v>
@@ -3968,70 +3968,70 @@
         <v>2.4</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.859999999999999</v>
+        <v>10</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="BO8" t="n">
         <v>1.14</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.95</v>
+        <v>4.86</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.86</v>
+        <v>5.09</v>
       </c>
       <c r="BR8" t="n">
-        <v>80.95</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BS8" t="n">
-        <v>71.43000000000001</v>
+        <v>72.73</v>
       </c>
       <c r="BT8" t="n">
-        <v>42.86</v>
+        <v>40.91</v>
       </c>
       <c r="BU8" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BV8" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BW8" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BX8" t="n">
-        <v>47.62</v>
+        <v>45.45</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="CA8" t="n">
         <v>3.4</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.45</v>
+        <v>3.44</v>
       </c>
       <c r="CC8" t="n">
         <v>3.55</v>
@@ -4043,16 +4043,16 @@
         <v>1.39</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="CH8" t="n">
         <v>1.38</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CJ8" t="n">
         <v>1.81</v>
@@ -4061,37 +4061,37 @@
         <v>1.58</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CM8" t="n">
         <v>2.22</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CO8" t="n">
         <v>1.3</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.22</v>
+        <v>3.26</v>
       </c>
       <c r="CR8" t="n">
         <v>1.41</v>
       </c>
       <c r="CS8" t="n">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="CU8" t="n">
         <v>1.39</v>
       </c>
       <c r="CV8" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CW8" t="n">
         <v>1.84</v>
@@ -4100,64 +4100,64 @@
         <v>1.61</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="DB8" t="n">
         <v>1.32</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.54</v>
+        <v>3.58</v>
       </c>
       <c r="DE8" t="n">
         <v>0.05</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="DH8" t="n">
-        <v>111.95</v>
+        <v>111.27</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.95</v>
+        <v>4.91</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="DM8" t="n">
-        <v>68.95</v>
+        <v>68.45</v>
       </c>
       <c r="DN8" t="n">
         <v>0.86</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.67</v>
+        <v>2.55</v>
       </c>
       <c r="DP8" t="n">
-        <v>15.14</v>
+        <v>15.04</v>
       </c>
       <c r="DQ8" t="n">
-        <v>13.43</v>
+        <v>13.5</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.76</v>
+        <v>7.73</v>
       </c>
       <c r="DS8" t="n">
         <v>0</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>49.57</v>
+        <v>48.95</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DX8" t="n">
-        <v>12.43</v>
+        <v>12.18</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.949999999999999</v>
+        <v>8.68</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.47</v>
+        <v>3.5</v>
       </c>
       <c r="EA8" t="n">
-        <v>22.33</v>
+        <v>21.91</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="9">
@@ -4266,7 +4266,7 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>52.08</v>
+        <v>52.17</v>
       </c>
       <c r="Y9" t="n">
         <v>0.08</v>
@@ -4572,7 +4572,7 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>51.91</v>
+        <v>51.96</v>
       </c>
       <c r="DW9" t="n">
         <v>0.09</v>
@@ -5153,7 +5153,7 @@
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>42.83</v>
+        <v>42.75</v>
       </c>
       <c r="AZ11" t="n">
         <v>0.25</v>
@@ -5378,7 +5378,7 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>45</v>
+        <v>44.95</v>
       </c>
       <c r="DW11" t="n">
         <v>0.18</v>

--- a/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" t="n">
         <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" t="n">
         <v>0.18</v>
@@ -1469,139 +1469,139 @@
         <v>2.09</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AH2" t="n">
-        <v>4.09</v>
+        <v>3.83</v>
       </c>
       <c r="AI2" t="n">
-        <v>119.36</v>
+        <v>120.75</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AL2" t="n">
-        <v>6.64</v>
+        <v>6.5</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AN2" t="n">
-        <v>75.55</v>
+        <v>75.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.55</v>
+        <v>2.67</v>
       </c>
       <c r="AQ2" t="n">
-        <v>13.91</v>
+        <v>13.75</v>
       </c>
       <c r="AR2" t="n">
-        <v>13.91</v>
+        <v>13.58</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.18</v>
+        <v>5.83</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>54.64</v>
+        <v>55.17</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BA2" t="n">
-        <v>15.64</v>
+        <v>15.83</v>
       </c>
       <c r="BB2" t="n">
-        <v>11</v>
+        <v>10.92</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.64</v>
+        <v>4.92</v>
       </c>
       <c r="BD2" t="n">
-        <v>24.18</v>
+        <v>24.33</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.91</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.73</v>
+        <v>0.87</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.59</v>
+        <v>4.57</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.27</v>
+        <v>5.09</v>
       </c>
       <c r="BR2" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS2" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BT2" t="n">
-        <v>63.64</v>
+        <v>65.22</v>
       </c>
       <c r="BU2" t="n">
-        <v>27.27</v>
+        <v>30.43</v>
       </c>
       <c r="BV2" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BW2" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX2" t="n">
-        <v>50</v>
+        <v>47.83</v>
       </c>
       <c r="BY2" t="n">
         <v>1.29</v>
@@ -1610,13 +1610,13 @@
         <v>1.31</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.67</v>
+        <v>4.64</v>
       </c>
       <c r="CB2" t="n">
-        <v>5.06</v>
+        <v>5.01</v>
       </c>
       <c r="CC2" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CD2" t="n">
         <v>1.72</v>
@@ -1628,7 +1628,7 @@
         <v>2.49</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="CH2" t="n">
         <v>1.49</v>
@@ -1637,13 +1637,13 @@
         <v>1.79</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CK2" t="n">
         <v>1.57</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CM2" t="n">
         <v>2.23</v>
@@ -1658,7 +1658,7 @@
         <v>1.74</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="CR2" t="n">
         <v>1.38</v>
@@ -1676,16 +1676,16 @@
         <v>1.84</v>
       </c>
       <c r="CW2" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CX2" t="n">
         <v>1.59</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="DA2" t="n">
         <v>1.77</v>
@@ -1697,49 +1697,49 @@
         <v>1.75</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="DE2" t="n">
         <v>0.13</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="DH2" t="n">
-        <v>121.64</v>
+        <v>122.26</v>
       </c>
       <c r="DI2" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.18</v>
+        <v>2.13</v>
       </c>
       <c r="DK2" t="n">
-        <v>6.5</v>
+        <v>6.43</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="DM2" t="n">
-        <v>75.45999999999999</v>
+        <v>75.43000000000001</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="DO2" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="DP2" t="n">
-        <v>12.63</v>
+        <v>12.61</v>
       </c>
       <c r="DQ2" t="n">
-        <v>13.32</v>
+        <v>13.17</v>
       </c>
       <c r="DR2" t="n">
-        <v>5.77</v>
+        <v>5.61</v>
       </c>
       <c r="DS2" t="n">
         <v>0.09</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>56.46</v>
+        <v>56.65</v>
       </c>
       <c r="DW2" t="n">
         <v>0.13</v>
       </c>
       <c r="DX2" t="n">
-        <v>16.32</v>
+        <v>16.39</v>
       </c>
       <c r="DY2" t="n">
-        <v>10.59</v>
+        <v>10.57</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5.73</v>
+        <v>5.83</v>
       </c>
       <c r="EA2" t="n">
-        <v>23.27</v>
+        <v>23.39</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="EC2" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C3" t="n">
         <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
         <v>0.17</v>
@@ -1875,49 +1875,49 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.9</v>
+        <v>1.64</v>
       </c>
       <c r="AI3" t="n">
-        <v>97.8</v>
+        <v>96.55</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AL3" t="n">
-        <v>5.3</v>
+        <v>5.18</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>54.8</v>
+        <v>54.36</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="AQ3" t="n">
-        <v>11.5</v>
+        <v>11.27</v>
       </c>
       <c r="AR3" t="n">
-        <v>12.9</v>
+        <v>13.09</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.27</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AU3" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
@@ -1929,82 +1929,82 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>45.5</v>
+        <v>44.91</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="BA3" t="n">
-        <v>12.7</v>
+        <v>12.91</v>
       </c>
       <c r="BB3" t="n">
-        <v>8.9</v>
+        <v>9.09</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="BD3" t="n">
-        <v>19.3</v>
+        <v>19.82</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="BH3" t="n">
-        <v>8.77</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="BP3" t="n">
-        <v>4</v>
+        <v>3.78</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.18</v>
+        <v>3.96</v>
       </c>
       <c r="BR3" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS3" t="n">
-        <v>72.73</v>
+        <v>73.91</v>
       </c>
       <c r="BT3" t="n">
-        <v>50</v>
+        <v>47.83</v>
       </c>
       <c r="BU3" t="n">
-        <v>27.27</v>
+        <v>26.09</v>
       </c>
       <c r="BV3" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>59.09</v>
+        <v>56.52</v>
       </c>
       <c r="BY3" t="n">
         <v>2.96</v>
@@ -2013,31 +2013,31 @@
         <v>3.11</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.51</v>
+        <v>3.49</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.61</v>
+        <v>3.58</v>
       </c>
       <c r="CC3" t="n">
-        <v>5.47</v>
+        <v>5.28</v>
       </c>
       <c r="CD3" t="n">
-        <v>5.62</v>
+        <v>5.37</v>
       </c>
       <c r="CE3" t="n">
         <v>1.4</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="CH3" t="n">
         <v>1.37</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CJ3" t="n">
         <v>1.9</v>
@@ -2061,7 +2061,7 @@
         <v>2.03</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.48</v>
+        <v>3.49</v>
       </c>
       <c r="CR3" t="n">
         <v>1.43</v>
@@ -2082,10 +2082,10 @@
         <v>1.91</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CZ3" t="n">
         <v>2.04</v>
@@ -2097,52 +2097,52 @@
         <v>1.34</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.7</v>
+        <v>3.71</v>
       </c>
       <c r="DE3" t="n">
         <v>0.09</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="DH3" t="n">
-        <v>98.14</v>
+        <v>97.53</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.41</v>
+        <v>2.35</v>
       </c>
       <c r="DK3" t="n">
-        <v>4.59</v>
+        <v>4.56</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.14</v>
+        <v>0.09</v>
       </c>
       <c r="DM3" t="n">
-        <v>51.87</v>
+        <v>51.78</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="DP3" t="n">
-        <v>11.59</v>
+        <v>11.48</v>
       </c>
       <c r="DQ3" t="n">
-        <v>13.41</v>
+        <v>13.48</v>
       </c>
       <c r="DR3" t="n">
-        <v>8.23</v>
+        <v>8.26</v>
       </c>
       <c r="DS3" t="n">
         <v>0.04</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>47.45</v>
+        <v>47.09</v>
       </c>
       <c r="DW3" t="n">
         <v>0.13</v>
       </c>
       <c r="DX3" t="n">
-        <v>11.77</v>
+        <v>11.91</v>
       </c>
       <c r="DY3" t="n">
-        <v>7.96</v>
+        <v>8.09</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.82</v>
+        <v>3.83</v>
       </c>
       <c r="EA3" t="n">
-        <v>20.46</v>
+        <v>20.65</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.18</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="4">
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
         <v>12</v>
@@ -2197,82 +2197,82 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="G4" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="H4" t="n">
-        <v>114.2</v>
+        <v>117.09</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1.9</v>
+        <v>2.09</v>
       </c>
       <c r="K4" t="n">
-        <v>3.8</v>
+        <v>3.91</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>70.2</v>
+        <v>70.64</v>
       </c>
       <c r="N4" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="O4" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="P4" t="n">
-        <v>12.6</v>
+        <v>13</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.3</v>
+        <v>11.82</v>
       </c>
       <c r="R4" t="n">
-        <v>7.4</v>
+        <v>7.27</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T4" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1</v>
+        <v>0.27</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1</v>
+        <v>0.27</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>42.1</v>
+        <v>43.73</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z4" t="n">
-        <v>12</v>
+        <v>11.64</v>
       </c>
       <c r="AA4" t="n">
-        <v>7.3</v>
+        <v>7.09</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.7</v>
+        <v>4.55</v>
       </c>
       <c r="AC4" t="n">
-        <v>20.1</v>
+        <v>20.36</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AF4" t="n">
         <v>0.17</v>
@@ -2356,70 +2356,70 @@
         <v>2.75</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.86</v>
+        <v>2.91</v>
       </c>
       <c r="BH4" t="n">
-        <v>10.05</v>
+        <v>10</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.86</v>
+        <v>2.91</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.45</v>
+        <v>0.52</v>
       </c>
       <c r="BL4" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="BP4" t="n">
-        <v>5.14</v>
+        <v>5.04</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.86</v>
+        <v>4.87</v>
       </c>
       <c r="BR4" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS4" t="n">
-        <v>81.81999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="BT4" t="n">
-        <v>59.09</v>
+        <v>60.87</v>
       </c>
       <c r="BU4" t="n">
-        <v>36.36</v>
+        <v>39.13</v>
       </c>
       <c r="BV4" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>68.18000000000001</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BY4" t="n">
-        <v>4.32</v>
+        <v>4.17</v>
       </c>
       <c r="BZ4" t="n">
-        <v>4.9</v>
+        <v>4.69</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.21</v>
+        <v>4.16</v>
       </c>
       <c r="CB4" t="n">
-        <v>4.33</v>
+        <v>4.28</v>
       </c>
       <c r="CC4" t="n">
         <v>6.54</v>
@@ -2434,22 +2434,22 @@
         <v>2.67</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="CH4" t="n">
         <v>1.44</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="CM4" t="n">
         <v>1.97</v>
@@ -2464,7 +2464,7 @@
         <v>1.86</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.08</v>
+        <v>3.09</v>
       </c>
       <c r="CR4" t="n">
         <v>1.38</v>
@@ -2479,106 +2479,106 @@
         <v>1.49</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="DA4" t="n">
         <v>1.7</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="DC4" t="n">
         <v>1.89</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="DE4" t="n">
         <v>0.09</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="DH4" t="n">
-        <v>108.27</v>
+        <v>109.91</v>
       </c>
       <c r="DI4" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="DK4" t="n">
-        <v>3.54</v>
+        <v>3.61</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DM4" t="n">
-        <v>61.36</v>
+        <v>61.96</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="DP4" t="n">
-        <v>12.68</v>
+        <v>12.87</v>
       </c>
       <c r="DQ4" t="n">
-        <v>11.23</v>
+        <v>11.04</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.23</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>41.27</v>
+        <v>42.09</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.36</v>
+        <v>10.26</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.82</v>
+        <v>6.74</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.54</v>
+        <v>3.52</v>
       </c>
       <c r="EA4" t="n">
-        <v>21.32</v>
+        <v>21.39</v>
       </c>
       <c r="EB4" t="n">
         <v>1.35</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.27</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="5">
@@ -2588,94 +2588,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5" t="n">
         <v>11</v>
       </c>
       <c r="E5" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="F5" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="G5" t="n">
-        <v>3.36</v>
+        <v>3.58</v>
       </c>
       <c r="H5" t="n">
-        <v>118.36</v>
+        <v>118.33</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>4.91</v>
+        <v>5</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="M5" t="n">
-        <v>65.55</v>
+        <v>66.5</v>
       </c>
       <c r="N5" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="O5" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="P5" t="n">
-        <v>12.09</v>
+        <v>11.92</v>
       </c>
       <c r="Q5" t="n">
-        <v>15.27</v>
+        <v>15.42</v>
       </c>
       <c r="R5" t="n">
-        <v>5.45</v>
+        <v>5.42</v>
       </c>
       <c r="S5" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="T5" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="U5" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="V5" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>60.36</v>
+        <v>60.42</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="Z5" t="n">
-        <v>15.82</v>
+        <v>15.42</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.91</v>
+        <v>9.42</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.91</v>
+        <v>6</v>
       </c>
       <c r="AC5" t="n">
-        <v>22.36</v>
+        <v>22.75</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AF5" t="n">
         <v>0.09</v>
@@ -2759,70 +2759,70 @@
         <v>2.55</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.18</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.91</v>
+        <v>3.78</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.14</v>
+        <v>5.22</v>
       </c>
       <c r="BR5" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS5" t="n">
-        <v>86.36</v>
+        <v>82.61</v>
       </c>
       <c r="BT5" t="n">
-        <v>40.91</v>
+        <v>39.13</v>
       </c>
       <c r="BU5" t="n">
-        <v>18.18</v>
+        <v>17.39</v>
       </c>
       <c r="BV5" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>36.36</v>
+        <v>34.78</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.65</v>
+        <v>3.63</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.61</v>
+        <v>3.59</v>
       </c>
       <c r="CC5" t="n">
         <v>2.31</v>
@@ -2834,10 +2834,10 @@
         <v>1.41</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="CH5" t="n">
         <v>1.36</v>
@@ -2849,25 +2849,25 @@
         <v>1.99</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CL5" t="n">
         <v>2.31</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CO5" t="n">
         <v>1.31</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.61</v>
+        <v>3.63</v>
       </c>
       <c r="CR5" t="n">
         <v>1.44</v>
@@ -2906,49 +2906,49 @@
         <v>2.14</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.8</v>
+        <v>3.81</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.22</v>
+        <v>3.35</v>
       </c>
       <c r="DH5" t="n">
-        <v>113.18</v>
+        <v>113.39</v>
       </c>
       <c r="DI5" t="n">
         <v>-0.04</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.54</v>
+        <v>5.56</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="DM5" t="n">
-        <v>64.81999999999999</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
       <c r="DP5" t="n">
-        <v>12.46</v>
+        <v>12.35</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15</v>
+        <v>15.09</v>
       </c>
       <c r="DR5" t="n">
-        <v>6.18</v>
+        <v>6.13</v>
       </c>
       <c r="DS5" t="n">
         <v>0.22</v>
@@ -2960,25 +2960,25 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>59.18</v>
+        <v>59.26</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="DX5" t="n">
-        <v>14.91</v>
+        <v>14.74</v>
       </c>
       <c r="DY5" t="n">
-        <v>9.73</v>
+        <v>9.48</v>
       </c>
       <c r="DZ5" t="n">
-        <v>5.18</v>
+        <v>5.26</v>
       </c>
       <c r="EA5" t="n">
-        <v>21.64</v>
+        <v>21.87</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="EC5" t="n">
         <v>2.09</v>
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D6" t="n">
         <v>12</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="F6" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="G6" t="n">
-        <v>1.9</v>
+        <v>1.64</v>
       </c>
       <c r="H6" t="n">
-        <v>105.5</v>
+        <v>106.36</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="J6" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="K6" t="n">
-        <v>4.1</v>
+        <v>4.18</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5</v>
+        <v>0.36</v>
       </c>
       <c r="M6" t="n">
-        <v>57.9</v>
+        <v>58</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="O6" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="P6" t="n">
-        <v>10.7</v>
+        <v>11.09</v>
       </c>
       <c r="Q6" t="n">
-        <v>11.9</v>
+        <v>11.64</v>
       </c>
       <c r="R6" t="n">
-        <v>10.2</v>
+        <v>10.27</v>
       </c>
       <c r="S6" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="T6" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -3057,28 +3057,28 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>50.9</v>
+        <v>51.82</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>11.8</v>
+        <v>11.27</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.1</v>
+        <v>7.64</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.7</v>
+        <v>3.64</v>
       </c>
       <c r="AC6" t="n">
-        <v>21.2</v>
+        <v>21.64</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AF6" t="n">
         <v>0.08</v>
@@ -3162,70 +3162,70 @@
         <v>2.17</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.77</v>
+        <v>2.74</v>
       </c>
       <c r="BH6" t="n">
-        <v>10.05</v>
+        <v>10</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.77</v>
+        <v>2.74</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.59</v>
+        <v>4.35</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.95</v>
+        <v>4.7</v>
       </c>
       <c r="BR6" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS6" t="n">
-        <v>81.81999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="BT6" t="n">
-        <v>63.64</v>
+        <v>60.87</v>
       </c>
       <c r="BU6" t="n">
-        <v>22.73</v>
+        <v>21.74</v>
       </c>
       <c r="BV6" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BW6" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX6" t="n">
-        <v>68.18000000000001</v>
+        <v>65.22</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="BZ6" t="n">
         <v>2.72</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.4</v>
+        <v>3.39</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.54</v>
+        <v>3.51</v>
       </c>
       <c r="CC6" t="n">
         <v>4.1</v>
@@ -3237,10 +3237,10 @@
         <v>1.4</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="CH6" t="n">
         <v>1.37</v>
@@ -3252,13 +3252,13 @@
         <v>1.86</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CL6" t="n">
         <v>2.38</v>
       </c>
       <c r="CM6" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CN6" t="n">
         <v>1.6</v>
@@ -3270,7 +3270,7 @@
         <v>2.03</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.46</v>
+        <v>3.47</v>
       </c>
       <c r="CR6" t="n">
         <v>1.43</v>
@@ -3285,7 +3285,7 @@
         <v>1.39</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CW6" t="n">
         <v>1.91</v>
@@ -3306,22 +3306,22 @@
         <v>1.34</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.66</v>
+        <v>3.67</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="DH6" t="n">
-        <v>106.09</v>
+        <v>106.47</v>
       </c>
       <c r="DI6" t="n">
         <v>0.13</v>
@@ -3330,28 +3330,28 @@
         <v>1.96</v>
       </c>
       <c r="DK6" t="n">
-        <v>3.91</v>
+        <v>3.96</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.41</v>
+        <v>0.34</v>
       </c>
       <c r="DM6" t="n">
-        <v>57.73</v>
+        <v>57.78</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="DP6" t="n">
-        <v>10.77</v>
+        <v>10.95</v>
       </c>
       <c r="DQ6" t="n">
-        <v>11.73</v>
+        <v>11.61</v>
       </c>
       <c r="DR6" t="n">
-        <v>10</v>
+        <v>10.04</v>
       </c>
       <c r="DS6" t="n">
         <v>0.04</v>
@@ -3363,25 +3363,25 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>49.23</v>
+        <v>49.74</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>10.18</v>
+        <v>10</v>
       </c>
       <c r="DY6" t="n">
-        <v>6.73</v>
+        <v>6.57</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.45</v>
+        <v>3.44</v>
       </c>
       <c r="EA6" t="n">
-        <v>22.23</v>
+        <v>22.39</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="EC6" t="n">
         <v>1.96</v>
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D7" t="n">
         <v>11</v>
@@ -3406,82 +3406,82 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="G7" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="H7" t="n">
-        <v>104.09</v>
+        <v>102</v>
       </c>
       <c r="I7" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="K7" t="n">
-        <v>3.82</v>
+        <v>3.75</v>
       </c>
       <c r="L7" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="M7" t="n">
-        <v>57.91</v>
+        <v>57.08</v>
       </c>
       <c r="N7" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="O7" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="P7" t="n">
-        <v>15</v>
+        <v>14.42</v>
       </c>
       <c r="Q7" t="n">
-        <v>13.09</v>
+        <v>13.25</v>
       </c>
       <c r="R7" t="n">
-        <v>7.55</v>
+        <v>7.25</v>
       </c>
       <c r="S7" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T7" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="U7" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="V7" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>50.27</v>
+        <v>50.5</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>10.64</v>
+        <v>10.83</v>
       </c>
       <c r="AA7" t="n">
-        <v>6.36</v>
+        <v>6.42</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.27</v>
+        <v>4.42</v>
       </c>
       <c r="AC7" t="n">
-        <v>22.55</v>
+        <v>22.83</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AF7" t="n">
         <v>0.36</v>
@@ -3565,70 +3565,70 @@
         <v>1.82</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.73</v>
+        <v>2.78</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.859999999999999</v>
+        <v>8.74</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.73</v>
+        <v>2.78</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.95</v>
+        <v>1.04</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.86</v>
+        <v>3.83</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5</v>
+        <v>4.91</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BT7" t="n">
-        <v>45.45</v>
+        <v>47.83</v>
       </c>
       <c r="BU7" t="n">
-        <v>22.73</v>
+        <v>26.09</v>
       </c>
       <c r="BV7" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BW7" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX7" t="n">
-        <v>72.73</v>
+        <v>73.91</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.97</v>
+        <v>2.9</v>
       </c>
       <c r="BZ7" t="n">
-        <v>3.06</v>
+        <v>3.02</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.56</v>
+        <v>3.55</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.59</v>
+        <v>3.57</v>
       </c>
       <c r="CC7" t="n">
         <v>4.39</v>
@@ -3640,10 +3640,10 @@
         <v>1.38</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="CH7" t="n">
         <v>1.4</v>
@@ -3652,16 +3652,16 @@
         <v>1.9</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CK7" t="n">
         <v>1.58</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CN7" t="n">
         <v>1.74</v>
@@ -3670,34 +3670,34 @@
         <v>1.27</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.28</v>
+        <v>3.31</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CX7" t="n">
         <v>1.6</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CZ7" t="n">
         <v>2.21</v>
@@ -3706,88 +3706,88 @@
         <v>1.74</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.47</v>
+        <v>3.52</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="DH7" t="n">
-        <v>108.09</v>
+        <v>106.83</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.32</v>
+        <v>4.26</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.22</v>
+        <v>0.26</v>
       </c>
       <c r="DM7" t="n">
-        <v>59.04</v>
+        <v>58.56</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="DP7" t="n">
-        <v>14.96</v>
+        <v>14.65</v>
       </c>
       <c r="DQ7" t="n">
-        <v>11.87</v>
+        <v>12</v>
       </c>
       <c r="DR7" t="n">
-        <v>7.23</v>
+        <v>7.09</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.27</v>
+        <v>0.31</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.27</v>
+        <v>0.31</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>51.14</v>
+        <v>51.22</v>
       </c>
       <c r="DW7" t="n">
         <v>0.09</v>
       </c>
       <c r="DX7" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="DY7" t="n">
-        <v>6.95</v>
+        <v>6.96</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.64</v>
+        <v>3.74</v>
       </c>
       <c r="EA7" t="n">
-        <v>21.64</v>
+        <v>21.83</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="8">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8" t="n">
         <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -3887,49 +3887,49 @@
         <v>2.17</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG8" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AI8" t="n">
-        <v>105</v>
+        <v>101.82</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>-0.09</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="AL8" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AN8" t="n">
-        <v>56.1</v>
+        <v>54.55</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AP8" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AQ8" t="n">
-        <v>15.6</v>
+        <v>15.64</v>
       </c>
       <c r="AR8" t="n">
-        <v>13.2</v>
+        <v>12.73</v>
       </c>
       <c r="AS8" t="n">
-        <v>8.300000000000001</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AU8" t="n">
         <v>1</v>
@@ -3944,82 +3944,82 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>48.8</v>
+        <v>48.64</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="BA8" t="n">
-        <v>12.2</v>
+        <v>11.91</v>
       </c>
       <c r="BB8" t="n">
-        <v>8.6</v>
+        <v>8.18</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.6</v>
+        <v>3.73</v>
       </c>
       <c r="BD8" t="n">
-        <v>22.5</v>
+        <v>22.64</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.32</v>
+        <v>2.39</v>
       </c>
       <c r="BH8" t="n">
-        <v>10</v>
+        <v>9.83</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.32</v>
+        <v>2.39</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.68</v>
+        <v>0.78</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.86</v>
+        <v>4.78</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.09</v>
+        <v>5</v>
       </c>
       <c r="BR8" t="n">
-        <v>81.81999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="BS8" t="n">
-        <v>72.73</v>
+        <v>73.91</v>
       </c>
       <c r="BT8" t="n">
-        <v>40.91</v>
+        <v>43.48</v>
       </c>
       <c r="BU8" t="n">
-        <v>18.18</v>
+        <v>21.74</v>
       </c>
       <c r="BV8" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BW8" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BX8" t="n">
-        <v>45.45</v>
+        <v>47.83</v>
       </c>
       <c r="BY8" t="n">
         <v>2.88</v>
@@ -4028,73 +4028,73 @@
         <v>2.9</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.4</v>
+        <v>3.39</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.44</v>
+        <v>3.42</v>
       </c>
       <c r="CC8" t="n">
-        <v>3.55</v>
+        <v>3.49</v>
       </c>
       <c r="CD8" t="n">
-        <v>3.96</v>
+        <v>3.88</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CF8" t="n">
         <v>2.86</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="CH8" t="n">
         <v>1.38</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CK8" t="n">
         <v>1.58</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CM8" t="n">
         <v>2.22</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CO8" t="n">
         <v>1.3</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.26</v>
+        <v>3.29</v>
       </c>
       <c r="CR8" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CS8" t="n">
-        <v>3.04</v>
+        <v>3.06</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CV8" t="n">
         <v>1.97</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CX8" t="n">
         <v>1.61</v>
@@ -4109,55 +4109,55 @@
         <v>1.74</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.58</v>
+        <v>3.61</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="DH8" t="n">
-        <v>111.27</v>
+        <v>109.48</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.04</v>
+        <v>-0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.91</v>
+        <v>4.82</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="DM8" t="n">
-        <v>68.45</v>
+        <v>67.18000000000001</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="DP8" t="n">
-        <v>15.04</v>
+        <v>15.09</v>
       </c>
       <c r="DQ8" t="n">
-        <v>13.5</v>
+        <v>13.26</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.73</v>
+        <v>7.78</v>
       </c>
       <c r="DS8" t="n">
         <v>0</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>48.95</v>
+        <v>48.87</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX8" t="n">
-        <v>12.18</v>
+        <v>12.05</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.68</v>
+        <v>8.48</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.5</v>
+        <v>3.57</v>
       </c>
       <c r="EA8" t="n">
-        <v>21.91</v>
+        <v>22</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="9">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
         <v>12</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E9" t="n">
         <v>0.25</v>
@@ -4290,139 +4290,139 @@
         <v>2.08</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AH9" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AI9" t="n">
-        <v>107.9</v>
+        <v>105.36</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="AL9" t="n">
-        <v>6.2</v>
+        <v>5.82</v>
       </c>
       <c r="AM9" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>59</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>12.82</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>13.27</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>6.82</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>50.55</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>13.82</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>10.55</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>22.64</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>10.57</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="BJ9" t="n">
         <v>0.7</v>
       </c>
-      <c r="AN9" t="n">
-        <v>59.7</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>51.7</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>10.68</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>0.73</v>
-      </c>
       <c r="BK9" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.91</v>
+        <v>4.74</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.77</v>
+        <v>5.83</v>
       </c>
       <c r="BR9" t="n">
-        <v>86.36</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="BS9" t="n">
-        <v>72.73</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BT9" t="n">
-        <v>50</v>
+        <v>47.83</v>
       </c>
       <c r="BU9" t="n">
-        <v>36.36</v>
+        <v>34.78</v>
       </c>
       <c r="BV9" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BW9" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX9" t="n">
-        <v>59.09</v>
+        <v>56.52</v>
       </c>
       <c r="BY9" t="n">
         <v>2.11</v>
@@ -4431,34 +4431,34 @@
         <v>2.1</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.48</v>
+        <v>3.47</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="CC9" t="n">
-        <v>2.77</v>
+        <v>2.86</v>
       </c>
       <c r="CD9" t="n">
-        <v>3.05</v>
+        <v>3.17</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="CH9" t="n">
         <v>1.36</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CK9" t="n">
         <v>1.61</v>
@@ -4476,10 +4476,10 @@
         <v>1.32</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.52</v>
+        <v>3.54</v>
       </c>
       <c r="CR9" t="n">
         <v>1.43</v>
@@ -4491,7 +4491,7 @@
         <v>2.84</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CV9" t="n">
         <v>1.83</v>
@@ -4518,49 +4518,49 @@
         <v>2.12</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.75</v>
+        <v>3.76</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="DG9" t="n">
-        <v>3.18</v>
+        <v>3.09</v>
       </c>
       <c r="DH9" t="n">
-        <v>112.82</v>
+        <v>111.39</v>
       </c>
       <c r="DI9" t="n">
         <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.73</v>
+        <v>2.78</v>
       </c>
       <c r="DK9" t="n">
-        <v>6.36</v>
+        <v>6.17</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="DM9" t="n">
-        <v>65.23</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.86</v>
+        <v>0.91</v>
       </c>
       <c r="DO9" t="n">
-        <v>3.18</v>
+        <v>3.09</v>
       </c>
       <c r="DP9" t="n">
-        <v>12.59</v>
+        <v>12.65</v>
       </c>
       <c r="DQ9" t="n">
-        <v>13.59</v>
+        <v>13.48</v>
       </c>
       <c r="DR9" t="n">
-        <v>7.23</v>
+        <v>7.04</v>
       </c>
       <c r="DS9" t="n">
         <v>0.13</v>
@@ -4572,28 +4572,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>51.96</v>
+        <v>51.4</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="DX9" t="n">
-        <v>15.23</v>
+        <v>14.83</v>
       </c>
       <c r="DY9" t="n">
-        <v>11.18</v>
+        <v>10.83</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="EA9" t="n">
-        <v>23.18</v>
+        <v>23.26</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="10">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C10" t="n">
         <v>11</v>
       </c>
       <c r="D10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E10" t="n">
         <v>0.27</v>
@@ -4693,139 +4693,139 @@
         <v>1.82</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AI10" t="n">
-        <v>107.09</v>
+        <v>109</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="AL10" t="n">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="AN10" t="n">
-        <v>49.45</v>
+        <v>49.92</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AQ10" t="n">
-        <v>15.36</v>
+        <v>14.83</v>
       </c>
       <c r="AR10" t="n">
-        <v>12.64</v>
+        <v>13</v>
       </c>
       <c r="AS10" t="n">
-        <v>8.82</v>
+        <v>8.5</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AU10" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>46</v>
+        <v>45.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BA10" t="n">
-        <v>10.09</v>
+        <v>9.83</v>
       </c>
       <c r="BB10" t="n">
-        <v>6.82</v>
+        <v>6.58</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="BD10" t="n">
-        <v>18.82</v>
+        <v>19.5</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
       <c r="BH10" t="n">
-        <v>7.18</v>
+        <v>7.26</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.77</v>
+        <v>0.83</v>
       </c>
       <c r="BL10" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="BQ10" t="n">
-        <v>3.23</v>
+        <v>3.3</v>
       </c>
       <c r="BR10" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BS10" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BT10" t="n">
-        <v>59.09</v>
+        <v>60.87</v>
       </c>
       <c r="BU10" t="n">
-        <v>27.27</v>
+        <v>30.43</v>
       </c>
       <c r="BV10" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BW10" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX10" t="n">
-        <v>68.18000000000001</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BY10" t="n">
         <v>2.64</v>
@@ -4834,25 +4834,25 @@
         <v>2.85</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.49</v>
+        <v>3.48</v>
       </c>
       <c r="CC10" t="n">
-        <v>4.55</v>
+        <v>4.38</v>
       </c>
       <c r="CD10" t="n">
-        <v>5.14</v>
+        <v>4.96</v>
       </c>
       <c r="CE10" t="n">
         <v>1.38</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="CH10" t="n">
         <v>1.39</v>
@@ -4861,13 +4861,13 @@
         <v>1.88</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CK10" t="n">
         <v>1.72</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="CM10" t="n">
         <v>2.02</v>
@@ -4879,7 +4879,7 @@
         <v>1.29</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CQ10" t="n">
         <v>3.34</v>
@@ -4909,10 +4909,10 @@
         <v>2.19</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="DB10" t="n">
         <v>1.32</v>
@@ -4924,79 +4924,79 @@
         <v>3.54</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="DH10" t="n">
-        <v>112</v>
+        <v>112.78</v>
       </c>
       <c r="DI10" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.46</v>
+        <v>2.39</v>
       </c>
       <c r="DK10" t="n">
-        <v>3.46</v>
+        <v>3.48</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.22</v>
+        <v>0.26</v>
       </c>
       <c r="DM10" t="n">
-        <v>55.45</v>
+        <v>55.43</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="DP10" t="n">
-        <v>14.31</v>
+        <v>14.08</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.91</v>
+        <v>13.09</v>
       </c>
       <c r="DR10" t="n">
-        <v>8.460000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>49.41</v>
+        <v>49</v>
       </c>
       <c r="DW10" t="n">
         <v>0.22</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.27</v>
+        <v>12.04</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.140000000000001</v>
+        <v>7.95</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.14</v>
+        <v>4.09</v>
       </c>
       <c r="EA10" t="n">
-        <v>22.04</v>
+        <v>22.26</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -5006,94 +5006,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D11" t="n">
         <v>12</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="F11" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="G11" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="H11" t="n">
-        <v>112.9</v>
+        <v>110.55</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="K11" t="n">
-        <v>4.3</v>
+        <v>3.91</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="M11" t="n">
-        <v>57.9</v>
+        <v>55.55</v>
       </c>
       <c r="N11" t="n">
-        <v>0.6</v>
+        <v>0.82</v>
       </c>
       <c r="O11" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>12.2</v>
+        <v>12</v>
       </c>
       <c r="Q11" t="n">
-        <v>12.5</v>
+        <v>12.45</v>
       </c>
       <c r="R11" t="n">
-        <v>7.9</v>
+        <v>7.64</v>
       </c>
       <c r="S11" t="n">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="T11" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>47.6</v>
+        <v>46.82</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z11" t="n">
-        <v>14.2</v>
+        <v>13.45</v>
       </c>
       <c r="AA11" t="n">
-        <v>9.9</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.3</v>
+        <v>4.09</v>
       </c>
       <c r="AC11" t="n">
-        <v>20.6</v>
+        <v>21.18</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AF11" t="n">
         <v>0.08</v>
@@ -5177,70 +5177,70 @@
         <v>2.25</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.859999999999999</v>
+        <v>9.65</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.41</v>
+        <v>0.57</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.27</v>
+        <v>1.39</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="BP11" t="n">
         <v>4.09</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.95</v>
+        <v>4.78</v>
       </c>
       <c r="BR11" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BS11" t="n">
-        <v>77.27</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="BT11" t="n">
-        <v>54.55</v>
+        <v>56.52</v>
       </c>
       <c r="BU11" t="n">
-        <v>36.36</v>
+        <v>39.13</v>
       </c>
       <c r="BV11" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BW11" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX11" t="n">
-        <v>63.64</v>
+        <v>60.87</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.83</v>
+        <v>3.09</v>
       </c>
       <c r="BZ11" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.33</v>
+        <v>3.37</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="CC11" t="n">
         <v>3.9</v>
@@ -5252,16 +5252,16 @@
         <v>1.43</v>
       </c>
       <c r="CF11" t="n">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CJ11" t="n">
         <v>1.92</v>
@@ -5273,7 +5273,7 @@
         <v>2.35</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CN11" t="n">
         <v>1.61</v>
@@ -5282,10 +5282,10 @@
         <v>1.33</v>
       </c>
       <c r="CP11" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.63</v>
+        <v>3.6</v>
       </c>
       <c r="CR11" t="n">
         <v>1.45</v>
@@ -5300,106 +5300,106 @@
         <v>1.36</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CZ11" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="DA11" t="n">
         <v>1.61</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.88</v>
+        <v>3.84</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="DG11" t="n">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="DH11" t="n">
-        <v>100.64</v>
+        <v>100.05</v>
       </c>
       <c r="DI11" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.14</v>
+        <v>3.96</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="DM11" t="n">
-        <v>51</v>
+        <v>50.18</v>
       </c>
       <c r="DN11" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="DP11" t="n">
-        <v>12.41</v>
+        <v>12.3</v>
       </c>
       <c r="DQ11" t="n">
-        <v>12.54</v>
+        <v>12.52</v>
       </c>
       <c r="DR11" t="n">
-        <v>8.130000000000001</v>
+        <v>8</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>44.95</v>
+        <v>44.7</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX11" t="n">
-        <v>12.23</v>
+        <v>11.95</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.359999999999999</v>
+        <v>8.17</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.86</v>
+        <v>3.78</v>
       </c>
       <c r="EA11" t="n">
-        <v>19.45</v>
+        <v>19.78</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
@@ -2654,7 +2654,7 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>60.42</v>
+        <v>60.33</v>
       </c>
       <c r="Y5" t="n">
         <v>0.25</v>
@@ -2960,7 +2960,7 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>59.26</v>
+        <v>59.22</v>
       </c>
       <c r="DW5" t="n">
         <v>0.13</v>
@@ -4347,7 +4347,7 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>50.55</v>
+        <v>50.64</v>
       </c>
       <c r="AZ9" t="n">
         <v>0.18</v>
@@ -4572,7 +4572,7 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>51.4</v>
+        <v>51.44</v>
       </c>
       <c r="DW9" t="n">
         <v>0.13</v>

--- a/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C4" t="n">
         <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2275,52 +2275,52 @@
         <v>1.91</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AI4" t="n">
-        <v>103.33</v>
+        <v>106.54</v>
       </c>
       <c r="AJ4" t="n">
         <v>0.08</v>
       </c>
       <c r="AK4" t="n">
-        <v>3.33</v>
+        <v>3.23</v>
       </c>
       <c r="AL4" t="n">
-        <v>3.33</v>
+        <v>3.31</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AN4" t="n">
-        <v>54</v>
+        <v>55.46</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AQ4" t="n">
-        <v>12.75</v>
+        <v>12.77</v>
       </c>
       <c r="AR4" t="n">
-        <v>10.33</v>
+        <v>11.08</v>
       </c>
       <c r="AS4" t="n">
         <v>8.92</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AV4" t="n">
         <v>0.08</v>
@@ -2332,82 +2332,82 @@
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>40.58</v>
+        <v>41.46</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BA4" t="n">
-        <v>9</v>
+        <v>8.85</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.42</v>
+        <v>6.38</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="BD4" t="n">
-        <v>22.33</v>
+        <v>22.23</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="BH4" t="n">
         <v>10</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BL4" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="BP4" t="n">
-        <v>5.04</v>
+        <v>4.96</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.87</v>
+        <v>4.96</v>
       </c>
       <c r="BR4" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS4" t="n">
-        <v>82.61</v>
+        <v>83.33</v>
       </c>
       <c r="BT4" t="n">
-        <v>60.87</v>
+        <v>58.33</v>
       </c>
       <c r="BU4" t="n">
-        <v>39.13</v>
+        <v>37.5</v>
       </c>
       <c r="BV4" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>69.56999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BY4" t="n">
         <v>4.17</v>
@@ -2416,82 +2416,82 @@
         <v>4.69</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.16</v>
+        <v>4.13</v>
       </c>
       <c r="CB4" t="n">
-        <v>4.28</v>
+        <v>4.23</v>
       </c>
       <c r="CC4" t="n">
-        <v>6.54</v>
+        <v>6.35</v>
       </c>
       <c r="CD4" t="n">
-        <v>9.06</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="CE4" t="n">
         <v>1.35</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="CH4" t="n">
         <v>1.44</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="CM4" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CO4" t="n">
         <v>1.26</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="CR4" t="n">
         <v>1.38</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.68</v>
+        <v>2.71</v>
       </c>
       <c r="CT4" t="n">
-        <v>3.05</v>
+        <v>3.03</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CV4" t="n">
         <v>1.91</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="DA4" t="n">
         <v>1.7</v>
@@ -2500,52 +2500,52 @@
         <v>1.28</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="DH4" t="n">
-        <v>109.91</v>
+        <v>111.38</v>
       </c>
       <c r="DI4" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.74</v>
+        <v>2.71</v>
       </c>
       <c r="DK4" t="n">
-        <v>3.61</v>
+        <v>3.59</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DM4" t="n">
-        <v>61.96</v>
+        <v>62.42</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="DP4" t="n">
-        <v>12.87</v>
+        <v>12.88</v>
       </c>
       <c r="DQ4" t="n">
-        <v>11.04</v>
+        <v>11.42</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.130000000000001</v>
+        <v>8.16</v>
       </c>
       <c r="DS4" t="n">
         <v>0.17</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>42.09</v>
+        <v>42.5</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.26</v>
+        <v>10.13</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.74</v>
+        <v>6.71</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.52</v>
+        <v>3.42</v>
       </c>
       <c r="EA4" t="n">
-        <v>21.39</v>
+        <v>21.37</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5" t="n">
         <v>12</v>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E5" t="n">
         <v>0.25</v>
@@ -2678,139 +2678,139 @@
         <v>1.67</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>3.09</v>
+        <v>3.33</v>
       </c>
       <c r="AI5" t="n">
-        <v>108</v>
+        <v>108.75</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="AL5" t="n">
-        <v>6.18</v>
+        <v>6.83</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.64</v>
+        <v>0.92</v>
       </c>
       <c r="AN5" t="n">
-        <v>64.09</v>
+        <v>67.33</v>
       </c>
       <c r="AO5" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.09</v>
+        <v>3.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>12.82</v>
+        <v>13.33</v>
       </c>
       <c r="AR5" t="n">
-        <v>14.73</v>
+        <v>14.42</v>
       </c>
       <c r="AS5" t="n">
-        <v>6.91</v>
+        <v>6.92</v>
       </c>
       <c r="AT5" t="n">
         <v>1</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>58</v>
+        <v>58.83</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>14</v>
+        <v>14.75</v>
       </c>
       <c r="BB5" t="n">
-        <v>9.550000000000001</v>
+        <v>10.25</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>20.91</v>
+        <v>20.92</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.130000000000001</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.78</v>
+        <v>4</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.22</v>
+        <v>5.25</v>
       </c>
       <c r="BR5" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS5" t="n">
-        <v>82.61</v>
+        <v>83.33</v>
       </c>
       <c r="BT5" t="n">
-        <v>39.13</v>
+        <v>37.5</v>
       </c>
       <c r="BU5" t="n">
-        <v>17.39</v>
+        <v>16.67</v>
       </c>
       <c r="BV5" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>34.78</v>
+        <v>37.5</v>
       </c>
       <c r="BY5" t="n">
         <v>1.68</v>
@@ -2819,16 +2819,16 @@
         <v>1.72</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.63</v>
+        <v>3.61</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.59</v>
+        <v>3.57</v>
       </c>
       <c r="CC5" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="CD5" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="CE5" t="n">
         <v>1.41</v>
@@ -2858,7 +2858,7 @@
         <v>2.06</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CO5" t="n">
         <v>1.31</v>
@@ -2867,16 +2867,16 @@
         <v>2.07</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.63</v>
+        <v>3.64</v>
       </c>
       <c r="CR5" t="n">
         <v>1.44</v>
       </c>
       <c r="CS5" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="CU5" t="n">
         <v>1.36</v>
@@ -2906,82 +2906,82 @@
         <v>2.14</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.81</v>
+        <v>3.82</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.35</v>
+        <v>3.46</v>
       </c>
       <c r="DH5" t="n">
-        <v>113.39</v>
+        <v>113.54</v>
       </c>
       <c r="DI5" t="n">
         <v>-0.04</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.56</v>
+        <v>5.92</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.35</v>
+        <v>0.5</v>
       </c>
       <c r="DM5" t="n">
-        <v>65.34999999999999</v>
+        <v>66.92</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.22</v>
+        <v>2.46</v>
       </c>
       <c r="DP5" t="n">
-        <v>12.35</v>
+        <v>12.62</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15.09</v>
+        <v>14.92</v>
       </c>
       <c r="DR5" t="n">
-        <v>6.13</v>
+        <v>6.17</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>59.22</v>
+        <v>59.58</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX5" t="n">
-        <v>14.74</v>
+        <v>15.08</v>
       </c>
       <c r="DY5" t="n">
-        <v>9.48</v>
+        <v>9.83</v>
       </c>
       <c r="DZ5" t="n">
-        <v>5.26</v>
+        <v>5.25</v>
       </c>
       <c r="EA5" t="n">
-        <v>21.87</v>
+        <v>21.83</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C6" t="n">
         <v>11</v>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E6" t="n">
         <v>0.27</v>
@@ -3084,49 +3084,49 @@
         <v>0.08</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.5</v>
+        <v>1.69</v>
       </c>
       <c r="AI6" t="n">
-        <v>106.58</v>
+        <v>103.77</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AL6" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="AN6" t="n">
-        <v>57.58</v>
+        <v>55.54</v>
       </c>
       <c r="AO6" t="n">
         <v>0.92</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ6" t="n">
-        <v>10.83</v>
+        <v>10.62</v>
       </c>
       <c r="AR6" t="n">
-        <v>11.58</v>
+        <v>11.23</v>
       </c>
       <c r="AS6" t="n">
-        <v>9.83</v>
+        <v>10.31</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AV6" t="n">
         <v>0.08</v>
@@ -3138,82 +3138,82 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>47.83</v>
+        <v>48.15</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>8.83</v>
+        <v>9</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.58</v>
+        <v>5.77</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="BD6" t="n">
-        <v>23.08</v>
+        <v>22.54</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.74</v>
+        <v>2.67</v>
       </c>
       <c r="BH6" t="n">
-        <v>10</v>
+        <v>10.08</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.74</v>
+        <v>2.67</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.35</v>
+        <v>4.38</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.7</v>
+        <v>4.79</v>
       </c>
       <c r="BR6" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS6" t="n">
-        <v>82.61</v>
+        <v>79.17</v>
       </c>
       <c r="BT6" t="n">
-        <v>60.87</v>
+        <v>58.33</v>
       </c>
       <c r="BU6" t="n">
-        <v>21.74</v>
+        <v>20.83</v>
       </c>
       <c r="BV6" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BW6" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX6" t="n">
-        <v>65.22</v>
+        <v>62.5</v>
       </c>
       <c r="BY6" t="n">
         <v>2.55</v>
@@ -3222,16 +3222,16 @@
         <v>2.72</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.39</v>
+        <v>3.38</v>
       </c>
       <c r="CB6" t="n">
         <v>3.51</v>
       </c>
       <c r="CC6" t="n">
-        <v>4.1</v>
+        <v>4.03</v>
       </c>
       <c r="CD6" t="n">
-        <v>4.75</v>
+        <v>4.68</v>
       </c>
       <c r="CE6" t="n">
         <v>1.4</v>
@@ -3240,25 +3240,25 @@
         <v>2.87</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="CH6" t="n">
         <v>1.37</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CN6" t="n">
         <v>1.6</v>
@@ -3270,25 +3270,25 @@
         <v>2.03</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.47</v>
+        <v>3.46</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="CU6" t="n">
         <v>1.39</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CX6" t="n">
         <v>1.78</v>
@@ -3306,52 +3306,52 @@
         <v>1.34</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.67</v>
+        <v>3.66</v>
       </c>
       <c r="DE6" t="n">
         <v>0.17</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="DH6" t="n">
-        <v>106.47</v>
+        <v>104.96</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="DJ6" t="n">
+        <v>2</v>
+      </c>
+      <c r="DK6" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="DL6" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="DM6" t="n">
+        <v>56.67</v>
+      </c>
+      <c r="DN6" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="DO6" t="n">
         <v>1.96</v>
       </c>
-      <c r="DK6" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="DL6" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="DM6" t="n">
-        <v>57.78</v>
-      </c>
-      <c r="DN6" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="DO6" t="n">
-        <v>1.92</v>
-      </c>
       <c r="DP6" t="n">
-        <v>10.95</v>
+        <v>10.84</v>
       </c>
       <c r="DQ6" t="n">
-        <v>11.61</v>
+        <v>11.42</v>
       </c>
       <c r="DR6" t="n">
-        <v>10.04</v>
+        <v>10.29</v>
       </c>
       <c r="DS6" t="n">
         <v>0.04</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>49.74</v>
+        <v>49.83</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>10</v>
+        <v>10.04</v>
       </c>
       <c r="DY6" t="n">
-        <v>6.57</v>
+        <v>6.63</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.44</v>
+        <v>3.42</v>
       </c>
       <c r="EA6" t="n">
-        <v>22.39</v>
+        <v>22.13</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -3797,10 +3797,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D8" t="n">
         <v>11</v>
@@ -3809,82 +3809,82 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="G8" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="H8" t="n">
-        <v>116.5</v>
+        <v>116.31</v>
       </c>
       <c r="I8" t="n">
         <v>0.08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="K8" t="n">
-        <v>5.58</v>
+        <v>5.69</v>
       </c>
       <c r="L8" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="M8" t="n">
-        <v>78.75</v>
+        <v>78.84999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="O8" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="P8" t="n">
-        <v>14.58</v>
+        <v>14.69</v>
       </c>
       <c r="Q8" t="n">
-        <v>13.75</v>
+        <v>13.77</v>
       </c>
       <c r="R8" t="n">
-        <v>7.25</v>
+        <v>6.85</v>
       </c>
       <c r="S8" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="T8" t="n">
-        <v>0.67</v>
+        <v>0.77</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>49.08</v>
+        <v>49</v>
       </c>
       <c r="Y8" t="n">
         <v>0.08</v>
       </c>
       <c r="Z8" t="n">
-        <v>12.17</v>
+        <v>12.23</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.75</v>
+        <v>8.77</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.42</v>
+        <v>3.46</v>
       </c>
       <c r="AC8" t="n">
-        <v>21.42</v>
+        <v>21.23</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.17</v>
+        <v>2.31</v>
       </c>
       <c r="AF8" t="n">
         <v>0.09</v>
@@ -3968,70 +3968,70 @@
         <v>2.18</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="BH8" t="n">
         <v>9.83</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.78</v>
+        <v>0.83</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.78</v>
+        <v>4.71</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5</v>
+        <v>5.08</v>
       </c>
       <c r="BR8" t="n">
-        <v>82.61</v>
+        <v>83.33</v>
       </c>
       <c r="BS8" t="n">
-        <v>73.91</v>
+        <v>75</v>
       </c>
       <c r="BT8" t="n">
-        <v>43.48</v>
+        <v>41.67</v>
       </c>
       <c r="BU8" t="n">
-        <v>21.74</v>
+        <v>20.83</v>
       </c>
       <c r="BV8" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BW8" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BX8" t="n">
-        <v>47.83</v>
+        <v>45.83</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="CA8" t="n">
         <v>3.39</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.42</v>
+        <v>3.41</v>
       </c>
       <c r="CC8" t="n">
         <v>3.49</v>
@@ -4061,7 +4061,7 @@
         <v>1.58</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="CM8" t="n">
         <v>2.22</v>
@@ -4070,10 +4070,10 @@
         <v>1.75</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CQ8" t="n">
         <v>3.29</v>
@@ -4100,13 +4100,13 @@
         <v>1.61</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="DB8" t="n">
         <v>1.33</v>
@@ -4115,82 +4115,82 @@
         <v>2.07</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.61</v>
+        <v>3.62</v>
       </c>
       <c r="DE8" t="n">
         <v>0.04</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="DH8" t="n">
-        <v>109.48</v>
+        <v>109.67</v>
       </c>
       <c r="DI8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.35</v>
+        <v>2.41</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.82</v>
+        <v>4.92</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="DM8" t="n">
-        <v>67.18000000000001</v>
+        <v>67.70999999999999</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="DP8" t="n">
-        <v>15.09</v>
+        <v>15.13</v>
       </c>
       <c r="DQ8" t="n">
-        <v>13.26</v>
+        <v>13.29</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.78</v>
+        <v>7.54</v>
       </c>
       <c r="DS8" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="DT8" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>48.87</v>
+        <v>48.84</v>
       </c>
       <c r="DW8" t="n">
         <v>0.17</v>
       </c>
       <c r="DX8" t="n">
-        <v>12.05</v>
+        <v>12.08</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.48</v>
+        <v>8.5</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.57</v>
+        <v>3.58</v>
       </c>
       <c r="EA8" t="n">
-        <v>22</v>
+        <v>21.88</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="9">
@@ -4603,94 +4603,94 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D10" t="n">
         <v>12</v>
       </c>
       <c r="E10" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="F10" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="G10" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="H10" t="n">
-        <v>116.91</v>
+        <v>115.75</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="K10" t="n">
-        <v>4</v>
+        <v>4.08</v>
       </c>
       <c r="L10" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="M10" t="n">
-        <v>61.45</v>
+        <v>61.25</v>
       </c>
       <c r="N10" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="O10" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="P10" t="n">
-        <v>13.27</v>
+        <v>12.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>13.18</v>
+        <v>12.92</v>
       </c>
       <c r="R10" t="n">
-        <v>8.09</v>
+        <v>8</v>
       </c>
       <c r="S10" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="T10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>52.42</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>14.83</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>9.92</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>24.83</v>
+      </c>
+      <c r="AD10" t="n">
         <v>1.73</v>
       </c>
-      <c r="U10" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>52.82</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>14.45</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>9.449999999999999</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>25.27</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.71</v>
-      </c>
       <c r="AE10" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AF10" t="n">
         <v>0.08</v>
@@ -4774,70 +4774,70 @@
         <v>2.17</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="BH10" t="n">
-        <v>7.26</v>
+        <v>7.46</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BL10" t="n">
         <v>1.04</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.13</v>
+        <v>3.21</v>
       </c>
       <c r="BQ10" t="n">
-        <v>3.3</v>
+        <v>3.46</v>
       </c>
       <c r="BR10" t="n">
-        <v>91.3</v>
+        <v>91.67</v>
       </c>
       <c r="BS10" t="n">
-        <v>91.3</v>
+        <v>87.5</v>
       </c>
       <c r="BT10" t="n">
-        <v>60.87</v>
+        <v>58.33</v>
       </c>
       <c r="BU10" t="n">
-        <v>30.43</v>
+        <v>29.17</v>
       </c>
       <c r="BV10" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BW10" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX10" t="n">
-        <v>69.56999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="BZ10" t="n">
-        <v>2.85</v>
+        <v>2.78</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.4</v>
+        <v>3.39</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.48</v>
+        <v>3.47</v>
       </c>
       <c r="CC10" t="n">
         <v>4.38</v>
@@ -4852,25 +4852,25 @@
         <v>2.85</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CK10" t="n">
         <v>1.72</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CN10" t="n">
         <v>1.61</v>
@@ -4879,7 +4879,7 @@
         <v>1.29</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CQ10" t="n">
         <v>3.34</v>
@@ -4891,16 +4891,16 @@
         <v>3.01</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="CU10" t="n">
         <v>1.39</v>
       </c>
       <c r="CV10" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CX10" t="n">
         <v>1.74</v>
@@ -4912,7 +4912,7 @@
         <v>2.01</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="DB10" t="n">
         <v>1.32</v>
@@ -4921,49 +4921,49 @@
         <v>2.04</v>
       </c>
       <c r="DD10" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="DE10" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="DF10" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="DG10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="DH10" t="n">
+        <v>112.38</v>
+      </c>
+      <c r="DI10" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="DJ10" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="DK10" t="n">
         <v>3.54</v>
       </c>
-      <c r="DE10" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="DF10" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="DG10" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="DH10" t="n">
-        <v>112.78</v>
-      </c>
-      <c r="DI10" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="DJ10" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="DK10" t="n">
-        <v>3.48</v>
-      </c>
       <c r="DL10" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DM10" t="n">
-        <v>55.43</v>
+        <v>55.58</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="DP10" t="n">
-        <v>14.08</v>
+        <v>13.79</v>
       </c>
       <c r="DQ10" t="n">
-        <v>13.09</v>
+        <v>12.96</v>
       </c>
       <c r="DR10" t="n">
-        <v>8.300000000000001</v>
+        <v>8.25</v>
       </c>
       <c r="DS10" t="n">
         <v>0.08</v>
@@ -4975,28 +4975,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>49</v>
+        <v>48.96</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.04</v>
+        <v>12.33</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.95</v>
+        <v>8.25</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.09</v>
+        <v>4.08</v>
       </c>
       <c r="EA10" t="n">
-        <v>22.26</v>
+        <v>22.17</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="EC10" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="11">
@@ -5006,94 +5006,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D11" t="n">
         <v>12</v>
       </c>
       <c r="E11" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="F11" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="G11" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="H11" t="n">
-        <v>110.55</v>
+        <v>107.92</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="K11" t="n">
-        <v>3.91</v>
+        <v>3.67</v>
       </c>
       <c r="L11" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="M11" t="n">
-        <v>55.55</v>
+        <v>54.5</v>
       </c>
       <c r="N11" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="O11" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="P11" t="n">
-        <v>12</v>
+        <v>11.92</v>
       </c>
       <c r="Q11" t="n">
-        <v>12.45</v>
+        <v>13</v>
       </c>
       <c r="R11" t="n">
-        <v>7.64</v>
+        <v>7.58</v>
       </c>
       <c r="S11" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="T11" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="U11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="V11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>46.82</v>
+        <v>45.58</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="Z11" t="n">
-        <v>13.45</v>
+        <v>12.83</v>
       </c>
       <c r="AA11" t="n">
-        <v>9.359999999999999</v>
+        <v>8.92</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.09</v>
+        <v>3.92</v>
       </c>
       <c r="AC11" t="n">
-        <v>21.18</v>
+        <v>20.83</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AF11" t="n">
         <v>0.08</v>
@@ -5177,70 +5177,70 @@
         <v>2.25</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.74</v>
+        <v>2.71</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.65</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.74</v>
+        <v>2.71</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.09</v>
+        <v>4.29</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.78</v>
+        <v>4.83</v>
       </c>
       <c r="BR11" t="n">
-        <v>91.3</v>
+        <v>91.67</v>
       </c>
       <c r="BS11" t="n">
-        <v>78.26000000000001</v>
+        <v>79.17</v>
       </c>
       <c r="BT11" t="n">
-        <v>56.52</v>
+        <v>54.17</v>
       </c>
       <c r="BU11" t="n">
-        <v>39.13</v>
+        <v>37.5</v>
       </c>
       <c r="BV11" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BW11" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX11" t="n">
-        <v>60.87</v>
+        <v>62.5</v>
       </c>
       <c r="BY11" t="n">
-        <v>3.09</v>
+        <v>3.13</v>
       </c>
       <c r="BZ11" t="n">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.37</v>
+        <v>3.35</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.4</v>
+        <v>3.39</v>
       </c>
       <c r="CC11" t="n">
         <v>3.9</v>
@@ -5252,13 +5252,13 @@
         <v>1.43</v>
       </c>
       <c r="CF11" t="n">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="CG11" t="n">
         <v>2.63</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CI11" t="n">
         <v>1.81</v>
@@ -5285,19 +5285,19 @@
         <v>2.08</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="CR11" t="n">
         <v>1.45</v>
       </c>
       <c r="CS11" t="n">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="CT11" t="n">
         <v>2.76</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CV11" t="n">
         <v>1.88</v>
@@ -5324,82 +5324,82 @@
         <v>2.16</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.84</v>
+        <v>3.85</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="DG11" t="n">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="DH11" t="n">
-        <v>100.05</v>
+        <v>99.17</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="DK11" t="n">
-        <v>3.96</v>
+        <v>3.83</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="DM11" t="n">
-        <v>50.18</v>
+        <v>49.88</v>
       </c>
       <c r="DN11" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="DP11" t="n">
-        <v>12.3</v>
+        <v>12.25</v>
       </c>
       <c r="DQ11" t="n">
-        <v>12.52</v>
+        <v>12.79</v>
       </c>
       <c r="DR11" t="n">
+        <v>7.96</v>
+      </c>
+      <c r="DS11" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="DT11" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="DU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV11" t="n">
+        <v>44.16</v>
+      </c>
+      <c r="DW11" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="DX11" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="DY11" t="n">
         <v>8</v>
       </c>
-      <c r="DS11" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="DT11" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="DU11" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV11" t="n">
-        <v>44.7</v>
-      </c>
-      <c r="DW11" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="DX11" t="n">
-        <v>11.95</v>
-      </c>
-      <c r="DY11" t="n">
-        <v>8.17</v>
-      </c>
       <c r="DZ11" t="n">
-        <v>3.78</v>
+        <v>3.71</v>
       </c>
       <c r="EA11" t="n">
-        <v>19.78</v>
+        <v>19.66</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" t="n">
         <v>12</v>
       </c>
       <c r="E2" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="F2" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="G2" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="H2" t="n">
-        <v>123.91</v>
+        <v>119.33</v>
       </c>
       <c r="I2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="J2" t="n">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="K2" t="n">
-        <v>6.36</v>
+        <v>6.25</v>
       </c>
       <c r="L2" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="M2" t="n">
-        <v>75.36</v>
+        <v>72.17</v>
       </c>
       <c r="N2" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="O2" t="n">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
       <c r="P2" t="n">
-        <v>11.36</v>
+        <v>11.08</v>
       </c>
       <c r="Q2" t="n">
-        <v>12.73</v>
+        <v>12.25</v>
       </c>
       <c r="R2" t="n">
-        <v>5.36</v>
+        <v>5.42</v>
       </c>
       <c r="S2" t="n">
-        <v>0.73</v>
+        <v>0.83</v>
       </c>
       <c r="T2" t="n">
-        <v>2.55</v>
+        <v>2.67</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>58.27</v>
+        <v>58.17</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z2" t="n">
-        <v>17</v>
+        <v>17.08</v>
       </c>
       <c r="AA2" t="n">
-        <v>10.18</v>
+        <v>10.25</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.82</v>
+        <v>6.83</v>
       </c>
       <c r="AC2" t="n">
-        <v>22.36</v>
+        <v>21.83</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AF2" t="n">
         <v>0.08</v>
@@ -1550,70 +1550,70 @@
         <v>1.83</v>
       </c>
       <c r="BG2" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.699999999999999</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="BI2" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.57</v>
+        <v>4.54</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.09</v>
+        <v>5.04</v>
       </c>
       <c r="BR2" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS2" t="n">
-        <v>91.3</v>
+        <v>91.67</v>
       </c>
       <c r="BT2" t="n">
-        <v>65.22</v>
+        <v>66.67</v>
       </c>
       <c r="BU2" t="n">
-        <v>30.43</v>
+        <v>33.33</v>
       </c>
       <c r="BV2" t="n">
-        <v>8.699999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="BW2" t="n">
-        <v>4.35</v>
+        <v>8.33</v>
       </c>
       <c r="BX2" t="n">
-        <v>47.83</v>
+        <v>50</v>
       </c>
       <c r="BY2" t="n">
         <v>1.29</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.64</v>
+        <v>4.66</v>
       </c>
       <c r="CB2" t="n">
-        <v>5.01</v>
+        <v>5.04</v>
       </c>
       <c r="CC2" t="n">
         <v>1.62</v>
@@ -1628,7 +1628,7 @@
         <v>2.49</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="CH2" t="n">
         <v>1.49</v>
@@ -1637,19 +1637,19 @@
         <v>1.79</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CL2" t="n">
         <v>2.15</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CO2" t="n">
         <v>1.22</v>
@@ -1658,7 +1658,7 @@
         <v>1.74</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="CR2" t="n">
         <v>1.38</v>
@@ -1673,10 +1673,10 @@
         <v>1.53</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CW2" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CX2" t="n">
         <v>1.59</v>
@@ -1700,79 +1700,79 @@
         <v>2.88</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.35</v>
+        <v>3.33</v>
       </c>
       <c r="DH2" t="n">
-        <v>122.26</v>
+        <v>120.04</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.13</v>
+        <v>2.04</v>
       </c>
       <c r="DK2" t="n">
-        <v>6.43</v>
+        <v>6.38</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="DM2" t="n">
-        <v>75.43000000000001</v>
+        <v>73.83</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.66</v>
+        <v>0.62</v>
       </c>
       <c r="DO2" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="DP2" t="n">
-        <v>12.61</v>
+        <v>12.42</v>
       </c>
       <c r="DQ2" t="n">
-        <v>13.17</v>
+        <v>12.92</v>
       </c>
       <c r="DR2" t="n">
-        <v>5.61</v>
+        <v>5.62</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>56.65</v>
+        <v>56.67</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX2" t="n">
-        <v>16.39</v>
+        <v>16.45</v>
       </c>
       <c r="DY2" t="n">
-        <v>10.57</v>
+        <v>10.58</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5.83</v>
+        <v>5.88</v>
       </c>
       <c r="EA2" t="n">
-        <v>23.39</v>
+        <v>23.08</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C3" t="n">
         <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3" t="n">
         <v>0.17</v>
@@ -1875,136 +1875,136 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AI3" t="n">
-        <v>96.55</v>
+        <v>93.83</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="AL3" t="n">
-        <v>5.18</v>
+        <v>5</v>
       </c>
       <c r="AM3" t="n">
         <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>54.36</v>
+        <v>52.75</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="AQ3" t="n">
-        <v>11.27</v>
+        <v>11</v>
       </c>
       <c r="AR3" t="n">
-        <v>13.09</v>
+        <v>12.58</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.27</v>
+        <v>8.42</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.36</v>
+        <v>1.58</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>44.91</v>
+        <v>44.75</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BA3" t="n">
-        <v>12.91</v>
+        <v>12.67</v>
       </c>
       <c r="BB3" t="n">
-        <v>9.09</v>
+        <v>8.83</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.82</v>
+        <v>3.83</v>
       </c>
       <c r="BD3" t="n">
-        <v>19.82</v>
+        <v>19.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="BH3" t="n">
-        <v>8.779999999999999</v>
+        <v>8.75</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.78</v>
+        <v>3.79</v>
       </c>
       <c r="BQ3" t="n">
         <v>3.96</v>
       </c>
       <c r="BR3" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS3" t="n">
-        <v>73.91</v>
+        <v>75</v>
       </c>
       <c r="BT3" t="n">
-        <v>47.83</v>
+        <v>50</v>
       </c>
       <c r="BU3" t="n">
-        <v>26.09</v>
+        <v>29.17</v>
       </c>
       <c r="BV3" t="n">
-        <v>4.35</v>
+        <v>8.33</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="BX3" t="n">
-        <v>56.52</v>
+        <v>58.33</v>
       </c>
       <c r="BY3" t="n">
         <v>2.96</v>
@@ -2013,40 +2013,40 @@
         <v>3.11</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.49</v>
+        <v>3.56</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.58</v>
+        <v>3.67</v>
       </c>
       <c r="CC3" t="n">
-        <v>5.28</v>
+        <v>5.54</v>
       </c>
       <c r="CD3" t="n">
-        <v>5.37</v>
+        <v>5.81</v>
       </c>
       <c r="CE3" t="n">
         <v>1.4</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CK3" t="n">
         <v>1.68</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="CM3" t="n">
         <v>2.06</v>
@@ -2058,10 +2058,10 @@
         <v>1.31</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.49</v>
+        <v>3.45</v>
       </c>
       <c r="CR3" t="n">
         <v>1.43</v>
@@ -2076,10 +2076,10 @@
         <v>1.39</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="CX3" t="n">
         <v>1.72</v>
@@ -2094,88 +2094,88 @@
         <v>1.63</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.71</v>
+        <v>3.68</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="DG3" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="DH3" t="n">
+        <v>96.12</v>
+      </c>
+      <c r="DI3" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="DJ3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="DK3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="DL3" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="DM3" t="n">
+        <v>51.08</v>
+      </c>
+      <c r="DN3" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="DO3" t="n">
         <v>1.92</v>
       </c>
-      <c r="DH3" t="n">
-        <v>97.53</v>
-      </c>
-      <c r="DI3" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="DJ3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="DK3" t="n">
-        <v>4.56</v>
-      </c>
-      <c r="DL3" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="DM3" t="n">
-        <v>51.78</v>
-      </c>
-      <c r="DN3" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="DO3" t="n">
-        <v>1.91</v>
-      </c>
       <c r="DP3" t="n">
-        <v>11.48</v>
+        <v>11.34</v>
       </c>
       <c r="DQ3" t="n">
-        <v>13.48</v>
+        <v>13.2</v>
       </c>
       <c r="DR3" t="n">
-        <v>8.26</v>
+        <v>8.33</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>47.09</v>
+        <v>46.92</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX3" t="n">
-        <v>11.91</v>
+        <v>11.84</v>
       </c>
       <c r="DY3" t="n">
-        <v>8.09</v>
+        <v>8</v>
       </c>
       <c r="DZ3" t="n">
         <v>3.83</v>
       </c>
       <c r="EA3" t="n">
-        <v>20.65</v>
+        <v>20.46</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="4">
@@ -2314,7 +2314,7 @@
         <v>11.08</v>
       </c>
       <c r="AS4" t="n">
-        <v>8.92</v>
+        <v>9</v>
       </c>
       <c r="AT4" t="n">
         <v>2.15</v>
@@ -2332,7 +2332,7 @@
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>41.46</v>
+        <v>41.54</v>
       </c>
       <c r="AZ4" t="n">
         <v>0.31</v>
@@ -2545,7 +2545,7 @@
         <v>11.42</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.16</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="DS4" t="n">
         <v>0.17</v>
@@ -2557,7 +2557,7 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>42.5</v>
+        <v>42.54</v>
       </c>
       <c r="DW4" t="n">
         <v>0.21</v>
@@ -2828,7 +2828,7 @@
         <v>2.28</v>
       </c>
       <c r="CD5" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="CE5" t="n">
         <v>1.41</v>
@@ -2885,13 +2885,13 @@
         <v>1.81</v>
       </c>
       <c r="CW5" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CX5" t="n">
         <v>1.71</v>
       </c>
       <c r="CY5" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CZ5" t="n">
         <v>2.06</v>
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C7" t="n">
         <v>12</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3484,139 +3484,139 @@
         <v>2.08</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.73</v>
+        <v>2.67</v>
       </c>
       <c r="AI7" t="n">
-        <v>112.09</v>
+        <v>113.83</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="AL7" t="n">
-        <v>4.82</v>
+        <v>4.75</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AN7" t="n">
-        <v>60.18</v>
+        <v>60.83</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AP7" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="AQ7" t="n">
-        <v>14.91</v>
+        <v>14.58</v>
       </c>
       <c r="AR7" t="n">
-        <v>10.64</v>
+        <v>10.75</v>
       </c>
       <c r="AS7" t="n">
-        <v>6.91</v>
+        <v>6.75</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AU7" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>52</v>
+        <v>52.58</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BA7" t="n">
-        <v>10.55</v>
+        <v>10.33</v>
       </c>
       <c r="BB7" t="n">
-        <v>7.55</v>
+        <v>7.33</v>
       </c>
       <c r="BC7" t="n">
         <v>3</v>
       </c>
       <c r="BD7" t="n">
-        <v>20.73</v>
+        <v>21.17</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.74</v>
+        <v>8.58</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BL7" t="n">
         <v>1.04</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.83</v>
+        <v>3.75</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.91</v>
+        <v>4.83</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>91.3</v>
+        <v>91.67</v>
       </c>
       <c r="BT7" t="n">
-        <v>47.83</v>
+        <v>45.83</v>
       </c>
       <c r="BU7" t="n">
-        <v>26.09</v>
+        <v>25</v>
       </c>
       <c r="BV7" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BW7" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX7" t="n">
-        <v>73.91</v>
+        <v>70.83</v>
       </c>
       <c r="BY7" t="n">
         <v>2.9</v>
@@ -3631,10 +3631,10 @@
         <v>3.57</v>
       </c>
       <c r="CC7" t="n">
-        <v>4.39</v>
+        <v>4.44</v>
       </c>
       <c r="CD7" t="n">
-        <v>4.67</v>
+        <v>4.72</v>
       </c>
       <c r="CE7" t="n">
         <v>1.38</v>
@@ -3658,10 +3658,10 @@
         <v>1.58</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CN7" t="n">
         <v>1.74</v>
@@ -3673,7 +3673,7 @@
         <v>1.96</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.31</v>
+        <v>3.29</v>
       </c>
       <c r="CR7" t="n">
         <v>1.4</v>
@@ -3682,7 +3682,7 @@
         <v>2.96</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="CU7" t="n">
         <v>1.4</v>
@@ -3712,79 +3712,79 @@
         <v>2.03</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.52</v>
+        <v>3.51</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="DH7" t="n">
-        <v>106.83</v>
+        <v>107.92</v>
       </c>
       <c r="DI7" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="DJ7" t="n">
         <v>2.08</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.26</v>
+        <v>4.25</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DM7" t="n">
-        <v>58.56</v>
+        <v>58.96</v>
       </c>
       <c r="DN7" t="n">
         <v>0.83</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="DP7" t="n">
-        <v>14.65</v>
+        <v>14.5</v>
       </c>
       <c r="DQ7" t="n">
         <v>12</v>
       </c>
       <c r="DR7" t="n">
-        <v>7.09</v>
+        <v>7</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>51.22</v>
+        <v>51.54</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX7" t="n">
-        <v>10.7</v>
+        <v>10.58</v>
       </c>
       <c r="DY7" t="n">
-        <v>6.96</v>
+        <v>6.88</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.74</v>
+        <v>3.71</v>
       </c>
       <c r="EA7" t="n">
-        <v>21.83</v>
+        <v>22</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="EC7" t="n">
         <v>1.96</v>
@@ -3863,7 +3863,7 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>49</v>
+        <v>48.92</v>
       </c>
       <c r="Y8" t="n">
         <v>0.08</v>
@@ -3878,7 +3878,7 @@
         <v>3.46</v>
       </c>
       <c r="AC8" t="n">
-        <v>21.23</v>
+        <v>21.31</v>
       </c>
       <c r="AD8" t="n">
         <v>1.59</v>
@@ -4169,7 +4169,7 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>48.84</v>
+        <v>48.79</v>
       </c>
       <c r="DW8" t="n">
         <v>0.17</v>
@@ -4184,7 +4184,7 @@
         <v>3.58</v>
       </c>
       <c r="EA8" t="n">
-        <v>21.88</v>
+        <v>21.92</v>
       </c>
       <c r="EB8" t="n">
         <v>1.51</v>
@@ -4200,61 +4200,61 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D9" t="n">
         <v>11</v>
       </c>
       <c r="E9" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="F9" t="n">
-        <v>1.42</v>
+        <v>1.62</v>
       </c>
       <c r="G9" t="n">
-        <v>3.17</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>116.92</v>
+        <v>117.62</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="K9" t="n">
-        <v>6.5</v>
+        <v>6.08</v>
       </c>
       <c r="L9" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="M9" t="n">
-        <v>69.83</v>
+        <v>69</v>
       </c>
       <c r="N9" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>3.33</v>
+        <v>3.08</v>
       </c>
       <c r="P9" t="n">
-        <v>12.5</v>
+        <v>12.38</v>
       </c>
       <c r="Q9" t="n">
-        <v>13.67</v>
+        <v>13.54</v>
       </c>
       <c r="R9" t="n">
-        <v>7.25</v>
+        <v>7.31</v>
       </c>
       <c r="S9" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="T9" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="U9" t="n">
         <v>0.08</v>
@@ -4266,28 +4266,28 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>52.17</v>
+        <v>51.31</v>
       </c>
       <c r="Y9" t="n">
         <v>0.08</v>
       </c>
       <c r="Z9" t="n">
-        <v>15.75</v>
+        <v>15.08</v>
       </c>
       <c r="AA9" t="n">
-        <v>11.08</v>
+        <v>10.62</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.67</v>
+        <v>4.46</v>
       </c>
       <c r="AC9" t="n">
-        <v>23.83</v>
+        <v>23.46</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.08</v>
+        <v>2.23</v>
       </c>
       <c r="AF9" t="n">
         <v>0.18</v>
@@ -4371,67 +4371,67 @@
         <v>3</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.57</v>
+        <v>2.54</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.57</v>
+        <v>10.33</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.57</v>
+        <v>2.54</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.74</v>
+        <v>4.62</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.83</v>
+        <v>5.71</v>
       </c>
       <c r="BR9" t="n">
-        <v>86.95999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BS9" t="n">
-        <v>69.56999999999999</v>
+        <v>70.83</v>
       </c>
       <c r="BT9" t="n">
-        <v>47.83</v>
+        <v>45.83</v>
       </c>
       <c r="BU9" t="n">
-        <v>34.78</v>
+        <v>33.33</v>
       </c>
       <c r="BV9" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BW9" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX9" t="n">
-        <v>56.52</v>
+        <v>54.17</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.47</v>
+        <v>3.48</v>
       </c>
       <c r="CB9" t="n">
         <v>3.6</v>
@@ -4443,28 +4443,28 @@
         <v>3.17</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CJ9" t="n">
         <v>1.95</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="CM9" t="n">
         <v>1.98</v>
@@ -4473,16 +4473,16 @@
         <v>1.58</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.54</v>
+        <v>3.51</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CS9" t="n">
         <v>3.09</v>
@@ -4503,10 +4503,10 @@
         <v>1.71</v>
       </c>
       <c r="CY9" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="DA9" t="n">
         <v>1.64</v>
@@ -4518,49 +4518,49 @@
         <v>2.12</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.76</v>
+        <v>3.75</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.74</v>
+        <v>1.84</v>
       </c>
       <c r="DG9" t="n">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="DH9" t="n">
-        <v>111.39</v>
+        <v>112</v>
       </c>
       <c r="DI9" t="n">
         <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.78</v>
+        <v>2.83</v>
       </c>
       <c r="DK9" t="n">
-        <v>6.17</v>
+        <v>5.96</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="DM9" t="n">
-        <v>64.65000000000001</v>
+        <v>64.42</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="DO9" t="n">
-        <v>3.09</v>
+        <v>2.96</v>
       </c>
       <c r="DP9" t="n">
-        <v>12.65</v>
+        <v>12.58</v>
       </c>
       <c r="DQ9" t="n">
-        <v>13.48</v>
+        <v>13.42</v>
       </c>
       <c r="DR9" t="n">
-        <v>7.04</v>
+        <v>7.09</v>
       </c>
       <c r="DS9" t="n">
         <v>0.13</v>
@@ -4572,28 +4572,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>51.44</v>
+        <v>51</v>
       </c>
       <c r="DW9" t="n">
         <v>0.13</v>
       </c>
       <c r="DX9" t="n">
-        <v>14.83</v>
+        <v>14.5</v>
       </c>
       <c r="DY9" t="n">
-        <v>10.83</v>
+        <v>10.59</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4</v>
+        <v>3.91</v>
       </c>
       <c r="EA9" t="n">
-        <v>23.26</v>
+        <v>23.08</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="10">
@@ -5234,7 +5234,7 @@
         <v>3.13</v>
       </c>
       <c r="BZ11" t="n">
-        <v>3.34</v>
+        <v>3.37</v>
       </c>
       <c r="CA11" t="n">
         <v>3.35</v>
@@ -5315,7 +5315,7 @@
         <v>2</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="DB11" t="n">
         <v>1.36</v>

--- a/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
@@ -3547,10 +3547,10 @@
         <v>0.17</v>
       </c>
       <c r="BA7" t="n">
-        <v>10.33</v>
+        <v>10.25</v>
       </c>
       <c r="BB7" t="n">
-        <v>7.33</v>
+        <v>7.25</v>
       </c>
       <c r="BC7" t="n">
         <v>3</v>
@@ -3559,7 +3559,7 @@
         <v>21.17</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="BF7" t="n">
         <v>1.83</v>
@@ -3772,10 +3772,10 @@
         <v>0.08</v>
       </c>
       <c r="DX7" t="n">
-        <v>10.58</v>
+        <v>10.54</v>
       </c>
       <c r="DY7" t="n">
-        <v>6.88</v>
+        <v>6.84</v>
       </c>
       <c r="DZ7" t="n">
         <v>3.71</v>
@@ -3784,7 +3784,7 @@
         <v>22</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="EC7" t="n">
         <v>1.96</v>

--- a/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
@@ -1782,61 +1782,61 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3" t="n">
         <v>12</v>
       </c>
       <c r="E3" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="G3" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="H3" t="n">
-        <v>98.42</v>
+        <v>96.31</v>
       </c>
       <c r="I3" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="J3" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="L3" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="M3" t="n">
-        <v>49.42</v>
+        <v>48.77</v>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="O3" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="P3" t="n">
-        <v>11.67</v>
+        <v>11.77</v>
       </c>
       <c r="Q3" t="n">
-        <v>13.83</v>
+        <v>13.85</v>
       </c>
       <c r="R3" t="n">
-        <v>8.25</v>
+        <v>8.08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="T3" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="U3" t="n">
         <v>0.08</v>
@@ -1848,28 +1848,28 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>49.08</v>
+        <v>48.46</v>
       </c>
       <c r="Y3" t="n">
         <v>0.08</v>
       </c>
       <c r="Z3" t="n">
-        <v>11</v>
+        <v>10.69</v>
       </c>
       <c r="AA3" t="n">
-        <v>7.17</v>
+        <v>6.92</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.83</v>
+        <v>3.77</v>
       </c>
       <c r="AC3" t="n">
-        <v>21.42</v>
+        <v>21.23</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -1953,70 +1953,70 @@
         <v>1.83</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="BH3" t="n">
-        <v>8.75</v>
+        <v>8.68</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.62</v>
+        <v>0.68</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.79</v>
+        <v>3.8</v>
       </c>
       <c r="BQ3" t="n">
-        <v>3.96</v>
+        <v>3.92</v>
       </c>
       <c r="BR3" t="n">
-        <v>95.83</v>
+        <v>96</v>
       </c>
       <c r="BS3" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BT3" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="BU3" t="n">
-        <v>29.17</v>
+        <v>32</v>
       </c>
       <c r="BV3" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="BW3" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="BX3" t="n">
-        <v>58.33</v>
+        <v>60</v>
       </c>
       <c r="BY3" t="n">
-        <v>2.96</v>
+        <v>2.91</v>
       </c>
       <c r="BZ3" t="n">
-        <v>3.11</v>
+        <v>3.06</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.56</v>
+        <v>3.54</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.67</v>
+        <v>3.65</v>
       </c>
       <c r="CC3" t="n">
         <v>5.54</v>
@@ -2028,10 +2028,10 @@
         <v>1.4</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="CH3" t="n">
         <v>1.38</v>
@@ -2043,10 +2043,10 @@
         <v>1.91</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="CM3" t="n">
         <v>2.06</v>
@@ -2061,7 +2061,7 @@
         <v>2.02</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.45</v>
+        <v>3.47</v>
       </c>
       <c r="CR3" t="n">
         <v>1.43</v>
@@ -2079,70 +2079,70 @@
         <v>1.9</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CX3" t="n">
         <v>1.72</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="DC3" t="n">
         <v>2.09</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.68</v>
+        <v>3.69</v>
       </c>
       <c r="DE3" t="n">
         <v>0.08</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="DG3" t="n">
         <v>1.88</v>
       </c>
       <c r="DH3" t="n">
-        <v>96.12</v>
+        <v>95.12</v>
       </c>
       <c r="DI3" t="n">
         <v>0.16</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="DK3" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="DL3" t="n">
         <v>0.08</v>
       </c>
       <c r="DM3" t="n">
-        <v>51.08</v>
+        <v>50.68</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="DP3" t="n">
-        <v>11.34</v>
+        <v>11.4</v>
       </c>
       <c r="DQ3" t="n">
-        <v>13.2</v>
+        <v>13.24</v>
       </c>
       <c r="DR3" t="n">
-        <v>8.33</v>
+        <v>8.24</v>
       </c>
       <c r="DS3" t="n">
         <v>0.08</v>
@@ -2154,25 +2154,25 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>46.92</v>
+        <v>46.68</v>
       </c>
       <c r="DW3" t="n">
         <v>0.12</v>
       </c>
       <c r="DX3" t="n">
-        <v>11.84</v>
+        <v>11.64</v>
       </c>
       <c r="DY3" t="n">
-        <v>8</v>
+        <v>7.84</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.83</v>
+        <v>3.8</v>
       </c>
       <c r="EA3" t="n">
-        <v>20.46</v>
+        <v>20.4</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="EC3" t="n">
         <v>2.12</v>
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D6" t="n">
         <v>13</v>
       </c>
       <c r="E6" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="F6" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="G6" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="H6" t="n">
-        <v>106.36</v>
+        <v>107.42</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="K6" t="n">
-        <v>4.18</v>
+        <v>4.42</v>
       </c>
       <c r="L6" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="M6" t="n">
-        <v>58</v>
+        <v>58.58</v>
       </c>
       <c r="N6" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="O6" t="n">
-        <v>1.55</v>
+        <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>11.09</v>
+        <v>11.42</v>
       </c>
       <c r="Q6" t="n">
-        <v>11.64</v>
+        <v>12</v>
       </c>
       <c r="R6" t="n">
-        <v>10.27</v>
+        <v>10.33</v>
       </c>
       <c r="S6" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T6" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -3057,28 +3057,28 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>51.82</v>
+        <v>52.25</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>11.27</v>
+        <v>11.33</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.64</v>
+        <v>7.83</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.64</v>
+        <v>3.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>21.64</v>
+        <v>22.33</v>
       </c>
       <c r="AD6" t="n">
         <v>1.39</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AF6" t="n">
         <v>0.08</v>
@@ -3162,70 +3162,70 @@
         <v>2.23</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="BH6" t="n">
-        <v>10.08</v>
+        <v>10.04</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.54</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.38</v>
+        <v>4.52</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.79</v>
+        <v>4.64</v>
       </c>
       <c r="BR6" t="n">
-        <v>95.83</v>
+        <v>96</v>
       </c>
       <c r="BS6" t="n">
-        <v>79.17</v>
+        <v>76</v>
       </c>
       <c r="BT6" t="n">
-        <v>58.33</v>
+        <v>56</v>
       </c>
       <c r="BU6" t="n">
-        <v>20.83</v>
+        <v>20</v>
       </c>
       <c r="BV6" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="BW6" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="BX6" t="n">
-        <v>62.5</v>
+        <v>60</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="BZ6" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.38</v>
+        <v>3.37</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.51</v>
+        <v>3.49</v>
       </c>
       <c r="CC6" t="n">
         <v>4.03</v>
@@ -3234,31 +3234,31 @@
         <v>4.68</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="CH6" t="n">
         <v>1.37</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="CM6" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CN6" t="n">
         <v>1.6</v>
@@ -3270,7 +3270,7 @@
         <v>2.03</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.46</v>
+        <v>3.49</v>
       </c>
       <c r="CR6" t="n">
         <v>1.42</v>
@@ -3285,7 +3285,7 @@
         <v>1.39</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CW6" t="n">
         <v>1.9</v>
@@ -3306,22 +3306,22 @@
         <v>1.34</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.66</v>
+        <v>3.69</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="DH6" t="n">
-        <v>104.96</v>
+        <v>105.52</v>
       </c>
       <c r="DI6" t="n">
         <v>0.16</v>
@@ -3330,28 +3330,28 @@
         <v>2</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.08</v>
+        <v>4.2</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="DM6" t="n">
-        <v>56.67</v>
+        <v>57</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.96</v>
+        <v>2.16</v>
       </c>
       <c r="DP6" t="n">
-        <v>10.84</v>
+        <v>11</v>
       </c>
       <c r="DQ6" t="n">
-        <v>11.42</v>
+        <v>11.6</v>
       </c>
       <c r="DR6" t="n">
-        <v>10.29</v>
+        <v>10.32</v>
       </c>
       <c r="DS6" t="n">
         <v>0.04</v>
@@ -3363,22 +3363,22 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>49.83</v>
+        <v>50.12</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>10.04</v>
+        <v>10.12</v>
       </c>
       <c r="DY6" t="n">
-        <v>6.63</v>
+        <v>6.76</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.42</v>
+        <v>3.36</v>
       </c>
       <c r="EA6" t="n">
-        <v>22.13</v>
+        <v>22.44</v>
       </c>
       <c r="EB6" t="n">
         <v>1.29</v>
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C8" t="n">
         <v>13</v>
       </c>
       <c r="D8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -3887,49 +3887,49 @@
         <v>2.31</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AI8" t="n">
-        <v>101.82</v>
+        <v>101.08</v>
       </c>
       <c r="AJ8" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.45</v>
+        <v>2.58</v>
       </c>
       <c r="AL8" t="n">
-        <v>4</v>
+        <v>3.83</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AN8" t="n">
-        <v>54.55</v>
+        <v>54.33</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.64</v>
+        <v>0.75</v>
       </c>
       <c r="AP8" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AQ8" t="n">
-        <v>15.64</v>
+        <v>15.67</v>
       </c>
       <c r="AR8" t="n">
-        <v>12.73</v>
+        <v>12.92</v>
       </c>
       <c r="AS8" t="n">
-        <v>8.359999999999999</v>
+        <v>7.92</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AU8" t="n">
         <v>1</v>
@@ -3944,82 +3944,82 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>48.64</v>
+        <v>48.17</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="BA8" t="n">
-        <v>11.91</v>
+        <v>11.67</v>
       </c>
       <c r="BB8" t="n">
-        <v>8.18</v>
+        <v>8</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.73</v>
+        <v>3.67</v>
       </c>
       <c r="BD8" t="n">
-        <v>22.64</v>
+        <v>22.75</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.18</v>
+        <v>2.33</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.83</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.46</v>
+        <v>0.48</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.71</v>
+        <v>4.84</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.08</v>
+        <v>4.92</v>
       </c>
       <c r="BR8" t="n">
-        <v>83.33</v>
+        <v>84</v>
       </c>
       <c r="BS8" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="BT8" t="n">
-        <v>41.67</v>
+        <v>40</v>
       </c>
       <c r="BU8" t="n">
-        <v>20.83</v>
+        <v>20</v>
       </c>
       <c r="BV8" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="BW8" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="BX8" t="n">
-        <v>45.83</v>
+        <v>44</v>
       </c>
       <c r="BY8" t="n">
         <v>2.8</v>
@@ -4028,31 +4028,31 @@
         <v>2.83</v>
       </c>
       <c r="CA8" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="CB8" t="n">
         <v>3.39</v>
       </c>
-      <c r="CB8" t="n">
-        <v>3.41</v>
-      </c>
       <c r="CC8" t="n">
-        <v>3.49</v>
+        <v>3.44</v>
       </c>
       <c r="CD8" t="n">
-        <v>3.88</v>
+        <v>3.78</v>
       </c>
       <c r="CE8" t="n">
         <v>1.4</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CJ8" t="n">
         <v>1.8</v>
@@ -4061,7 +4061,7 @@
         <v>1.58</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CM8" t="n">
         <v>2.22</v>
@@ -4070,13 +4070,13 @@
         <v>1.75</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.29</v>
+        <v>3.32</v>
       </c>
       <c r="CR8" t="n">
         <v>1.42</v>
@@ -4091,7 +4091,7 @@
         <v>1.38</v>
       </c>
       <c r="CV8" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CW8" t="n">
         <v>1.85</v>
@@ -4112,52 +4112,52 @@
         <v>1.33</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.62</v>
+        <v>3.65</v>
       </c>
       <c r="DE8" t="n">
         <v>0.04</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="DH8" t="n">
-        <v>109.67</v>
+        <v>109</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.41</v>
+        <v>2.48</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.92</v>
+        <v>4.8</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="DM8" t="n">
-        <v>67.70999999999999</v>
+        <v>67.08</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.79</v>
+        <v>0.84</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="DP8" t="n">
-        <v>15.13</v>
+        <v>15.16</v>
       </c>
       <c r="DQ8" t="n">
-        <v>13.29</v>
+        <v>13.36</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.54</v>
+        <v>7.36</v>
       </c>
       <c r="DS8" t="n">
         <v>0.04</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>48.79</v>
+        <v>48.56</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DX8" t="n">
-        <v>12.08</v>
+        <v>11.96</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.58</v>
+        <v>3.56</v>
       </c>
       <c r="EA8" t="n">
-        <v>21.92</v>
+        <v>22</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="9">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C10" t="n">
         <v>12</v>
       </c>
       <c r="D10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E10" t="n">
         <v>0.25</v>
@@ -4696,49 +4696,49 @@
         <v>0.08</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.5</v>
+        <v>1.69</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AI10" t="n">
-        <v>109</v>
+        <v>107.15</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.5</v>
+        <v>2.77</v>
       </c>
       <c r="AL10" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AN10" t="n">
-        <v>49.92</v>
+        <v>50.23</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.83</v>
+        <v>0.92</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.33</v>
+        <v>1.54</v>
       </c>
       <c r="AQ10" t="n">
-        <v>14.83</v>
+        <v>14.62</v>
       </c>
       <c r="AR10" t="n">
-        <v>13</v>
+        <v>13.08</v>
       </c>
       <c r="AS10" t="n">
-        <v>8.5</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AV10" t="n">
         <v>0.08</v>
@@ -4750,82 +4750,82 @@
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>45.5</v>
+        <v>46.54</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="BA10" t="n">
-        <v>9.83</v>
+        <v>10</v>
       </c>
       <c r="BB10" t="n">
-        <v>6.58</v>
+        <v>6.85</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="BD10" t="n">
-        <v>19.5</v>
+        <v>20.69</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.17</v>
+        <v>2.46</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="BH10" t="n">
-        <v>7.46</v>
+        <v>7.44</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="BL10" t="n">
         <v>1.04</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.21</v>
+        <v>3.24</v>
       </c>
       <c r="BQ10" t="n">
-        <v>3.46</v>
+        <v>3.44</v>
       </c>
       <c r="BR10" t="n">
-        <v>91.67</v>
+        <v>92</v>
       </c>
       <c r="BS10" t="n">
-        <v>87.5</v>
+        <v>88</v>
       </c>
       <c r="BT10" t="n">
-        <v>58.33</v>
+        <v>60</v>
       </c>
       <c r="BU10" t="n">
-        <v>29.17</v>
+        <v>32</v>
       </c>
       <c r="BV10" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BW10" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="BX10" t="n">
-        <v>66.67</v>
+        <v>68</v>
       </c>
       <c r="BY10" t="n">
         <v>2.6</v>
@@ -4834,25 +4834,25 @@
         <v>2.78</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.39</v>
+        <v>3.38</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.47</v>
+        <v>3.46</v>
       </c>
       <c r="CC10" t="n">
-        <v>4.38</v>
+        <v>4.29</v>
       </c>
       <c r="CD10" t="n">
-        <v>4.96</v>
+        <v>4.83</v>
       </c>
       <c r="CE10" t="n">
         <v>1.38</v>
       </c>
       <c r="CF10" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="CG10" t="n">
         <v>2.85</v>
-      </c>
-      <c r="CG10" t="n">
-        <v>2.86</v>
       </c>
       <c r="CH10" t="n">
         <v>1.38</v>
@@ -4864,16 +4864,16 @@
         <v>1.82</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="CM10" t="n">
         <v>2.01</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CO10" t="n">
         <v>1.29</v>
@@ -4882,7 +4882,7 @@
         <v>1.96</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.34</v>
+        <v>3.37</v>
       </c>
       <c r="CR10" t="n">
         <v>1.41</v>
@@ -4906,7 +4906,7 @@
         <v>1.74</v>
       </c>
       <c r="CY10" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="CZ10" t="n">
         <v>2.01</v>
@@ -4918,52 +4918,52 @@
         <v>1.32</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.53</v>
+        <v>3.55</v>
       </c>
       <c r="DE10" t="n">
         <v>0.16</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="DH10" t="n">
-        <v>112.38</v>
+        <v>111.28</v>
       </c>
       <c r="DI10" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="DK10" t="n">
-        <v>3.54</v>
+        <v>3.6</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DM10" t="n">
-        <v>55.58</v>
+        <v>55.52</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="DP10" t="n">
-        <v>13.79</v>
+        <v>13.72</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.96</v>
+        <v>13</v>
       </c>
       <c r="DR10" t="n">
-        <v>8.25</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="DS10" t="n">
         <v>0.08</v>
@@ -4975,28 +4975,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>48.96</v>
+        <v>49.36</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.33</v>
+        <v>12.32</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.25</v>
+        <v>8.32</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.08</v>
+        <v>4</v>
       </c>
       <c r="EA10" t="n">
-        <v>22.17</v>
+        <v>22.68</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="11">

--- a/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
@@ -645,7 +645,7 @@
     <col width="9.6" customWidth="1" min="73" max="73"/>
     <col width="9.6" customWidth="1" min="74" max="74"/>
     <col width="9.6" customWidth="1" min="75" max="75"/>
-    <col width="8.4" customWidth="1" min="76" max="76"/>
+    <col width="7.199999999999999" customWidth="1" min="76" max="76"/>
     <col width="18" customWidth="1" min="77" max="77"/>
     <col width="27.6" customWidth="1" min="78" max="78"/>
     <col width="18" customWidth="1" min="79" max="79"/>
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C2" t="n">
         <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E2" t="n">
         <v>0.25</v>
@@ -1469,139 +1469,139 @@
         <v>1.92</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AH2" t="n">
-        <v>3.83</v>
+        <v>3.85</v>
       </c>
       <c r="AI2" t="n">
-        <v>120.75</v>
+        <v>119.54</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AL2" t="n">
-        <v>6.5</v>
+        <v>6.54</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="AN2" t="n">
-        <v>75.5</v>
+        <v>74.31</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="AQ2" t="n">
-        <v>13.75</v>
+        <v>14.08</v>
       </c>
       <c r="AR2" t="n">
-        <v>13.58</v>
+        <v>13.31</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.83</v>
+        <v>6</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AU2" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>55.17</v>
+        <v>54.46</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="BA2" t="n">
-        <v>15.83</v>
+        <v>16</v>
       </c>
       <c r="BB2" t="n">
         <v>10.92</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.92</v>
+        <v>5.08</v>
       </c>
       <c r="BD2" t="n">
-        <v>24.33</v>
+        <v>24.54</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.12</v>
+        <v>3.16</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.619999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.12</v>
+        <v>3.16</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.54</v>
+        <v>0.64</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.54</v>
+        <v>4.64</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.04</v>
+        <v>5.12</v>
       </c>
       <c r="BR2" t="n">
-        <v>95.83</v>
+        <v>96</v>
       </c>
       <c r="BS2" t="n">
-        <v>91.67</v>
+        <v>92</v>
       </c>
       <c r="BT2" t="n">
-        <v>66.67</v>
+        <v>68</v>
       </c>
       <c r="BU2" t="n">
-        <v>33.33</v>
+        <v>36</v>
       </c>
       <c r="BV2" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BW2" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="BX2" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="BY2" t="n">
         <v>1.29</v>
@@ -1610,34 +1610,34 @@
         <v>1.3</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.66</v>
+        <v>4.6</v>
       </c>
       <c r="CB2" t="n">
-        <v>5.04</v>
+        <v>4.97</v>
       </c>
       <c r="CC2" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="CD2" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="CE2" t="n">
         <v>1.31</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.49</v>
+        <v>2.51</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="CH2" t="n">
         <v>1.49</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CK2" t="n">
         <v>1.58</v>
@@ -1646,7 +1646,7 @@
         <v>2.15</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CN2" t="n">
         <v>1.75</v>
@@ -1655,40 +1655,40 @@
         <v>1.22</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="CR2" t="n">
         <v>1.38</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="CT2" t="n">
         <v>3.04</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CW2" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="DB2" t="n">
         <v>1.24</v>
@@ -1700,46 +1700,46 @@
         <v>2.88</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.33</v>
+        <v>3.36</v>
       </c>
       <c r="DH2" t="n">
-        <v>120.04</v>
+        <v>119.44</v>
       </c>
       <c r="DI2" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="DK2" t="n">
-        <v>6.38</v>
+        <v>6.4</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="DM2" t="n">
-        <v>73.83</v>
+        <v>73.28</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="DO2" t="n">
         <v>3</v>
       </c>
       <c r="DP2" t="n">
-        <v>12.42</v>
+        <v>12.64</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.92</v>
+        <v>12.8</v>
       </c>
       <c r="DR2" t="n">
-        <v>5.62</v>
+        <v>5.72</v>
       </c>
       <c r="DS2" t="n">
         <v>0.12</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>56.67</v>
+        <v>56.24</v>
       </c>
       <c r="DW2" t="n">
         <v>0.12</v>
       </c>
       <c r="DX2" t="n">
-        <v>16.45</v>
+        <v>16.52</v>
       </c>
       <c r="DY2" t="n">
-        <v>10.58</v>
+        <v>10.6</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5.88</v>
+        <v>5.92</v>
       </c>
       <c r="EA2" t="n">
-        <v>23.08</v>
+        <v>23.24</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="3">
@@ -1797,7 +1797,7 @@
         <v>1.54</v>
       </c>
       <c r="G3" t="n">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="H3" t="n">
         <v>96.31</v>
@@ -1809,13 +1809,13 @@
         <v>2.46</v>
       </c>
       <c r="K3" t="n">
-        <v>3.85</v>
+        <v>3.92</v>
       </c>
       <c r="L3" t="n">
         <v>0.15</v>
       </c>
       <c r="M3" t="n">
-        <v>48.77</v>
+        <v>49.31</v>
       </c>
       <c r="N3" t="n">
         <v>0.92</v>
@@ -1824,10 +1824,10 @@
         <v>1.54</v>
       </c>
       <c r="P3" t="n">
-        <v>11.77</v>
+        <v>11.85</v>
       </c>
       <c r="Q3" t="n">
-        <v>13.85</v>
+        <v>13.92</v>
       </c>
       <c r="R3" t="n">
         <v>8.08</v>
@@ -1848,7 +1848,7 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>48.46</v>
+        <v>48.54</v>
       </c>
       <c r="Y3" t="n">
         <v>0.08</v>
@@ -1956,7 +1956,7 @@
         <v>2.68</v>
       </c>
       <c r="BH3" t="n">
-        <v>8.68</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="BI3" t="n">
         <v>2.68</v>
@@ -1983,7 +1983,7 @@
         <v>3.8</v>
       </c>
       <c r="BQ3" t="n">
-        <v>3.92</v>
+        <v>3.96</v>
       </c>
       <c r="BR3" t="n">
         <v>96</v>
@@ -2010,7 +2010,7 @@
         <v>2.91</v>
       </c>
       <c r="BZ3" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="CA3" t="n">
         <v>3.54</v>
@@ -2109,7 +2109,7 @@
         <v>1.44</v>
       </c>
       <c r="DG3" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="DH3" t="n">
         <v>95.12</v>
@@ -2121,13 +2121,13 @@
         <v>2.32</v>
       </c>
       <c r="DK3" t="n">
-        <v>4.4</v>
+        <v>4.44</v>
       </c>
       <c r="DL3" t="n">
         <v>0.08</v>
       </c>
       <c r="DM3" t="n">
-        <v>50.68</v>
+        <v>50.96</v>
       </c>
       <c r="DN3" t="n">
         <v>0.8</v>
@@ -2136,10 +2136,10 @@
         <v>1.84</v>
       </c>
       <c r="DP3" t="n">
-        <v>11.4</v>
+        <v>11.44</v>
       </c>
       <c r="DQ3" t="n">
-        <v>13.24</v>
+        <v>13.28</v>
       </c>
       <c r="DR3" t="n">
         <v>8.24</v>
@@ -2154,7 +2154,7 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>46.68</v>
+        <v>46.72</v>
       </c>
       <c r="DW3" t="n">
         <v>0.12</v>
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
         <v>13</v>
@@ -2197,82 +2197,82 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="G4" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="H4" t="n">
-        <v>117.09</v>
+        <v>118.75</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>3.91</v>
+        <v>3.75</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>70.64</v>
+        <v>72.25</v>
       </c>
       <c r="N4" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="O4" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="P4" t="n">
-        <v>13</v>
+        <v>13.08</v>
       </c>
       <c r="Q4" t="n">
-        <v>11.82</v>
+        <v>11.83</v>
       </c>
       <c r="R4" t="n">
-        <v>7.27</v>
+        <v>7.33</v>
       </c>
       <c r="S4" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T4" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="U4" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="V4" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>43.73</v>
+        <v>44.42</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z4" t="n">
-        <v>11.64</v>
+        <v>11.42</v>
       </c>
       <c r="AA4" t="n">
-        <v>7.09</v>
+        <v>7.17</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.55</v>
+        <v>4.25</v>
       </c>
       <c r="AC4" t="n">
-        <v>20.36</v>
+        <v>21.08</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AF4" t="n">
         <v>0.15</v>
@@ -2356,70 +2356,70 @@
         <v>2.69</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="BH4" t="n">
-        <v>10</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BL4" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.46</v>
+        <v>0.48</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.96</v>
+        <v>4.8</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.96</v>
+        <v>4.84</v>
       </c>
       <c r="BR4" t="n">
-        <v>95.83</v>
+        <v>96</v>
       </c>
       <c r="BS4" t="n">
-        <v>83.33</v>
+        <v>80</v>
       </c>
       <c r="BT4" t="n">
-        <v>58.33</v>
+        <v>56</v>
       </c>
       <c r="BU4" t="n">
-        <v>37.5</v>
+        <v>36</v>
       </c>
       <c r="BV4" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>66.67</v>
+        <v>64</v>
       </c>
       <c r="BY4" t="n">
-        <v>4.17</v>
+        <v>4.15</v>
       </c>
       <c r="BZ4" t="n">
-        <v>4.69</v>
+        <v>4.59</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.13</v>
+        <v>4.1</v>
       </c>
       <c r="CB4" t="n">
-        <v>4.23</v>
+        <v>4.19</v>
       </c>
       <c r="CC4" t="n">
         <v>6.35</v>
@@ -2434,7 +2434,7 @@
         <v>2.68</v>
       </c>
       <c r="CG4" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="CH4" t="n">
         <v>1.44</v>
@@ -2446,10 +2446,10 @@
         <v>1.89</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="CM4" t="n">
         <v>1.98</v>
@@ -2485,100 +2485,100 @@
         <v>1.94</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="DB4" t="n">
         <v>1.28</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="DE4" t="n">
         <v>0.08</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="DH4" t="n">
-        <v>111.38</v>
+        <v>112.4</v>
       </c>
       <c r="DI4" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.71</v>
+        <v>2.64</v>
       </c>
       <c r="DK4" t="n">
-        <v>3.59</v>
+        <v>3.52</v>
       </c>
       <c r="DL4" t="n">
         <v>0.12</v>
       </c>
       <c r="DM4" t="n">
-        <v>62.42</v>
+        <v>63.52</v>
       </c>
       <c r="DN4" t="n">
         <v>0.8</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="DP4" t="n">
-        <v>12.88</v>
+        <v>12.92</v>
       </c>
       <c r="DQ4" t="n">
-        <v>11.42</v>
+        <v>11.44</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.210000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>42.54</v>
+        <v>42.92</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.13</v>
+        <v>10.08</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.71</v>
+        <v>6.76</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.42</v>
+        <v>3.32</v>
       </c>
       <c r="EA4" t="n">
-        <v>21.37</v>
+        <v>21.68</v>
       </c>
       <c r="EB4" t="n">
         <v>1.34</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.33</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="5">
@@ -2588,94 +2588,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D5" t="n">
         <v>12</v>
       </c>
       <c r="E5" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="F5" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="G5" t="n">
-        <v>3.58</v>
+        <v>3.54</v>
       </c>
       <c r="H5" t="n">
-        <v>118.33</v>
+        <v>118.08</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="K5" t="n">
-        <v>5</v>
+        <v>5.15</v>
       </c>
       <c r="L5" t="n">
         <v>0.08</v>
       </c>
       <c r="M5" t="n">
-        <v>66.5</v>
+        <v>66.77</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="O5" t="n">
-        <v>1.42</v>
+        <v>1.62</v>
       </c>
       <c r="P5" t="n">
-        <v>11.92</v>
+        <v>11.77</v>
       </c>
       <c r="Q5" t="n">
-        <v>15.42</v>
+        <v>15.62</v>
       </c>
       <c r="R5" t="n">
-        <v>5.42</v>
+        <v>5.77</v>
       </c>
       <c r="S5" t="n">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="T5" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="U5" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="V5" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>60.33</v>
+        <v>59.85</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="Z5" t="n">
-        <v>15.42</v>
+        <v>15.23</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.42</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="AB5" t="n">
-        <v>6</v>
+        <v>5.77</v>
       </c>
       <c r="AC5" t="n">
-        <v>22.75</v>
+        <v>22.69</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AF5" t="n">
         <v>0.08</v>
@@ -2759,70 +2759,70 @@
         <v>2.42</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.380000000000001</v>
+        <v>9.56</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="BP5" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>96</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>84</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>40</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>20</v>
+      </c>
+      <c r="BV5" t="n">
         <v>4</v>
       </c>
-      <c r="BQ5" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>95.83</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>83.33</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>16.67</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>4.17</v>
-      </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>37.5</v>
+        <v>40</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1.72</v>
+        <v>1.86</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.61</v>
+        <v>3.6</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.57</v>
+        <v>3.56</v>
       </c>
       <c r="CC5" t="n">
         <v>2.28</v>
@@ -2843,10 +2843,10 @@
         <v>1.36</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CK5" t="n">
         <v>1.69</v>
@@ -2858,7 +2858,7 @@
         <v>2.06</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CO5" t="n">
         <v>1.31</v>
@@ -2867,34 +2867,34 @@
         <v>2.07</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.64</v>
+        <v>3.62</v>
       </c>
       <c r="CR5" t="n">
         <v>1.44</v>
       </c>
       <c r="CS5" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="CU5" t="n">
         <v>1.36</v>
       </c>
       <c r="CV5" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CW5" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CX5" t="n">
         <v>1.71</v>
       </c>
       <c r="CY5" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="DA5" t="n">
         <v>1.64</v>
@@ -2912,76 +2912,76 @@
         <v>0.16</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.46</v>
+        <v>3.44</v>
       </c>
       <c r="DH5" t="n">
-        <v>113.54</v>
+        <v>113.6</v>
       </c>
       <c r="DI5" t="n">
         <v>-0.04</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.21</v>
+        <v>2.16</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.92</v>
+        <v>5.96</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="DM5" t="n">
-        <v>66.92</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="DP5" t="n">
-        <v>12.62</v>
+        <v>12.52</v>
       </c>
       <c r="DQ5" t="n">
-        <v>14.92</v>
+        <v>15.04</v>
       </c>
       <c r="DR5" t="n">
-        <v>6.17</v>
+        <v>6.32</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>59.58</v>
+        <v>59.36</v>
       </c>
       <c r="DW5" t="n">
         <v>0.12</v>
       </c>
       <c r="DX5" t="n">
-        <v>15.08</v>
+        <v>15</v>
       </c>
       <c r="DY5" t="n">
-        <v>9.83</v>
+        <v>9.84</v>
       </c>
       <c r="DZ5" t="n">
-        <v>5.25</v>
+        <v>5.16</v>
       </c>
       <c r="EA5" t="n">
-        <v>21.83</v>
+        <v>21.84</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D7" t="n">
         <v>12</v>
@@ -3406,82 +3406,82 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="G7" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="H7" t="n">
-        <v>102</v>
+        <v>101.46</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="K7" t="n">
-        <v>3.75</v>
+        <v>4.15</v>
       </c>
       <c r="L7" t="n">
-        <v>0.33</v>
+        <v>0.46</v>
       </c>
       <c r="M7" t="n">
-        <v>57.08</v>
+        <v>57.54</v>
       </c>
       <c r="N7" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="O7" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="P7" t="n">
-        <v>14.42</v>
+        <v>14.38</v>
       </c>
       <c r="Q7" t="n">
-        <v>13.25</v>
+        <v>13.08</v>
       </c>
       <c r="R7" t="n">
-        <v>7.25</v>
+        <v>7.15</v>
       </c>
       <c r="S7" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="T7" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="U7" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="V7" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>50.5</v>
+        <v>49.92</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>10.83</v>
+        <v>11.38</v>
       </c>
       <c r="AA7" t="n">
-        <v>6.42</v>
+        <v>7.23</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.42</v>
+        <v>4.15</v>
       </c>
       <c r="AC7" t="n">
-        <v>22.83</v>
+        <v>23</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AF7" t="n">
         <v>0.33</v>
@@ -3565,70 +3565,70 @@
         <v>1.83</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.58</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.46</v>
+        <v>0.48</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.75</v>
+        <v>3.84</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.83</v>
+        <v>4.8</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>91.67</v>
+        <v>92</v>
       </c>
       <c r="BT7" t="n">
-        <v>45.83</v>
+        <v>44</v>
       </c>
       <c r="BU7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BV7" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="BW7" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="BX7" t="n">
-        <v>70.83</v>
+        <v>72</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="BZ7" t="n">
-        <v>3.02</v>
+        <v>2.94</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.55</v>
+        <v>3.53</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.57</v>
+        <v>3.56</v>
       </c>
       <c r="CC7" t="n">
         <v>4.44</v>
@@ -3643,10 +3643,10 @@
         <v>2.82</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CI7" t="n">
         <v>1.9</v>
@@ -3655,7 +3655,7 @@
         <v>1.8</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CL7" t="n">
         <v>2.14</v>
@@ -3673,7 +3673,7 @@
         <v>1.96</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.29</v>
+        <v>3.3</v>
       </c>
       <c r="CR7" t="n">
         <v>1.4</v>
@@ -3712,82 +3712,82 @@
         <v>2.03</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.51</v>
+        <v>3.52</v>
       </c>
       <c r="DE7" t="n">
         <v>0.16</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="DH7" t="n">
-        <v>107.92</v>
+        <v>107.4</v>
       </c>
       <c r="DI7" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.25</v>
+        <v>4.44</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.25</v>
+        <v>0.32</v>
       </c>
       <c r="DM7" t="n">
-        <v>58.96</v>
+        <v>59.12</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.79</v>
+        <v>1.96</v>
       </c>
       <c r="DP7" t="n">
-        <v>14.5</v>
+        <v>14.48</v>
       </c>
       <c r="DQ7" t="n">
-        <v>12</v>
+        <v>11.96</v>
       </c>
       <c r="DR7" t="n">
-        <v>7</v>
+        <v>6.96</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>51.54</v>
+        <v>51.2</v>
       </c>
       <c r="DW7" t="n">
         <v>0.08</v>
       </c>
       <c r="DX7" t="n">
-        <v>10.54</v>
+        <v>10.84</v>
       </c>
       <c r="DY7" t="n">
-        <v>6.84</v>
+        <v>7.24</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.71</v>
+        <v>3.6</v>
       </c>
       <c r="EA7" t="n">
-        <v>22</v>
+        <v>22.12</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
         <v>13</v>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E9" t="n">
         <v>0.23</v>
@@ -4290,139 +4290,139 @@
         <v>2.23</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AH9" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="AI9" t="n">
-        <v>105.36</v>
+        <v>109.75</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>3.36</v>
+        <v>3.08</v>
       </c>
       <c r="AL9" t="n">
-        <v>5.82</v>
+        <v>5.42</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AN9" t="n">
-        <v>59</v>
+        <v>61.67</v>
       </c>
       <c r="AO9" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.82</v>
+        <v>2.58</v>
       </c>
       <c r="AQ9" t="n">
-        <v>12.82</v>
+        <v>12.75</v>
       </c>
       <c r="AR9" t="n">
-        <v>13.27</v>
+        <v>13.25</v>
       </c>
       <c r="AS9" t="n">
-        <v>6.82</v>
+        <v>6.92</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>50.64</v>
+        <v>50.42</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BA9" t="n">
-        <v>13.82</v>
+        <v>13.33</v>
       </c>
       <c r="BB9" t="n">
-        <v>10.55</v>
+        <v>10.17</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.27</v>
+        <v>3.17</v>
       </c>
       <c r="BD9" t="n">
-        <v>22.64</v>
+        <v>22.42</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="BF9" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.33</v>
+        <v>10.04</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.46</v>
+        <v>0.48</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.62</v>
+        <v>4.48</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.71</v>
+        <v>5.56</v>
       </c>
       <c r="BR9" t="n">
-        <v>87.5</v>
+        <v>88</v>
       </c>
       <c r="BS9" t="n">
-        <v>70.83</v>
+        <v>68</v>
       </c>
       <c r="BT9" t="n">
-        <v>45.83</v>
+        <v>44</v>
       </c>
       <c r="BU9" t="n">
-        <v>33.33</v>
+        <v>32</v>
       </c>
       <c r="BV9" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BW9" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="BX9" t="n">
-        <v>54.17</v>
+        <v>52</v>
       </c>
       <c r="BY9" t="n">
         <v>2.07</v>
@@ -4434,19 +4434,19 @@
         <v>3.48</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="CC9" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="CD9" t="n">
-        <v>3.17</v>
+        <v>3.1</v>
       </c>
       <c r="CE9" t="n">
         <v>1.4</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="CG9" t="n">
         <v>2.73</v>
@@ -4455,16 +4455,16 @@
         <v>1.37</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CK9" t="n">
         <v>1.62</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="CM9" t="n">
         <v>1.98</v>
@@ -4479,7 +4479,7 @@
         <v>2.02</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.51</v>
+        <v>3.5</v>
       </c>
       <c r="CR9" t="n">
         <v>1.42</v>
@@ -4494,22 +4494,22 @@
         <v>1.37</v>
       </c>
       <c r="CV9" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="CY9" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="DB9" t="n">
         <v>1.35</v>
@@ -4521,79 +4521,79 @@
         <v>3.75</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.84</v>
+        <v>1.76</v>
       </c>
       <c r="DG9" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="DH9" t="n">
-        <v>112</v>
+        <v>113.84</v>
       </c>
       <c r="DI9" t="n">
         <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.83</v>
+        <v>2.72</v>
       </c>
       <c r="DK9" t="n">
-        <v>5.96</v>
+        <v>5.76</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="DM9" t="n">
-        <v>64.42</v>
+        <v>65.48</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.87</v>
+        <v>0.84</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.96</v>
+        <v>2.84</v>
       </c>
       <c r="DP9" t="n">
-        <v>12.58</v>
+        <v>12.56</v>
       </c>
       <c r="DQ9" t="n">
-        <v>13.42</v>
+        <v>13.4</v>
       </c>
       <c r="DR9" t="n">
-        <v>7.09</v>
+        <v>7.12</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>51</v>
+        <v>50.88</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX9" t="n">
-        <v>14.5</v>
+        <v>14.24</v>
       </c>
       <c r="DY9" t="n">
-        <v>10.59</v>
+        <v>10.4</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3.91</v>
+        <v>3.84</v>
       </c>
       <c r="EA9" t="n">
-        <v>23.08</v>
+        <v>22.96</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.58</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="10">
@@ -4717,7 +4717,7 @@
         <v>0.31</v>
       </c>
       <c r="AN10" t="n">
-        <v>50.23</v>
+        <v>50.38</v>
       </c>
       <c r="AO10" t="n">
         <v>0.92</v>
@@ -4726,7 +4726,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ10" t="n">
-        <v>14.62</v>
+        <v>14.85</v>
       </c>
       <c r="AR10" t="n">
         <v>13.08</v>
@@ -4750,7 +4750,7 @@
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>46.54</v>
+        <v>46.46</v>
       </c>
       <c r="AZ10" t="n">
         <v>0.15</v>
@@ -4777,7 +4777,7 @@
         <v>2.92</v>
       </c>
       <c r="BH10" t="n">
-        <v>7.44</v>
+        <v>7.48</v>
       </c>
       <c r="BI10" t="n">
         <v>2.92</v>
@@ -4804,7 +4804,7 @@
         <v>3.24</v>
       </c>
       <c r="BQ10" t="n">
-        <v>3.44</v>
+        <v>3.48</v>
       </c>
       <c r="BR10" t="n">
         <v>92</v>
@@ -4843,7 +4843,7 @@
         <v>4.29</v>
       </c>
       <c r="CD10" t="n">
-        <v>4.83</v>
+        <v>4.85</v>
       </c>
       <c r="CE10" t="n">
         <v>1.38</v>
@@ -4948,7 +4948,7 @@
         <v>0.24</v>
       </c>
       <c r="DM10" t="n">
-        <v>55.52</v>
+        <v>55.6</v>
       </c>
       <c r="DN10" t="n">
         <v>0.64</v>
@@ -4957,7 +4957,7 @@
         <v>1.32</v>
       </c>
       <c r="DP10" t="n">
-        <v>13.72</v>
+        <v>13.84</v>
       </c>
       <c r="DQ10" t="n">
         <v>13</v>
@@ -4975,7 +4975,7 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>49.36</v>
+        <v>49.32</v>
       </c>
       <c r="DW10" t="n">
         <v>0.2</v>
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
         <v>12</v>
       </c>
       <c r="D11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E11" t="n">
         <v>0.25</v>
@@ -5102,133 +5102,133 @@
         <v>1.08</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AI11" t="n">
-        <v>90.42</v>
+        <v>92.38</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="AL11" t="n">
-        <v>4</v>
+        <v>3.77</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AN11" t="n">
-        <v>45.25</v>
+        <v>46.77</v>
       </c>
       <c r="AO11" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AQ11" t="n">
-        <v>12.58</v>
+        <v>12.46</v>
       </c>
       <c r="AR11" t="n">
-        <v>12.58</v>
+        <v>12.69</v>
       </c>
       <c r="AS11" t="n">
-        <v>8.33</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AU11" t="n">
         <v>1.08</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>42.75</v>
+        <v>43.85</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="BA11" t="n">
-        <v>10.58</v>
+        <v>10.38</v>
       </c>
       <c r="BB11" t="n">
-        <v>7.08</v>
+        <v>7</v>
       </c>
       <c r="BC11" t="n">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="BD11" t="n">
-        <v>18.5</v>
+        <v>18.69</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="BH11" t="n">
         <v>9.880000000000001</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.54</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.29</v>
+        <v>4.36</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.83</v>
+        <v>4.8</v>
       </c>
       <c r="BR11" t="n">
-        <v>91.67</v>
+        <v>92</v>
       </c>
       <c r="BS11" t="n">
-        <v>79.17</v>
+        <v>80</v>
       </c>
       <c r="BT11" t="n">
-        <v>54.17</v>
+        <v>52</v>
       </c>
       <c r="BU11" t="n">
-        <v>37.5</v>
+        <v>36</v>
       </c>
       <c r="BV11" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="BW11" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="BX11" t="n">
-        <v>62.5</v>
+        <v>64</v>
       </c>
       <c r="BY11" t="n">
         <v>3.13</v>
@@ -5243,16 +5243,16 @@
         <v>3.39</v>
       </c>
       <c r="CC11" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="CD11" t="n">
-        <v>4.28</v>
+        <v>4.24</v>
       </c>
       <c r="CE11" t="n">
         <v>1.43</v>
       </c>
       <c r="CF11" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="CG11" t="n">
         <v>2.63</v>
@@ -5267,10 +5267,10 @@
         <v>1.92</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="CM11" t="n">
         <v>2.02</v>
@@ -5285,7 +5285,7 @@
         <v>2.08</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.62</v>
+        <v>3.61</v>
       </c>
       <c r="CR11" t="n">
         <v>1.45</v>
@@ -5303,7 +5303,7 @@
         <v>1.88</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CX11" t="n">
         <v>1.75</v>
@@ -5330,76 +5330,76 @@
         <v>0.16</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="DG11" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="DH11" t="n">
-        <v>99.17</v>
+        <v>99.84</v>
       </c>
       <c r="DI11" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="DK11" t="n">
-        <v>3.83</v>
+        <v>3.72</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="DM11" t="n">
-        <v>49.88</v>
+        <v>50.48</v>
       </c>
       <c r="DN11" t="n">
         <v>1.08</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.84</v>
+        <v>1.76</v>
       </c>
       <c r="DP11" t="n">
-        <v>12.25</v>
+        <v>12.2</v>
       </c>
       <c r="DQ11" t="n">
-        <v>12.79</v>
+        <v>12.84</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.96</v>
+        <v>8.08</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>44.16</v>
+        <v>44.68</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DX11" t="n">
-        <v>11.7</v>
+        <v>11.56</v>
       </c>
       <c r="DY11" t="n">
-        <v>8</v>
+        <v>7.92</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.71</v>
+        <v>3.64</v>
       </c>
       <c r="EA11" t="n">
-        <v>19.66</v>
+        <v>19.72</v>
       </c>
       <c r="EB11" t="n">
         <v>1.36</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
@@ -2669,7 +2669,7 @@
         <v>5.77</v>
       </c>
       <c r="AC5" t="n">
-        <v>22.69</v>
+        <v>22.77</v>
       </c>
       <c r="AD5" t="n">
         <v>1.85</v>
@@ -2975,7 +2975,7 @@
         <v>5.16</v>
       </c>
       <c r="EA5" t="n">
-        <v>21.84</v>
+        <v>21.88</v>
       </c>
       <c r="EB5" t="n">
         <v>1.79</v>

--- a/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
@@ -645,7 +645,7 @@
     <col width="9.6" customWidth="1" min="73" max="73"/>
     <col width="9.6" customWidth="1" min="74" max="74"/>
     <col width="9.6" customWidth="1" min="75" max="75"/>
-    <col width="7.199999999999999" customWidth="1" min="76" max="76"/>
+    <col width="8.4" customWidth="1" min="76" max="76"/>
     <col width="18" customWidth="1" min="77" max="77"/>
     <col width="27.6" customWidth="1" min="78" max="78"/>
     <col width="18" customWidth="1" min="79" max="79"/>
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C4" t="n">
         <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2275,139 +2275,139 @@
         <v>1.83</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AH4" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AI4" t="n">
-        <v>106.54</v>
+        <v>108.36</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AK4" t="n">
-        <v>3.23</v>
+        <v>3.14</v>
       </c>
       <c r="AL4" t="n">
-        <v>3.31</v>
+        <v>3.29</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AN4" t="n">
-        <v>55.46</v>
+        <v>56.36</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AQ4" t="n">
-        <v>12.77</v>
+        <v>12.86</v>
       </c>
       <c r="AR4" t="n">
-        <v>11.08</v>
+        <v>11</v>
       </c>
       <c r="AS4" t="n">
-        <v>9</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>41.54</v>
+        <v>42.43</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="BA4" t="n">
-        <v>8.85</v>
+        <v>8.93</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.38</v>
+        <v>6.43</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>22.23</v>
+        <v>22.36</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.69</v>
+        <v>2.64</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.720000000000001</v>
+        <v>9.69</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="BL4" t="n">
         <v>1.12</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.8</v>
+        <v>4.77</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.84</v>
+        <v>4.85</v>
       </c>
       <c r="BR4" t="n">
-        <v>96</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="BS4" t="n">
-        <v>80</v>
+        <v>80.77</v>
       </c>
       <c r="BT4" t="n">
-        <v>56</v>
+        <v>53.85</v>
       </c>
       <c r="BU4" t="n">
-        <v>36</v>
+        <v>34.62</v>
       </c>
       <c r="BV4" t="n">
-        <v>12</v>
+        <v>11.54</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>64</v>
+        <v>61.54</v>
       </c>
       <c r="BY4" t="n">
         <v>4.15</v>
@@ -2416,34 +2416,34 @@
         <v>4.59</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.1</v>
+        <v>4.08</v>
       </c>
       <c r="CB4" t="n">
-        <v>4.19</v>
+        <v>4.15</v>
       </c>
       <c r="CC4" t="n">
-        <v>6.35</v>
+        <v>6.14</v>
       </c>
       <c r="CD4" t="n">
-        <v>8.720000000000001</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CK4" t="n">
         <v>1.61</v>
@@ -2452,7 +2452,7 @@
         <v>2.2</v>
       </c>
       <c r="CM4" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CN4" t="n">
         <v>1.59</v>
@@ -2461,10 +2461,10 @@
         <v>1.26</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="CR4" t="n">
         <v>1.38</v>
@@ -2479,10 +2479,10 @@
         <v>1.48</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CX4" t="n">
         <v>1.66</v>
@@ -2494,91 +2494,91 @@
         <v>2.13</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="DB4" t="n">
         <v>1.28</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="DE4" t="n">
         <v>0.08</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="DH4" t="n">
-        <v>112.4</v>
+        <v>113.16</v>
       </c>
       <c r="DI4" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.64</v>
+        <v>2.61</v>
       </c>
       <c r="DK4" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DM4" t="n">
-        <v>63.52</v>
+        <v>63.69</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="DP4" t="n">
-        <v>12.92</v>
+        <v>12.96</v>
       </c>
       <c r="DQ4" t="n">
-        <v>11.44</v>
+        <v>11.38</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>42.92</v>
+        <v>43.35</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DX4" t="n">
         <v>10.08</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.76</v>
+        <v>6.77</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.32</v>
+        <v>3.31</v>
       </c>
       <c r="EA4" t="n">
-        <v>21.68</v>
+        <v>21.77</v>
       </c>
       <c r="EB4" t="n">
         <v>1.34</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="5">
@@ -5006,94 +5006,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D11" t="n">
         <v>13</v>
       </c>
       <c r="E11" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="F11" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="G11" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="H11" t="n">
-        <v>107.92</v>
+        <v>108.38</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="K11" t="n">
-        <v>3.67</v>
+        <v>3.85</v>
       </c>
       <c r="L11" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="M11" t="n">
-        <v>54.5</v>
+        <v>54.92</v>
       </c>
       <c r="N11" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="O11" t="n">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="P11" t="n">
-        <v>11.92</v>
+        <v>11.77</v>
       </c>
       <c r="Q11" t="n">
-        <v>13</v>
+        <v>13.15</v>
       </c>
       <c r="R11" t="n">
-        <v>7.58</v>
+        <v>7.69</v>
       </c>
       <c r="S11" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="T11" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="U11" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="V11" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>45.58</v>
+        <v>45.62</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="Z11" t="n">
-        <v>12.83</v>
+        <v>13.54</v>
       </c>
       <c r="AA11" t="n">
-        <v>8.92</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="AB11" t="n">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="AC11" t="n">
-        <v>20.83</v>
+        <v>21.23</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AF11" t="n">
         <v>0.08</v>
@@ -5177,70 +5177,70 @@
         <v>2.23</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.68</v>
+        <v>2.65</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.880000000000001</v>
+        <v>9.85</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.68</v>
+        <v>2.65</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.72</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.36</v>
+        <v>4.35</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.8</v>
+        <v>4.81</v>
       </c>
       <c r="BR11" t="n">
-        <v>92</v>
+        <v>92.31</v>
       </c>
       <c r="BS11" t="n">
-        <v>80</v>
+        <v>80.77</v>
       </c>
       <c r="BT11" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="BU11" t="n">
-        <v>36</v>
+        <v>34.62</v>
       </c>
       <c r="BV11" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BW11" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BX11" t="n">
-        <v>64</v>
+        <v>61.54</v>
       </c>
       <c r="BY11" t="n">
-        <v>3.13</v>
+        <v>3.05</v>
       </c>
       <c r="BZ11" t="n">
-        <v>3.37</v>
+        <v>3.28</v>
       </c>
       <c r="CA11" t="n">
         <v>3.35</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.39</v>
+        <v>3.38</v>
       </c>
       <c r="CC11" t="n">
         <v>3.85</v>
@@ -5264,13 +5264,13 @@
         <v>1.81</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CK11" t="n">
         <v>1.71</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="CM11" t="n">
         <v>2.02</v>
@@ -5285,7 +5285,7 @@
         <v>2.08</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.61</v>
+        <v>3.6</v>
       </c>
       <c r="CR11" t="n">
         <v>1.45</v>
@@ -5300,7 +5300,7 @@
         <v>1.35</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CW11" t="n">
         <v>1.93</v>
@@ -5321,85 +5321,85 @@
         <v>1.36</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.85</v>
+        <v>3.83</v>
       </c>
       <c r="DE11" t="n">
         <v>0.16</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="DG11" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="DH11" t="n">
-        <v>99.84</v>
+        <v>100.38</v>
       </c>
       <c r="DI11" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="DK11" t="n">
-        <v>3.72</v>
+        <v>3.81</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="DM11" t="n">
-        <v>50.48</v>
+        <v>50.84</v>
       </c>
       <c r="DN11" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="DP11" t="n">
-        <v>12.2</v>
+        <v>12.12</v>
       </c>
       <c r="DQ11" t="n">
-        <v>12.84</v>
+        <v>12.92</v>
       </c>
       <c r="DR11" t="n">
-        <v>8.08</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>44.68</v>
+        <v>44.74</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DX11" t="n">
-        <v>11.56</v>
+        <v>11.96</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.92</v>
+        <v>8.27</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.64</v>
+        <v>3.69</v>
       </c>
       <c r="EA11" t="n">
-        <v>19.72</v>
+        <v>19.96</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" t="n">
         <v>13</v>
       </c>
       <c r="E2" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="F2" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="G2" t="n">
-        <v>2.83</v>
+        <v>2.69</v>
       </c>
       <c r="H2" t="n">
-        <v>119.33</v>
+        <v>121.38</v>
       </c>
       <c r="I2" t="n">
-        <v>0.17</v>
+        <v>0.08</v>
       </c>
       <c r="J2" t="n">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="K2" t="n">
-        <v>6.25</v>
+        <v>6.15</v>
       </c>
       <c r="L2" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="M2" t="n">
-        <v>72.17</v>
+        <v>72.31</v>
       </c>
       <c r="N2" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="O2" t="n">
-        <v>3.33</v>
+        <v>3.38</v>
       </c>
       <c r="P2" t="n">
-        <v>11.08</v>
+        <v>10.85</v>
       </c>
       <c r="Q2" t="n">
-        <v>12.25</v>
+        <v>11.92</v>
       </c>
       <c r="R2" t="n">
-        <v>5.42</v>
+        <v>5.46</v>
       </c>
       <c r="S2" t="n">
-        <v>0.83</v>
+        <v>0.92</v>
       </c>
       <c r="T2" t="n">
-        <v>2.67</v>
+        <v>2.77</v>
       </c>
       <c r="U2" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="V2" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>58.17</v>
+        <v>58.62</v>
       </c>
       <c r="Y2" t="n">
         <v>0.08</v>
       </c>
       <c r="Z2" t="n">
-        <v>17.08</v>
+        <v>17.23</v>
       </c>
       <c r="AA2" t="n">
-        <v>10.25</v>
+        <v>10.15</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.83</v>
+        <v>7.08</v>
       </c>
       <c r="AC2" t="n">
-        <v>21.83</v>
+        <v>21.46</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AF2" t="n">
         <v>0.15</v>
@@ -1550,70 +1550,70 @@
         <v>1.92</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.16</v>
+        <v>3.27</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.800000000000001</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.16</v>
+        <v>3.27</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.92</v>
+        <v>1.04</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.64</v>
+        <v>4.62</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.12</v>
+        <v>4.96</v>
       </c>
       <c r="BR2" t="n">
-        <v>96</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="BS2" t="n">
-        <v>92</v>
+        <v>92.31</v>
       </c>
       <c r="BT2" t="n">
-        <v>68</v>
+        <v>69.23</v>
       </c>
       <c r="BU2" t="n">
-        <v>36</v>
+        <v>38.46</v>
       </c>
       <c r="BV2" t="n">
-        <v>12</v>
+        <v>15.38</v>
       </c>
       <c r="BW2" t="n">
-        <v>8</v>
+        <v>11.54</v>
       </c>
       <c r="BX2" t="n">
-        <v>52</v>
+        <v>53.85</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="BZ2" t="n">
         <v>1.3</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.6</v>
+        <v>4.64</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.97</v>
+        <v>5.01</v>
       </c>
       <c r="CC2" t="n">
         <v>1.65</v>
@@ -1625,52 +1625,52 @@
         <v>1.31</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="CH2" t="n">
         <v>1.49</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CJ2" t="n">
         <v>1.97</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CO2" t="n">
         <v>1.22</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="CR2" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="CT2" t="n">
-        <v>3.04</v>
+        <v>3.06</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CV2" t="n">
         <v>1.84</v>
@@ -1679,100 +1679,100 @@
         <v>2</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="DB2" t="n">
         <v>1.24</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.36</v>
+        <v>3.27</v>
       </c>
       <c r="DH2" t="n">
-        <v>119.44</v>
+        <v>120.46</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="DK2" t="n">
-        <v>6.4</v>
+        <v>6.34</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="DM2" t="n">
-        <v>73.28</v>
+        <v>73.31</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.6</v>
+        <v>0.58</v>
       </c>
       <c r="DO2" t="n">
-        <v>3</v>
+        <v>3.03</v>
       </c>
       <c r="DP2" t="n">
-        <v>12.64</v>
+        <v>12.46</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.8</v>
+        <v>12.62</v>
       </c>
       <c r="DR2" t="n">
-        <v>5.72</v>
+        <v>5.73</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>56.24</v>
+        <v>56.54</v>
       </c>
       <c r="DW2" t="n">
         <v>0.12</v>
       </c>
       <c r="DX2" t="n">
-        <v>16.52</v>
+        <v>16.62</v>
       </c>
       <c r="DY2" t="n">
-        <v>10.6</v>
+        <v>10.54</v>
       </c>
       <c r="DZ2" t="n">
-        <v>5.92</v>
+        <v>6.08</v>
       </c>
       <c r="EA2" t="n">
-        <v>23.24</v>
+        <v>23</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C3" t="n">
         <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E3" t="n">
         <v>0.15</v>
@@ -1875,49 +1875,49 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.58</v>
+        <v>1.77</v>
       </c>
       <c r="AI3" t="n">
-        <v>93.83</v>
+        <v>94.69</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AL3" t="n">
-        <v>5</v>
+        <v>5.15</v>
       </c>
       <c r="AM3" t="n">
         <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>52.75</v>
+        <v>54</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ3" t="n">
         <v>11</v>
       </c>
       <c r="AR3" t="n">
-        <v>12.58</v>
+        <v>12.69</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.42</v>
+        <v>8.69</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AV3" t="n">
         <v>0.08</v>
@@ -1929,82 +1929,82 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>44.75</v>
+        <v>44.54</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="BA3" t="n">
-        <v>12.67</v>
+        <v>12.69</v>
       </c>
       <c r="BB3" t="n">
-        <v>8.83</v>
+        <v>8.85</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.83</v>
+        <v>3.85</v>
       </c>
       <c r="BD3" t="n">
-        <v>19.5</v>
+        <v>20.38</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.68</v>
+        <v>2.58</v>
       </c>
       <c r="BH3" t="n">
-        <v>8.720000000000001</v>
+        <v>8.85</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.68</v>
+        <v>2.58</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.72</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.8</v>
+        <v>3.81</v>
       </c>
       <c r="BQ3" t="n">
-        <v>3.96</v>
+        <v>4.12</v>
       </c>
       <c r="BR3" t="n">
-        <v>96</v>
+        <v>92.31</v>
       </c>
       <c r="BS3" t="n">
-        <v>76</v>
+        <v>73.08</v>
       </c>
       <c r="BT3" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="BU3" t="n">
-        <v>32</v>
+        <v>30.77</v>
       </c>
       <c r="BV3" t="n">
-        <v>8</v>
+        <v>7.69</v>
       </c>
       <c r="BW3" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BX3" t="n">
-        <v>60</v>
+        <v>57.69</v>
       </c>
       <c r="BY3" t="n">
         <v>2.91</v>
@@ -2013,37 +2013,37 @@
         <v>3.04</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.54</v>
+        <v>3.51</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.65</v>
+        <v>3.61</v>
       </c>
       <c r="CC3" t="n">
-        <v>5.54</v>
+        <v>5.35</v>
       </c>
       <c r="CD3" t="n">
-        <v>5.81</v>
+        <v>5.64</v>
       </c>
       <c r="CE3" t="n">
         <v>1.4</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="CG3" t="n">
         <v>2.78</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CI3" t="n">
         <v>1.83</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CL3" t="n">
         <v>2.35</v>
@@ -2058,19 +2058,19 @@
         <v>1.31</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.47</v>
+        <v>3.49</v>
       </c>
       <c r="CR3" t="n">
         <v>1.43</v>
       </c>
       <c r="CS3" t="n">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="CT3" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="CU3" t="n">
         <v>1.39</v>
@@ -2085,64 +2085,64 @@
         <v>1.72</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="DB3" t="n">
         <v>1.34</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.69</v>
+        <v>3.71</v>
       </c>
       <c r="DE3" t="n">
         <v>0.08</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="DG3" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="DH3" t="n">
-        <v>95.12</v>
+        <v>95.5</v>
       </c>
       <c r="DI3" t="n">
         <v>0.16</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.32</v>
+        <v>2.23</v>
       </c>
       <c r="DK3" t="n">
-        <v>4.44</v>
+        <v>4.54</v>
       </c>
       <c r="DL3" t="n">
         <v>0.08</v>
       </c>
       <c r="DM3" t="n">
-        <v>50.96</v>
+        <v>51.66</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="DP3" t="n">
-        <v>11.44</v>
+        <v>11.42</v>
       </c>
       <c r="DQ3" t="n">
-        <v>13.28</v>
+        <v>13.3</v>
       </c>
       <c r="DR3" t="n">
-        <v>8.24</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="DS3" t="n">
         <v>0.08</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>46.72</v>
+        <v>46.54</v>
       </c>
       <c r="DW3" t="n">
         <v>0.12</v>
       </c>
       <c r="DX3" t="n">
-        <v>11.64</v>
+        <v>11.69</v>
       </c>
       <c r="DY3" t="n">
-        <v>7.84</v>
+        <v>7.88</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.8</v>
+        <v>3.81</v>
       </c>
       <c r="EA3" t="n">
-        <v>20.4</v>
+        <v>20.81</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.12</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="4">
@@ -2588,94 +2588,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5" t="n">
         <v>12</v>
       </c>
       <c r="E5" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="F5" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="G5" t="n">
-        <v>3.54</v>
+        <v>3.43</v>
       </c>
       <c r="H5" t="n">
-        <v>118.08</v>
+        <v>117.5</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="K5" t="n">
-        <v>5.15</v>
+        <v>5.14</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>66.77</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="O5" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="P5" t="n">
-        <v>11.77</v>
+        <v>12.14</v>
       </c>
       <c r="Q5" t="n">
-        <v>15.62</v>
+        <v>14.93</v>
       </c>
       <c r="R5" t="n">
-        <v>5.77</v>
+        <v>5.57</v>
       </c>
       <c r="S5" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="T5" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="U5" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="V5" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>59.85</v>
+        <v>58.86</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="Z5" t="n">
-        <v>15.23</v>
+        <v>15.64</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.460000000000001</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.77</v>
+        <v>6</v>
       </c>
       <c r="AC5" t="n">
-        <v>22.77</v>
+        <v>22.71</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AF5" t="n">
         <v>0.08</v>
@@ -2759,70 +2759,70 @@
         <v>2.42</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.56</v>
+        <v>9.77</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.64</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.6</v>
+        <v>0.58</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.12</v>
+        <v>4.19</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.32</v>
+        <v>5.46</v>
       </c>
       <c r="BR5" t="n">
-        <v>96</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="BS5" t="n">
-        <v>84</v>
+        <v>84.62</v>
       </c>
       <c r="BT5" t="n">
-        <v>40</v>
+        <v>42.31</v>
       </c>
       <c r="BU5" t="n">
-        <v>20</v>
+        <v>19.23</v>
       </c>
       <c r="BV5" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>40</v>
+        <v>42.31</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.6</v>
+        <v>3.61</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.56</v>
+        <v>3.59</v>
       </c>
       <c r="CC5" t="n">
         <v>2.28</v>
@@ -2834,7 +2834,7 @@
         <v>1.41</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="CG5" t="n">
         <v>2.72</v>
@@ -2849,13 +2849,13 @@
         <v>1.98</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CN5" t="n">
         <v>1.64</v>
@@ -2864,19 +2864,19 @@
         <v>1.31</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CQ5" t="n">
         <v>3.62</v>
       </c>
       <c r="CR5" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CS5" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="CU5" t="n">
         <v>1.36</v>
@@ -2885,19 +2885,19 @@
         <v>1.82</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CX5" t="n">
         <v>1.71</v>
       </c>
       <c r="CY5" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="DB5" t="n">
         <v>1.36</v>
@@ -2906,82 +2906,82 @@
         <v>2.14</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.44</v>
+        <v>3.38</v>
       </c>
       <c r="DH5" t="n">
-        <v>113.6</v>
+        <v>113.46</v>
       </c>
       <c r="DI5" t="n">
         <v>-0.04</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.96</v>
+        <v>5.92</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="DM5" t="n">
-        <v>67.04000000000001</v>
+        <v>67.45999999999999</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.72</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="DP5" t="n">
-        <v>12.52</v>
+        <v>12.69</v>
       </c>
       <c r="DQ5" t="n">
-        <v>15.04</v>
+        <v>14.69</v>
       </c>
       <c r="DR5" t="n">
-        <v>6.32</v>
+        <v>6.19</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>59.36</v>
+        <v>58.85</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX5" t="n">
-        <v>15</v>
+        <v>15.23</v>
       </c>
       <c r="DY5" t="n">
-        <v>9.84</v>
+        <v>9.92</v>
       </c>
       <c r="DZ5" t="n">
-        <v>5.16</v>
+        <v>5.31</v>
       </c>
       <c r="EA5" t="n">
         <v>21.88</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="EC5" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C6" t="n">
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E6" t="n">
         <v>0.25</v>
@@ -3081,139 +3081,139 @@
         <v>1.75</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.08</v>
+        <v>0.21</v>
       </c>
       <c r="AG6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>102.29</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>54.14</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>10.79</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>10.93</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>11.21</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>46.79</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>8.789999999999999</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>22.14</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>10.08</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BO6" t="n">
         <v>1.31</v>
       </c>
-      <c r="AH6" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>103.77</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>4</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>55.54</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>10.62</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>11.23</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>10.31</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>48.15</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>9</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>5.77</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>22.54</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>10.04</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>1.28</v>
-      </c>
       <c r="BP6" t="n">
-        <v>4.52</v>
+        <v>4.42</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.64</v>
+        <v>4.81</v>
       </c>
       <c r="BR6" t="n">
-        <v>96</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="BS6" t="n">
-        <v>76</v>
+        <v>76.92</v>
       </c>
       <c r="BT6" t="n">
-        <v>56</v>
+        <v>53.85</v>
       </c>
       <c r="BU6" t="n">
-        <v>20</v>
+        <v>19.23</v>
       </c>
       <c r="BV6" t="n">
-        <v>8</v>
+        <v>7.69</v>
       </c>
       <c r="BW6" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BX6" t="n">
-        <v>60</v>
+        <v>57.69</v>
       </c>
       <c r="BY6" t="n">
         <v>2.56</v>
@@ -3222,16 +3222,16 @@
         <v>2.73</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.37</v>
+        <v>3.39</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.49</v>
+        <v>3.5</v>
       </c>
       <c r="CC6" t="n">
-        <v>4.03</v>
+        <v>4.25</v>
       </c>
       <c r="CD6" t="n">
-        <v>4.68</v>
+        <v>4.82</v>
       </c>
       <c r="CE6" t="n">
         <v>1.41</v>
@@ -3255,7 +3255,7 @@
         <v>1.73</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="CM6" t="n">
         <v>2.01</v>
@@ -3270,7 +3270,7 @@
         <v>2.03</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.49</v>
+        <v>3.48</v>
       </c>
       <c r="CR6" t="n">
         <v>1.42</v>
@@ -3291,16 +3291,16 @@
         <v>1.9</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="CZ6" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="DB6" t="n">
         <v>1.34</v>
@@ -3309,19 +3309,19 @@
         <v>2.09</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.69</v>
+        <v>3.68</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.16</v>
+        <v>0.23</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="DH6" t="n">
-        <v>105.52</v>
+        <v>104.66</v>
       </c>
       <c r="DI6" t="n">
         <v>0.16</v>
@@ -3330,28 +3330,28 @@
         <v>2</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.2</v>
+        <v>4.04</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="DM6" t="n">
-        <v>57</v>
+        <v>56.19</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="DP6" t="n">
-        <v>11</v>
+        <v>11.08</v>
       </c>
       <c r="DQ6" t="n">
-        <v>11.6</v>
+        <v>11.42</v>
       </c>
       <c r="DR6" t="n">
-        <v>10.32</v>
+        <v>10.8</v>
       </c>
       <c r="DS6" t="n">
         <v>0.04</v>
@@ -3363,25 +3363,25 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>50.12</v>
+        <v>49.31</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>10.12</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="DY6" t="n">
-        <v>6.76</v>
+        <v>6.65</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.36</v>
+        <v>3.31</v>
       </c>
       <c r="EA6" t="n">
-        <v>22.44</v>
+        <v>22.23</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="EC6" t="n">
         <v>2</v>
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C7" t="n">
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3484,46 +3484,46 @@
         <v>2.15</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="AI7" t="n">
-        <v>113.83</v>
+        <v>111.92</v>
       </c>
       <c r="AJ7" t="n">
         <v>0.08</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AL7" t="n">
-        <v>4.75</v>
+        <v>5.15</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AN7" t="n">
-        <v>60.83</v>
+        <v>60.38</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AP7" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ7" t="n">
-        <v>14.58</v>
+        <v>13.92</v>
       </c>
       <c r="AR7" t="n">
-        <v>10.75</v>
+        <v>11.23</v>
       </c>
       <c r="AS7" t="n">
-        <v>6.75</v>
+        <v>7.15</v>
       </c>
       <c r="AT7" t="n">
         <v>1.92</v>
@@ -3532,91 +3532,91 @@
         <v>0.92</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>52.58</v>
+        <v>52.69</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="BA7" t="n">
-        <v>10.25</v>
+        <v>10.77</v>
       </c>
       <c r="BB7" t="n">
-        <v>7.25</v>
+        <v>7.62</v>
       </c>
       <c r="BC7" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="BD7" t="n">
-        <v>21.17</v>
+        <v>21.08</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.640000000000001</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.68</v>
+        <v>0.73</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="BL7" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.84</v>
+        <v>3.92</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.8</v>
+        <v>4.96</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>92</v>
+        <v>92.31</v>
       </c>
       <c r="BT7" t="n">
-        <v>44</v>
+        <v>46.15</v>
       </c>
       <c r="BU7" t="n">
-        <v>24</v>
+        <v>23.08</v>
       </c>
       <c r="BV7" t="n">
-        <v>8</v>
+        <v>7.69</v>
       </c>
       <c r="BW7" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BX7" t="n">
-        <v>72</v>
+        <v>73.08</v>
       </c>
       <c r="BY7" t="n">
         <v>2.83</v>
@@ -3625,16 +3625,16 @@
         <v>2.94</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.53</v>
+        <v>3.55</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.56</v>
+        <v>3.58</v>
       </c>
       <c r="CC7" t="n">
-        <v>4.44</v>
+        <v>4.55</v>
       </c>
       <c r="CD7" t="n">
-        <v>4.72</v>
+        <v>4.84</v>
       </c>
       <c r="CE7" t="n">
         <v>1.38</v>
@@ -3652,7 +3652,7 @@
         <v>1.9</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CK7" t="n">
         <v>1.59</v>
@@ -3676,22 +3676,22 @@
         <v>3.3</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="CU7" t="n">
         <v>1.4</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CX7" t="n">
         <v>1.6</v>
@@ -3718,76 +3718,76 @@
         <v>0.16</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.48</v>
+        <v>2.66</v>
       </c>
       <c r="DH7" t="n">
-        <v>107.4</v>
+        <v>106.69</v>
       </c>
       <c r="DI7" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.44</v>
+        <v>4.65</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="DM7" t="n">
-        <v>59.12</v>
+        <v>58.96</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="DP7" t="n">
-        <v>14.48</v>
+        <v>14.15</v>
       </c>
       <c r="DQ7" t="n">
-        <v>11.96</v>
+        <v>12.16</v>
       </c>
       <c r="DR7" t="n">
-        <v>6.96</v>
+        <v>7.15</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>51.2</v>
+        <v>51.3</v>
       </c>
       <c r="DW7" t="n">
         <v>0.08</v>
       </c>
       <c r="DX7" t="n">
-        <v>10.84</v>
+        <v>11.08</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.24</v>
+        <v>7.43</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="EA7" t="n">
-        <v>22.12</v>
+        <v>22.04</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="EC7" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="8">
@@ -3797,10 +3797,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D8" t="n">
         <v>12</v>
@@ -3809,82 +3809,82 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="G8" t="n">
-        <v>2.85</v>
+        <v>2.93</v>
       </c>
       <c r="H8" t="n">
-        <v>116.31</v>
+        <v>114.43</v>
       </c>
       <c r="I8" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="K8" t="n">
-        <v>5.69</v>
+        <v>5.64</v>
       </c>
       <c r="L8" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="M8" t="n">
-        <v>78.84999999999999</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="O8" t="n">
-        <v>2.77</v>
+        <v>2.64</v>
       </c>
       <c r="P8" t="n">
-        <v>14.69</v>
+        <v>14.57</v>
       </c>
       <c r="Q8" t="n">
-        <v>13.77</v>
+        <v>13.57</v>
       </c>
       <c r="R8" t="n">
-        <v>6.85</v>
+        <v>6.64</v>
       </c>
       <c r="S8" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="T8" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="U8" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>48.92</v>
+        <v>49.57</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Z8" t="n">
-        <v>12.23</v>
+        <v>12.71</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.77</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.46</v>
+        <v>3.36</v>
       </c>
       <c r="AC8" t="n">
-        <v>21.31</v>
+        <v>20.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="AF8" t="n">
         <v>0.08</v>
@@ -3968,70 +3968,70 @@
         <v>2.33</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.32</v>
+        <v>2.23</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.800000000000001</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.32</v>
+        <v>2.23</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.84</v>
+        <v>4.81</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.92</v>
+        <v>5.04</v>
       </c>
       <c r="BR8" t="n">
-        <v>84</v>
+        <v>80.77</v>
       </c>
       <c r="BS8" t="n">
-        <v>72</v>
+        <v>69.23</v>
       </c>
       <c r="BT8" t="n">
-        <v>40</v>
+        <v>38.46</v>
       </c>
       <c r="BU8" t="n">
-        <v>20</v>
+        <v>19.23</v>
       </c>
       <c r="BV8" t="n">
-        <v>8</v>
+        <v>7.69</v>
       </c>
       <c r="BW8" t="n">
-        <v>8</v>
+        <v>7.69</v>
       </c>
       <c r="BX8" t="n">
-        <v>44</v>
+        <v>42.31</v>
       </c>
       <c r="BY8" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BZ8" t="n">
         <v>2.8</v>
       </c>
-      <c r="BZ8" t="n">
-        <v>2.83</v>
-      </c>
       <c r="CA8" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="CB8" t="n">
         <v>3.37</v>
-      </c>
-      <c r="CB8" t="n">
-        <v>3.39</v>
       </c>
       <c r="CC8" t="n">
         <v>3.44</v>
@@ -4055,13 +4055,13 @@
         <v>1.9</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CK8" t="n">
         <v>1.58</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CM8" t="n">
         <v>2.22</v>
@@ -4076,7 +4076,7 @@
         <v>1.99</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.32</v>
+        <v>3.34</v>
       </c>
       <c r="CR8" t="n">
         <v>1.42</v>
@@ -4085,7 +4085,7 @@
         <v>3.06</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="CU8" t="n">
         <v>1.38</v>
@@ -4103,7 +4103,7 @@
         <v>2.01</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="DA8" t="n">
         <v>1.75</v>
@@ -4112,52 +4112,52 @@
         <v>1.33</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.65</v>
+        <v>3.67</v>
       </c>
       <c r="DE8" t="n">
         <v>0.04</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.32</v>
+        <v>2.39</v>
       </c>
       <c r="DH8" t="n">
-        <v>109</v>
+        <v>108.27</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="DK8" t="n">
         <v>4.8</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.72</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DM8" t="n">
-        <v>67.08</v>
+        <v>66.69</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="DP8" t="n">
-        <v>15.16</v>
+        <v>15.08</v>
       </c>
       <c r="DQ8" t="n">
-        <v>13.36</v>
+        <v>13.27</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.36</v>
+        <v>7.23</v>
       </c>
       <c r="DS8" t="n">
         <v>0.04</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>48.56</v>
+        <v>48.92</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DX8" t="n">
-        <v>11.96</v>
+        <v>12.23</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.4</v>
+        <v>8.73</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.56</v>
+        <v>3.5</v>
       </c>
       <c r="EA8" t="n">
-        <v>22</v>
+        <v>21.54</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.32</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="9">
@@ -4200,94 +4200,94 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D9" t="n">
         <v>12</v>
       </c>
       <c r="E9" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="F9" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="G9" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="H9" t="n">
+        <v>120.64</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="K9" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="M9" t="n">
+        <v>72</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="O9" t="n">
         <v>3</v>
       </c>
-      <c r="H9" t="n">
-        <v>117.62</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="K9" t="n">
-        <v>6.08</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="M9" t="n">
-        <v>69</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="O9" t="n">
-        <v>3.08</v>
-      </c>
       <c r="P9" t="n">
-        <v>12.38</v>
+        <v>12</v>
       </c>
       <c r="Q9" t="n">
-        <v>13.54</v>
+        <v>13.5</v>
       </c>
       <c r="R9" t="n">
-        <v>7.31</v>
+        <v>7.14</v>
       </c>
       <c r="S9" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="T9" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="U9" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="V9" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>51.31</v>
+        <v>52.71</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Z9" t="n">
-        <v>15.08</v>
+        <v>16.07</v>
       </c>
       <c r="AA9" t="n">
-        <v>10.62</v>
+        <v>11.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.46</v>
+        <v>4.57</v>
       </c>
       <c r="AC9" t="n">
-        <v>23.46</v>
+        <v>23.64</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.76</v>
+        <v>1.86</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="AF9" t="n">
         <v>0.17</v>
@@ -4371,70 +4371,70 @@
         <v>2.75</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.04</v>
+        <v>10.08</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.48</v>
+        <v>0.54</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.84</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.48</v>
+        <v>4.38</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.56</v>
+        <v>5.69</v>
       </c>
       <c r="BR9" t="n">
-        <v>88</v>
+        <v>88.45999999999999</v>
       </c>
       <c r="BS9" t="n">
-        <v>68</v>
+        <v>69.23</v>
       </c>
       <c r="BT9" t="n">
-        <v>44</v>
+        <v>42.31</v>
       </c>
       <c r="BU9" t="n">
-        <v>32</v>
+        <v>30.77</v>
       </c>
       <c r="BV9" t="n">
-        <v>12</v>
+        <v>11.54</v>
       </c>
       <c r="BW9" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BX9" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.58</v>
+        <v>3.59</v>
       </c>
       <c r="CC9" t="n">
         <v>2.78</v>
@@ -4464,13 +4464,13 @@
         <v>1.62</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CM9" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CO9" t="n">
         <v>1.31</v>
@@ -4479,7 +4479,7 @@
         <v>2.02</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.5</v>
+        <v>3.49</v>
       </c>
       <c r="CR9" t="n">
         <v>1.42</v>
@@ -4497,19 +4497,19 @@
         <v>1.84</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CY9" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="DB9" t="n">
         <v>1.35</v>
@@ -4521,79 +4521,79 @@
         <v>3.75</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.92</v>
+        <v>3.15</v>
       </c>
       <c r="DH9" t="n">
-        <v>113.84</v>
+        <v>115.61</v>
       </c>
       <c r="DI9" t="n">
         <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.72</v>
+        <v>2.69</v>
       </c>
       <c r="DK9" t="n">
-        <v>5.76</v>
+        <v>5.96</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="DM9" t="n">
-        <v>65.48</v>
+        <v>67.23</v>
       </c>
       <c r="DN9" t="n">
         <v>0.84</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.84</v>
+        <v>2.81</v>
       </c>
       <c r="DP9" t="n">
-        <v>12.56</v>
+        <v>12.35</v>
       </c>
       <c r="DQ9" t="n">
-        <v>13.4</v>
+        <v>13.38</v>
       </c>
       <c r="DR9" t="n">
-        <v>7.12</v>
+        <v>7.04</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>50.88</v>
+        <v>51.65</v>
       </c>
       <c r="DW9" t="n">
         <v>0.12</v>
       </c>
       <c r="DX9" t="n">
-        <v>14.24</v>
+        <v>14.81</v>
       </c>
       <c r="DY9" t="n">
-        <v>10.4</v>
+        <v>10.89</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3.84</v>
+        <v>3.92</v>
       </c>
       <c r="EA9" t="n">
-        <v>22.96</v>
+        <v>23.08</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="10">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C10" t="n">
         <v>12</v>
       </c>
       <c r="D10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E10" t="n">
         <v>0.25</v>
@@ -4693,139 +4693,139 @@
         <v>1.92</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AH10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>48.93</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>14.43</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>12.71</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>45.71</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>9.640000000000001</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>20.93</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>7.38</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="BN10" t="n">
         <v>1.62</v>
       </c>
-      <c r="AI10" t="n">
-        <v>107.15</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>50.38</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>14.85</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>13.08</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>8.380000000000001</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>46.46</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>10</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>6.85</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>7.48</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>1.48</v>
-      </c>
       <c r="BO10" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.24</v>
+        <v>3.27</v>
       </c>
       <c r="BQ10" t="n">
-        <v>3.48</v>
+        <v>3.38</v>
       </c>
       <c r="BR10" t="n">
-        <v>92</v>
+        <v>92.31</v>
       </c>
       <c r="BS10" t="n">
-        <v>88</v>
+        <v>88.45999999999999</v>
       </c>
       <c r="BT10" t="n">
-        <v>60</v>
+        <v>61.54</v>
       </c>
       <c r="BU10" t="n">
-        <v>32</v>
+        <v>34.62</v>
       </c>
       <c r="BV10" t="n">
-        <v>12</v>
+        <v>15.38</v>
       </c>
       <c r="BW10" t="n">
-        <v>4</v>
+        <v>7.69</v>
       </c>
       <c r="BX10" t="n">
-        <v>68</v>
+        <v>69.23</v>
       </c>
       <c r="BY10" t="n">
         <v>2.6</v>
@@ -4834,79 +4834,79 @@
         <v>2.78</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.38</v>
+        <v>3.45</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.46</v>
+        <v>3.55</v>
       </c>
       <c r="CC10" t="n">
-        <v>4.29</v>
+        <v>4.65</v>
       </c>
       <c r="CD10" t="n">
-        <v>4.85</v>
+        <v>5.26</v>
       </c>
       <c r="CE10" t="n">
         <v>1.38</v>
       </c>
       <c r="CF10" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="CG10" t="n">
         <v>2.86</v>
       </c>
-      <c r="CG10" t="n">
-        <v>2.85</v>
-      </c>
       <c r="CH10" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CK10" t="n">
         <v>1.73</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="CM10" t="n">
         <v>2.01</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CO10" t="n">
         <v>1.29</v>
       </c>
       <c r="CP10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="CS10" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="CT10" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="CU10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="CV10" t="n">
         <v>1.96</v>
       </c>
-      <c r="CQ10" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="CR10" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="CS10" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="CT10" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="CU10" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="CV10" t="n">
-        <v>1.97</v>
-      </c>
       <c r="CW10" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CX10" t="n">
         <v>1.74</v>
       </c>
       <c r="CY10" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CZ10" t="n">
         <v>2.01</v>
@@ -4915,88 +4915,88 @@
         <v>1.61</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.55</v>
+        <v>3.51</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.76</v>
+        <v>1.69</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.76</v>
+        <v>1.69</v>
       </c>
       <c r="DH10" t="n">
-        <v>111.28</v>
+        <v>110.77</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.56</v>
+        <v>2.46</v>
       </c>
       <c r="DK10" t="n">
-        <v>3.6</v>
+        <v>3.46</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="DM10" t="n">
-        <v>55.6</v>
+        <v>54.62</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="DP10" t="n">
-        <v>13.84</v>
+        <v>13.65</v>
       </c>
       <c r="DQ10" t="n">
-        <v>13</v>
+        <v>12.81</v>
       </c>
       <c r="DR10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.19</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>49.32</v>
+        <v>48.81</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.32</v>
+        <v>12.04</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.32</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4</v>
+        <v>3.92</v>
       </c>
       <c r="EA10" t="n">
-        <v>22.68</v>
+        <v>22.73</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="11">

--- a/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
@@ -3520,7 +3520,7 @@
         <v>13.92</v>
       </c>
       <c r="AR7" t="n">
-        <v>11.23</v>
+        <v>11.15</v>
       </c>
       <c r="AS7" t="n">
         <v>7.15</v>
@@ -3556,7 +3556,7 @@
         <v>3.15</v>
       </c>
       <c r="BD7" t="n">
-        <v>21.08</v>
+        <v>21.15</v>
       </c>
       <c r="BE7" t="n">
         <v>1.34</v>
@@ -3751,7 +3751,7 @@
         <v>14.15</v>
       </c>
       <c r="DQ7" t="n">
-        <v>12.16</v>
+        <v>12.12</v>
       </c>
       <c r="DR7" t="n">
         <v>7.15</v>
@@ -3781,7 +3781,7 @@
         <v>3.65</v>
       </c>
       <c r="EA7" t="n">
-        <v>22.04</v>
+        <v>22.08</v>
       </c>
       <c r="EB7" t="n">
         <v>1.39</v>
@@ -4212,7 +4212,7 @@
         <v>0.21</v>
       </c>
       <c r="F9" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="G9" t="n">
         <v>3.43</v>
@@ -4224,7 +4224,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2.36</v>
+        <v>2.43</v>
       </c>
       <c r="K9" t="n">
         <v>6.43</v>
@@ -4287,7 +4287,7 @@
         <v>1.86</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.21</v>
+        <v>2.29</v>
       </c>
       <c r="AF9" t="n">
         <v>0.17</v>
@@ -4524,7 +4524,7 @@
         <v>0.19</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="DG9" t="n">
         <v>3.15</v>
@@ -4536,7 +4536,7 @@
         <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="DK9" t="n">
         <v>5.96</v>
@@ -4593,7 +4593,7 @@
         <v>1.7</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="10">

--- a/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D6" t="n">
         <v>14</v>
       </c>
       <c r="E6" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="F6" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="G6" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="H6" t="n">
-        <v>107.42</v>
+        <v>108.08</v>
       </c>
       <c r="I6" t="n">
         <v>-0.08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="K6" t="n">
-        <v>4.42</v>
+        <v>4.38</v>
       </c>
       <c r="L6" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="M6" t="n">
-        <v>58.58</v>
+        <v>59.08</v>
       </c>
       <c r="N6" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="O6" t="n">
         <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>11.42</v>
+        <v>11.23</v>
       </c>
       <c r="Q6" t="n">
-        <v>12</v>
+        <v>12.38</v>
       </c>
       <c r="R6" t="n">
-        <v>10.33</v>
+        <v>10.38</v>
       </c>
       <c r="S6" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="T6" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -3057,28 +3057,28 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>52.25</v>
+        <v>51.85</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>11.33</v>
+        <v>11.23</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.83</v>
+        <v>7.62</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.5</v>
+        <v>3.62</v>
       </c>
       <c r="AC6" t="n">
-        <v>22.33</v>
+        <v>22.62</v>
       </c>
       <c r="AD6" t="n">
         <v>1.39</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AF6" t="n">
         <v>0.21</v>
@@ -3162,70 +3162,70 @@
         <v>2.21</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="BH6" t="n">
-        <v>10.08</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.73</v>
+        <v>0.78</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.42</v>
+        <v>4.37</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.81</v>
+        <v>4.78</v>
       </c>
       <c r="BR6" t="n">
-        <v>96.15000000000001</v>
+        <v>96.3</v>
       </c>
       <c r="BS6" t="n">
-        <v>76.92</v>
+        <v>77.78</v>
       </c>
       <c r="BT6" t="n">
-        <v>53.85</v>
+        <v>55.56</v>
       </c>
       <c r="BU6" t="n">
-        <v>19.23</v>
+        <v>18.52</v>
       </c>
       <c r="BV6" t="n">
-        <v>7.69</v>
+        <v>7.41</v>
       </c>
       <c r="BW6" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="BX6" t="n">
-        <v>57.69</v>
+        <v>59.26</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="BZ6" t="n">
         <v>2.73</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.39</v>
+        <v>3.38</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="CC6" t="n">
         <v>4.25</v>
@@ -3240,7 +3240,7 @@
         <v>2.88</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="CH6" t="n">
         <v>1.37</v>
@@ -3279,13 +3279,13 @@
         <v>3.03</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="CU6" t="n">
         <v>1.39</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CW6" t="n">
         <v>1.9</v>
@@ -3300,7 +3300,7 @@
         <v>1.98</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="DB6" t="n">
         <v>1.34</v>
@@ -3312,46 +3312,46 @@
         <v>3.68</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="DH6" t="n">
-        <v>104.66</v>
+        <v>105.08</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.04</v>
+        <v>4.03</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="DM6" t="n">
-        <v>56.19</v>
+        <v>56.52</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="DP6" t="n">
-        <v>11.08</v>
+        <v>11</v>
       </c>
       <c r="DQ6" t="n">
-        <v>11.42</v>
+        <v>11.63</v>
       </c>
       <c r="DR6" t="n">
-        <v>10.8</v>
+        <v>10.81</v>
       </c>
       <c r="DS6" t="n">
         <v>0.04</v>
@@ -3363,7 +3363,7 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>49.31</v>
+        <v>49.23</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
@@ -3372,19 +3372,19 @@
         <v>9.960000000000001</v>
       </c>
       <c r="DY6" t="n">
-        <v>6.65</v>
+        <v>6.59</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.31</v>
+        <v>3.37</v>
       </c>
       <c r="EA6" t="n">
-        <v>22.23</v>
+        <v>22.37</v>
       </c>
       <c r="EB6" t="n">
         <v>1.28</v>
       </c>
       <c r="EC6" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="7">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
         <v>13</v>
       </c>
       <c r="D11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E11" t="n">
         <v>0.23</v>
@@ -5096,139 +5096,139 @@
         <v>2.23</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AI11" t="n">
-        <v>92.38</v>
+        <v>94.56999999999999</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.54</v>
+        <v>2.36</v>
       </c>
       <c r="AL11" t="n">
-        <v>3.77</v>
+        <v>3.71</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AN11" t="n">
-        <v>46.77</v>
+        <v>47.86</v>
       </c>
       <c r="AO11" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AQ11" t="n">
-        <v>12.46</v>
+        <v>12.79</v>
       </c>
       <c r="AR11" t="n">
-        <v>12.69</v>
+        <v>12.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>8.539999999999999</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>43.85</v>
+        <v>44.5</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="BA11" t="n">
-        <v>10.38</v>
+        <v>10.71</v>
       </c>
       <c r="BB11" t="n">
-        <v>7</v>
+        <v>7.29</v>
       </c>
       <c r="BC11" t="n">
-        <v>3.38</v>
+        <v>3.43</v>
       </c>
       <c r="BD11" t="n">
-        <v>18.69</v>
+        <v>19.36</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.85</v>
+        <v>9.74</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.77</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.35</v>
+        <v>4.3</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.81</v>
+        <v>4.78</v>
       </c>
       <c r="BR11" t="n">
-        <v>92.31</v>
+        <v>92.59</v>
       </c>
       <c r="BS11" t="n">
-        <v>80.77</v>
+        <v>81.48</v>
       </c>
       <c r="BT11" t="n">
-        <v>50</v>
+        <v>51.85</v>
       </c>
       <c r="BU11" t="n">
-        <v>34.62</v>
+        <v>33.33</v>
       </c>
       <c r="BV11" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="BW11" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="BX11" t="n">
-        <v>61.54</v>
+        <v>62.96</v>
       </c>
       <c r="BY11" t="n">
         <v>3.05</v>
@@ -5237,16 +5237,16 @@
         <v>3.28</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.38</v>
+        <v>3.36</v>
       </c>
       <c r="CC11" t="n">
-        <v>3.85</v>
+        <v>3.77</v>
       </c>
       <c r="CD11" t="n">
-        <v>4.24</v>
+        <v>4.15</v>
       </c>
       <c r="CE11" t="n">
         <v>1.43</v>
@@ -5255,28 +5255,28 @@
         <v>3</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="CH11" t="n">
         <v>1.34</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CJ11" t="n">
         <v>1.91</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="CM11" t="n">
         <v>2.02</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CO11" t="n">
         <v>1.33</v>
@@ -5285,34 +5285,34 @@
         <v>2.08</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.6</v>
+        <v>3.59</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CS11" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="CT11" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="DA11" t="n">
         <v>1.62</v>
@@ -5324,82 +5324,82 @@
         <v>2.15</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.83</v>
+        <v>3.82</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="DG11" t="n">
         <v>1.7</v>
       </c>
       <c r="DH11" t="n">
-        <v>100.38</v>
+        <v>101.22</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.46</v>
+        <v>2.37</v>
       </c>
       <c r="DK11" t="n">
-        <v>3.81</v>
+        <v>3.78</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="DM11" t="n">
-        <v>50.84</v>
+        <v>51.26</v>
       </c>
       <c r="DN11" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="DP11" t="n">
-        <v>12.12</v>
+        <v>12.3</v>
       </c>
       <c r="DQ11" t="n">
-        <v>12.92</v>
+        <v>12.81</v>
       </c>
       <c r="DR11" t="n">
-        <v>8.109999999999999</v>
+        <v>7.92</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>44.74</v>
+        <v>45.04</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DX11" t="n">
-        <v>11.96</v>
+        <v>12.07</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.27</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.69</v>
+        <v>3.7</v>
       </c>
       <c r="EA11" t="n">
-        <v>19.96</v>
+        <v>20.26</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C2" t="n">
         <v>13</v>
       </c>
       <c r="D2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E2" t="n">
         <v>0.23</v>
@@ -1469,139 +1469,139 @@
         <v>1.77</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AH2" t="n">
-        <v>3.85</v>
+        <v>3.71</v>
       </c>
       <c r="AI2" t="n">
-        <v>119.54</v>
+        <v>120</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AL2" t="n">
-        <v>6.54</v>
+        <v>6.57</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.46</v>
+        <v>0.57</v>
       </c>
       <c r="AN2" t="n">
-        <v>74.31</v>
+        <v>74.64</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.69</v>
+        <v>2.86</v>
       </c>
       <c r="AQ2" t="n">
-        <v>14.08</v>
+        <v>13.71</v>
       </c>
       <c r="AR2" t="n">
-        <v>13.31</v>
+        <v>13</v>
       </c>
       <c r="AS2" t="n">
-        <v>6</v>
+        <v>6.07</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AU2" t="n">
-        <v>2.08</v>
+        <v>2.29</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>54.46</v>
+        <v>55.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="BA2" t="n">
-        <v>16</v>
+        <v>16.36</v>
       </c>
       <c r="BB2" t="n">
-        <v>10.92</v>
+        <v>10.86</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.08</v>
+        <v>5.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>24.54</v>
+        <v>23.64</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.27</v>
+        <v>3.33</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.619999999999999</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.27</v>
+        <v>3.33</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.65</v>
+        <v>0.74</v>
       </c>
       <c r="BL2" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.85</v>
+        <v>0.89</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.62</v>
+        <v>4.67</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.96</v>
+        <v>4.93</v>
       </c>
       <c r="BR2" t="n">
-        <v>96.15000000000001</v>
+        <v>96.3</v>
       </c>
       <c r="BS2" t="n">
-        <v>92.31</v>
+        <v>92.59</v>
       </c>
       <c r="BT2" t="n">
-        <v>69.23</v>
+        <v>70.37</v>
       </c>
       <c r="BU2" t="n">
-        <v>38.46</v>
+        <v>40.74</v>
       </c>
       <c r="BV2" t="n">
-        <v>15.38</v>
+        <v>18.52</v>
       </c>
       <c r="BW2" t="n">
-        <v>11.54</v>
+        <v>11.11</v>
       </c>
       <c r="BX2" t="n">
-        <v>53.85</v>
+        <v>51.85</v>
       </c>
       <c r="BY2" t="n">
         <v>1.28</v>
@@ -1613,13 +1613,13 @@
         <v>4.64</v>
       </c>
       <c r="CB2" t="n">
-        <v>5.01</v>
+        <v>5</v>
       </c>
       <c r="CC2" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="CD2" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="CE2" t="n">
         <v>1.31</v>
@@ -1637,19 +1637,19 @@
         <v>1.79</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CO2" t="n">
         <v>1.22</v>
@@ -1658,16 +1658,16 @@
         <v>1.74</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.83</v>
+        <v>2.81</v>
       </c>
       <c r="CR2" t="n">
         <v>1.37</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="CT2" t="n">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="CU2" t="n">
         <v>1.53</v>
@@ -1697,82 +1697,82 @@
         <v>1.74</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.19</v>
+        <v>0.22</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.27</v>
+        <v>3.22</v>
       </c>
       <c r="DH2" t="n">
-        <v>120.46</v>
+        <v>120.66</v>
       </c>
       <c r="DI2" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="DK2" t="n">
-        <v>6.34</v>
+        <v>6.37</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DM2" t="n">
-        <v>73.31</v>
+        <v>73.52</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DO2" t="n">
-        <v>3.03</v>
+        <v>3.11</v>
       </c>
       <c r="DP2" t="n">
-        <v>12.46</v>
+        <v>12.33</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.62</v>
+        <v>12.48</v>
       </c>
       <c r="DR2" t="n">
-        <v>5.73</v>
+        <v>5.78</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>56.54</v>
+        <v>57</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX2" t="n">
-        <v>16.62</v>
+        <v>16.78</v>
       </c>
       <c r="DY2" t="n">
-        <v>10.54</v>
+        <v>10.52</v>
       </c>
       <c r="DZ2" t="n">
-        <v>6.08</v>
+        <v>6.26</v>
       </c>
       <c r="EA2" t="n">
-        <v>23</v>
+        <v>22.59</v>
       </c>
       <c r="EB2" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="3">
@@ -1782,94 +1782,94 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D3" t="n">
         <v>13</v>
       </c>
       <c r="E3" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="F3" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="G3" t="n">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="H3" t="n">
-        <v>96.31</v>
+        <v>96.56999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="J3" t="n">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="K3" t="n">
-        <v>3.92</v>
+        <v>3.71</v>
       </c>
       <c r="L3" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="M3" t="n">
-        <v>49.31</v>
+        <v>49.07</v>
       </c>
       <c r="N3" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="O3" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="P3" t="n">
-        <v>11.85</v>
+        <v>11.64</v>
       </c>
       <c r="Q3" t="n">
-        <v>13.92</v>
+        <v>13.93</v>
       </c>
       <c r="R3" t="n">
-        <v>8.08</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="T3" t="n">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="U3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="V3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>48.54</v>
+        <v>48.14</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Z3" t="n">
-        <v>10.69</v>
+        <v>10.64</v>
       </c>
       <c r="AA3" t="n">
-        <v>6.92</v>
+        <v>6.71</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.77</v>
+        <v>3.93</v>
       </c>
       <c r="AC3" t="n">
-        <v>21.23</v>
+        <v>20.93</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -1953,70 +1953,70 @@
         <v>1.69</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.58</v>
+        <v>2.63</v>
       </c>
       <c r="BH3" t="n">
-        <v>8.85</v>
+        <v>8.74</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.58</v>
+        <v>2.63</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.78</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.81</v>
+        <v>3.74</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.12</v>
+        <v>4.11</v>
       </c>
       <c r="BR3" t="n">
-        <v>92.31</v>
+        <v>92.59</v>
       </c>
       <c r="BS3" t="n">
-        <v>73.08</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="BT3" t="n">
-        <v>50</v>
+        <v>51.85</v>
       </c>
       <c r="BU3" t="n">
-        <v>30.77</v>
+        <v>33.33</v>
       </c>
       <c r="BV3" t="n">
-        <v>7.69</v>
+        <v>7.41</v>
       </c>
       <c r="BW3" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="BX3" t="n">
-        <v>57.69</v>
+        <v>55.56</v>
       </c>
       <c r="BY3" t="n">
-        <v>2.91</v>
+        <v>2.93</v>
       </c>
       <c r="BZ3" t="n">
         <v>3.04</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.51</v>
+        <v>3.5</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.61</v>
+        <v>3.59</v>
       </c>
       <c r="CC3" t="n">
         <v>5.35</v>
@@ -2028,10 +2028,10 @@
         <v>1.4</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="CH3" t="n">
         <v>1.37</v>
@@ -2040,13 +2040,13 @@
         <v>1.83</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CK3" t="n">
         <v>1.68</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="CM3" t="n">
         <v>2.06</v>
@@ -2058,22 +2058,22 @@
         <v>1.31</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.49</v>
+        <v>3.51</v>
       </c>
       <c r="CR3" t="n">
         <v>1.43</v>
       </c>
       <c r="CS3" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="CT3" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CV3" t="n">
         <v>1.9</v>
@@ -2097,85 +2097,85 @@
         <v>1.34</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.71</v>
+        <v>3.74</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="DG3" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="DH3" t="n">
-        <v>95.5</v>
+        <v>95.66</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="DK3" t="n">
-        <v>4.54</v>
+        <v>4.4</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DM3" t="n">
-        <v>51.66</v>
+        <v>51.44</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="DP3" t="n">
-        <v>11.42</v>
+        <v>11.33</v>
       </c>
       <c r="DQ3" t="n">
-        <v>13.3</v>
+        <v>13.33</v>
       </c>
       <c r="DR3" t="n">
-        <v>8.380000000000001</v>
+        <v>8.48</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>46.54</v>
+        <v>46.41</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX3" t="n">
-        <v>11.69</v>
+        <v>11.63</v>
       </c>
       <c r="DY3" t="n">
-        <v>7.88</v>
+        <v>7.74</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.81</v>
+        <v>3.89</v>
       </c>
       <c r="EA3" t="n">
-        <v>20.81</v>
+        <v>20.67</v>
       </c>
       <c r="EB3" t="n">
         <v>1.38</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4" t="n">
         <v>14</v>
@@ -2197,82 +2197,82 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="G4" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="H4" t="n">
-        <v>118.75</v>
+        <v>120.23</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="K4" t="n">
-        <v>3.75</v>
+        <v>3.69</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>72.25</v>
+        <v>71.69</v>
       </c>
       <c r="N4" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="P4" t="n">
-        <v>13.08</v>
+        <v>12.85</v>
       </c>
       <c r="Q4" t="n">
-        <v>11.83</v>
+        <v>11.77</v>
       </c>
       <c r="R4" t="n">
-        <v>7.33</v>
+        <v>7.31</v>
       </c>
       <c r="S4" t="n">
-        <v>1.33</v>
+        <v>1.69</v>
       </c>
       <c r="T4" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="U4" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="V4" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>44.42</v>
+        <v>44.54</v>
       </c>
       <c r="Y4" t="n">
         <v>0.08</v>
       </c>
       <c r="Z4" t="n">
-        <v>11.42</v>
+        <v>11.08</v>
       </c>
       <c r="AA4" t="n">
-        <v>7.17</v>
+        <v>6.85</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.25</v>
+        <v>4.23</v>
       </c>
       <c r="AC4" t="n">
         <v>21.08</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AF4" t="n">
         <v>0.14</v>
@@ -2356,70 +2356,70 @@
         <v>2.64</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.77</v>
+        <v>2.89</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.69</v>
+        <v>9.52</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.77</v>
+        <v>2.89</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.46</v>
+        <v>0.52</v>
       </c>
       <c r="BL4" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.46</v>
+        <v>0.59</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.77</v>
+        <v>4.7</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.85</v>
+        <v>4.74</v>
       </c>
       <c r="BR4" t="n">
-        <v>96.15000000000001</v>
+        <v>96.3</v>
       </c>
       <c r="BS4" t="n">
-        <v>80.77</v>
+        <v>81.48</v>
       </c>
       <c r="BT4" t="n">
-        <v>53.85</v>
+        <v>55.56</v>
       </c>
       <c r="BU4" t="n">
-        <v>34.62</v>
+        <v>37.04</v>
       </c>
       <c r="BV4" t="n">
-        <v>11.54</v>
+        <v>14.81</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BX4" t="n">
-        <v>61.54</v>
+        <v>59.26</v>
       </c>
       <c r="BY4" t="n">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="BZ4" t="n">
-        <v>4.59</v>
+        <v>4.64</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.08</v>
+        <v>4.06</v>
       </c>
       <c r="CB4" t="n">
-        <v>4.15</v>
+        <v>4.13</v>
       </c>
       <c r="CC4" t="n">
         <v>6.14</v>
@@ -2434,7 +2434,7 @@
         <v>2.69</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="CH4" t="n">
         <v>1.43</v>
@@ -2473,7 +2473,7 @@
         <v>2.71</v>
       </c>
       <c r="CT4" t="n">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="CU4" t="n">
         <v>1.48</v>
@@ -2482,7 +2482,7 @@
         <v>1.92</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CX4" t="n">
         <v>1.66</v>
@@ -2500,52 +2500,52 @@
         <v>1.28</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="DH4" t="n">
-        <v>113.16</v>
+        <v>114.08</v>
       </c>
       <c r="DI4" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.61</v>
+        <v>2.52</v>
       </c>
       <c r="DK4" t="n">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="DL4" t="n">
         <v>0.11</v>
       </c>
       <c r="DM4" t="n">
-        <v>63.69</v>
+        <v>63.74</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="DP4" t="n">
-        <v>12.96</v>
+        <v>12.86</v>
       </c>
       <c r="DQ4" t="n">
-        <v>11.38</v>
+        <v>11.37</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.390000000000001</v>
+        <v>8.34</v>
       </c>
       <c r="DS4" t="n">
         <v>0.15</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>43.35</v>
+        <v>43.45</v>
       </c>
       <c r="DW4" t="n">
         <v>0.19</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.08</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.77</v>
+        <v>6.63</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.31</v>
+        <v>3.33</v>
       </c>
       <c r="EA4" t="n">
-        <v>21.77</v>
+        <v>21.74</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.27</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C5" t="n">
         <v>14</v>
       </c>
       <c r="D5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E5" t="n">
         <v>0.21</v>
@@ -2678,139 +2678,139 @@
         <v>1.57</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AH5" t="n">
-        <v>3.33</v>
+        <v>3.23</v>
       </c>
       <c r="AI5" t="n">
-        <v>108.75</v>
+        <v>109.38</v>
       </c>
       <c r="AJ5" t="n">
         <v>-0.08</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.42</v>
+        <v>2.31</v>
       </c>
       <c r="AL5" t="n">
-        <v>6.83</v>
+        <v>6.46</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AN5" t="n">
-        <v>67.33</v>
+        <v>68.31</v>
       </c>
       <c r="AO5" t="n">
         <v>0.92</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.5</v>
+        <v>3.23</v>
       </c>
       <c r="AQ5" t="n">
-        <v>13.33</v>
+        <v>13.15</v>
       </c>
       <c r="AR5" t="n">
-        <v>14.42</v>
+        <v>14</v>
       </c>
       <c r="AS5" t="n">
-        <v>6.92</v>
+        <v>6.54</v>
       </c>
       <c r="AT5" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.33</v>
+        <v>1.69</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>58.83</v>
+        <v>58.46</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>14.75</v>
+        <v>15.08</v>
       </c>
       <c r="BB5" t="n">
-        <v>10.25</v>
+        <v>10.08</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BD5" t="n">
         <v>20.92</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.42</v>
+        <v>2.31</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.46</v>
+        <v>2.59</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.77</v>
+        <v>9.59</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.46</v>
+        <v>2.59</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.58</v>
+        <v>0.63</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.54</v>
+        <v>0.67</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.19</v>
+        <v>4.15</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.46</v>
+        <v>5.33</v>
       </c>
       <c r="BR5" t="n">
-        <v>96.15000000000001</v>
+        <v>96.3</v>
       </c>
       <c r="BS5" t="n">
-        <v>84.62</v>
+        <v>85.19</v>
       </c>
       <c r="BT5" t="n">
-        <v>42.31</v>
+        <v>44.44</v>
       </c>
       <c r="BU5" t="n">
-        <v>19.23</v>
+        <v>22.22</v>
       </c>
       <c r="BV5" t="n">
-        <v>3.85</v>
+        <v>7.41</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BX5" t="n">
-        <v>42.31</v>
+        <v>40.74</v>
       </c>
       <c r="BY5" t="n">
         <v>1.78</v>
@@ -2825,16 +2825,16 @@
         <v>3.59</v>
       </c>
       <c r="CC5" t="n">
-        <v>2.28</v>
+        <v>2.23</v>
       </c>
       <c r="CD5" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="CE5" t="n">
         <v>1.41</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="CG5" t="n">
         <v>2.72</v>
@@ -2846,7 +2846,7 @@
         <v>1.76</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CK5" t="n">
         <v>1.68</v>
@@ -2864,34 +2864,34 @@
         <v>1.31</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="CR5" t="n">
         <v>1.43</v>
       </c>
       <c r="CS5" t="n">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="CU5" t="n">
         <v>1.36</v>
       </c>
       <c r="CV5" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CW5" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CY5" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CZ5" t="n">
         <v>2.06</v>
@@ -2900,88 +2900,88 @@
         <v>1.65</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.8</v>
+        <v>3.78</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.38</v>
+        <v>3.33</v>
       </c>
       <c r="DH5" t="n">
-        <v>113.46</v>
+        <v>113.59</v>
       </c>
       <c r="DI5" t="n">
         <v>-0.04</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.92</v>
+        <v>5.78</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="DM5" t="n">
-        <v>67.45999999999999</v>
+        <v>67.93000000000001</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.54</v>
+        <v>2.44</v>
       </c>
       <c r="DP5" t="n">
-        <v>12.69</v>
+        <v>12.63</v>
       </c>
       <c r="DQ5" t="n">
-        <v>14.69</v>
+        <v>14.48</v>
       </c>
       <c r="DR5" t="n">
-        <v>6.19</v>
+        <v>6.04</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.19</v>
+        <v>0.22</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.19</v>
+        <v>0.22</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>58.85</v>
+        <v>58.67</v>
       </c>
       <c r="DW5" t="n">
         <v>0.11</v>
       </c>
       <c r="DX5" t="n">
-        <v>15.23</v>
+        <v>15.37</v>
       </c>
       <c r="DY5" t="n">
-        <v>9.92</v>
+        <v>9.85</v>
       </c>
       <c r="DZ5" t="n">
-        <v>5.31</v>
+        <v>5.52</v>
       </c>
       <c r="EA5" t="n">
-        <v>21.88</v>
+        <v>21.85</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="6">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D7" t="n">
         <v>13</v>
@@ -3406,82 +3406,82 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="G7" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="H7" t="n">
-        <v>101.46</v>
+        <v>99.64</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="K7" t="n">
-        <v>4.15</v>
+        <v>4.07</v>
       </c>
       <c r="L7" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="M7" t="n">
-        <v>57.54</v>
+        <v>56.14</v>
       </c>
       <c r="N7" t="n">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="O7" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="P7" t="n">
-        <v>14.38</v>
+        <v>14.07</v>
       </c>
       <c r="Q7" t="n">
-        <v>13.08</v>
+        <v>12.79</v>
       </c>
       <c r="R7" t="n">
-        <v>7.15</v>
+        <v>7.29</v>
       </c>
       <c r="S7" t="n">
-        <v>1.15</v>
+        <v>1.43</v>
       </c>
       <c r="T7" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="U7" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="V7" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>49.92</v>
+        <v>48.57</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Z7" t="n">
-        <v>11.38</v>
+        <v>10.71</v>
       </c>
       <c r="AA7" t="n">
-        <v>7.23</v>
+        <v>6.86</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.15</v>
+        <v>3.86</v>
       </c>
       <c r="AC7" t="n">
-        <v>23</v>
+        <v>22.36</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AF7" t="n">
         <v>0.31</v>
@@ -3565,70 +3565,70 @@
         <v>1.77</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.73</v>
+        <v>2.81</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.880000000000001</v>
+        <v>8.93</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.73</v>
+        <v>2.81</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.54</v>
+        <v>0.63</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.96</v>
+        <v>0.93</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.96</v>
+        <v>4.93</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>92.31</v>
+        <v>92.59</v>
       </c>
       <c r="BT7" t="n">
-        <v>46.15</v>
+        <v>48.15</v>
       </c>
       <c r="BU7" t="n">
-        <v>23.08</v>
+        <v>25.93</v>
       </c>
       <c r="BV7" t="n">
-        <v>7.69</v>
+        <v>11.11</v>
       </c>
       <c r="BW7" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="BX7" t="n">
-        <v>73.08</v>
+        <v>70.37</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.83</v>
+        <v>3.06</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.94</v>
+        <v>3.29</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.55</v>
+        <v>3.59</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.58</v>
+        <v>3.63</v>
       </c>
       <c r="CC7" t="n">
         <v>4.55</v>
@@ -3640,28 +3640,28 @@
         <v>1.38</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CN7" t="n">
         <v>1.74</v>
@@ -3670,22 +3670,22 @@
         <v>1.27</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.3</v>
+        <v>3.27</v>
       </c>
       <c r="CR7" t="n">
         <v>1.39</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.97</v>
+        <v>2.98</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CV7" t="n">
         <v>1.96</v>
@@ -3706,55 +3706,55 @@
         <v>1.74</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.52</v>
+        <v>3.49</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
       <c r="DH7" t="n">
-        <v>106.69</v>
+        <v>105.55</v>
       </c>
       <c r="DI7" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.65</v>
+        <v>4.59</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="DM7" t="n">
-        <v>58.96</v>
+        <v>58.18</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.77</v>
+        <v>0.85</v>
       </c>
       <c r="DO7" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="DP7" t="n">
-        <v>14.15</v>
+        <v>14</v>
       </c>
       <c r="DQ7" t="n">
-        <v>12.12</v>
+        <v>12</v>
       </c>
       <c r="DR7" t="n">
-        <v>7.15</v>
+        <v>7.22</v>
       </c>
       <c r="DS7" t="n">
         <v>0.26</v>
@@ -3766,25 +3766,25 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>51.3</v>
+        <v>50.55</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="DX7" t="n">
-        <v>11.08</v>
+        <v>10.74</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.43</v>
+        <v>7.23</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.65</v>
+        <v>3.52</v>
       </c>
       <c r="EA7" t="n">
-        <v>22.08</v>
+        <v>21.78</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="EC7" t="n">
         <v>1.96</v>
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" t="n">
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -3890,49 +3890,49 @@
         <v>0.08</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AI8" t="n">
-        <v>101.08</v>
+        <v>100.31</v>
       </c>
       <c r="AJ8" t="n">
         <v>-0.08</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="AL8" t="n">
-        <v>3.83</v>
+        <v>3.77</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AN8" t="n">
-        <v>54.33</v>
+        <v>53.69</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="AP8" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AQ8" t="n">
-        <v>15.67</v>
+        <v>15.23</v>
       </c>
       <c r="AR8" t="n">
         <v>12.92</v>
       </c>
       <c r="AS8" t="n">
-        <v>7.92</v>
+        <v>7.62</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AU8" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AV8" t="n">
         <v>0</v>
@@ -3944,82 +3944,82 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>48.17</v>
+        <v>48.69</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="BA8" t="n">
-        <v>11.67</v>
+        <v>11.62</v>
       </c>
       <c r="BB8" t="n">
-        <v>8</v>
+        <v>8.08</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.67</v>
+        <v>3.54</v>
       </c>
       <c r="BD8" t="n">
-        <v>22.75</v>
+        <v>22.92</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.880000000000001</v>
+        <v>9.85</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="BO8" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.81</v>
+        <v>4.78</v>
       </c>
       <c r="BQ8" t="n">
         <v>5.04</v>
       </c>
       <c r="BR8" t="n">
-        <v>80.77</v>
+        <v>77.78</v>
       </c>
       <c r="BS8" t="n">
-        <v>69.23</v>
+        <v>66.67</v>
       </c>
       <c r="BT8" t="n">
-        <v>38.46</v>
+        <v>37.04</v>
       </c>
       <c r="BU8" t="n">
-        <v>19.23</v>
+        <v>18.52</v>
       </c>
       <c r="BV8" t="n">
-        <v>7.69</v>
+        <v>7.41</v>
       </c>
       <c r="BW8" t="n">
-        <v>7.69</v>
+        <v>7.41</v>
       </c>
       <c r="BX8" t="n">
-        <v>42.31</v>
+        <v>40.74</v>
       </c>
       <c r="BY8" t="n">
         <v>2.76</v>
@@ -4028,25 +4028,25 @@
         <v>2.8</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.36</v>
+        <v>3.34</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.37</v>
+        <v>3.35</v>
       </c>
       <c r="CC8" t="n">
-        <v>3.44</v>
+        <v>3.42</v>
       </c>
       <c r="CD8" t="n">
-        <v>3.78</v>
+        <v>3.77</v>
       </c>
       <c r="CE8" t="n">
         <v>1.4</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.73</v>
+        <v>2.71</v>
       </c>
       <c r="CH8" t="n">
         <v>1.37</v>
@@ -4058,43 +4058,43 @@
         <v>1.81</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CL8" t="n">
         <v>2.15</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CO8" t="n">
         <v>1.3</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.34</v>
+        <v>3.38</v>
       </c>
       <c r="CR8" t="n">
         <v>1.42</v>
       </c>
       <c r="CS8" t="n">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="CU8" t="n">
         <v>1.38</v>
       </c>
       <c r="CV8" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CX8" t="n">
         <v>1.61</v>
@@ -4109,55 +4109,55 @@
         <v>1.75</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.67</v>
+        <v>3.7</v>
       </c>
       <c r="DE8" t="n">
         <v>0.04</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="DH8" t="n">
-        <v>108.27</v>
+        <v>107.63</v>
       </c>
       <c r="DI8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.8</v>
+        <v>4.74</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="DM8" t="n">
-        <v>66.69</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.85</v>
+        <v>0.89</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="DP8" t="n">
-        <v>15.08</v>
+        <v>14.89</v>
       </c>
       <c r="DQ8" t="n">
-        <v>13.27</v>
+        <v>13.26</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.23</v>
+        <v>7.11</v>
       </c>
       <c r="DS8" t="n">
         <v>0.04</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>48.92</v>
+        <v>49.15</v>
       </c>
       <c r="DW8" t="n">
         <v>0.15</v>
       </c>
       <c r="DX8" t="n">
-        <v>12.23</v>
+        <v>12.19</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.73</v>
+        <v>8.74</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="EA8" t="n">
-        <v>21.54</v>
+        <v>21.67</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="9">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
         <v>14</v>
       </c>
       <c r="D9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E9" t="n">
         <v>0.21</v>
@@ -4290,139 +4290,139 @@
         <v>2.29</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AG9" t="n">
         <v>1.92</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="AI9" t="n">
-        <v>109.75</v>
+        <v>113.46</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="AL9" t="n">
-        <v>5.42</v>
+        <v>5.38</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.67</v>
+        <v>0.77</v>
       </c>
       <c r="AN9" t="n">
-        <v>61.67</v>
+        <v>62.38</v>
       </c>
       <c r="AO9" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>12.77</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AU9" t="n">
         <v>1</v>
       </c>
-      <c r="AP9" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>12.75</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>13.25</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>6.92</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AV9" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>50.42</v>
+        <v>50.92</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="BA9" t="n">
-        <v>13.33</v>
+        <v>13.15</v>
       </c>
       <c r="BB9" t="n">
-        <v>10.17</v>
+        <v>10</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.17</v>
+        <v>3.15</v>
       </c>
       <c r="BD9" t="n">
-        <v>22.42</v>
+        <v>22.85</v>
       </c>
       <c r="BE9" t="n">
         <v>1.51</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.08</v>
+        <v>9.93</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.89</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="BO9" t="n">
         <v>1.19</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.38</v>
+        <v>4.3</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.69</v>
+        <v>5.63</v>
       </c>
       <c r="BR9" t="n">
-        <v>88.45999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BS9" t="n">
-        <v>69.23</v>
+        <v>70.37</v>
       </c>
       <c r="BT9" t="n">
-        <v>42.31</v>
+        <v>44.44</v>
       </c>
       <c r="BU9" t="n">
-        <v>30.77</v>
+        <v>33.33</v>
       </c>
       <c r="BV9" t="n">
-        <v>11.54</v>
+        <v>11.11</v>
       </c>
       <c r="BW9" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="BX9" t="n">
-        <v>50</v>
+        <v>48.15</v>
       </c>
       <c r="BY9" t="n">
         <v>2.03</v>
@@ -4431,28 +4431,28 @@
         <v>2.03</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.59</v>
+        <v>3.57</v>
       </c>
       <c r="CC9" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="CD9" t="n">
-        <v>3.1</v>
+        <v>3.06</v>
       </c>
       <c r="CE9" t="n">
         <v>1.4</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CI9" t="n">
         <v>1.79</v>
@@ -4473,22 +4473,22 @@
         <v>1.59</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.49</v>
+        <v>3.51</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CS9" t="n">
         <v>3.09</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="CU9" t="n">
         <v>1.37</v>
@@ -4497,7 +4497,7 @@
         <v>1.84</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CX9" t="n">
         <v>1.68</v>
@@ -4515,13 +4515,13 @@
         <v>1.35</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.75</v>
+        <v>3.77</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DF9" t="n">
         <v>1.77</v>
@@ -4530,37 +4530,37 @@
         <v>3.15</v>
       </c>
       <c r="DH9" t="n">
-        <v>115.61</v>
+        <v>117.18</v>
       </c>
       <c r="DI9" t="n">
         <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="DK9" t="n">
-        <v>5.96</v>
+        <v>5.92</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.73</v>
+        <v>0.78</v>
       </c>
       <c r="DM9" t="n">
-        <v>67.23</v>
+        <v>67.37</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.84</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.81</v>
+        <v>2.78</v>
       </c>
       <c r="DP9" t="n">
-        <v>12.35</v>
+        <v>12.37</v>
       </c>
       <c r="DQ9" t="n">
-        <v>13.38</v>
+        <v>13.26</v>
       </c>
       <c r="DR9" t="n">
-        <v>7.04</v>
+        <v>6.89</v>
       </c>
       <c r="DS9" t="n">
         <v>0.15</v>
@@ -4572,28 +4572,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>51.65</v>
+        <v>51.85</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX9" t="n">
-        <v>14.81</v>
+        <v>14.66</v>
       </c>
       <c r="DY9" t="n">
-        <v>10.89</v>
+        <v>10.78</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3.92</v>
+        <v>3.89</v>
       </c>
       <c r="EA9" t="n">
-        <v>23.08</v>
+        <v>23.26</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="10">
@@ -4603,61 +4603,61 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D10" t="n">
         <v>14</v>
       </c>
       <c r="E10" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="F10" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="G10" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>115.75</v>
+        <v>115.08</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="K10" t="n">
-        <v>4.08</v>
+        <v>4.23</v>
       </c>
       <c r="L10" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="M10" t="n">
-        <v>61.25</v>
+        <v>59.62</v>
       </c>
       <c r="N10" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="O10" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="P10" t="n">
-        <v>12.75</v>
+        <v>12.69</v>
       </c>
       <c r="Q10" t="n">
-        <v>12.92</v>
+        <v>12.77</v>
       </c>
       <c r="R10" t="n">
-        <v>8</v>
+        <v>7.92</v>
       </c>
       <c r="S10" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="T10" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="U10" t="n">
         <v>0.08</v>
@@ -4669,25 +4669,25 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>52.42</v>
+        <v>51.85</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="Z10" t="n">
-        <v>14.83</v>
+        <v>14.31</v>
       </c>
       <c r="AA10" t="n">
-        <v>9.92</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="AB10" t="n">
-        <v>4.92</v>
+        <v>4.69</v>
       </c>
       <c r="AC10" t="n">
-        <v>24.83</v>
+        <v>25.38</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AE10" t="n">
         <v>1.92</v>
@@ -4774,70 +4774,70 @@
         <v>2.29</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.04</v>
+        <v>2.93</v>
       </c>
       <c r="BH10" t="n">
-        <v>7.38</v>
+        <v>7.44</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.04</v>
+        <v>2.93</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="BL10" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.27</v>
+        <v>3.3</v>
       </c>
       <c r="BQ10" t="n">
-        <v>3.38</v>
+        <v>3.44</v>
       </c>
       <c r="BR10" t="n">
-        <v>92.31</v>
+        <v>88.89</v>
       </c>
       <c r="BS10" t="n">
-        <v>88.45999999999999</v>
+        <v>85.19</v>
       </c>
       <c r="BT10" t="n">
-        <v>61.54</v>
+        <v>59.26</v>
       </c>
       <c r="BU10" t="n">
-        <v>34.62</v>
+        <v>33.33</v>
       </c>
       <c r="BV10" t="n">
-        <v>15.38</v>
+        <v>14.81</v>
       </c>
       <c r="BW10" t="n">
-        <v>7.69</v>
+        <v>7.41</v>
       </c>
       <c r="BX10" t="n">
-        <v>69.23</v>
+        <v>66.67</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="BZ10" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.45</v>
+        <v>3.44</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.55</v>
+        <v>3.53</v>
       </c>
       <c r="CC10" t="n">
         <v>4.65</v>
@@ -4849,25 +4849,25 @@
         <v>1.38</v>
       </c>
       <c r="CF10" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="CG10" t="n">
         <v>2.84</v>
       </c>
-      <c r="CG10" t="n">
-        <v>2.86</v>
-      </c>
       <c r="CH10" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CI10" t="n">
         <v>1.88</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="CM10" t="n">
         <v>2.01</v>
@@ -4879,28 +4879,28 @@
         <v>1.29</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.34</v>
+        <v>3.37</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.97</v>
+        <v>2.99</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.93</v>
+        <v>2.91</v>
       </c>
       <c r="CU10" t="n">
         <v>1.4</v>
       </c>
       <c r="CV10" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CX10" t="n">
         <v>1.74</v>
@@ -4915,55 +4915,55 @@
         <v>1.61</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.51</v>
+        <v>3.55</v>
       </c>
       <c r="DE10" t="n">
         <v>0.15</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="DH10" t="n">
-        <v>110.77</v>
+        <v>110.63</v>
       </c>
       <c r="DI10" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="DK10" t="n">
-        <v>3.46</v>
+        <v>3.56</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DM10" t="n">
-        <v>54.62</v>
+        <v>54.08</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="DP10" t="n">
-        <v>13.65</v>
+        <v>13.59</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.81</v>
+        <v>12.74</v>
       </c>
       <c r="DR10" t="n">
-        <v>8.19</v>
+        <v>8.15</v>
       </c>
       <c r="DS10" t="n">
         <v>0.07000000000000001</v>
@@ -4975,28 +4975,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>48.81</v>
+        <v>48.67</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.04</v>
+        <v>11.89</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.119999999999999</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.92</v>
+        <v>3.85</v>
       </c>
       <c r="EA10" t="n">
-        <v>22.73</v>
+        <v>23.07</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="11">

--- a/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
@@ -1848,7 +1848,7 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>48.14</v>
+        <v>48.07</v>
       </c>
       <c r="Y3" t="n">
         <v>0.07000000000000001</v>
@@ -2154,7 +2154,7 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>46.41</v>
+        <v>46.37</v>
       </c>
       <c r="DW3" t="n">
         <v>0.11</v>
@@ -4347,7 +4347,7 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>50.92</v>
+        <v>51</v>
       </c>
       <c r="AZ9" t="n">
         <v>0.15</v>
@@ -4572,7 +4572,7 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>51.85</v>
+        <v>51.89</v>
       </c>
       <c r="DW9" t="n">
         <v>0.11</v>

--- a/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
@@ -1794,7 +1794,7 @@
         <v>0.14</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="G3" t="n">
         <v>2.14</v>
@@ -1806,7 +1806,7 @@
         <v>0.29</v>
       </c>
       <c r="J3" t="n">
-        <v>2.36</v>
+        <v>2.43</v>
       </c>
       <c r="K3" t="n">
         <v>3.71</v>
@@ -1869,7 +1869,7 @@
         <v>1.31</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.29</v>
+        <v>2.36</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -2106,7 +2106,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="DG3" t="n">
         <v>1.96</v>
@@ -2118,7 +2118,7 @@
         <v>0.15</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="DK3" t="n">
         <v>4.4</v>
@@ -2175,7 +2175,7 @@
         <v>1.38</v>
       </c>
       <c r="EC3" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="4">
@@ -2278,7 +2278,7 @@
         <v>0.14</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AH4" t="n">
         <v>2.07</v>
@@ -2290,7 +2290,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="AK4" t="n">
-        <v>3.14</v>
+        <v>3.07</v>
       </c>
       <c r="AL4" t="n">
         <v>3.29</v>
@@ -2332,7 +2332,7 @@
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>42.43</v>
+        <v>42.5</v>
       </c>
       <c r="AZ4" t="n">
         <v>0.29</v>
@@ -2353,7 +2353,7 @@
         <v>1.16</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.64</v>
+        <v>2.57</v>
       </c>
       <c r="BG4" t="n">
         <v>2.89</v>
@@ -2509,7 +2509,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="DG4" t="n">
         <v>2.07</v>
@@ -2521,7 +2521,7 @@
         <v>0.04</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="DK4" t="n">
         <v>3.48</v>
@@ -2557,7 +2557,7 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>43.45</v>
+        <v>43.48</v>
       </c>
       <c r="DW4" t="n">
         <v>0.19</v>
@@ -2578,7 +2578,7 @@
         <v>1.33</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="5">
@@ -3406,7 +3406,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="G7" t="n">
         <v>2.29</v>
@@ -3418,7 +3418,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>2.29</v>
+        <v>2.36</v>
       </c>
       <c r="K7" t="n">
         <v>4.07</v>
@@ -3481,7 +3481,7 @@
         <v>1.36</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.14</v>
+        <v>2.21</v>
       </c>
       <c r="AF7" t="n">
         <v>0.31</v>
@@ -3718,7 +3718,7 @@
         <v>0.15</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="DG7" t="n">
         <v>2.63</v>
@@ -3730,7 +3730,7 @@
         <v>0.04</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="DK7" t="n">
         <v>4.59</v>
@@ -3787,7 +3787,7 @@
         <v>1.35</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -5072,25 +5072,25 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>45.62</v>
+        <v>45.54</v>
       </c>
       <c r="Y11" t="n">
         <v>0.15</v>
       </c>
       <c r="Z11" t="n">
-        <v>13.54</v>
+        <v>13.62</v>
       </c>
       <c r="AA11" t="n">
         <v>9.539999999999999</v>
       </c>
       <c r="AB11" t="n">
-        <v>4</v>
+        <v>4.08</v>
       </c>
       <c r="AC11" t="n">
         <v>21.23</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AE11" t="n">
         <v>2.23</v>
@@ -5378,19 +5378,19 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>45.04</v>
+        <v>45</v>
       </c>
       <c r="DW11" t="n">
         <v>0.18</v>
       </c>
       <c r="DX11" t="n">
-        <v>12.07</v>
+        <v>12.11</v>
       </c>
       <c r="DY11" t="n">
         <v>8.369999999999999</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.7</v>
+        <v>3.74</v>
       </c>
       <c r="EA11" t="n">
         <v>20.26</v>

--- a/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D2" t="n">
         <v>14</v>
       </c>
       <c r="E2" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="F2" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="G2" t="n">
-        <v>2.69</v>
+        <v>2.64</v>
       </c>
       <c r="H2" t="n">
-        <v>121.38</v>
+        <v>119.93</v>
       </c>
       <c r="I2" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="K2" t="n">
-        <v>6.15</v>
+        <v>6.5</v>
       </c>
       <c r="L2" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="M2" t="n">
-        <v>72.31</v>
+        <v>72.43000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="O2" t="n">
-        <v>3.38</v>
+        <v>3.79</v>
       </c>
       <c r="P2" t="n">
-        <v>10.85</v>
+        <v>10.93</v>
       </c>
       <c r="Q2" t="n">
-        <v>11.92</v>
+        <v>11.5</v>
       </c>
       <c r="R2" t="n">
-        <v>5.46</v>
+        <v>5.29</v>
       </c>
       <c r="S2" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="T2" t="n">
-        <v>2.77</v>
+        <v>3.07</v>
       </c>
       <c r="U2" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="V2" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>58.62</v>
+        <v>59.14</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Z2" t="n">
-        <v>17.23</v>
+        <v>17.93</v>
       </c>
       <c r="AA2" t="n">
-        <v>10.15</v>
+        <v>10.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>7.08</v>
+        <v>7.43</v>
       </c>
       <c r="AC2" t="n">
-        <v>21.46</v>
+        <v>21.71</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.11</v>
+        <v>2.18</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AF2" t="n">
         <v>0.21</v>
@@ -1550,70 +1550,70 @@
         <v>1.86</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.33</v>
+        <v>3.46</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.630000000000001</v>
+        <v>9.68</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.33</v>
+        <v>3.46</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.7</v>
+        <v>0.79</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="BL2" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.89</v>
+        <v>1.96</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.67</v>
+        <v>4.82</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.93</v>
+        <v>4.82</v>
       </c>
       <c r="BR2" t="n">
-        <v>96.3</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="BS2" t="n">
-        <v>92.59</v>
+        <v>92.86</v>
       </c>
       <c r="BT2" t="n">
-        <v>70.37</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BU2" t="n">
-        <v>40.74</v>
+        <v>42.86</v>
       </c>
       <c r="BV2" t="n">
-        <v>18.52</v>
+        <v>21.43</v>
       </c>
       <c r="BW2" t="n">
-        <v>11.11</v>
+        <v>14.29</v>
       </c>
       <c r="BX2" t="n">
-        <v>51.85</v>
+        <v>50</v>
       </c>
       <c r="BY2" t="n">
         <v>1.28</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.64</v>
+        <v>4.67</v>
       </c>
       <c r="CB2" t="n">
-        <v>5</v>
+        <v>5.05</v>
       </c>
       <c r="CC2" t="n">
         <v>1.63</v>
@@ -1634,7 +1634,7 @@
         <v>1.49</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CJ2" t="n">
         <v>1.96</v>
@@ -1643,7 +1643,7 @@
         <v>1.58</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CM2" t="n">
         <v>2.21</v>
@@ -1658,7 +1658,7 @@
         <v>1.74</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="CR2" t="n">
         <v>1.37</v>
@@ -1691,88 +1691,88 @@
         <v>1.75</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="DC2" t="n">
         <v>1.74</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.22</v>
+        <v>3.18</v>
       </c>
       <c r="DH2" t="n">
-        <v>120.66</v>
+        <v>119.96</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="DJ2" t="n">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="DK2" t="n">
-        <v>6.37</v>
+        <v>6.54</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="DM2" t="n">
-        <v>73.52</v>
+        <v>73.54000000000001</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="DO2" t="n">
-        <v>3.11</v>
+        <v>3.32</v>
       </c>
       <c r="DP2" t="n">
-        <v>12.33</v>
+        <v>12.32</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.48</v>
+        <v>12.25</v>
       </c>
       <c r="DR2" t="n">
-        <v>5.78</v>
+        <v>5.68</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.18</v>
+        <v>0.21</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.18</v>
+        <v>0.21</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>57</v>
+        <v>57.32</v>
       </c>
       <c r="DW2" t="n">
         <v>0.11</v>
       </c>
       <c r="DX2" t="n">
-        <v>16.78</v>
+        <v>17.14</v>
       </c>
       <c r="DY2" t="n">
-        <v>10.52</v>
+        <v>10.68</v>
       </c>
       <c r="DZ2" t="n">
-        <v>6.26</v>
+        <v>6.46</v>
       </c>
       <c r="EA2" t="n">
-        <v>22.59</v>
+        <v>22.68</v>
       </c>
       <c r="EB2" t="n">
-        <v>2.03</v>
+        <v>2.07</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C3" t="n">
         <v>14</v>
       </c>
       <c r="D3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E3" t="n">
         <v>0.14</v>
@@ -1875,136 +1875,136 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.23</v>
+        <v>1.43</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AI3" t="n">
-        <v>94.69</v>
+        <v>92.93000000000001</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>2</v>
+        <v>2.21</v>
       </c>
       <c r="AL3" t="n">
-        <v>5.15</v>
+        <v>4.86</v>
       </c>
       <c r="AM3" t="n">
         <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="AQ3" t="n">
-        <v>11</v>
+        <v>11.07</v>
       </c>
       <c r="AR3" t="n">
-        <v>12.69</v>
+        <v>13.14</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.69</v>
+        <v>8.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>44.54</v>
+        <v>44.93</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="BA3" t="n">
-        <v>12.69</v>
+        <v>12.14</v>
       </c>
       <c r="BB3" t="n">
-        <v>8.85</v>
+        <v>8.43</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.85</v>
+        <v>3.71</v>
       </c>
       <c r="BD3" t="n">
-        <v>20.38</v>
+        <v>19.93</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.69</v>
+        <v>1.93</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="BH3" t="n">
-        <v>8.74</v>
+        <v>8.75</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.74</v>
+        <v>3.75</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.11</v>
+        <v>4.14</v>
       </c>
       <c r="BR3" t="n">
-        <v>92.59</v>
+        <v>92.86</v>
       </c>
       <c r="BS3" t="n">
-        <v>74.06999999999999</v>
+        <v>75</v>
       </c>
       <c r="BT3" t="n">
-        <v>51.85</v>
+        <v>50</v>
       </c>
       <c r="BU3" t="n">
-        <v>33.33</v>
+        <v>32.14</v>
       </c>
       <c r="BV3" t="n">
-        <v>7.41</v>
+        <v>7.14</v>
       </c>
       <c r="BW3" t="n">
-        <v>3.7</v>
+        <v>3.57</v>
       </c>
       <c r="BX3" t="n">
-        <v>55.56</v>
+        <v>57.14</v>
       </c>
       <c r="BY3" t="n">
         <v>2.93</v>
@@ -2013,22 +2013,22 @@
         <v>3.04</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.59</v>
+        <v>3.58</v>
       </c>
       <c r="CC3" t="n">
-        <v>5.35</v>
+        <v>5.18</v>
       </c>
       <c r="CD3" t="n">
-        <v>5.64</v>
+        <v>5.42</v>
       </c>
       <c r="CE3" t="n">
         <v>1.4</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="CG3" t="n">
         <v>2.76</v>
@@ -2040,19 +2040,19 @@
         <v>1.83</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CL3" t="n">
         <v>2.34</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CO3" t="n">
         <v>1.31</v>
@@ -2061,7 +2061,7 @@
         <v>2.04</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.51</v>
+        <v>3.5</v>
       </c>
       <c r="CR3" t="n">
         <v>1.43</v>
@@ -2088,10 +2088,10 @@
         <v>2.17</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="DB3" t="n">
         <v>1.34</v>
@@ -2100,49 +2100,49 @@
         <v>2.11</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.74</v>
+        <v>3.73</v>
       </c>
       <c r="DE3" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="DG3" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="DH3" t="n">
-        <v>95.66</v>
+        <v>94.75</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="DK3" t="n">
-        <v>4.4</v>
+        <v>4.28</v>
       </c>
       <c r="DL3" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DM3" t="n">
-        <v>51.44</v>
+        <v>50.54</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="DP3" t="n">
-        <v>11.33</v>
+        <v>11.36</v>
       </c>
       <c r="DQ3" t="n">
-        <v>13.33</v>
+        <v>13.54</v>
       </c>
       <c r="DR3" t="n">
-        <v>8.48</v>
+        <v>8.4</v>
       </c>
       <c r="DS3" t="n">
         <v>0.07000000000000001</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>46.37</v>
+        <v>46.5</v>
       </c>
       <c r="DW3" t="n">
         <v>0.11</v>
       </c>
       <c r="DX3" t="n">
-        <v>11.63</v>
+        <v>11.39</v>
       </c>
       <c r="DY3" t="n">
-        <v>7.74</v>
+        <v>7.57</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.89</v>
+        <v>3.82</v>
       </c>
       <c r="EA3" t="n">
-        <v>20.67</v>
+        <v>20.43</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="4">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C8" t="n">
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -3887,52 +3887,52 @@
         <v>2.21</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AI8" t="n">
-        <v>100.31</v>
+        <v>96.93000000000001</v>
       </c>
       <c r="AJ8" t="n">
-        <v>-0.08</v>
+        <v>-0.14</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.54</v>
+        <v>2.36</v>
       </c>
       <c r="AL8" t="n">
-        <v>3.77</v>
+        <v>3.5</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AN8" t="n">
-        <v>53.69</v>
+        <v>51.14</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AP8" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AQ8" t="n">
-        <v>15.23</v>
+        <v>14.64</v>
       </c>
       <c r="AR8" t="n">
-        <v>12.92</v>
+        <v>12.86</v>
       </c>
       <c r="AS8" t="n">
-        <v>7.62</v>
+        <v>7.57</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.54</v>
+        <v>1.93</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AV8" t="n">
         <v>0</v>
@@ -3944,82 +3944,82 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>48.69</v>
+        <v>47.64</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="BA8" t="n">
-        <v>11.62</v>
+        <v>11.21</v>
       </c>
       <c r="BB8" t="n">
-        <v>8.08</v>
+        <v>7.79</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.54</v>
+        <v>3.43</v>
       </c>
       <c r="BD8" t="n">
-        <v>22.92</v>
+        <v>22.14</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.15</v>
+        <v>2.32</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.85</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.15</v>
+        <v>2.32</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.37</v>
+        <v>0.46</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.74</v>
+        <v>0.86</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.96</v>
+        <v>1.04</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.78</v>
+        <v>4.93</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.04</v>
+        <v>4.93</v>
       </c>
       <c r="BR8" t="n">
-        <v>77.78</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BS8" t="n">
-        <v>66.67</v>
+        <v>67.86</v>
       </c>
       <c r="BT8" t="n">
-        <v>37.04</v>
+        <v>39.29</v>
       </c>
       <c r="BU8" t="n">
-        <v>18.52</v>
+        <v>21.43</v>
       </c>
       <c r="BV8" t="n">
-        <v>7.41</v>
+        <v>10.71</v>
       </c>
       <c r="BW8" t="n">
-        <v>7.41</v>
+        <v>10.71</v>
       </c>
       <c r="BX8" t="n">
-        <v>40.74</v>
+        <v>39.29</v>
       </c>
       <c r="BY8" t="n">
         <v>2.76</v>
@@ -4028,34 +4028,34 @@
         <v>2.8</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.35</v>
+        <v>3.46</v>
       </c>
       <c r="CC8" t="n">
-        <v>3.42</v>
+        <v>4.07</v>
       </c>
       <c r="CD8" t="n">
-        <v>3.77</v>
+        <v>4.42</v>
       </c>
       <c r="CE8" t="n">
         <v>1.4</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="CH8" t="n">
         <v>1.37</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CK8" t="n">
         <v>1.59</v>
@@ -4070,19 +4070,19 @@
         <v>1.74</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.38</v>
+        <v>3.34</v>
       </c>
       <c r="CR8" t="n">
         <v>1.42</v>
       </c>
       <c r="CS8" t="n">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="CT8" t="n">
         <v>2.85</v>
@@ -4106,58 +4106,58 @@
         <v>2.21</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.7</v>
+        <v>3.66</v>
       </c>
       <c r="DE8" t="n">
         <v>0.04</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.37</v>
+        <v>2.28</v>
       </c>
       <c r="DH8" t="n">
-        <v>107.63</v>
+        <v>105.68</v>
       </c>
       <c r="DI8" t="n">
-        <v>-0</v>
+        <v>-0.04</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.41</v>
+        <v>2.32</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.74</v>
+        <v>4.57</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="DM8" t="n">
-        <v>65.93000000000001</v>
+        <v>64.22</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="DP8" t="n">
-        <v>14.89</v>
+        <v>14.61</v>
       </c>
       <c r="DQ8" t="n">
-        <v>13.26</v>
+        <v>13.22</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.11</v>
+        <v>7.1</v>
       </c>
       <c r="DS8" t="n">
         <v>0.04</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>49.15</v>
+        <v>48.6</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX8" t="n">
-        <v>12.19</v>
+        <v>11.96</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.74</v>
+        <v>8.57</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="EA8" t="n">
-        <v>21.67</v>
+        <v>21.32</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.26</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="9">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C9" t="n">
         <v>14</v>
       </c>
       <c r="D9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E9" t="n">
         <v>0.21</v>
@@ -4290,139 +4290,139 @@
         <v>2.29</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="AI9" t="n">
-        <v>113.46</v>
+        <v>111.79</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="AL9" t="n">
-        <v>5.38</v>
+        <v>5.43</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="AN9" t="n">
-        <v>62.38</v>
+        <v>61.29</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.54</v>
+        <v>2.43</v>
       </c>
       <c r="AQ9" t="n">
-        <v>12.77</v>
+        <v>12.93</v>
       </c>
       <c r="AR9" t="n">
+        <v>12.86</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>50.57</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="BA9" t="n">
         <v>13</v>
       </c>
-      <c r="AS9" t="n">
-        <v>6.62</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>51</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>13.15</v>
-      </c>
       <c r="BB9" t="n">
-        <v>10</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.15</v>
+        <v>3.21</v>
       </c>
       <c r="BD9" t="n">
-        <v>22.85</v>
+        <v>22.5</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.69</v>
+        <v>2.57</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.93</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.52</v>
+        <v>0.57</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.3</v>
+        <v>4.29</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.63</v>
+        <v>5.68</v>
       </c>
       <c r="BR9" t="n">
-        <v>88.89</v>
+        <v>89.29000000000001</v>
       </c>
       <c r="BS9" t="n">
-        <v>70.37</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT9" t="n">
-        <v>44.44</v>
+        <v>42.86</v>
       </c>
       <c r="BU9" t="n">
-        <v>33.33</v>
+        <v>32.14</v>
       </c>
       <c r="BV9" t="n">
-        <v>11.11</v>
+        <v>10.71</v>
       </c>
       <c r="BW9" t="n">
-        <v>3.7</v>
+        <v>3.57</v>
       </c>
       <c r="BX9" t="n">
-        <v>48.15</v>
+        <v>46.43</v>
       </c>
       <c r="BY9" t="n">
         <v>2.03</v>
@@ -4431,16 +4431,16 @@
         <v>2.03</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.48</v>
+        <v>3.47</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.57</v>
+        <v>3.55</v>
       </c>
       <c r="CC9" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="CD9" t="n">
-        <v>3.06</v>
+        <v>3.02</v>
       </c>
       <c r="CE9" t="n">
         <v>1.4</v>
@@ -4458,13 +4458,13 @@
         <v>1.79</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CK9" t="n">
         <v>1.62</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="CM9" t="n">
         <v>1.99</v>
@@ -4476,16 +4476,16 @@
         <v>1.32</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.51</v>
+        <v>3.52</v>
       </c>
       <c r="CR9" t="n">
         <v>1.43</v>
       </c>
       <c r="CS9" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="CT9" t="n">
         <v>2.83</v>
@@ -4518,82 +4518,82 @@
         <v>2.13</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.77</v>
+        <v>3.78</v>
       </c>
       <c r="DE9" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="DF9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DG9" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>116.22</v>
+      </c>
+      <c r="DI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ9" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="DK9" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="DL9" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DM9" t="n">
+        <v>66.64</v>
+      </c>
+      <c r="DN9" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="DO9" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="DP9" t="n">
+        <v>12.46</v>
+      </c>
+      <c r="DQ9" t="n">
+        <v>13.18</v>
+      </c>
+      <c r="DR9" t="n">
+        <v>6.96</v>
+      </c>
+      <c r="DS9" t="n">
         <v>0.18</v>
       </c>
-      <c r="DF9" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="DG9" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="DH9" t="n">
-        <v>117.18</v>
-      </c>
-      <c r="DI9" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ9" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="DK9" t="n">
-        <v>5.92</v>
-      </c>
-      <c r="DL9" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="DM9" t="n">
-        <v>67.37</v>
-      </c>
-      <c r="DN9" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="DO9" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="DP9" t="n">
-        <v>12.37</v>
-      </c>
-      <c r="DQ9" t="n">
-        <v>13.26</v>
-      </c>
-      <c r="DR9" t="n">
-        <v>6.89</v>
-      </c>
-      <c r="DS9" t="n">
-        <v>0.15</v>
-      </c>
       <c r="DT9" t="n">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>51.89</v>
+        <v>51.64</v>
       </c>
       <c r="DW9" t="n">
         <v>0.11</v>
       </c>
       <c r="DX9" t="n">
-        <v>14.66</v>
+        <v>14.54</v>
       </c>
       <c r="DY9" t="n">
-        <v>10.78</v>
+        <v>10.64</v>
       </c>
       <c r="DZ9" t="n">
         <v>3.89</v>
       </c>
       <c r="EA9" t="n">
-        <v>23.26</v>
+        <v>23.07</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.48</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="10">
@@ -4603,94 +4603,94 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D10" t="n">
         <v>14</v>
       </c>
       <c r="E10" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="F10" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="G10" t="n">
         <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>115.08</v>
+        <v>114.29</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="K10" t="n">
-        <v>4.23</v>
+        <v>4.29</v>
       </c>
       <c r="L10" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="M10" t="n">
-        <v>59.62</v>
+        <v>60.29</v>
       </c>
       <c r="N10" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="O10" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="P10" t="n">
-        <v>12.69</v>
+        <v>12.64</v>
       </c>
       <c r="Q10" t="n">
-        <v>12.77</v>
+        <v>12.93</v>
       </c>
       <c r="R10" t="n">
-        <v>7.92</v>
+        <v>7.93</v>
       </c>
       <c r="S10" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="T10" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="U10" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="V10" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>51.85</v>
+        <v>52.07</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="Z10" t="n">
-        <v>14.31</v>
+        <v>14.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>9.619999999999999</v>
+        <v>10</v>
       </c>
       <c r="AB10" t="n">
-        <v>4.69</v>
+        <v>4.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>25.38</v>
+        <v>25.5</v>
       </c>
       <c r="AD10" t="n">
         <v>1.67</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AF10" t="n">
         <v>0.07000000000000001</v>
@@ -4774,70 +4774,70 @@
         <v>2.29</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.93</v>
+        <v>2.89</v>
       </c>
       <c r="BH10" t="n">
-        <v>7.44</v>
+        <v>7.57</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.93</v>
+        <v>2.89</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.74</v>
+        <v>0.79</v>
       </c>
       <c r="BL10" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="BQ10" t="n">
-        <v>3.44</v>
+        <v>3.57</v>
       </c>
       <c r="BR10" t="n">
-        <v>88.89</v>
+        <v>89.29000000000001</v>
       </c>
       <c r="BS10" t="n">
-        <v>85.19</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT10" t="n">
-        <v>59.26</v>
+        <v>57.14</v>
       </c>
       <c r="BU10" t="n">
-        <v>33.33</v>
+        <v>32.14</v>
       </c>
       <c r="BV10" t="n">
-        <v>14.81</v>
+        <v>14.29</v>
       </c>
       <c r="BW10" t="n">
-        <v>7.41</v>
+        <v>7.14</v>
       </c>
       <c r="BX10" t="n">
-        <v>66.67</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="BZ10" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.44</v>
+        <v>3.42</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.53</v>
+        <v>3.51</v>
       </c>
       <c r="CC10" t="n">
         <v>4.65</v>
@@ -4849,7 +4849,7 @@
         <v>1.38</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="CG10" t="n">
         <v>2.84</v>
@@ -4858,16 +4858,16 @@
         <v>1.38</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CK10" t="n">
         <v>1.72</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="CM10" t="n">
         <v>2.01</v>
@@ -4879,19 +4879,19 @@
         <v>1.29</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.37</v>
+        <v>3.39</v>
       </c>
       <c r="CR10" t="n">
         <v>1.41</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="CU10" t="n">
         <v>1.4</v>
@@ -4921,49 +4921,49 @@
         <v>2.05</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.55</v>
+        <v>3.56</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="DH10" t="n">
-        <v>110.63</v>
+        <v>110.4</v>
       </c>
       <c r="DI10" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="DK10" t="n">
-        <v>3.56</v>
+        <v>3.61</v>
       </c>
       <c r="DL10" t="n">
         <v>0.22</v>
       </c>
       <c r="DM10" t="n">
-        <v>54.08</v>
+        <v>54.61</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="DP10" t="n">
-        <v>13.59</v>
+        <v>13.54</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.74</v>
+        <v>12.82</v>
       </c>
       <c r="DR10" t="n">
-        <v>8.15</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="DS10" t="n">
         <v>0.07000000000000001</v>
@@ -4975,28 +4975,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>48.67</v>
+        <v>48.89</v>
       </c>
       <c r="DW10" t="n">
         <v>0.18</v>
       </c>
       <c r="DX10" t="n">
-        <v>11.89</v>
+        <v>12.07</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.039999999999999</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.85</v>
+        <v>3.78</v>
       </c>
       <c r="EA10" t="n">
-        <v>23.07</v>
+        <v>23.22</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.11</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="11">
@@ -5006,94 +5006,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D11" t="n">
         <v>14</v>
       </c>
       <c r="E11" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="F11" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="G11" t="n">
-        <v>1.77</v>
+        <v>1.93</v>
       </c>
       <c r="H11" t="n">
-        <v>108.38</v>
+        <v>106.21</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="K11" t="n">
-        <v>3.85</v>
+        <v>4.14</v>
       </c>
       <c r="L11" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="M11" t="n">
-        <v>54.92</v>
+        <v>54.79</v>
       </c>
       <c r="N11" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="O11" t="n">
-        <v>2.08</v>
+        <v>2.21</v>
       </c>
       <c r="P11" t="n">
-        <v>11.77</v>
+        <v>12.29</v>
       </c>
       <c r="Q11" t="n">
-        <v>13.15</v>
+        <v>13.07</v>
       </c>
       <c r="R11" t="n">
-        <v>7.69</v>
+        <v>7.57</v>
       </c>
       <c r="S11" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T11" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="U11" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="V11" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>45.54</v>
+        <v>45.86</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="Z11" t="n">
-        <v>13.62</v>
+        <v>13.79</v>
       </c>
       <c r="AA11" t="n">
-        <v>9.539999999999999</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.08</v>
+        <v>4.14</v>
       </c>
       <c r="AC11" t="n">
-        <v>21.23</v>
+        <v>21.71</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AF11" t="n">
         <v>0.07000000000000001</v>
@@ -5177,64 +5177,64 @@
         <v>2.07</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.74</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.79</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.3</v>
+        <v>4.29</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.78</v>
+        <v>4.79</v>
       </c>
       <c r="BR11" t="n">
-        <v>92.59</v>
+        <v>92.86</v>
       </c>
       <c r="BS11" t="n">
-        <v>81.48</v>
+        <v>82.14</v>
       </c>
       <c r="BT11" t="n">
-        <v>51.85</v>
+        <v>50</v>
       </c>
       <c r="BU11" t="n">
-        <v>33.33</v>
+        <v>32.14</v>
       </c>
       <c r="BV11" t="n">
-        <v>3.7</v>
+        <v>3.57</v>
       </c>
       <c r="BW11" t="n">
-        <v>3.7</v>
+        <v>3.57</v>
       </c>
       <c r="BX11" t="n">
-        <v>62.96</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BY11" t="n">
-        <v>3.05</v>
+        <v>3.01</v>
       </c>
       <c r="BZ11" t="n">
-        <v>3.28</v>
+        <v>3.24</v>
       </c>
       <c r="CA11" t="n">
         <v>3.34</v>
@@ -5249,22 +5249,22 @@
         <v>4.15</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CF11" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="CG11" t="n">
         <v>2.64</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CI11" t="n">
         <v>1.82</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CK11" t="n">
         <v>1.72</v>
@@ -5273,28 +5273,28 @@
         <v>2.34</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CN11" t="n">
         <v>1.6</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CP11" t="n">
         <v>2.08</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.59</v>
+        <v>3.58</v>
       </c>
       <c r="CR11" t="n">
         <v>1.44</v>
       </c>
       <c r="CS11" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="CT11" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="CU11" t="n">
         <v>1.36</v>
@@ -5306,16 +5306,16 @@
         <v>1.92</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="DB11" t="n">
         <v>1.36</v>
@@ -5324,49 +5324,49 @@
         <v>2.15</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.82</v>
+        <v>3.81</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="DG11" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="DH11" t="n">
-        <v>101.22</v>
+        <v>100.39</v>
       </c>
       <c r="DI11" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="DK11" t="n">
-        <v>3.78</v>
+        <v>3.92</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="DM11" t="n">
-        <v>51.26</v>
+        <v>51.32</v>
       </c>
       <c r="DN11" t="n">
         <v>1.04</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="DP11" t="n">
-        <v>12.3</v>
+        <v>12.54</v>
       </c>
       <c r="DQ11" t="n">
-        <v>12.81</v>
+        <v>12.78</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.92</v>
+        <v>7.86</v>
       </c>
       <c r="DS11" t="n">
         <v>0.18</v>
@@ -5378,28 +5378,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>45</v>
+        <v>45.18</v>
       </c>
       <c r="DW11" t="n">
         <v>0.18</v>
       </c>
       <c r="DX11" t="n">
-        <v>12.11</v>
+        <v>12.25</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.369999999999999</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.74</v>
+        <v>3.78</v>
       </c>
       <c r="EA11" t="n">
-        <v>20.26</v>
+        <v>20.54</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
@@ -1451,10 +1451,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="Z2" t="n">
-        <v>17.93</v>
+        <v>18</v>
       </c>
       <c r="AA2" t="n">
-        <v>10.5</v>
+        <v>10.57</v>
       </c>
       <c r="AB2" t="n">
         <v>7.43</v>
@@ -1757,10 +1757,10 @@
         <v>0.11</v>
       </c>
       <c r="DX2" t="n">
-        <v>17.14</v>
+        <v>17.18</v>
       </c>
       <c r="DY2" t="n">
-        <v>10.68</v>
+        <v>10.72</v>
       </c>
       <c r="DZ2" t="n">
         <v>6.46</v>
@@ -1929,7 +1929,7 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>44.93</v>
+        <v>44.86</v>
       </c>
       <c r="AZ3" t="n">
         <v>0.14</v>
@@ -2154,7 +2154,7 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>46.5</v>
+        <v>46.46</v>
       </c>
       <c r="DW3" t="n">
         <v>0.11</v>
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" t="n">
         <v>14</v>
@@ -2197,82 +2197,82 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="G4" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="H4" t="n">
-        <v>120.23</v>
+        <v>119.71</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="K4" t="n">
-        <v>3.69</v>
+        <v>3.71</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>71.69</v>
+        <v>70.79000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="O4" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="P4" t="n">
-        <v>12.85</v>
+        <v>13.21</v>
       </c>
       <c r="Q4" t="n">
-        <v>11.77</v>
+        <v>12.21</v>
       </c>
       <c r="R4" t="n">
-        <v>7.31</v>
+        <v>7.5</v>
       </c>
       <c r="S4" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="T4" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="U4" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="V4" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>44.54</v>
+        <v>44.36</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Z4" t="n">
-        <v>11.08</v>
+        <v>10.64</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.85</v>
+        <v>6.43</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.23</v>
+        <v>4.21</v>
       </c>
       <c r="AC4" t="n">
-        <v>21.08</v>
+        <v>21.43</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AF4" t="n">
         <v>0.14</v>
@@ -2356,70 +2356,70 @@
         <v>2.57</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.89</v>
+        <v>2.86</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.52</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.89</v>
+        <v>2.86</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BL4" t="n">
         <v>1.07</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.7</v>
+        <v>4.71</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.74</v>
+        <v>4.68</v>
       </c>
       <c r="BR4" t="n">
-        <v>96.3</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="BS4" t="n">
-        <v>81.48</v>
+        <v>82.14</v>
       </c>
       <c r="BT4" t="n">
-        <v>55.56</v>
+        <v>53.57</v>
       </c>
       <c r="BU4" t="n">
-        <v>37.04</v>
+        <v>35.71</v>
       </c>
       <c r="BV4" t="n">
-        <v>14.81</v>
+        <v>14.29</v>
       </c>
       <c r="BW4" t="n">
-        <v>3.7</v>
+        <v>3.57</v>
       </c>
       <c r="BX4" t="n">
-        <v>59.26</v>
+        <v>60.71</v>
       </c>
       <c r="BY4" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BZ4" t="n">
-        <v>4.64</v>
+        <v>4.53</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.06</v>
+        <v>4.04</v>
       </c>
       <c r="CB4" t="n">
-        <v>4.13</v>
+        <v>4.1</v>
       </c>
       <c r="CC4" t="n">
         <v>6.14</v>
@@ -2434,25 +2434,25 @@
         <v>2.69</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.97</v>
+        <v>2.98</v>
       </c>
       <c r="CH4" t="n">
         <v>1.43</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CK4" t="n">
         <v>1.61</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CM4" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CN4" t="n">
         <v>1.59</v>
@@ -2470,7 +2470,7 @@
         <v>1.38</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="CT4" t="n">
         <v>3.04</v>
@@ -2509,76 +2509,76 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="DG4" t="n">
         <v>2.07</v>
       </c>
       <c r="DH4" t="n">
-        <v>114.08</v>
+        <v>114.03</v>
       </c>
       <c r="DI4" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.48</v>
+        <v>2.43</v>
       </c>
       <c r="DK4" t="n">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DM4" t="n">
-        <v>63.74</v>
+        <v>63.58</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.74</v>
+        <v>0.72</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="DP4" t="n">
-        <v>12.86</v>
+        <v>13.04</v>
       </c>
       <c r="DQ4" t="n">
-        <v>11.37</v>
+        <v>11.6</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.34</v>
+        <v>8.4</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>43.48</v>
+        <v>43.43</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DX4" t="n">
-        <v>9.970000000000001</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.63</v>
+        <v>6.43</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.33</v>
+        <v>3.36</v>
       </c>
       <c r="EA4" t="n">
-        <v>21.74</v>
+        <v>21.9</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C5" t="n">
         <v>14</v>
       </c>
       <c r="D5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E5" t="n">
         <v>0.21</v>
@@ -2678,139 +2678,139 @@
         <v>1.57</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AH5" t="n">
-        <v>3.23</v>
+        <v>3.14</v>
       </c>
       <c r="AI5" t="n">
-        <v>109.38</v>
+        <v>110.07</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="AL5" t="n">
-        <v>6.46</v>
+        <v>6.57</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AN5" t="n">
-        <v>68.31</v>
+        <v>68.06999999999999</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.23</v>
+        <v>3.43</v>
       </c>
       <c r="AQ5" t="n">
-        <v>13.15</v>
+        <v>13.07</v>
       </c>
       <c r="AR5" t="n">
-        <v>14</v>
+        <v>14.29</v>
       </c>
       <c r="AS5" t="n">
-        <v>6.54</v>
+        <v>6.57</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>58.46</v>
+        <v>59.14</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>15.08</v>
+        <v>15.36</v>
       </c>
       <c r="BB5" t="n">
-        <v>10.08</v>
+        <v>10.14</v>
       </c>
       <c r="BC5" t="n">
-        <v>5</v>
+        <v>5.21</v>
       </c>
       <c r="BD5" t="n">
-        <v>20.92</v>
+        <v>20.64</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.59</v>
+        <v>2.64</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.59</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.59</v>
+        <v>2.64</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.15</v>
+        <v>4.21</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.33</v>
+        <v>5.29</v>
       </c>
       <c r="BR5" t="n">
-        <v>96.3</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="BS5" t="n">
-        <v>85.19</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT5" t="n">
-        <v>44.44</v>
+        <v>46.43</v>
       </c>
       <c r="BU5" t="n">
-        <v>22.22</v>
+        <v>25</v>
       </c>
       <c r="BV5" t="n">
-        <v>7.41</v>
+        <v>7.14</v>
       </c>
       <c r="BW5" t="n">
-        <v>3.7</v>
+        <v>3.57</v>
       </c>
       <c r="BX5" t="n">
-        <v>40.74</v>
+        <v>42.86</v>
       </c>
       <c r="BY5" t="n">
         <v>1.78</v>
@@ -2822,31 +2822,31 @@
         <v>3.61</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.59</v>
+        <v>3.6</v>
       </c>
       <c r="CC5" t="n">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="CD5" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="CE5" t="n">
         <v>1.41</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="CH5" t="n">
         <v>1.36</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CK5" t="n">
         <v>1.68</v>
@@ -2858,7 +2858,7 @@
         <v>2.07</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CO5" t="n">
         <v>1.31</v>
@@ -2867,19 +2867,19 @@
         <v>2.05</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.6</v>
+        <v>3.57</v>
       </c>
       <c r="CR5" t="n">
         <v>1.43</v>
       </c>
       <c r="CS5" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CV5" t="n">
         <v>1.83</v>
@@ -2903,10 +2903,10 @@
         <v>1.35</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.78</v>
+        <v>3.75</v>
       </c>
       <c r="DE5" t="n">
         <v>0.18</v>
@@ -2915,10 +2915,10 @@
         <v>1.33</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.33</v>
+        <v>3.28</v>
       </c>
       <c r="DH5" t="n">
-        <v>113.59</v>
+        <v>113.78</v>
       </c>
       <c r="DI5" t="n">
         <v>-0.04</v>
@@ -2927,58 +2927,58 @@
         <v>2.08</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.78</v>
+        <v>5.86</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="DM5" t="n">
-        <v>67.93000000000001</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.7</v>
+        <v>0.72</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.44</v>
+        <v>2.57</v>
       </c>
       <c r="DP5" t="n">
-        <v>12.63</v>
+        <v>12.61</v>
       </c>
       <c r="DQ5" t="n">
-        <v>14.48</v>
+        <v>14.61</v>
       </c>
       <c r="DR5" t="n">
-        <v>6.04</v>
+        <v>6.07</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>58.67</v>
+        <v>59</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX5" t="n">
-        <v>15.37</v>
+        <v>15.5</v>
       </c>
       <c r="DY5" t="n">
-        <v>9.85</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="DZ5" t="n">
-        <v>5.52</v>
+        <v>5.6</v>
       </c>
       <c r="EA5" t="n">
-        <v>21.85</v>
+        <v>21.68</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="EC5" t="n">
         <v>1.93</v>
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D6" t="n">
         <v>14</v>
       </c>
       <c r="E6" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="F6" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="G6" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="H6" t="n">
-        <v>108.08</v>
+        <v>107.71</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.08</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="K6" t="n">
-        <v>4.38</v>
+        <v>4.21</v>
       </c>
       <c r="L6" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="M6" t="n">
-        <v>59.08</v>
+        <v>57.71</v>
       </c>
       <c r="N6" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="O6" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="P6" t="n">
-        <v>11.23</v>
+        <v>11.71</v>
       </c>
       <c r="Q6" t="n">
-        <v>12.38</v>
+        <v>12.36</v>
       </c>
       <c r="R6" t="n">
-        <v>10.38</v>
+        <v>10.29</v>
       </c>
       <c r="S6" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="T6" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -3057,28 +3057,28 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>51.85</v>
+        <v>50.43</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>11.23</v>
+        <v>10.93</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.62</v>
+        <v>7.43</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.62</v>
+        <v>3.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>22.62</v>
+        <v>22.36</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AF6" t="n">
         <v>0.21</v>
@@ -3162,70 +3162,70 @@
         <v>2.21</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.59</v>
+        <v>2.64</v>
       </c>
       <c r="BH6" t="n">
         <v>9.960000000000001</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.59</v>
+        <v>2.64</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.52</v>
+        <v>0.57</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.37</v>
+        <v>4.43</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.78</v>
+        <v>4.75</v>
       </c>
       <c r="BR6" t="n">
-        <v>96.3</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="BS6" t="n">
-        <v>77.78</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BT6" t="n">
-        <v>55.56</v>
+        <v>57.14</v>
       </c>
       <c r="BU6" t="n">
-        <v>18.52</v>
+        <v>21.43</v>
       </c>
       <c r="BV6" t="n">
-        <v>7.41</v>
+        <v>7.14</v>
       </c>
       <c r="BW6" t="n">
-        <v>3.7</v>
+        <v>3.57</v>
       </c>
       <c r="BX6" t="n">
-        <v>59.26</v>
+        <v>60.71</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.54</v>
+        <v>2.66</v>
       </c>
       <c r="BZ6" t="n">
-        <v>2.73</v>
+        <v>2.9</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.38</v>
+        <v>3.39</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="CC6" t="n">
         <v>4.25</v>
@@ -3234,22 +3234,22 @@
         <v>4.82</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="CH6" t="n">
         <v>1.37</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CK6" t="n">
         <v>1.73</v>
@@ -3267,19 +3267,19 @@
         <v>1.32</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.48</v>
+        <v>3.46</v>
       </c>
       <c r="CR6" t="n">
         <v>1.42</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.03</v>
+        <v>3.01</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="CU6" t="n">
         <v>1.39</v>
@@ -3291,13 +3291,13 @@
         <v>1.9</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CZ6" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="DA6" t="n">
         <v>1.6</v>
@@ -3306,52 +3306,52 @@
         <v>1.34</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.68</v>
+        <v>3.66</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="DH6" t="n">
-        <v>105.08</v>
+        <v>105</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="DJ6" t="n">
         <v>1.96</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.03</v>
+        <v>3.96</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="DM6" t="n">
-        <v>56.52</v>
+        <v>55.92</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="DP6" t="n">
-        <v>11</v>
+        <v>11.25</v>
       </c>
       <c r="DQ6" t="n">
-        <v>11.63</v>
+        <v>11.64</v>
       </c>
       <c r="DR6" t="n">
-        <v>10.81</v>
+        <v>10.75</v>
       </c>
       <c r="DS6" t="n">
         <v>0.04</v>
@@ -3363,25 +3363,25 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>49.23</v>
+        <v>48.61</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>9.960000000000001</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="DY6" t="n">
-        <v>6.59</v>
+        <v>6.53</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.37</v>
+        <v>3.32</v>
       </c>
       <c r="EA6" t="n">
-        <v>22.37</v>
+        <v>22.25</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="EC6" t="n">
         <v>1.96</v>
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C7" t="n">
         <v>14</v>
       </c>
       <c r="D7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3484,139 +3484,139 @@
         <v>2.21</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AH7" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>114.93</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>62.64</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>14.21</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>11.64</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>53.07</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>10.43</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="BC7" t="n">
         <v>3</v>
       </c>
-      <c r="AI7" t="n">
-        <v>111.92</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>60.38</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>13.92</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>11.15</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>7.15</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>52.69</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>10.77</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>7.62</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>3.15</v>
-      </c>
       <c r="BD7" t="n">
-        <v>21.15</v>
+        <v>21</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.93</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="BL7" t="n">
         <v>0.93</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="BP7" t="n">
-        <v>4</v>
+        <v>4.04</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.93</v>
+        <v>4.86</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>92.59</v>
+        <v>92.86</v>
       </c>
       <c r="BT7" t="n">
-        <v>48.15</v>
+        <v>46.43</v>
       </c>
       <c r="BU7" t="n">
-        <v>25.93</v>
+        <v>25</v>
       </c>
       <c r="BV7" t="n">
-        <v>11.11</v>
+        <v>10.71</v>
       </c>
       <c r="BW7" t="n">
-        <v>3.7</v>
+        <v>3.57</v>
       </c>
       <c r="BX7" t="n">
-        <v>70.37</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BY7" t="n">
         <v>3.06</v>
@@ -3628,28 +3628,28 @@
         <v>3.59</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.63</v>
+        <v>3.61</v>
       </c>
       <c r="CC7" t="n">
-        <v>4.55</v>
+        <v>4.39</v>
       </c>
       <c r="CD7" t="n">
-        <v>4.84</v>
+        <v>4.67</v>
       </c>
       <c r="CE7" t="n">
         <v>1.38</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="CH7" t="n">
         <v>1.4</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CJ7" t="n">
         <v>1.8</v>
@@ -3658,7 +3658,7 @@
         <v>1.58</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CM7" t="n">
         <v>2.21</v>
@@ -3670,10 +3670,10 @@
         <v>1.27</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
       <c r="CR7" t="n">
         <v>1.39</v>
@@ -3682,7 +3682,7 @@
         <v>2.93</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="CU7" t="n">
         <v>1.41</v>
@@ -3712,82 +3712,82 @@
         <v>2.01</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.49</v>
+        <v>3.47</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.63</v>
+        <v>2.58</v>
       </c>
       <c r="DH7" t="n">
-        <v>105.55</v>
+        <v>107.28</v>
       </c>
       <c r="DI7" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.59</v>
+        <v>4.57</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.3</v>
+        <v>0.32</v>
       </c>
       <c r="DM7" t="n">
-        <v>58.18</v>
+        <v>59.39</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="DP7" t="n">
-        <v>14</v>
+        <v>14.14</v>
       </c>
       <c r="DQ7" t="n">
-        <v>12</v>
+        <v>12.22</v>
       </c>
       <c r="DR7" t="n">
-        <v>7.22</v>
+        <v>7.21</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>50.55</v>
+        <v>50.82</v>
       </c>
       <c r="DW7" t="n">
         <v>0.11</v>
       </c>
       <c r="DX7" t="n">
-        <v>10.74</v>
+        <v>10.57</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.23</v>
+        <v>7.14</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.52</v>
+        <v>3.43</v>
       </c>
       <c r="EA7" t="n">
-        <v>21.78</v>
+        <v>21.68</v>
       </c>
       <c r="EB7" t="n">
         <v>1.35</v>
       </c>
       <c r="EC7" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="8">
@@ -4347,7 +4347,7 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>50.57</v>
+        <v>50.5</v>
       </c>
       <c r="AZ9" t="n">
         <v>0.14</v>
@@ -4572,7 +4572,7 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>51.64</v>
+        <v>51.6</v>
       </c>
       <c r="DW9" t="n">
         <v>0.11</v>
@@ -4669,7 +4669,7 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>52.07</v>
+        <v>52.14</v>
       </c>
       <c r="Y10" t="n">
         <v>0.21</v>
@@ -4975,7 +4975,7 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>48.89</v>
+        <v>48.92</v>
       </c>
       <c r="DW10" t="n">
         <v>0.18</v>
@@ -5072,7 +5072,7 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>45.86</v>
+        <v>45.93</v>
       </c>
       <c r="Y11" t="n">
         <v>0.14</v>
@@ -5378,7 +5378,7 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>45.18</v>
+        <v>45.22</v>
       </c>
       <c r="DW11" t="n">
         <v>0.18</v>

--- a/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C6" t="n">
         <v>14</v>
       </c>
       <c r="D6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E6" t="n">
         <v>0.21</v>
@@ -3081,52 +3081,52 @@
         <v>1.71</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AI6" t="n">
-        <v>102.29</v>
+        <v>102.47</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="AL6" t="n">
-        <v>3.71</v>
+        <v>3.73</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AN6" t="n">
-        <v>54.14</v>
+        <v>55.13</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AQ6" t="n">
-        <v>10.79</v>
+        <v>10.93</v>
       </c>
       <c r="AR6" t="n">
-        <v>10.93</v>
+        <v>11.07</v>
       </c>
       <c r="AS6" t="n">
-        <v>11.21</v>
+        <v>10.87</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AV6" t="n">
         <v>0.07000000000000001</v>
@@ -3138,82 +3138,82 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>46.79</v>
+        <v>47.4</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>8.789999999999999</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.64</v>
+        <v>6</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="BD6" t="n">
-        <v>22.14</v>
+        <v>22.33</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.960000000000001</v>
+        <v>9.93</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.43</v>
+        <v>4.38</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.75</v>
+        <v>4.79</v>
       </c>
       <c r="BR6" t="n">
-        <v>96.43000000000001</v>
+        <v>96.55</v>
       </c>
       <c r="BS6" t="n">
-        <v>78.56999999999999</v>
+        <v>79.31</v>
       </c>
       <c r="BT6" t="n">
-        <v>57.14</v>
+        <v>55.17</v>
       </c>
       <c r="BU6" t="n">
-        <v>21.43</v>
+        <v>20.69</v>
       </c>
       <c r="BV6" t="n">
-        <v>7.14</v>
+        <v>6.9</v>
       </c>
       <c r="BW6" t="n">
-        <v>3.57</v>
+        <v>3.45</v>
       </c>
       <c r="BX6" t="n">
-        <v>60.71</v>
+        <v>58.62</v>
       </c>
       <c r="BY6" t="n">
         <v>2.66</v>
@@ -3225,22 +3225,22 @@
         <v>3.39</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.5</v>
+        <v>3.51</v>
       </c>
       <c r="CC6" t="n">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="CD6" t="n">
-        <v>4.82</v>
+        <v>4.83</v>
       </c>
       <c r="CE6" t="n">
         <v>1.4</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="CH6" t="n">
         <v>1.37</v>
@@ -3252,34 +3252,34 @@
         <v>1.85</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="CP6" t="n">
         <v>2.02</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.46</v>
+        <v>3.45</v>
       </c>
       <c r="CR6" t="n">
         <v>1.42</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="CU6" t="n">
         <v>1.39</v>
@@ -3303,55 +3303,55 @@
         <v>1.6</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.66</v>
+        <v>3.64</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="DH6" t="n">
         <v>105</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DJ6" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="DK6" t="n">
         <v>3.96</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="DM6" t="n">
-        <v>55.92</v>
+        <v>56.38</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="DO6" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="DP6" t="n">
-        <v>11.25</v>
+        <v>11.31</v>
       </c>
       <c r="DQ6" t="n">
-        <v>11.64</v>
+        <v>11.69</v>
       </c>
       <c r="DR6" t="n">
-        <v>10.75</v>
+        <v>10.59</v>
       </c>
       <c r="DS6" t="n">
         <v>0.04</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>48.61</v>
+        <v>48.86</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>9.859999999999999</v>
+        <v>10</v>
       </c>
       <c r="DY6" t="n">
-        <v>6.53</v>
+        <v>6.69</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.32</v>
+        <v>3.31</v>
       </c>
       <c r="EA6" t="n">
-        <v>22.25</v>
+        <v>22.34</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="7">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D7" t="n">
         <v>14</v>
@@ -3406,82 +3406,82 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="G7" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="H7" t="n">
-        <v>99.64</v>
+        <v>99.53</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>2.36</v>
+        <v>2.47</v>
       </c>
       <c r="K7" t="n">
-        <v>4.07</v>
+        <v>4.13</v>
       </c>
       <c r="L7" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="M7" t="n">
-        <v>56.14</v>
+        <v>57.27</v>
       </c>
       <c r="N7" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="O7" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="P7" t="n">
-        <v>14.07</v>
+        <v>13.93</v>
       </c>
       <c r="Q7" t="n">
-        <v>12.79</v>
+        <v>12.8</v>
       </c>
       <c r="R7" t="n">
-        <v>7.29</v>
+        <v>7.27</v>
       </c>
       <c r="S7" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="T7" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="U7" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="V7" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>48.57</v>
+        <v>48.27</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="Z7" t="n">
-        <v>10.71</v>
+        <v>10.67</v>
       </c>
       <c r="AA7" t="n">
-        <v>6.86</v>
+        <v>6.87</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.86</v>
+        <v>3.8</v>
       </c>
       <c r="AC7" t="n">
-        <v>22.36</v>
+        <v>22</v>
       </c>
       <c r="AD7" t="n">
         <v>1.36</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AF7" t="n">
         <v>0.29</v>
@@ -3565,70 +3565,70 @@
         <v>1.86</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.79</v>
+        <v>2.76</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.890000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.79</v>
+        <v>2.76</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.68</v>
+        <v>0.72</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.61</v>
+        <v>0.59</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.04</v>
+        <v>4</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.86</v>
+        <v>4.9</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>92.86</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="BT7" t="n">
-        <v>46.43</v>
+        <v>44.83</v>
       </c>
       <c r="BU7" t="n">
-        <v>25</v>
+        <v>24.14</v>
       </c>
       <c r="BV7" t="n">
-        <v>10.71</v>
+        <v>10.34</v>
       </c>
       <c r="BW7" t="n">
-        <v>3.57</v>
+        <v>3.45</v>
       </c>
       <c r="BX7" t="n">
-        <v>71.43000000000001</v>
+        <v>68.97</v>
       </c>
       <c r="BY7" t="n">
-        <v>3.06</v>
+        <v>2.99</v>
       </c>
       <c r="BZ7" t="n">
-        <v>3.29</v>
+        <v>3.19</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.59</v>
+        <v>3.58</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.61</v>
+        <v>3.62</v>
       </c>
       <c r="CC7" t="n">
         <v>4.39</v>
@@ -3652,7 +3652,7 @@
         <v>1.9</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CK7" t="n">
         <v>1.58</v>
@@ -3661,7 +3661,7 @@
         <v>2.13</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CN7" t="n">
         <v>1.74</v>
@@ -3712,76 +3712,76 @@
         <v>2.01</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.47</v>
+        <v>3.46</v>
       </c>
       <c r="DE7" t="n">
         <v>0.14</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="DH7" t="n">
-        <v>107.28</v>
+        <v>106.96</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.57</v>
+        <v>4.58</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.32</v>
+        <v>0.34</v>
       </c>
       <c r="DM7" t="n">
-        <v>59.39</v>
+        <v>59.86</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.9</v>
+        <v>0.87</v>
       </c>
       <c r="DO7" t="n">
         <v>2</v>
       </c>
       <c r="DP7" t="n">
-        <v>14.14</v>
+        <v>14.07</v>
       </c>
       <c r="DQ7" t="n">
-        <v>12.22</v>
+        <v>12.24</v>
       </c>
       <c r="DR7" t="n">
         <v>7.21</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>50.82</v>
+        <v>50.59</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="DX7" t="n">
-        <v>10.57</v>
+        <v>10.55</v>
       </c>
       <c r="DY7" t="n">
         <v>7.14</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.43</v>
+        <v>3.41</v>
       </c>
       <c r="EA7" t="n">
-        <v>21.68</v>
+        <v>21.52</v>
       </c>
       <c r="EB7" t="n">
         <v>1.35</v>

--- a/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -706,667 +694,667 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team_name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>total_games</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>home_games</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>away_games</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>home_avg_0_10_min_goals</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>home_avg_2h_cards</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>home_avg_2h_corners</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>home_avg_attacks</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>home_avg_cards_0_10_min</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>home_avg_cards_num</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>home_avg_corners</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>home_avg_corners_0_10_min</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>home_avg_dangerous_attacks</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>home_avg_fh_cards</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>home_avg_fh_corners</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>home_avg_fouls</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>home_avg_freekicks</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>home_avg_goalkicks</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>home_avg_goals_conceded</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>home_avg_goals_scored</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>home_avg_penalties_won</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>home_avg_penalty_goals</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>home_avg_penalty_missed</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>home_avg_possession</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>home_avg_red_cards</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>home_avg_shots</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>home_avg_shotsOffTarget</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>home_avg_shotsOnTarget</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>home_avg_throwins</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>home_avg_xg</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>home_avg_yellow_cards</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>away_avg_0_10_min_goals</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>away_avg_2h_cards</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>away_avg_2h_corners</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>away_avg_attacks</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>away_avg_cards_0_10_min</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>away_avg_cards_num</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>away_avg_corners</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>away_avg_corners_0_10_min</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>away_avg_dangerous_attacks</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>away_avg_fh_cards</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>away_avg_fh_corners</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>away_avg_fouls</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>away_avg_freekicks</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>away_avg_goalkicks</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>away_avg_goals_conceded</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>away_avg_goals_scored</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>away_avg_penalties_won</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>away_avg_penalty_goals</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>away_avg_penalty_missed</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>away_avg_possession</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>away_avg_red_cards</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>away_avg_shots</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>away_avg_shotsOffTarget</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>away_avg_shotsOnTarget</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>away_avg_throwins</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>away_avg_xg</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>away_avg_yellow_cards</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>totalGoalCount</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>totalCornerCount</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>overallGoalCount</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>ht_goals_team_a</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>ht_goals_team_b</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>goals_2hg_team_a</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>goals_2hg_team_b</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>GoalCount_2hg</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>HTGoalCount</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>corner_fh_count</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>corner_2h_count</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>over05</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>over15</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>over25</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>over35</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>over45</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>over55</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>btts</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>avg_odds_ft_1</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_1_odd</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>avg_odds_ft_x</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_x_odd</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CC1" t="inlineStr">
         <is>
           <t>avg_odds_ft_2</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CD1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_2_odd</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CE1" t="inlineStr">
         <is>
           <t>avg_odds_1st_half_over05</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CF1" t="inlineStr">
         <is>
           <t>avg_odds_1st_half_over15</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CG1" t="inlineStr">
         <is>
           <t>avg_odds_1st_half_under05</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CH1" t="inlineStr">
         <is>
           <t>avg_odds_1st_half_under15</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CI1" t="inlineStr">
         <is>
           <t>avg_odds_btts_no</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CJ1" t="inlineStr">
         <is>
           <t>avg_odds_btts_yes</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CK1" t="inlineStr">
         <is>
           <t>avg_odds_corners_over_85</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CL1" t="inlineStr">
         <is>
           <t>avg_odds_corners_over_95</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CM1" t="inlineStr">
         <is>
           <t>avg_odds_corners_under_85</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CN1" t="inlineStr">
         <is>
           <t>avg_odds_corners_under_95</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CO1" t="inlineStr">
         <is>
           <t>avg_odds_ft_over15</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CP1" t="inlineStr">
         <is>
           <t>avg_odds_ft_over25</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CQ1" t="inlineStr">
         <is>
           <t>avg_odds_ft_over35</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CR1" t="inlineStr">
         <is>
           <t>avg_pinnacle_1st_half_over05_odd</t>
         </is>
       </c>
-      <c r="CS1" s="1" t="inlineStr">
+      <c r="CS1" t="inlineStr">
         <is>
           <t>avg_pinnacle_1st_half_over15_odd</t>
         </is>
       </c>
-      <c r="CT1" s="1" t="inlineStr">
+      <c r="CT1" t="inlineStr">
         <is>
           <t>avg_pinnacle_1st_half_under05_odd</t>
         </is>
       </c>
-      <c r="CU1" s="1" t="inlineStr">
+      <c r="CU1" t="inlineStr">
         <is>
           <t>avg_pinnacle_1st_half_under15_odd</t>
         </is>
       </c>
-      <c r="CV1" s="1" t="inlineStr">
+      <c r="CV1" t="inlineStr">
         <is>
           <t>avg_pinnacle_btts_no_odd</t>
         </is>
       </c>
-      <c r="CW1" s="1" t="inlineStr">
+      <c r="CW1" t="inlineStr">
         <is>
           <t>avg_pinnacle_btts_yes_odd</t>
         </is>
       </c>
-      <c r="CX1" s="1" t="inlineStr">
+      <c r="CX1" t="inlineStr">
         <is>
           <t>avg_pinnacle_corners_over_85_odd</t>
         </is>
       </c>
-      <c r="CY1" s="1" t="inlineStr">
+      <c r="CY1" t="inlineStr">
         <is>
           <t>avg_pinnacle_corners_over_95_odd</t>
         </is>
       </c>
-      <c r="CZ1" s="1" t="inlineStr">
+      <c r="CZ1" t="inlineStr">
         <is>
           <t>avg_pinnacle_corners_under_85_odd</t>
         </is>
       </c>
-      <c r="DA1" s="1" t="inlineStr">
+      <c r="DA1" t="inlineStr">
         <is>
           <t>avg_pinnacle_corners_under_95_odd</t>
         </is>
       </c>
-      <c r="DB1" s="1" t="inlineStr">
+      <c r="DB1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_over15_odd</t>
         </is>
       </c>
-      <c r="DC1" s="1" t="inlineStr">
+      <c r="DC1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_over25_odd</t>
         </is>
       </c>
-      <c r="DD1" s="1" t="inlineStr">
+      <c r="DD1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_over35_odd</t>
         </is>
       </c>
-      <c r="DE1" s="1" t="inlineStr">
+      <c r="DE1" t="inlineStr">
         <is>
           <t>total_avg_0_10_min_goals</t>
         </is>
       </c>
-      <c r="DF1" s="1" t="inlineStr">
+      <c r="DF1" t="inlineStr">
         <is>
           <t>total_avg_2h_cards</t>
         </is>
       </c>
-      <c r="DG1" s="1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
         <is>
           <t>total_avg_2h_corners</t>
         </is>
       </c>
-      <c r="DH1" s="1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
         <is>
           <t>total_avg_attacks</t>
         </is>
       </c>
-      <c r="DI1" s="1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
         <is>
           <t>total_avg_cards_0_10_min</t>
         </is>
       </c>
-      <c r="DJ1" s="1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>total_avg_cards_num</t>
         </is>
       </c>
-      <c r="DK1" s="1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>total_avg_corners</t>
         </is>
       </c>
-      <c r="DL1" s="1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>total_avg_corners_0_10_min</t>
         </is>
       </c>
-      <c r="DM1" s="1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>total_avg_dangerous_attacks</t>
         </is>
       </c>
-      <c r="DN1" s="1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>total_avg_fh_cards</t>
         </is>
       </c>
-      <c r="DO1" s="1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>total_avg_fh_corners</t>
         </is>
       </c>
-      <c r="DP1" s="1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
         <is>
           <t>total_avg_fouls</t>
         </is>
       </c>
-      <c r="DQ1" s="1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>total_avg_freekicks</t>
         </is>
       </c>
-      <c r="DR1" s="1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>total_avg_goalkicks</t>
         </is>
       </c>
-      <c r="DS1" s="1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
         <is>
           <t>total_avg_penalties_won</t>
         </is>
       </c>
-      <c r="DT1" s="1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>total_avg_penalty_goals</t>
         </is>
       </c>
-      <c r="DU1" s="1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>total_avg_penalty_missed</t>
         </is>
       </c>
-      <c r="DV1" s="1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>total_avg_possession</t>
         </is>
       </c>
-      <c r="DW1" s="1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>total_avg_red_cards</t>
         </is>
       </c>
-      <c r="DX1" s="1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>total_avg_shots</t>
         </is>
       </c>
-      <c r="DY1" s="1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>total_avg_shotsOffTarget</t>
         </is>
       </c>
-      <c r="DZ1" s="1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>total_avg_shotsOnTarget</t>
         </is>
       </c>
-      <c r="EA1" s="1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>total_avg_throwins</t>
         </is>
       </c>
-      <c r="EB1" s="1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>total_avg_xg</t>
         </is>
       </c>
-      <c r="EC1" s="1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>total_avg_yellow_cards</t>
         </is>
@@ -1379,214 +1367,214 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D2" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E2" t="n">
-        <v>0.21</v>
+        <v>0.24</v>
       </c>
       <c r="F2" t="n">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="G2" t="n">
-        <v>2.64</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>119.93</v>
+        <v>113.94</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="K2" t="n">
-        <v>6.5</v>
+        <v>6.53</v>
       </c>
       <c r="L2" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="M2" t="n">
-        <v>72.43000000000001</v>
+        <v>68.41</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="O2" t="n">
-        <v>3.79</v>
+        <v>3.47</v>
       </c>
       <c r="P2" t="n">
-        <v>10.93</v>
+        <v>10.94</v>
       </c>
       <c r="Q2" t="n">
-        <v>11.5</v>
+        <v>11.65</v>
       </c>
       <c r="R2" t="n">
-        <v>5.29</v>
+        <v>5.41</v>
       </c>
       <c r="S2" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="T2" t="n">
-        <v>3.07</v>
+        <v>2.88</v>
       </c>
       <c r="U2" t="n">
-        <v>0.21</v>
+        <v>0.24</v>
       </c>
       <c r="V2" t="n">
-        <v>0.21</v>
+        <v>0.24</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>59.14</v>
+        <v>59</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="Z2" t="n">
-        <v>18</v>
+        <v>17.53</v>
       </c>
       <c r="AA2" t="n">
-        <v>10.57</v>
+        <v>10.29</v>
       </c>
       <c r="AB2" t="n">
-        <v>7.43</v>
+        <v>7.24</v>
       </c>
       <c r="AC2" t="n">
         <v>21.71</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.43</v>
+        <v>1.28</v>
       </c>
       <c r="AH2" t="n">
-        <v>3.71</v>
+        <v>3.39</v>
       </c>
       <c r="AI2" t="n">
-        <v>120</v>
+        <v>118.5</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AL2" t="n">
-        <v>6.57</v>
+        <v>6.17</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.57</v>
+        <v>0.61</v>
       </c>
       <c r="AN2" t="n">
-        <v>74.64</v>
+        <v>74.11</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="AQ2" t="n">
-        <v>13.71</v>
+        <v>12.78</v>
       </c>
       <c r="AR2" t="n">
-        <v>13</v>
+        <v>12.22</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.07</v>
+        <v>5.94</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="AU2" t="n">
-        <v>2.29</v>
+        <v>2.44</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>55.5</v>
+        <v>56.11</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.14</v>
+        <v>0.11</v>
       </c>
       <c r="BA2" t="n">
-        <v>16.36</v>
+        <v>15.94</v>
       </c>
       <c r="BB2" t="n">
-        <v>10.86</v>
+        <v>10.22</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.5</v>
+        <v>5.72</v>
       </c>
       <c r="BD2" t="n">
-        <v>23.64</v>
+        <v>23.28</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="BG2" t="n">
         <v>3.46</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.68</v>
+        <v>9.74</v>
       </c>
       <c r="BI2" t="n">
         <v>3.46</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.79</v>
+        <v>0.74</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BL2" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.96</v>
+        <v>2.03</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.82</v>
+        <v>4.66</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.82</v>
+        <v>5.06</v>
       </c>
       <c r="BR2" t="n">
-        <v>96.43000000000001</v>
+        <v>97.14</v>
       </c>
       <c r="BS2" t="n">
-        <v>92.86</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="BT2" t="n">
         <v>71.43000000000001</v>
@@ -1595,82 +1583,82 @@
         <v>42.86</v>
       </c>
       <c r="BV2" t="n">
-        <v>21.43</v>
+        <v>22.86</v>
       </c>
       <c r="BW2" t="n">
-        <v>14.29</v>
+        <v>11.43</v>
       </c>
       <c r="BX2" t="n">
-        <v>50</v>
+        <v>54.29</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="BZ2" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="CE2" t="n">
         <v>1.29</v>
       </c>
-      <c r="CA2" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="CB2" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="CC2" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="CD2" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="CE2" t="n">
-        <v>1.31</v>
-      </c>
       <c r="CF2" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.19</v>
+        <v>3.28</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="CK2" t="n">
         <v>1.58</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CN2" t="n">
         <v>1.75</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="CR2" t="n">
         <v>1.37</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.57</v>
+        <v>2.52</v>
       </c>
       <c r="CT2" t="n">
         <v>3.08</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="CV2" t="n">
         <v>1.84</v>
@@ -1679,100 +1667,100 @@
         <v>2</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CY2" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="DA2" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="DB2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="DC2" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="DD2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>116.29</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ2" t="n">
         <v>1.75</v>
       </c>
-      <c r="DB2" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="DC2" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="DD2" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="DE2" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="DF2" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="DG2" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="DH2" t="n">
-        <v>119.96</v>
-      </c>
-      <c r="DI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ2" t="n">
-        <v>1.9</v>
-      </c>
       <c r="DK2" t="n">
-        <v>6.54</v>
+        <v>6.34</v>
       </c>
       <c r="DL2" t="n">
         <v>0.57</v>
       </c>
       <c r="DM2" t="n">
-        <v>73.54000000000001</v>
+        <v>71.34</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.54</v>
+        <v>0.51</v>
       </c>
       <c r="DO2" t="n">
-        <v>3.32</v>
+        <v>3.12</v>
       </c>
       <c r="DP2" t="n">
-        <v>12.32</v>
+        <v>11.89</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.25</v>
+        <v>11.94</v>
       </c>
       <c r="DR2" t="n">
         <v>5.68</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.21</v>
+        <v>0.23</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.21</v>
+        <v>0.23</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>57.32</v>
+        <v>57.51</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="DX2" t="n">
-        <v>17.18</v>
+        <v>16.71</v>
       </c>
       <c r="DY2" t="n">
-        <v>10.72</v>
+        <v>10.25</v>
       </c>
       <c r="DZ2" t="n">
         <v>6.46</v>
       </c>
       <c r="EA2" t="n">
-        <v>22.68</v>
+        <v>22.52</v>
       </c>
       <c r="EB2" t="n">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="3">
@@ -1782,304 +1770,304 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C3" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D3" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E3" t="n">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
       <c r="F3" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="G3" t="n">
-        <v>2.14</v>
+        <v>2.5</v>
       </c>
       <c r="H3" t="n">
-        <v>96.56999999999999</v>
+        <v>90.44</v>
       </c>
       <c r="I3" t="n">
-        <v>0.29</v>
+        <v>0.22</v>
       </c>
       <c r="J3" t="n">
-        <v>2.43</v>
+        <v>2.22</v>
       </c>
       <c r="K3" t="n">
-        <v>3.71</v>
+        <v>4.5</v>
       </c>
       <c r="L3" t="n">
-        <v>0.14</v>
+        <v>0.33</v>
       </c>
       <c r="M3" t="n">
-        <v>49.07</v>
+        <v>48.67</v>
       </c>
       <c r="N3" t="n">
-        <v>0.86</v>
+        <v>0.72</v>
       </c>
       <c r="O3" t="n">
-        <v>1.43</v>
+        <v>1.89</v>
       </c>
       <c r="P3" t="n">
-        <v>11.64</v>
+        <v>11.33</v>
       </c>
       <c r="Q3" t="n">
-        <v>13.93</v>
+        <v>13.83</v>
       </c>
       <c r="R3" t="n">
-        <v>8.289999999999999</v>
+        <v>8.17</v>
       </c>
       <c r="S3" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="T3" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="U3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="V3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>48.07</v>
+        <v>47.72</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="Z3" t="n">
-        <v>10.64</v>
+        <v>10.39</v>
       </c>
       <c r="AA3" t="n">
-        <v>6.71</v>
+        <v>6.56</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.93</v>
+        <v>3.83</v>
       </c>
       <c r="AC3" t="n">
-        <v>20.93</v>
+        <v>20.83</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AI3" t="n">
-        <v>92.93000000000001</v>
+        <v>97.06</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.21</v>
+        <v>2.12</v>
       </c>
       <c r="AL3" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>51.41</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>11.29</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>13.59</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>45.53</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>11.59</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>7.82</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>20.76</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>8.77</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>94.29000000000001</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>71.43000000000001</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>45.71</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>25.71</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>51.43</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="CB3" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="CC3" t="n">
         <v>4.86</v>
       </c>
-      <c r="AM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>52</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>11.07</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>13.14</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>44.86</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>12.14</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>8.43</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>19.93</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>4.14</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>92.86</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>75</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>50</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>32.14</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>7.14</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="BX3" t="n">
-        <v>57.14</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="BZ3" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="CA3" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="CB3" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="CC3" t="n">
+      <c r="CD3" t="n">
         <v>5.18</v>
       </c>
-      <c r="CD3" t="n">
-        <v>5.42</v>
-      </c>
       <c r="CE3" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="CK3" t="n">
         <v>1.69</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CN3" t="n">
         <v>1.64</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="CR3" t="n">
         <v>1.43</v>
       </c>
       <c r="CS3" t="n">
-        <v>3.05</v>
+        <v>3.03</v>
       </c>
       <c r="CT3" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CX3" t="n">
         <v>1.72</v>
@@ -2088,94 +2076,94 @@
         <v>2.17</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="DA3" t="n">
         <v>1.62</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.73</v>
+        <v>3.62</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="DG3" t="n">
-        <v>1.92</v>
+        <v>2.09</v>
       </c>
       <c r="DH3" t="n">
-        <v>94.75</v>
+        <v>93.66</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.14</v>
+        <v>0.11</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.32</v>
+        <v>2.17</v>
       </c>
       <c r="DK3" t="n">
-        <v>4.28</v>
+        <v>4.4</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.17</v>
       </c>
       <c r="DM3" t="n">
-        <v>50.54</v>
+        <v>50</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.75</v>
+        <v>0.66</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="DP3" t="n">
-        <v>11.36</v>
+        <v>11.31</v>
       </c>
       <c r="DQ3" t="n">
-        <v>13.54</v>
+        <v>13.71</v>
       </c>
       <c r="DR3" t="n">
-        <v>8.4</v>
+        <v>8.34</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>46.46</v>
+        <v>46.66</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="DX3" t="n">
-        <v>11.39</v>
+        <v>10.97</v>
       </c>
       <c r="DY3" t="n">
-        <v>7.57</v>
+        <v>7.17</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="EA3" t="n">
-        <v>20.43</v>
+        <v>20.8</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.14</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="4">
@@ -2185,298 +2173,298 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C4" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D4" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="G4" t="n">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="H4" t="n">
-        <v>119.71</v>
+        <v>120.28</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>3.71</v>
+        <v>3.83</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="M4" t="n">
-        <v>70.79000000000001</v>
+        <v>70.89</v>
       </c>
       <c r="N4" t="n">
-        <v>0.64</v>
+        <v>0.78</v>
       </c>
       <c r="O4" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="P4" t="n">
-        <v>13.21</v>
+        <v>13.67</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.21</v>
+        <v>12.5</v>
       </c>
       <c r="R4" t="n">
-        <v>7.5</v>
+        <v>7.56</v>
       </c>
       <c r="S4" t="n">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="T4" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="U4" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="V4" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>44.36</v>
+        <v>44.11</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="Z4" t="n">
-        <v>10.64</v>
+        <v>10.56</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.43</v>
+        <v>6.67</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.21</v>
+        <v>3.89</v>
       </c>
       <c r="AC4" t="n">
-        <v>21.43</v>
+        <v>21.22</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.64</v>
+        <v>1.89</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="AI4" t="n">
-        <v>108.36</v>
+        <v>102.88</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="AK4" t="n">
-        <v>3.07</v>
+        <v>3.12</v>
       </c>
       <c r="AL4" t="n">
-        <v>3.29</v>
+        <v>3.12</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.21</v>
+        <v>0.24</v>
       </c>
       <c r="AN4" t="n">
-        <v>56.36</v>
+        <v>53.29</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.79</v>
+        <v>0.88</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.21</v>
+        <v>1.06</v>
       </c>
       <c r="AQ4" t="n">
-        <v>12.86</v>
+        <v>12.47</v>
       </c>
       <c r="AR4" t="n">
-        <v>11</v>
+        <v>11.47</v>
       </c>
       <c r="AS4" t="n">
-        <v>9.289999999999999</v>
+        <v>9.59</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.57</v>
+        <v>0.71</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>42.5</v>
+        <v>41.18</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.29</v>
+        <v>0.24</v>
       </c>
       <c r="BA4" t="n">
-        <v>8.93</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.43</v>
+        <v>6.35</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="BD4" t="n">
-        <v>22.36</v>
+        <v>21.76</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.57</v>
+        <v>2.71</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.86</v>
+        <v>2.89</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.460000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.86</v>
+        <v>2.89</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.68</v>
+        <v>0.66</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="BL4" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.61</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.71</v>
+        <v>4.49</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.68</v>
+        <v>4.66</v>
       </c>
       <c r="BR4" t="n">
-        <v>96.43000000000001</v>
+        <v>97.14</v>
       </c>
       <c r="BS4" t="n">
-        <v>82.14</v>
+        <v>82.86</v>
       </c>
       <c r="BT4" t="n">
-        <v>53.57</v>
+        <v>57.14</v>
       </c>
       <c r="BU4" t="n">
-        <v>35.71</v>
+        <v>34.29</v>
       </c>
       <c r="BV4" t="n">
         <v>14.29</v>
       </c>
       <c r="BW4" t="n">
-        <v>3.57</v>
+        <v>2.86</v>
       </c>
       <c r="BX4" t="n">
-        <v>60.71</v>
+        <v>60</v>
       </c>
       <c r="BY4" t="n">
-        <v>4.1</v>
+        <v>4.53</v>
       </c>
       <c r="BZ4" t="n">
-        <v>4.53</v>
+        <v>4.8</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.04</v>
+        <v>4.09</v>
       </c>
       <c r="CB4" t="n">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="CC4" t="n">
-        <v>6.14</v>
+        <v>6.12</v>
       </c>
       <c r="CD4" t="n">
-        <v>8.359999999999999</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.98</v>
+        <v>3.02</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="CK4" t="n">
         <v>1.61</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CM4" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.11</v>
+        <v>3.05</v>
       </c>
       <c r="CR4" t="n">
         <v>1.38</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="CT4" t="n">
         <v>3.04</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CV4" t="n">
         <v>1.92</v>
@@ -2494,91 +2482,91 @@
         <v>2.13</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="DB4" t="n">
         <v>1.28</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.24</v>
+        <v>3.19</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="DH4" t="n">
-        <v>114.03</v>
+        <v>111.83</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.43</v>
+        <v>2.54</v>
       </c>
       <c r="DK4" t="n">
-        <v>3.5</v>
+        <v>3.49</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.1</v>
+        <v>0.17</v>
       </c>
       <c r="DM4" t="n">
-        <v>63.58</v>
+        <v>62.34</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.72</v>
+        <v>0.83</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="DP4" t="n">
-        <v>13.04</v>
+        <v>13.09</v>
       </c>
       <c r="DQ4" t="n">
-        <v>11.6</v>
+        <v>12</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.4</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>43.43</v>
+        <v>42.69</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="DX4" t="n">
-        <v>9.779999999999999</v>
+        <v>9.74</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.43</v>
+        <v>6.51</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.36</v>
+        <v>3.23</v>
       </c>
       <c r="EA4" t="n">
-        <v>21.9</v>
+        <v>21.48</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.1</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="5">
@@ -2588,298 +2576,298 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C5" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D5" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E5" t="n">
-        <v>0.21</v>
+        <v>0.24</v>
       </c>
       <c r="F5" t="n">
-        <v>1.29</v>
+        <v>1.06</v>
       </c>
       <c r="G5" t="n">
-        <v>3.43</v>
+        <v>3.12</v>
       </c>
       <c r="H5" t="n">
-        <v>117.5</v>
+        <v>121.12</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="J5" t="n">
-        <v>1.86</v>
+        <v>1.76</v>
       </c>
       <c r="K5" t="n">
-        <v>5.14</v>
+        <v>4.65</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="M5" t="n">
-        <v>67.56999999999999</v>
+        <v>67.41</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="O5" t="n">
-        <v>1.71</v>
+        <v>1.53</v>
       </c>
       <c r="P5" t="n">
-        <v>12.14</v>
+        <v>12.12</v>
       </c>
       <c r="Q5" t="n">
-        <v>14.93</v>
+        <v>14.65</v>
       </c>
       <c r="R5" t="n">
-        <v>5.57</v>
+        <v>5.35</v>
       </c>
       <c r="S5" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="T5" t="n">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="U5" t="n">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="V5" t="n">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>58.86</v>
+        <v>58.71</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="Z5" t="n">
-        <v>15.64</v>
+        <v>15.06</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.640000000000001</v>
+        <v>9</v>
       </c>
       <c r="AB5" t="n">
-        <v>6</v>
+        <v>6.06</v>
       </c>
       <c r="AC5" t="n">
-        <v>22.71</v>
+        <v>23.18</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AH5" t="n">
-        <v>3.14</v>
+        <v>2.94</v>
       </c>
       <c r="AI5" t="n">
-        <v>110.07</v>
+        <v>105.83</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="AL5" t="n">
-        <v>6.57</v>
+        <v>5.61</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.79</v>
+        <v>0.61</v>
       </c>
       <c r="AN5" t="n">
-        <v>68.06999999999999</v>
+        <v>62.44</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.93</v>
+        <v>0.83</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.43</v>
+        <v>2.67</v>
       </c>
       <c r="AQ5" t="n">
-        <v>13.07</v>
+        <v>12.83</v>
       </c>
       <c r="AR5" t="n">
-        <v>14.29</v>
+        <v>14.22</v>
       </c>
       <c r="AS5" t="n">
-        <v>6.57</v>
+        <v>7.17</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.79</v>
+        <v>1.56</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.21</v>
+        <v>0.17</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.21</v>
+        <v>0.17</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>59.14</v>
+        <v>57.17</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>15.36</v>
+        <v>13.89</v>
       </c>
       <c r="BB5" t="n">
-        <v>10.14</v>
+        <v>9.17</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.21</v>
+        <v>4.72</v>
       </c>
       <c r="BD5" t="n">
-        <v>20.64</v>
+        <v>20.56</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.83</v>
+        <v>1.66</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.64</v>
+        <v>2.51</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.609999999999999</v>
+        <v>9.26</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.64</v>
+        <v>2.51</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.64</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="BO5" t="n">
         <v>1.29</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.21</v>
+        <v>3.89</v>
       </c>
       <c r="BQ5" t="n">
         <v>5.29</v>
       </c>
       <c r="BR5" t="n">
-        <v>96.43000000000001</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="BS5" t="n">
-        <v>85.70999999999999</v>
+        <v>80</v>
       </c>
       <c r="BT5" t="n">
-        <v>46.43</v>
+        <v>42.86</v>
       </c>
       <c r="BU5" t="n">
-        <v>25</v>
+        <v>25.71</v>
       </c>
       <c r="BV5" t="n">
-        <v>7.14</v>
+        <v>5.71</v>
       </c>
       <c r="BW5" t="n">
-        <v>3.57</v>
+        <v>2.86</v>
       </c>
       <c r="BX5" t="n">
         <v>42.86</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1.84</v>
+        <v>1.76</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.61</v>
+        <v>3.66</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.6</v>
+        <v>3.71</v>
       </c>
       <c r="CC5" t="n">
-        <v>2.19</v>
+        <v>2.32</v>
       </c>
       <c r="CD5" t="n">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="CE5" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="CN5" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="CO5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="CP5" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="CQ5" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="CR5" t="n">
         <v>1.41</v>
       </c>
-      <c r="CF5" t="n">
+      <c r="CS5" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="CT5" t="n">
         <v>2.91</v>
       </c>
-      <c r="CG5" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="CH5" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="CI5" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="CJ5" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="CK5" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="CL5" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="CM5" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="CN5" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="CO5" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="CP5" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="CQ5" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="CR5" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="CS5" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="CT5" t="n">
-        <v>2.85</v>
-      </c>
       <c r="CU5" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="CV5" t="n">
         <v>1.83</v>
@@ -2888,100 +2876,100 @@
         <v>1.99</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="CY5" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="DC5" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="DD5" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="DE5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="DF5" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="DG5" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="DH5" t="n">
+        <v>113.26</v>
+      </c>
+      <c r="DI5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DJ5" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="DK5" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="DL5" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="DM5" t="n">
+        <v>64.84999999999999</v>
+      </c>
+      <c r="DN5" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="DO5" t="n">
         <v>2.12</v>
       </c>
-      <c r="DD5" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="DE5" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="DF5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="DG5" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="DH5" t="n">
-        <v>113.78</v>
-      </c>
-      <c r="DI5" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="DJ5" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="DK5" t="n">
-        <v>5.86</v>
-      </c>
-      <c r="DL5" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="DM5" t="n">
-        <v>67.81999999999999</v>
-      </c>
-      <c r="DN5" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="DO5" t="n">
-        <v>2.57</v>
-      </c>
       <c r="DP5" t="n">
-        <v>12.61</v>
+        <v>12.49</v>
       </c>
       <c r="DQ5" t="n">
-        <v>14.61</v>
+        <v>14.43</v>
       </c>
       <c r="DR5" t="n">
-        <v>6.07</v>
+        <v>6.29</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.21</v>
+        <v>0.17</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.21</v>
+        <v>0.17</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>59</v>
+        <v>57.92</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX5" t="n">
-        <v>15.5</v>
+        <v>14.46</v>
       </c>
       <c r="DY5" t="n">
-        <v>9.890000000000001</v>
+        <v>9.09</v>
       </c>
       <c r="DZ5" t="n">
-        <v>5.6</v>
+        <v>5.37</v>
       </c>
       <c r="EA5" t="n">
-        <v>21.68</v>
+        <v>21.83</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.86</v>
+        <v>1.76</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="6">
@@ -2991,61 +2979,61 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C6" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E6" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="F6" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="G6" t="n">
-        <v>1.57</v>
+        <v>2.06</v>
       </c>
       <c r="H6" t="n">
-        <v>107.71</v>
+        <v>108.89</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>-0.11</v>
       </c>
       <c r="J6" t="n">
-        <v>1.71</v>
+        <v>1.56</v>
       </c>
       <c r="K6" t="n">
-        <v>4.21</v>
+        <v>4.56</v>
       </c>
       <c r="L6" t="n">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="M6" t="n">
-        <v>57.71</v>
+        <v>59.94</v>
       </c>
       <c r="N6" t="n">
-        <v>0.43</v>
+        <v>0.39</v>
       </c>
       <c r="O6" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="P6" t="n">
-        <v>11.71</v>
+        <v>11.94</v>
       </c>
       <c r="Q6" t="n">
-        <v>12.36</v>
+        <v>12</v>
       </c>
       <c r="R6" t="n">
-        <v>10.29</v>
+        <v>10.17</v>
       </c>
       <c r="S6" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T6" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -3057,232 +3045,232 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>50.43</v>
+        <v>51</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>10.93</v>
+        <v>10.94</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.43</v>
+        <v>7.72</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.5</v>
+        <v>3.22</v>
       </c>
       <c r="AC6" t="n">
-        <v>22.36</v>
+        <v>21.94</v>
       </c>
       <c r="AD6" t="n">
         <v>1.36</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.71</v>
+        <v>1.56</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.33</v>
+        <v>1.59</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AI6" t="n">
         <v>102.47</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.13</v>
+        <v>2.35</v>
       </c>
       <c r="AL6" t="n">
-        <v>3.73</v>
+        <v>3.82</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="AN6" t="n">
-        <v>55.13</v>
+        <v>54.94</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="AQ6" t="n">
-        <v>10.93</v>
+        <v>11</v>
       </c>
       <c r="AR6" t="n">
-        <v>11.07</v>
+        <v>11.06</v>
       </c>
       <c r="AS6" t="n">
-        <v>10.87</v>
+        <v>10.65</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>47.4</v>
+        <v>47.71</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>9.130000000000001</v>
+        <v>9.65</v>
       </c>
       <c r="BB6" t="n">
-        <v>6</v>
+        <v>6.47</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.13</v>
+        <v>3.18</v>
       </c>
       <c r="BD6" t="n">
-        <v>22.33</v>
+        <v>23</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.13</v>
+        <v>2.35</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.62</v>
+        <v>2.49</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.93</v>
+        <v>10.14</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.62</v>
+        <v>2.49</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.76</v>
+        <v>0.66</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.55</v>
+        <v>0.49</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.31</v>
+        <v>1.14</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.38</v>
+        <v>4.54</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.79</v>
+        <v>4.97</v>
       </c>
       <c r="BR6" t="n">
-        <v>96.55</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="BS6" t="n">
-        <v>79.31</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="BT6" t="n">
-        <v>55.17</v>
+        <v>51.43</v>
       </c>
       <c r="BU6" t="n">
-        <v>20.69</v>
+        <v>20</v>
       </c>
       <c r="BV6" t="n">
-        <v>6.9</v>
+        <v>5.71</v>
       </c>
       <c r="BW6" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>54.29</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="CA6" t="n">
         <v>3.45</v>
       </c>
-      <c r="BX6" t="n">
-        <v>58.62</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="BZ6" t="n">
+      <c r="CB6" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="CN6" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="CO6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="CP6" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="CQ6" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="CR6" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="CS6" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="CT6" t="n">
         <v>2.9</v>
       </c>
-      <c r="CA6" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="CB6" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="CC6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="CD6" t="n">
-        <v>4.83</v>
-      </c>
-      <c r="CE6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="CF6" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="CG6" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="CH6" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="CI6" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="CJ6" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="CK6" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="CL6" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="CM6" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="CN6" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="CO6" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="CP6" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="CQ6" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="CR6" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="CS6" t="n">
-        <v>3</v>
-      </c>
-      <c r="CT6" t="n">
-        <v>2.89</v>
-      </c>
       <c r="CU6" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="CV6" t="n">
         <v>1.92</v>
@@ -3291,100 +3279,100 @@
         <v>1.9</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="CZ6" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.64</v>
+        <v>3.54</v>
       </c>
       <c r="DE6" t="n">
         <v>0.2</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="DH6" t="n">
-        <v>105</v>
+        <v>105.77</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.17</v>
+        <v>0.08</v>
       </c>
       <c r="DJ6" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="DK6" t="n">
-        <v>3.96</v>
+        <v>4.2</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.31</v>
+        <v>0.34</v>
       </c>
       <c r="DM6" t="n">
-        <v>56.38</v>
+        <v>57.51</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="DO6" t="n">
         <v>1.97</v>
       </c>
       <c r="DP6" t="n">
-        <v>11.31</v>
+        <v>11.48</v>
       </c>
       <c r="DQ6" t="n">
-        <v>11.69</v>
+        <v>11.54</v>
       </c>
       <c r="DR6" t="n">
-        <v>10.59</v>
+        <v>10.4</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>48.86</v>
+        <v>49.4</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>10</v>
+        <v>10.31</v>
       </c>
       <c r="DY6" t="n">
-        <v>6.69</v>
+        <v>7.11</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.31</v>
+        <v>3.2</v>
       </c>
       <c r="EA6" t="n">
-        <v>22.34</v>
+        <v>22.45</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="7">
@@ -3394,271 +3382,271 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C7" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D7" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="G7" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="H7" t="n">
-        <v>99.53</v>
+        <v>101.56</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>2.47</v>
+        <v>2.28</v>
       </c>
       <c r="K7" t="n">
-        <v>4.13</v>
+        <v>4.22</v>
       </c>
       <c r="L7" t="n">
-        <v>0.47</v>
+        <v>0.39</v>
       </c>
       <c r="M7" t="n">
-        <v>57.27</v>
+        <v>57.44</v>
       </c>
       <c r="N7" t="n">
-        <v>0.87</v>
+        <v>0.78</v>
       </c>
       <c r="O7" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="P7" t="n">
-        <v>13.93</v>
+        <v>14.06</v>
       </c>
       <c r="Q7" t="n">
-        <v>12.8</v>
+        <v>12.56</v>
       </c>
       <c r="R7" t="n">
-        <v>7.27</v>
+        <v>7.33</v>
       </c>
       <c r="S7" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="T7" t="n">
         <v>1.33</v>
       </c>
-      <c r="T7" t="n">
-        <v>1.4</v>
-      </c>
       <c r="U7" t="n">
-        <v>0.33</v>
+        <v>0.28</v>
       </c>
       <c r="V7" t="n">
-        <v>0.33</v>
+        <v>0.28</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>48.27</v>
+        <v>48.17</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="Z7" t="n">
-        <v>10.67</v>
+        <v>10.78</v>
       </c>
       <c r="AA7" t="n">
-        <v>6.87</v>
+        <v>7</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.8</v>
+        <v>3.78</v>
       </c>
       <c r="AC7" t="n">
         <v>22</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.29</v>
+        <v>0.24</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.14</v>
+        <v>1.35</v>
       </c>
       <c r="AH7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>110.35</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>60.94</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>14.24</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>12.18</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>7.53</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>52.82</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>6.82</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>22.12</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>8.91</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>97.14</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>91.43000000000001</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>42.86</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>20</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>8.57</v>
+      </c>
+      <c r="BW7" t="n">
         <v>2.86</v>
       </c>
-      <c r="AI7" t="n">
-        <v>114.93</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>5.07</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>62.64</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>14.21</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>11.64</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>7.14</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>53.07</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>10.43</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>7.43</v>
-      </c>
-      <c r="BC7" t="n">
+      <c r="BX7" t="n">
+        <v>65.70999999999999</v>
+      </c>
+      <c r="BY7" t="n">
         <v>3</v>
       </c>
-      <c r="BD7" t="n">
-        <v>21</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>4</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>100</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>93.09999999999999</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>44.83</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>24.14</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>10.34</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>68.97</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>2.99</v>
-      </c>
       <c r="BZ7" t="n">
-        <v>3.19</v>
+        <v>3.21</v>
       </c>
       <c r="CA7" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="CB7" t="n">
         <v>3.58</v>
       </c>
-      <c r="CB7" t="n">
-        <v>3.62</v>
-      </c>
       <c r="CC7" t="n">
-        <v>4.39</v>
+        <v>4.18</v>
       </c>
       <c r="CD7" t="n">
-        <v>4.67</v>
+        <v>4.44</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="CH7" t="n">
         <v>1.4</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CK7" t="n">
         <v>1.58</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CM7" t="n">
         <v>2.2</v>
@@ -3679,10 +3667,10 @@
         <v>1.39</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="CU7" t="n">
         <v>1.41</v>
@@ -3703,91 +3691,91 @@
         <v>2.21</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.46</v>
+        <v>3.43</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.59</v>
+        <v>2.74</v>
       </c>
       <c r="DH7" t="n">
-        <v>106.96</v>
+        <v>105.83</v>
       </c>
       <c r="DI7" t="n">
         <v>0.03</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.28</v>
+        <v>2.23</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.58</v>
+        <v>4.63</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.34</v>
+        <v>0.29</v>
       </c>
       <c r="DM7" t="n">
-        <v>59.86</v>
+        <v>59.14</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.87</v>
+        <v>0.77</v>
       </c>
       <c r="DO7" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="DP7" t="n">
-        <v>14.07</v>
+        <v>14.15</v>
       </c>
       <c r="DQ7" t="n">
-        <v>12.24</v>
+        <v>12.38</v>
       </c>
       <c r="DR7" t="n">
-        <v>7.21</v>
+        <v>7.43</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.24</v>
+        <v>0.2</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.24</v>
+        <v>0.2</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>50.59</v>
+        <v>50.43</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="DX7" t="n">
-        <v>10.55</v>
+        <v>10.23</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.14</v>
+        <v>6.91</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.41</v>
+        <v>3.31</v>
       </c>
       <c r="EA7" t="n">
-        <v>21.52</v>
+        <v>22.06</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="8">
@@ -3797,142 +3785,142 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C8" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D8" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="G8" t="n">
-        <v>2.93</v>
+        <v>3.06</v>
       </c>
       <c r="H8" t="n">
-        <v>114.43</v>
+        <v>118.47</v>
       </c>
       <c r="I8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="J8" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="K8" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="M8" t="n">
+        <v>78.29000000000001</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="P8" t="n">
+        <v>14.06</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>13.65</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6.24</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>51.53</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>13.18</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>9.59</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>21.71</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AE8" t="n">
         <v>2.29</v>
       </c>
-      <c r="K8" t="n">
-        <v>5.64</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="M8" t="n">
-        <v>77.29000000000001</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="O8" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="P8" t="n">
-        <v>14.57</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>13.57</v>
-      </c>
-      <c r="R8" t="n">
-        <v>6.64</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>49.57</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>12.71</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>9.359999999999999</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>2.21</v>
-      </c>
       <c r="AF8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.64</v>
+        <v>1.89</v>
       </c>
       <c r="AI8" t="n">
-        <v>96.93000000000001</v>
+        <v>98.94</v>
       </c>
       <c r="AJ8" t="n">
-        <v>-0.14</v>
+        <v>-0.11</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="AL8" t="n">
-        <v>3.5</v>
+        <v>3.83</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.57</v>
+        <v>0.61</v>
       </c>
       <c r="AN8" t="n">
-        <v>51.14</v>
+        <v>52.83</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.79</v>
+        <v>0.72</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="AQ8" t="n">
-        <v>14.64</v>
+        <v>15.39</v>
       </c>
       <c r="AR8" t="n">
-        <v>12.86</v>
+        <v>12.67</v>
       </c>
       <c r="AS8" t="n">
-        <v>7.57</v>
+        <v>7.83</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.93</v>
+        <v>1.67</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="AV8" t="n">
         <v>0</v>
@@ -3944,253 +3932,253 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>47.64</v>
+        <v>47.11</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.21</v>
+        <v>0.17</v>
       </c>
       <c r="BA8" t="n">
-        <v>11.21</v>
+        <v>11.11</v>
       </c>
       <c r="BB8" t="n">
-        <v>7.79</v>
+        <v>7.72</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.43</v>
+        <v>3.39</v>
       </c>
       <c r="BD8" t="n">
-        <v>22.14</v>
+        <v>21.22</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.32</v>
+        <v>2.11</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.890000000000001</v>
+        <v>10</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.32</v>
+        <v>2.11</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="BK8" t="n">
         <v>0.57</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.86</v>
+        <v>0.71</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.29</v>
+        <v>1.11</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.93</v>
+        <v>4.94</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.93</v>
+        <v>5.03</v>
       </c>
       <c r="BR8" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BS8" t="n">
-        <v>67.86</v>
+        <v>62.86</v>
       </c>
       <c r="BT8" t="n">
-        <v>39.29</v>
+        <v>31.43</v>
       </c>
       <c r="BU8" t="n">
-        <v>21.43</v>
+        <v>17.14</v>
       </c>
       <c r="BV8" t="n">
-        <v>10.71</v>
+        <v>8.57</v>
       </c>
       <c r="BW8" t="n">
-        <v>10.71</v>
+        <v>8.57</v>
       </c>
       <c r="BX8" t="n">
-        <v>39.29</v>
+        <v>31.43</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.76</v>
+        <v>2.64</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.42</v>
+        <v>3.43</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.46</v>
+        <v>3.47</v>
       </c>
       <c r="CC8" t="n">
-        <v>4.07</v>
+        <v>4.21</v>
       </c>
       <c r="CD8" t="n">
-        <v>4.42</v>
+        <v>4.62</v>
       </c>
       <c r="CE8" t="n">
         <v>1.4</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CI8" t="n">
         <v>1.88</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CO8" t="n">
         <v>1.29</v>
       </c>
       <c r="CP8" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.34</v>
+        <v>3.36</v>
       </c>
       <c r="CR8" t="n">
         <v>1.42</v>
       </c>
       <c r="CS8" t="n">
-        <v>3.05</v>
+        <v>3.03</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CV8" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CW8" t="n">
         <v>1.86</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="DB8" t="n">
         <v>1.33</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.66</v>
+        <v>3.62</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.28</v>
+        <v>2.46</v>
       </c>
       <c r="DH8" t="n">
-        <v>105.68</v>
+        <v>108.43</v>
       </c>
       <c r="DI8" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.57</v>
+        <v>4.74</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="DM8" t="n">
-        <v>64.22</v>
+        <v>65.2</v>
       </c>
       <c r="DN8" t="n">
         <v>0.86</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="DP8" t="n">
-        <v>14.61</v>
+        <v>14.74</v>
       </c>
       <c r="DQ8" t="n">
-        <v>13.22</v>
+        <v>13.15</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.1</v>
+        <v>7.06</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>48.6</v>
+        <v>49.26</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DX8" t="n">
-        <v>11.96</v>
+        <v>12.12</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.57</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.4</v>
+        <v>3.49</v>
       </c>
       <c r="EA8" t="n">
-        <v>21.32</v>
+        <v>21.46</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="9">
@@ -4200,298 +4188,298 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C9" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D9" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E9" t="n">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="F9" t="n">
-        <v>1.64</v>
+        <v>1.47</v>
       </c>
       <c r="G9" t="n">
-        <v>3.43</v>
+        <v>3.76</v>
       </c>
       <c r="H9" t="n">
-        <v>120.64</v>
+        <v>119.88</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2.43</v>
+        <v>2.35</v>
       </c>
       <c r="K9" t="n">
-        <v>6.43</v>
+        <v>7</v>
       </c>
       <c r="L9" t="n">
-        <v>0.79</v>
+        <v>0.82</v>
       </c>
       <c r="M9" t="n">
-        <v>72</v>
+        <v>72.23999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>0.71</v>
+        <v>0.82</v>
       </c>
       <c r="O9" t="n">
-        <v>3</v>
+        <v>3.24</v>
       </c>
       <c r="P9" t="n">
-        <v>12</v>
+        <v>12.35</v>
       </c>
       <c r="Q9" t="n">
-        <v>13.5</v>
+        <v>13.35</v>
       </c>
       <c r="R9" t="n">
-        <v>7.14</v>
+        <v>6.76</v>
       </c>
       <c r="S9" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="T9" t="n">
-        <v>1.71</v>
+        <v>1.59</v>
       </c>
       <c r="U9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="V9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>52.71</v>
+        <v>55</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="Z9" t="n">
-        <v>16.07</v>
+        <v>16.29</v>
       </c>
       <c r="AA9" t="n">
-        <v>11.5</v>
+        <v>11.35</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.57</v>
+        <v>4.94</v>
       </c>
       <c r="AC9" t="n">
-        <v>23.64</v>
+        <v>24.53</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.29</v>
+        <v>2.24</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.21</v>
+        <v>0.17</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="AH9" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="AI9" t="n">
-        <v>111.79</v>
+        <v>110.06</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.86</v>
+        <v>2.72</v>
       </c>
       <c r="AL9" t="n">
-        <v>5.43</v>
+        <v>5.56</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AN9" t="n">
-        <v>61.29</v>
+        <v>59.06</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.86</v>
+        <v>0.78</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.43</v>
+        <v>2.61</v>
       </c>
       <c r="AQ9" t="n">
-        <v>12.93</v>
+        <v>12.72</v>
       </c>
       <c r="AR9" t="n">
-        <v>12.86</v>
+        <v>12.89</v>
       </c>
       <c r="AS9" t="n">
-        <v>6.79</v>
+        <v>6.78</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>50.5</v>
+        <v>50.44</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.14</v>
+        <v>0.22</v>
       </c>
       <c r="BA9" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BB9" t="n">
-        <v>9.789999999999999</v>
+        <v>9.33</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.21</v>
+        <v>3.17</v>
       </c>
       <c r="BD9" t="n">
-        <v>22.5</v>
+        <v>23.28</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.57</v>
+        <v>2.33</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.960000000000001</v>
+        <v>10.11</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.64</v>
+        <v>0.57</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.57</v>
+        <v>0.51</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.43</v>
+        <v>0.49</v>
       </c>
       <c r="BN9" t="n">
         <v>1.29</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.21</v>
+        <v>1.09</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.29</v>
+        <v>4.31</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.68</v>
+        <v>5.8</v>
       </c>
       <c r="BR9" t="n">
-        <v>89.29000000000001</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS9" t="n">
-        <v>71.43000000000001</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="BT9" t="n">
         <v>42.86</v>
       </c>
       <c r="BU9" t="n">
-        <v>32.14</v>
+        <v>28.57</v>
       </c>
       <c r="BV9" t="n">
-        <v>10.71</v>
+        <v>8.57</v>
       </c>
       <c r="BW9" t="n">
-        <v>3.57</v>
+        <v>2.86</v>
       </c>
       <c r="BX9" t="n">
-        <v>46.43</v>
+        <v>40</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.03</v>
+        <v>1.99</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.03</v>
+        <v>1.98</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.47</v>
+        <v>3.54</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.55</v>
+        <v>3.66</v>
       </c>
       <c r="CC9" t="n">
-        <v>2.71</v>
+        <v>2.88</v>
       </c>
       <c r="CD9" t="n">
-        <v>3.02</v>
+        <v>3.14</v>
       </c>
       <c r="CE9" t="n">
         <v>1.4</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="CK9" t="n">
         <v>1.62</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CM9" t="n">
-        <v>1.99</v>
+        <v>2.03</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.52</v>
+        <v>3.46</v>
       </c>
       <c r="CR9" t="n">
         <v>1.43</v>
       </c>
       <c r="CS9" t="n">
-        <v>3.1</v>
+        <v>3.07</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CV9" t="n">
         <v>1.84</v>
@@ -4500,100 +4488,100 @@
         <v>1.97</v>
       </c>
       <c r="CX9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="CY9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="CZ9" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="DA9" t="n">
         <v>1.68</v>
       </c>
-      <c r="CY9" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="CZ9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="DA9" t="n">
-        <v>1.67</v>
-      </c>
       <c r="DB9" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.13</v>
+        <v>2.09</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.78</v>
+        <v>3.69</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.21</v>
+        <v>0.17</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="DG9" t="n">
-        <v>3.22</v>
+        <v>3.34</v>
       </c>
       <c r="DH9" t="n">
-        <v>116.22</v>
+        <v>114.83</v>
       </c>
       <c r="DI9" t="n">
         <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.64</v>
+        <v>2.54</v>
       </c>
       <c r="DK9" t="n">
-        <v>5.93</v>
+        <v>6.26</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
       <c r="DM9" t="n">
-        <v>66.64</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.72</v>
+        <v>2.92</v>
       </c>
       <c r="DP9" t="n">
-        <v>12.46</v>
+        <v>12.54</v>
       </c>
       <c r="DQ9" t="n">
-        <v>13.18</v>
+        <v>13.11</v>
       </c>
       <c r="DR9" t="n">
-        <v>6.96</v>
+        <v>6.77</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>51.6</v>
+        <v>52.65</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.11</v>
+        <v>0.14</v>
       </c>
       <c r="DX9" t="n">
-        <v>14.54</v>
+        <v>14.34</v>
       </c>
       <c r="DY9" t="n">
-        <v>10.64</v>
+        <v>10.31</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3.89</v>
+        <v>4.03</v>
       </c>
       <c r="EA9" t="n">
-        <v>23.07</v>
+        <v>23.89</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.43</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="10">
@@ -4603,286 +4591,286 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C10" t="n">
+        <v>18</v>
+      </c>
+      <c r="D10" t="n">
+        <v>17</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="H10" t="n">
+        <v>109.11</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="K10" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="M10" t="n">
+        <v>56.56</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P10" t="n">
+        <v>12.83</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>12.44</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>51.06</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="Z10" t="n">
         <v>14</v>
       </c>
-      <c r="D10" t="n">
-        <v>14</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="G10" t="n">
+      <c r="AA10" t="n">
+        <v>9.56</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>24.17</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>106.76</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>51.94</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>13.94</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>12.41</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>8.35</v>
+      </c>
+      <c r="AT10" t="n">
         <v>2</v>
       </c>
-      <c r="H10" t="n">
-        <v>114.29</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="K10" t="n">
-        <v>4.29</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="M10" t="n">
-        <v>60.29</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="P10" t="n">
-        <v>12.64</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>12.93</v>
-      </c>
-      <c r="R10" t="n">
-        <v>7.93</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>52.14</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>106.5</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>48.93</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>14.43</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>12.71</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>8.359999999999999</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>1.93</v>
-      </c>
       <c r="AU10" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>45.71</v>
+        <v>46.12</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA10" t="n">
-        <v>9.640000000000001</v>
+        <v>10.41</v>
       </c>
       <c r="BB10" t="n">
-        <v>6.57</v>
+        <v>7.18</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.07</v>
+        <v>3.24</v>
       </c>
       <c r="BD10" t="n">
-        <v>20.93</v>
+        <v>20.94</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="BH10" t="n">
-        <v>7.57</v>
+        <v>7.63</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.61</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
       <c r="BL10" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.43</v>
+        <v>0.51</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.32</v>
+        <v>3.29</v>
       </c>
       <c r="BQ10" t="n">
-        <v>3.57</v>
+        <v>3.8</v>
       </c>
       <c r="BR10" t="n">
-        <v>89.29000000000001</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="BS10" t="n">
         <v>85.70999999999999</v>
       </c>
       <c r="BT10" t="n">
-        <v>57.14</v>
+        <v>62.86</v>
       </c>
       <c r="BU10" t="n">
-        <v>32.14</v>
+        <v>37.14</v>
       </c>
       <c r="BV10" t="n">
         <v>14.29</v>
       </c>
       <c r="BW10" t="n">
-        <v>7.14</v>
+        <v>5.71</v>
       </c>
       <c r="BX10" t="n">
-        <v>64.29000000000001</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="BZ10" t="n">
-        <v>2.78</v>
+        <v>3.02</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.42</v>
+        <v>3.44</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.51</v>
+        <v>3.54</v>
       </c>
       <c r="CC10" t="n">
-        <v>4.65</v>
+        <v>4.35</v>
       </c>
       <c r="CD10" t="n">
-        <v>5.26</v>
+        <v>4.99</v>
       </c>
       <c r="CE10" t="n">
         <v>1.38</v>
       </c>
       <c r="CF10" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="CG10" t="n">
         <v>2.86</v>
       </c>
-      <c r="CG10" t="n">
-        <v>2.84</v>
-      </c>
       <c r="CH10" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CL10" t="n">
         <v>2.39</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CN10" t="n">
         <v>1.61</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.39</v>
+        <v>3.32</v>
       </c>
       <c r="CR10" t="n">
         <v>1.41</v>
@@ -4891,7 +4879,7 @@
         <v>3</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="CU10" t="n">
         <v>1.4</v>
@@ -4903,7 +4891,7 @@
         <v>1.87</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CY10" t="n">
         <v>2.19</v>
@@ -4915,88 +4903,88 @@
         <v>1.61</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.56</v>
+        <v>3.49</v>
       </c>
       <c r="DE10" t="n">
         <v>0.14</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="DH10" t="n">
-        <v>110.4</v>
+        <v>107.97</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="DK10" t="n">
-        <v>3.61</v>
+        <v>3.86</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.22</v>
+        <v>0.29</v>
       </c>
       <c r="DM10" t="n">
-        <v>54.61</v>
+        <v>54.32</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.61</v>
+        <v>0.51</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="DP10" t="n">
-        <v>13.54</v>
+        <v>13.37</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.82</v>
+        <v>12.43</v>
       </c>
       <c r="DR10" t="n">
-        <v>8.140000000000001</v>
+        <v>8.08</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>48.92</v>
+        <v>48.66</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.07</v>
+        <v>12.26</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.279999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.78</v>
+        <v>3.86</v>
       </c>
       <c r="EA10" t="n">
-        <v>23.22</v>
+        <v>22.6</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.04</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="11">
@@ -5006,298 +4994,298 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C11" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E11" t="n">
-        <v>0.21</v>
+        <v>0.24</v>
       </c>
       <c r="F11" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="G11" t="n">
-        <v>1.93</v>
+        <v>1.76</v>
       </c>
       <c r="H11" t="n">
-        <v>106.21</v>
+        <v>105.18</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2.43</v>
+        <v>2.35</v>
       </c>
       <c r="K11" t="n">
-        <v>4.14</v>
+        <v>3.76</v>
       </c>
       <c r="L11" t="n">
-        <v>0.43</v>
+        <v>0.35</v>
       </c>
       <c r="M11" t="n">
-        <v>54.79</v>
+        <v>54</v>
       </c>
       <c r="N11" t="n">
-        <v>0.79</v>
+        <v>0.71</v>
       </c>
       <c r="O11" t="n">
-        <v>2.21</v>
+        <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>12.29</v>
+        <v>12</v>
       </c>
       <c r="Q11" t="n">
-        <v>13.07</v>
+        <v>13.12</v>
       </c>
       <c r="R11" t="n">
-        <v>7.57</v>
+        <v>7.65</v>
       </c>
       <c r="S11" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="T11" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="U11" t="n">
-        <v>0.14</v>
+        <v>0.24</v>
       </c>
       <c r="V11" t="n">
-        <v>0.14</v>
+        <v>0.24</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>45.93</v>
+        <v>46.12</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z11" t="n">
-        <v>13.79</v>
+        <v>12.47</v>
       </c>
       <c r="AA11" t="n">
-        <v>9.640000000000001</v>
+        <v>8.59</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.14</v>
+        <v>3.88</v>
       </c>
       <c r="AC11" t="n">
-        <v>21.71</v>
+        <v>22.47</v>
       </c>
       <c r="AD11" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>94.56</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>49.22</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AP11" t="n">
         <v>1.56</v>
       </c>
-      <c r="AE11" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>94.56999999999999</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>47.86</v>
-      </c>
-      <c r="AO11" t="n">
+      <c r="AQ11" t="n">
+        <v>12.94</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>11.94</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>8.390000000000001</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>43.61</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>10.61</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>19.72</v>
+      </c>
+      <c r="BE11" t="n">
         <v>1.29</v>
       </c>
-      <c r="AP11" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>12.79</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>8.140000000000001</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>44.5</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>10.71</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>7.29</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>19.36</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.27</v>
-      </c>
       <c r="BF11" t="n">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="BH11" t="n">
         <v>9.710000000000001</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="BK11" t="n">
         <v>0.71</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.29</v>
+        <v>4.23</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.79</v>
+        <v>4.97</v>
       </c>
       <c r="BR11" t="n">
-        <v>92.86</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="BS11" t="n">
-        <v>82.14</v>
+        <v>82.86</v>
       </c>
       <c r="BT11" t="n">
-        <v>50</v>
+        <v>48.57</v>
       </c>
       <c r="BU11" t="n">
-        <v>32.14</v>
+        <v>28.57</v>
       </c>
       <c r="BV11" t="n">
-        <v>3.57</v>
+        <v>2.86</v>
       </c>
       <c r="BW11" t="n">
-        <v>3.57</v>
+        <v>2.86</v>
       </c>
       <c r="BX11" t="n">
-        <v>64.29000000000001</v>
+        <v>62.86</v>
       </c>
       <c r="BY11" t="n">
-        <v>3.01</v>
+        <v>2.86</v>
       </c>
       <c r="BZ11" t="n">
-        <v>3.24</v>
+        <v>3.08</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.34</v>
+        <v>3.44</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.36</v>
+        <v>3.51</v>
       </c>
       <c r="CC11" t="n">
-        <v>3.77</v>
+        <v>4.17</v>
       </c>
       <c r="CD11" t="n">
-        <v>4.15</v>
+        <v>4.89</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.99</v>
+        <v>2.94</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.64</v>
+        <v>2.73</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="CP11" t="n">
-        <v>2.08</v>
+        <v>2.03</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.58</v>
+        <v>3.47</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CS11" t="n">
-        <v>3.17</v>
+        <v>3.07</v>
       </c>
       <c r="CT11" t="n">
-        <v>2.78</v>
+        <v>2.83</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="CV11" t="n">
         <v>1.9</v>
@@ -5306,100 +5294,100 @@
         <v>1.92</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.81</v>
+        <v>3.68</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.32</v>
+        <v>1.46</v>
       </c>
       <c r="DG11" t="n">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="DH11" t="n">
-        <v>100.39</v>
+        <v>99.72</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ11" t="n">
         <v>2.4</v>
       </c>
       <c r="DK11" t="n">
-        <v>3.92</v>
+        <v>3.68</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.61</v>
+        <v>0.51</v>
       </c>
       <c r="DM11" t="n">
-        <v>51.32</v>
+        <v>51.54</v>
       </c>
       <c r="DN11" t="n">
-        <v>1.04</v>
+        <v>0.89</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.89</v>
+        <v>1.77</v>
       </c>
       <c r="DP11" t="n">
-        <v>12.54</v>
+        <v>12.48</v>
       </c>
       <c r="DQ11" t="n">
-        <v>12.78</v>
+        <v>12.51</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.86</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>45.22</v>
+        <v>44.83</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX11" t="n">
-        <v>12.25</v>
+        <v>11.51</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.460000000000001</v>
+        <v>7.74</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.78</v>
+        <v>3.77</v>
       </c>
       <c r="EA11" t="n">
-        <v>20.54</v>
+        <v>21.06</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Croatia_HNL_2025-2026.xlsx
@@ -1367,94 +1367,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D2" t="n">
         <v>18</v>
       </c>
       <c r="E2" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="F2" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="H2" t="n">
-        <v>113.94</v>
+        <v>114.39</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
       <c r="J2" t="n">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="K2" t="n">
-        <v>6.53</v>
+        <v>6.39</v>
       </c>
       <c r="L2" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="M2" t="n">
-        <v>68.41</v>
+        <v>68.67</v>
       </c>
       <c r="N2" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="O2" t="n">
-        <v>3.47</v>
+        <v>3.39</v>
       </c>
       <c r="P2" t="n">
-        <v>10.94</v>
+        <v>10.89</v>
       </c>
       <c r="Q2" t="n">
-        <v>11.65</v>
+        <v>11.83</v>
       </c>
       <c r="R2" t="n">
-        <v>5.41</v>
+        <v>5.22</v>
       </c>
       <c r="S2" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="T2" t="n">
-        <v>2.88</v>
+        <v>2.72</v>
       </c>
       <c r="U2" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="V2" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>59</v>
+        <v>59.17</v>
       </c>
       <c r="Y2" t="n">
         <v>0.06</v>
       </c>
       <c r="Z2" t="n">
-        <v>17.53</v>
+        <v>17.28</v>
       </c>
       <c r="AA2" t="n">
-        <v>10.29</v>
+        <v>10.39</v>
       </c>
       <c r="AB2" t="n">
-        <v>7.24</v>
+        <v>6.89</v>
       </c>
       <c r="AC2" t="n">
-        <v>21.71</v>
+        <v>21.61</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="AF2" t="n">
         <v>0.22</v>
@@ -1538,70 +1538,70 @@
         <v>1.67</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.46</v>
+        <v>3.36</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.74</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.46</v>
+        <v>3.36</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.74</v>
+        <v>0.72</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="BL2" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="BM2" t="n">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="BN2" t="n">
-        <v>2.03</v>
+        <v>1.97</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.66</v>
+        <v>4.61</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.06</v>
+        <v>5</v>
       </c>
       <c r="BR2" t="n">
-        <v>97.14</v>
+        <v>94.44</v>
       </c>
       <c r="BS2" t="n">
-        <v>94.29000000000001</v>
+        <v>91.67</v>
       </c>
       <c r="BT2" t="n">
-        <v>71.43000000000001</v>
+        <v>69.44</v>
       </c>
       <c r="BU2" t="n">
-        <v>42.86</v>
+        <v>41.67</v>
       </c>
       <c r="BV2" t="n">
-        <v>22.86</v>
+        <v>22.22</v>
       </c>
       <c r="BW2" t="n">
-        <v>11.43</v>
+        <v>11.11</v>
       </c>
       <c r="BX2" t="n">
-        <v>54.29</v>
+        <v>52.78</v>
       </c>
       <c r="BY2" t="n">
         <v>1.29</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.82</v>
+        <v>4.83</v>
       </c>
       <c r="CB2" t="n">
-        <v>5.18</v>
+        <v>5.21</v>
       </c>
       <c r="CC2" t="n">
         <v>1.55</v>
@@ -1613,52 +1613,52 @@
         <v>1.29</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.28</v>
+        <v>3.32</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CO2" t="n">
         <v>1.2</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="CR2" t="n">
         <v>1.37</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="CT2" t="n">
         <v>3.08</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CV2" t="n">
         <v>1.84</v>
@@ -1667,100 +1667,100 @@
         <v>2</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="DB2" t="n">
         <v>1.22</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.2</v>
+        <v>3.16</v>
       </c>
       <c r="DH2" t="n">
-        <v>116.29</v>
+        <v>116.44</v>
       </c>
       <c r="DI2" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="DJ2" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="DK2" t="n">
-        <v>6.34</v>
+        <v>6.28</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DM2" t="n">
-        <v>71.34</v>
+        <v>71.39</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="DO2" t="n">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="DP2" t="n">
-        <v>11.89</v>
+        <v>11.84</v>
       </c>
       <c r="DQ2" t="n">
-        <v>11.94</v>
+        <v>12.02</v>
       </c>
       <c r="DR2" t="n">
-        <v>5.68</v>
+        <v>5.58</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>57.51</v>
+        <v>57.64</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX2" t="n">
-        <v>16.71</v>
+        <v>16.61</v>
       </c>
       <c r="DY2" t="n">
-        <v>10.25</v>
+        <v>10.3</v>
       </c>
       <c r="DZ2" t="n">
-        <v>6.46</v>
+        <v>6.3</v>
       </c>
       <c r="EA2" t="n">
-        <v>22.52</v>
+        <v>22.44</v>
       </c>
       <c r="EB2" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="3">
@@ -1770,13 +1770,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C3" t="n">
         <v>18</v>
       </c>
       <c r="D3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E3" t="n">
         <v>0.17</v>
@@ -1863,136 +1863,136 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AI3" t="n">
-        <v>97.06</v>
+        <v>95.78</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="AL3" t="n">
-        <v>4.29</v>
+        <v>4.22</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="AN3" t="n">
-        <v>51.41</v>
+        <v>50.78</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AQ3" t="n">
-        <v>11.29</v>
+        <v>11.17</v>
       </c>
       <c r="AR3" t="n">
-        <v>13.59</v>
+        <v>13.44</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.529999999999999</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="AU3" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>45.53</v>
+        <v>45.28</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA3" t="n">
-        <v>11.59</v>
+        <v>11.11</v>
       </c>
       <c r="BB3" t="n">
-        <v>7.82</v>
+        <v>7.44</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.76</v>
+        <v>3.67</v>
       </c>
       <c r="BD3" t="n">
-        <v>20.76</v>
+        <v>20.61</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="BH3" t="n">
-        <v>8.77</v>
+        <v>8.81</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.77</v>
+        <v>3.81</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.31</v>
+        <v>4.33</v>
       </c>
       <c r="BR3" t="n">
-        <v>94.29000000000001</v>
+        <v>94.44</v>
       </c>
       <c r="BS3" t="n">
-        <v>71.43000000000001</v>
+        <v>72.22</v>
       </c>
       <c r="BT3" t="n">
-        <v>45.71</v>
+        <v>44.44</v>
       </c>
       <c r="BU3" t="n">
-        <v>25.71</v>
+        <v>25</v>
       </c>
       <c r="BV3" t="n">
-        <v>5.71</v>
+        <v>5.56</v>
       </c>
       <c r="BW3" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="BX3" t="n">
-        <v>51.43</v>
+        <v>50</v>
       </c>
       <c r="BY3" t="n">
         <v>2.94</v>
@@ -2001,22 +2001,22 @@
         <v>3.06</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.61</v>
+        <v>3.63</v>
       </c>
       <c r="CC3" t="n">
-        <v>4.86</v>
+        <v>4.91</v>
       </c>
       <c r="CD3" t="n">
-        <v>5.18</v>
+        <v>5.23</v>
       </c>
       <c r="CE3" t="n">
         <v>1.39</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="CG3" t="n">
         <v>2.82</v>
@@ -2034,10 +2034,10 @@
         <v>1.69</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CN3" t="n">
         <v>1.64</v>
@@ -2052,13 +2052,13 @@
         <v>3.42</v>
       </c>
       <c r="CR3" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CS3" t="n">
-        <v>3.03</v>
+        <v>3.01</v>
       </c>
       <c r="CT3" t="n">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="CU3" t="n">
         <v>1.39</v>
@@ -2082,88 +2082,88 @@
         <v>1.62</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="DC3" t="n">
         <v>2.06</v>
       </c>
       <c r="DD3" t="n">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="DH3" t="n">
-        <v>93.66</v>
+        <v>93.11</v>
       </c>
       <c r="DI3" t="n">
         <v>0.11</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="DK3" t="n">
-        <v>4.4</v>
+        <v>4.36</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="DM3" t="n">
-        <v>50</v>
+        <v>49.72</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="DP3" t="n">
-        <v>11.31</v>
+        <v>11.25</v>
       </c>
       <c r="DQ3" t="n">
-        <v>13.71</v>
+        <v>13.64</v>
       </c>
       <c r="DR3" t="n">
-        <v>8.34</v>
+        <v>8.48</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>46.66</v>
+        <v>46.5</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX3" t="n">
-        <v>10.97</v>
+        <v>10.75</v>
       </c>
       <c r="DY3" t="n">
-        <v>7.17</v>
+        <v>7</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="EA3" t="n">
-        <v>20.8</v>
+        <v>20.72</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="4">
@@ -2173,13 +2173,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C4" t="n">
         <v>18</v>
       </c>
       <c r="D4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2263,139 +2263,139 @@
         <v>1.89</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AH4" t="n">
         <v>2.06</v>
       </c>
       <c r="AI4" t="n">
-        <v>102.88</v>
+        <v>101.67</v>
       </c>
       <c r="AJ4" t="n">
         <v>0.06</v>
       </c>
       <c r="AK4" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="AL4" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="AN4" t="n">
-        <v>53.29</v>
+        <v>52.61</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="AP4" t="n">
         <v>1.06</v>
       </c>
       <c r="AQ4" t="n">
-        <v>12.47</v>
+        <v>12.33</v>
       </c>
       <c r="AR4" t="n">
-        <v>11.47</v>
+        <v>11.61</v>
       </c>
       <c r="AS4" t="n">
-        <v>9.59</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.12</v>
+        <v>2.33</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.71</v>
+        <v>0.83</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>41.18</v>
+        <v>40.89</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="BA4" t="n">
-        <v>8.880000000000001</v>
+        <v>8.83</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.35</v>
+        <v>6.28</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="BD4" t="n">
-        <v>21.76</v>
+        <v>22.06</v>
       </c>
       <c r="BE4" t="n">
         <v>1.13</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.71</v>
+        <v>2.61</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.89</v>
+        <v>3.06</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.25</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.89</v>
+        <v>3.06</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.66</v>
+        <v>0.72</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.54</v>
+        <v>0.58</v>
       </c>
       <c r="BL4" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="BM4" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.49</v>
+        <v>4.56</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.66</v>
+        <v>4.64</v>
       </c>
       <c r="BR4" t="n">
-        <v>97.14</v>
+        <v>97.22</v>
       </c>
       <c r="BS4" t="n">
-        <v>82.86</v>
+        <v>83.33</v>
       </c>
       <c r="BT4" t="n">
-        <v>57.14</v>
+        <v>58.33</v>
       </c>
       <c r="BU4" t="n">
-        <v>34.29</v>
+        <v>36.11</v>
       </c>
       <c r="BV4" t="n">
-        <v>14.29</v>
+        <v>16.67</v>
       </c>
       <c r="BW4" t="n">
-        <v>2.86</v>
+        <v>5.56</v>
       </c>
       <c r="BX4" t="n">
-        <v>60</v>
+        <v>61.11</v>
       </c>
       <c r="BY4" t="n">
         <v>4.53</v>
@@ -2404,34 +2404,34 @@
         <v>4.8</v>
       </c>
       <c r="CA4" t="n">
-        <v>4.09</v>
+        <v>4.12</v>
       </c>
       <c r="CB4" t="n">
-        <v>4.15</v>
+        <v>4.18</v>
       </c>
       <c r="CC4" t="n">
-        <v>6.12</v>
+        <v>6.22</v>
       </c>
       <c r="CD4" t="n">
-        <v>8.050000000000001</v>
+        <v>8.09</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CI4" t="n">
         <v>1.87</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CK4" t="n">
         <v>1.61</v>
@@ -2443,22 +2443,22 @@
         <v>2.03</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CO4" t="n">
         <v>1.25</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.05</v>
+        <v>3.03</v>
       </c>
       <c r="CR4" t="n">
         <v>1.38</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="CT4" t="n">
         <v>3.04</v>
@@ -2485,88 +2485,88 @@
         <v>1.72</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="DD4" t="n">
-        <v>3.19</v>
+        <v>3.17</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="DH4" t="n">
-        <v>111.83</v>
+        <v>110.98</v>
       </c>
       <c r="DI4" t="n">
         <v>0.03</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="DK4" t="n">
-        <v>3.49</v>
+        <v>3.47</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DM4" t="n">
-        <v>62.34</v>
+        <v>61.75</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="DP4" t="n">
-        <v>13.09</v>
+        <v>13</v>
       </c>
       <c r="DQ4" t="n">
-        <v>12</v>
+        <v>12.06</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.550000000000001</v>
+        <v>8.48</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>42.69</v>
+        <v>42.5</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX4" t="n">
-        <v>9.74</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.51</v>
+        <v>6.48</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="EA4" t="n">
-        <v>21.48</v>
+        <v>21.64</v>
       </c>
       <c r="EB4" t="n">
         <v>1.3</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="5">
@@ -2576,94 +2576,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D5" t="n">
         <v>18</v>
       </c>
       <c r="E5" t="n">
-        <v>0.24</v>
+        <v>0.28</v>
       </c>
       <c r="F5" t="n">
         <v>1.06</v>
       </c>
       <c r="G5" t="n">
-        <v>3.12</v>
+        <v>3.06</v>
       </c>
       <c r="H5" t="n">
-        <v>121.12</v>
+        <v>120.17</v>
       </c>
       <c r="I5" t="n">
         <v>0.06</v>
       </c>
       <c r="J5" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="K5" t="n">
-        <v>4.65</v>
+        <v>4.83</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="M5" t="n">
-        <v>67.41</v>
+        <v>66.83</v>
       </c>
       <c r="N5" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="O5" t="n">
-        <v>1.53</v>
+        <v>1.78</v>
       </c>
       <c r="P5" t="n">
-        <v>12.12</v>
+        <v>12.28</v>
       </c>
       <c r="Q5" t="n">
-        <v>14.65</v>
+        <v>14.33</v>
       </c>
       <c r="R5" t="n">
-        <v>5.35</v>
+        <v>5.39</v>
       </c>
       <c r="S5" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>1.59</v>
+        <v>1.83</v>
       </c>
       <c r="U5" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="V5" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>58.71</v>
+        <v>59</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="Z5" t="n">
-        <v>15.06</v>
+        <v>14.89</v>
       </c>
       <c r="AA5" t="n">
-        <v>9</v>
+        <v>8.67</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.06</v>
+        <v>6.22</v>
       </c>
       <c r="AC5" t="n">
-        <v>23.18</v>
+        <v>23.22</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AF5" t="n">
         <v>0.17</v>
@@ -2747,70 +2747,70 @@
         <v>2.28</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.51</v>
+        <v>2.69</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.26</v>
+        <v>9.31</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.51</v>
+        <v>2.69</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.89</v>
+        <v>3.97</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.29</v>
+        <v>5.25</v>
       </c>
       <c r="BR5" t="n">
-        <v>94.29000000000001</v>
+        <v>94.44</v>
       </c>
       <c r="BS5" t="n">
-        <v>80</v>
+        <v>80.56</v>
       </c>
       <c r="BT5" t="n">
-        <v>42.86</v>
+        <v>44.44</v>
       </c>
       <c r="BU5" t="n">
-        <v>25.71</v>
+        <v>27.78</v>
       </c>
       <c r="BV5" t="n">
-        <v>5.71</v>
+        <v>8.33</v>
       </c>
       <c r="BW5" t="n">
-        <v>2.86</v>
+        <v>5.56</v>
       </c>
       <c r="BX5" t="n">
-        <v>42.86</v>
+        <v>44.44</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.66</v>
+        <v>3.71</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.71</v>
+        <v>3.74</v>
       </c>
       <c r="CC5" t="n">
         <v>2.32</v>
@@ -2819,16 +2819,16 @@
         <v>2.41</v>
       </c>
       <c r="CE5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="CH5" t="n">
         <v>1.39</v>
-      </c>
-      <c r="CF5" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="CG5" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="CH5" t="n">
-        <v>1.38</v>
       </c>
       <c r="CI5" t="n">
         <v>1.81</v>
@@ -2849,19 +2849,19 @@
         <v>1.67</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.42</v>
+        <v>3.39</v>
       </c>
       <c r="CR5" t="n">
         <v>1.41</v>
       </c>
       <c r="CS5" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="CT5" t="n">
         <v>2.91</v>
@@ -2888,88 +2888,88 @@
         <v>1.68</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="DD5" t="n">
-        <v>3.58</v>
+        <v>3.54</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.2</v>
+        <v>0.23</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.03</v>
+        <v>3</v>
       </c>
       <c r="DH5" t="n">
-        <v>113.26</v>
+        <v>113</v>
       </c>
       <c r="DI5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.14</v>
+        <v>5.22</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.34</v>
+        <v>0.36</v>
       </c>
       <c r="DM5" t="n">
-        <v>64.84999999999999</v>
+        <v>64.64</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.74</v>
+        <v>0.72</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="DP5" t="n">
-        <v>12.49</v>
+        <v>12.56</v>
       </c>
       <c r="DQ5" t="n">
-        <v>14.43</v>
+        <v>14.27</v>
       </c>
       <c r="DR5" t="n">
-        <v>6.29</v>
+        <v>6.28</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>57.92</v>
+        <v>58.08</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX5" t="n">
-        <v>14.46</v>
+        <v>14.39</v>
       </c>
       <c r="DY5" t="n">
-        <v>9.09</v>
+        <v>8.92</v>
       </c>
       <c r="DZ5" t="n">
-        <v>5.37</v>
+        <v>5.47</v>
       </c>
       <c r="EA5" t="n">
-        <v>21.83</v>
+        <v>21.89</v>
       </c>
       <c r="EB5" t="n">
         <v>1.76</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="6">
@@ -2979,13 +2979,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C6" t="n">
         <v>18</v>
       </c>
       <c r="D6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E6" t="n">
         <v>0.22</v>
@@ -3069,52 +3069,52 @@
         <v>1.56</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AI6" t="n">
-        <v>102.47</v>
+        <v>101.61</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.35</v>
+        <v>2.39</v>
       </c>
       <c r="AL6" t="n">
-        <v>3.82</v>
+        <v>3.78</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="AN6" t="n">
         <v>54.94</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.76</v>
+        <v>0.89</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.06</v>
+        <v>1.94</v>
       </c>
       <c r="AQ6" t="n">
         <v>11</v>
       </c>
       <c r="AR6" t="n">
-        <v>11.06</v>
+        <v>11.44</v>
       </c>
       <c r="AS6" t="n">
-        <v>10.65</v>
+        <v>10.39</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AV6" t="n">
         <v>0.06</v>
@@ -3126,82 +3126,82 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>47.71</v>
+        <v>48.33</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>9.65</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="BB6" t="n">
-        <v>6.47</v>
+        <v>6.5</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.18</v>
+        <v>3.22</v>
       </c>
       <c r="BD6" t="n">
-        <v>23</v>
+        <v>22.89</v>
       </c>
       <c r="BE6" t="n">
         <v>1.24</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.35</v>
+        <v>2.39</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="BH6" t="n">
-        <v>10.14</v>
+        <v>10</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.57</v>
+        <v>0.61</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.77</v>
+        <v>0.75</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.49</v>
+        <v>0.47</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.54</v>
+        <v>4.47</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.97</v>
+        <v>4.92</v>
       </c>
       <c r="BR6" t="n">
-        <v>94.29000000000001</v>
+        <v>94.44</v>
       </c>
       <c r="BS6" t="n">
-        <v>74.29000000000001</v>
+        <v>75</v>
       </c>
       <c r="BT6" t="n">
-        <v>51.43</v>
+        <v>50</v>
       </c>
       <c r="BU6" t="n">
-        <v>20</v>
+        <v>19.44</v>
       </c>
       <c r="BV6" t="n">
-        <v>5.71</v>
+        <v>5.56</v>
       </c>
       <c r="BW6" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="BX6" t="n">
-        <v>54.29</v>
+        <v>52.78</v>
       </c>
       <c r="BY6" t="n">
         <v>3.02</v>
@@ -3213,10 +3213,10 @@
         <v>3.45</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.58</v>
+        <v>3.59</v>
       </c>
       <c r="CC6" t="n">
-        <v>4.14</v>
+        <v>4.07</v>
       </c>
       <c r="CD6" t="n">
         <v>4.65</v>
@@ -3228,16 +3228,16 @@
         <v>2.83</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="CH6" t="n">
         <v>1.39</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CK6" t="n">
         <v>1.71</v>
@@ -3246,7 +3246,7 @@
         <v>2.34</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CN6" t="n">
         <v>1.62</v>
@@ -3258,13 +3258,13 @@
         <v>1.98</v>
       </c>
       <c r="CQ6" t="n">
-        <v>3.38</v>
+        <v>3.36</v>
       </c>
       <c r="CR6" t="n">
         <v>1.41</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="CT6" t="n">
         <v>2.9</v>
@@ -3279,7 +3279,7 @@
         <v>1.9</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CY6" t="n">
         <v>2.18</v>
@@ -3297,49 +3297,49 @@
         <v>2.03</v>
       </c>
       <c r="DD6" t="n">
-        <v>3.54</v>
+        <v>3.53</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="DG6" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="DH6" t="n">
-        <v>105.77</v>
+        <v>105.25</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="DJ6" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.2</v>
+        <v>4.17</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.34</v>
+        <v>0.33</v>
       </c>
       <c r="DM6" t="n">
-        <v>57.51</v>
+        <v>57.44</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="DP6" t="n">
-        <v>11.48</v>
+        <v>11.47</v>
       </c>
       <c r="DQ6" t="n">
-        <v>11.54</v>
+        <v>11.72</v>
       </c>
       <c r="DR6" t="n">
-        <v>10.4</v>
+        <v>10.28</v>
       </c>
       <c r="DS6" t="n">
         <v>0.03</v>
@@ -3351,28 +3351,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>49.4</v>
+        <v>49.66</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>10.31</v>
+        <v>10.33</v>
       </c>
       <c r="DY6" t="n">
         <v>7.11</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="EA6" t="n">
-        <v>22.45</v>
+        <v>22.42</v>
       </c>
       <c r="EB6" t="n">
         <v>1.3</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="7">
@@ -3382,13 +3382,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C7" t="n">
         <v>18</v>
       </c>
       <c r="D7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3472,139 +3472,139 @@
         <v>2.06</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AH7" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="AI7" t="n">
-        <v>110.35</v>
+        <v>109.83</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="AL7" t="n">
-        <v>5.06</v>
+        <v>4.89</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AN7" t="n">
-        <v>60.94</v>
+        <v>60.5</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="AP7" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AQ7" t="n">
-        <v>14.24</v>
+        <v>14.28</v>
       </c>
       <c r="AR7" t="n">
-        <v>12.18</v>
+        <v>12.06</v>
       </c>
       <c r="AS7" t="n">
-        <v>7.53</v>
+        <v>7.67</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>52.82</v>
+        <v>52</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA7" t="n">
-        <v>9.65</v>
+        <v>9.56</v>
       </c>
       <c r="BB7" t="n">
-        <v>6.82</v>
+        <v>6.61</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.82</v>
+        <v>2.94</v>
       </c>
       <c r="BD7" t="n">
-        <v>22.12</v>
+        <v>22.06</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="BF7" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.91</v>
+        <v>8.83</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.6</v>
+        <v>0.58</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.77</v>
+        <v>0.75</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.77</v>
+        <v>3.75</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.14</v>
+        <v>5.08</v>
       </c>
       <c r="BR7" t="n">
-        <v>97.14</v>
+        <v>94.44</v>
       </c>
       <c r="BS7" t="n">
-        <v>91.43000000000001</v>
+        <v>88.89</v>
       </c>
       <c r="BT7" t="n">
-        <v>42.86</v>
+        <v>41.67</v>
       </c>
       <c r="BU7" t="n">
-        <v>20</v>
+        <v>19.44</v>
       </c>
       <c r="BV7" t="n">
-        <v>8.57</v>
+        <v>8.33</v>
       </c>
       <c r="BW7" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="BX7" t="n">
-        <v>65.70999999999999</v>
+        <v>63.89</v>
       </c>
       <c r="BY7" t="n">
         <v>3</v>
@@ -3613,34 +3613,34 @@
         <v>3.21</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.53</v>
+        <v>3.58</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.58</v>
+        <v>3.65</v>
       </c>
       <c r="CC7" t="n">
-        <v>4.18</v>
+        <v>4.41</v>
       </c>
       <c r="CD7" t="n">
-        <v>4.44</v>
+        <v>4.77</v>
       </c>
       <c r="CE7" t="n">
         <v>1.37</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.79</v>
+        <v>2.77</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.86</v>
+        <v>2.91</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CK7" t="n">
         <v>1.58</v>
@@ -3649,31 +3649,31 @@
         <v>2.14</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="CQ7" t="n">
-        <v>3.26</v>
+        <v>3.22</v>
       </c>
       <c r="CR7" t="n">
         <v>1.39</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="CT7" t="n">
         <v>3</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="CV7" t="n">
         <v>1.96</v>
@@ -3682,67 +3682,67 @@
         <v>1.85</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CY7" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="DB7" t="n">
         <v>1.3</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="DD7" t="n">
-        <v>3.43</v>
+        <v>3.38</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="DH7" t="n">
-        <v>105.83</v>
+        <v>105.7</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.63</v>
+        <v>4.56</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DM7" t="n">
-        <v>59.14</v>
+        <v>58.97</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.77</v>
+        <v>0.75</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="DP7" t="n">
-        <v>14.15</v>
+        <v>14.17</v>
       </c>
       <c r="DQ7" t="n">
-        <v>12.38</v>
+        <v>12.31</v>
       </c>
       <c r="DR7" t="n">
-        <v>7.43</v>
+        <v>7.5</v>
       </c>
       <c r="DS7" t="n">
         <v>0.2</v>
@@ -3754,28 +3754,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>50.43</v>
+        <v>50.08</v>
       </c>
       <c r="DW7" t="n">
         <v>0.11</v>
       </c>
       <c r="DX7" t="n">
-        <v>10.23</v>
+        <v>10.17</v>
       </c>
       <c r="DY7" t="n">
-        <v>6.91</v>
+        <v>6.81</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.31</v>
+        <v>3.36</v>
       </c>
       <c r="EA7" t="n">
-        <v>22.06</v>
+        <v>22.03</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.03</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="8">
@@ -3785,10 +3785,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D8" t="n">
         <v>18</v>
@@ -3797,49 +3797,49 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="G8" t="n">
-        <v>3.06</v>
+        <v>3.28</v>
       </c>
       <c r="H8" t="n">
-        <v>118.47</v>
+        <v>115.39</v>
       </c>
       <c r="I8" t="n">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="J8" t="n">
-        <v>2.35</v>
+        <v>2.22</v>
       </c>
       <c r="K8" t="n">
-        <v>5.71</v>
+        <v>6.28</v>
       </c>
       <c r="L8" t="n">
-        <v>0.59</v>
+        <v>0.72</v>
       </c>
       <c r="M8" t="n">
-        <v>78.29000000000001</v>
+        <v>76.72</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>2.59</v>
+        <v>2.94</v>
       </c>
       <c r="P8" t="n">
-        <v>14.06</v>
+        <v>14.33</v>
       </c>
       <c r="Q8" t="n">
-        <v>13.65</v>
+        <v>13.56</v>
       </c>
       <c r="R8" t="n">
-        <v>6.24</v>
+        <v>6.39</v>
       </c>
       <c r="S8" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="T8" t="n">
-        <v>0.59</v>
+        <v>0.67</v>
       </c>
       <c r="U8" t="n">
         <v>0.06</v>
@@ -3851,28 +3851,28 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>51.53</v>
+        <v>51.61</v>
       </c>
       <c r="Y8" t="n">
         <v>0.06</v>
       </c>
       <c r="Z8" t="n">
-        <v>13.18</v>
+        <v>13.78</v>
       </c>
       <c r="AA8" t="n">
-        <v>9.59</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.59</v>
+        <v>3.89</v>
       </c>
       <c r="AC8" t="n">
-        <v>21.71</v>
+        <v>21.39</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.29</v>
+        <v>2.17</v>
       </c>
       <c r="AF8" t="n">
         <v>0.11</v>
@@ -3959,61 +3959,61 @@
         <v>2.11</v>
       </c>
       <c r="BH8" t="n">
-        <v>10</v>
+        <v>10.22</v>
       </c>
       <c r="BI8" t="n">
         <v>2.11</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="BO8" t="n">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.94</v>
+        <v>5.11</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.03</v>
+        <v>5.08</v>
       </c>
       <c r="BR8" t="n">
-        <v>80</v>
+        <v>80.56</v>
       </c>
       <c r="BS8" t="n">
-        <v>62.86</v>
+        <v>63.89</v>
       </c>
       <c r="BT8" t="n">
-        <v>31.43</v>
+        <v>30.56</v>
       </c>
       <c r="BU8" t="n">
-        <v>17.14</v>
+        <v>16.67</v>
       </c>
       <c r="BV8" t="n">
-        <v>8.57</v>
+        <v>8.33</v>
       </c>
       <c r="BW8" t="n">
-        <v>8.57</v>
+        <v>8.33</v>
       </c>
       <c r="BX8" t="n">
-        <v>31.43</v>
+        <v>30.56</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="CA8" t="n">
         <v>3.43</v>
@@ -4031,10 +4031,10 @@
         <v>1.4</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="CH8" t="n">
         <v>1.38</v>
@@ -4043,13 +4043,13 @@
         <v>1.88</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CK8" t="n">
         <v>1.58</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CM8" t="n">
         <v>2.22</v>
@@ -4061,10 +4061,10 @@
         <v>1.29</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.36</v>
+        <v>3.34</v>
       </c>
       <c r="CR8" t="n">
         <v>1.42</v>
@@ -4100,52 +4100,52 @@
         <v>1.33</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="DE8" t="n">
         <v>0.06</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.46</v>
+        <v>2.58</v>
       </c>
       <c r="DH8" t="n">
-        <v>108.43</v>
+        <v>107.16</v>
       </c>
       <c r="DI8" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.74</v>
+        <v>5.06</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.6</v>
+        <v>0.66</v>
       </c>
       <c r="DM8" t="n">
-        <v>65.2</v>
+        <v>64.78</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.26</v>
+        <v>2.44</v>
       </c>
       <c r="DP8" t="n">
-        <v>14.74</v>
+        <v>14.86</v>
       </c>
       <c r="DQ8" t="n">
-        <v>13.15</v>
+        <v>13.12</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.06</v>
+        <v>7.11</v>
       </c>
       <c r="DS8" t="n">
         <v>0.03</v>
@@ -4157,28 +4157,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>49.26</v>
+        <v>49.36</v>
       </c>
       <c r="DW8" t="n">
         <v>0.12</v>
       </c>
       <c r="DX8" t="n">
-        <v>12.12</v>
+        <v>12.44</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.630000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.49</v>
+        <v>3.64</v>
       </c>
       <c r="EA8" t="n">
-        <v>21.46</v>
+        <v>21.3</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="9">
@@ -4188,61 +4188,61 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D9" t="n">
         <v>18</v>
       </c>
       <c r="E9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F9" t="n">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="G9" t="n">
-        <v>3.76</v>
+        <v>3.72</v>
       </c>
       <c r="H9" t="n">
-        <v>119.88</v>
+        <v>120.56</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2.35</v>
+        <v>2.22</v>
       </c>
       <c r="K9" t="n">
         <v>7</v>
       </c>
       <c r="L9" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="M9" t="n">
-        <v>72.23999999999999</v>
+        <v>72.78</v>
       </c>
       <c r="N9" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="O9" t="n">
-        <v>3.24</v>
+        <v>3.28</v>
       </c>
       <c r="P9" t="n">
-        <v>12.35</v>
+        <v>12.28</v>
       </c>
       <c r="Q9" t="n">
-        <v>13.35</v>
+        <v>13.11</v>
       </c>
       <c r="R9" t="n">
-        <v>6.76</v>
+        <v>6.78</v>
       </c>
       <c r="S9" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="T9" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="U9" t="n">
         <v>0.06</v>
@@ -4254,28 +4254,28 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>55</v>
+        <v>55.22</v>
       </c>
       <c r="Y9" t="n">
         <v>0.06</v>
       </c>
       <c r="Z9" t="n">
-        <v>16.29</v>
+        <v>16.56</v>
       </c>
       <c r="AA9" t="n">
-        <v>11.35</v>
+        <v>11.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.94</v>
+        <v>5.06</v>
       </c>
       <c r="AC9" t="n">
-        <v>24.53</v>
+        <v>24.33</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.24</v>
+        <v>2.11</v>
       </c>
       <c r="AF9" t="n">
         <v>0.17</v>
@@ -4359,70 +4359,70 @@
         <v>2.33</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="BH9" t="n">
         <v>10.11</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.49</v>
+        <v>0.47</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.31</v>
+        <v>4.33</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.8</v>
+        <v>5.78</v>
       </c>
       <c r="BR9" t="n">
-        <v>85.70999999999999</v>
+        <v>86.11</v>
       </c>
       <c r="BS9" t="n">
-        <v>68.56999999999999</v>
+        <v>69.44</v>
       </c>
       <c r="BT9" t="n">
-        <v>42.86</v>
+        <v>41.67</v>
       </c>
       <c r="BU9" t="n">
-        <v>28.57</v>
+        <v>27.78</v>
       </c>
       <c r="BV9" t="n">
-        <v>8.57</v>
+        <v>8.33</v>
       </c>
       <c r="BW9" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="BX9" t="n">
-        <v>40</v>
+        <v>38.89</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="BZ9" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.54</v>
+        <v>3.55</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.66</v>
+        <v>3.68</v>
       </c>
       <c r="CC9" t="n">
         <v>2.88</v>
@@ -4431,16 +4431,16 @@
         <v>3.14</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CI9" t="n">
         <v>1.8</v>
@@ -4449,10 +4449,10 @@
         <v>1.91</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="CM9" t="n">
         <v>2.03</v>
@@ -4464,19 +4464,19 @@
         <v>1.31</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CQ9" t="n">
         <v>3.46</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CS9" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="CU9" t="n">
         <v>1.38</v>
@@ -4488,10 +4488,10 @@
         <v>1.97</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CY9" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CZ9" t="n">
         <v>2.11</v>
@@ -4503,52 +4503,52 @@
         <v>1.34</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="DD9" t="n">
-        <v>3.69</v>
+        <v>3.67</v>
       </c>
       <c r="DE9" t="n">
         <v>0.17</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="DG9" t="n">
-        <v>3.34</v>
+        <v>3.33</v>
       </c>
       <c r="DH9" t="n">
-        <v>114.83</v>
+        <v>115.31</v>
       </c>
       <c r="DI9" t="n">
         <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.54</v>
+        <v>2.47</v>
       </c>
       <c r="DK9" t="n">
-        <v>6.26</v>
+        <v>6.28</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
       <c r="DM9" t="n">
-        <v>65.45999999999999</v>
+        <v>65.92</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.8</v>
+        <v>0.78</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="DP9" t="n">
-        <v>12.54</v>
+        <v>12.5</v>
       </c>
       <c r="DQ9" t="n">
-        <v>13.11</v>
+        <v>13</v>
       </c>
       <c r="DR9" t="n">
-        <v>6.77</v>
+        <v>6.78</v>
       </c>
       <c r="DS9" t="n">
         <v>0.2</v>
@@ -4560,28 +4560,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>52.65</v>
+        <v>52.83</v>
       </c>
       <c r="DW9" t="n">
         <v>0.14</v>
       </c>
       <c r="DX9" t="n">
-        <v>14.34</v>
+        <v>14.53</v>
       </c>
       <c r="DY9" t="n">
-        <v>10.31</v>
+        <v>10.42</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.03</v>
+        <v>4.11</v>
       </c>
       <c r="EA9" t="n">
-        <v>23.89</v>
+        <v>23.8</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.29</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="10">
@@ -4591,13 +4591,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10" t="n">
         <v>18</v>
       </c>
       <c r="D10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E10" t="n">
         <v>0.22</v>
@@ -4684,136 +4684,136 @@
         <v>0.06</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AI10" t="n">
-        <v>106.76</v>
+        <v>104.22</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.24</v>
+        <v>2.11</v>
       </c>
       <c r="AL10" t="n">
-        <v>3.59</v>
+        <v>3.5</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="AN10" t="n">
-        <v>51.94</v>
+        <v>50.39</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AQ10" t="n">
-        <v>13.94</v>
+        <v>13.83</v>
       </c>
       <c r="AR10" t="n">
-        <v>12.41</v>
+        <v>12.78</v>
       </c>
       <c r="AS10" t="n">
-        <v>8.35</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="AT10" t="n">
         <v>2</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>46.12</v>
+        <v>46.17</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA10" t="n">
-        <v>10.41</v>
+        <v>10.39</v>
       </c>
       <c r="BB10" t="n">
-        <v>7.18</v>
+        <v>7.22</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.24</v>
+        <v>3.17</v>
       </c>
       <c r="BD10" t="n">
-        <v>20.94</v>
+        <v>20.17</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="BF10" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="BG10" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="BH10" t="n">
-        <v>7.63</v>
+        <v>7.92</v>
       </c>
       <c r="BI10" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.77</v>
+        <v>0.75</v>
       </c>
       <c r="BL10" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.29</v>
+        <v>3.5</v>
       </c>
       <c r="BQ10" t="n">
-        <v>3.8</v>
+        <v>3.89</v>
       </c>
       <c r="BR10" t="n">
-        <v>91.43000000000001</v>
+        <v>91.67</v>
       </c>
       <c r="BS10" t="n">
-        <v>85.70999999999999</v>
+        <v>86.11</v>
       </c>
       <c r="BT10" t="n">
-        <v>62.86</v>
+        <v>61.11</v>
       </c>
       <c r="BU10" t="n">
-        <v>37.14</v>
+        <v>36.11</v>
       </c>
       <c r="BV10" t="n">
-        <v>14.29</v>
+        <v>13.89</v>
       </c>
       <c r="BW10" t="n">
-        <v>5.71</v>
+        <v>5.56</v>
       </c>
       <c r="BX10" t="n">
-        <v>68.56999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BY10" t="n">
         <v>2.9</v>
@@ -4822,22 +4822,22 @@
         <v>3.02</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.44</v>
+        <v>3.43</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.54</v>
+        <v>3.53</v>
       </c>
       <c r="CC10" t="n">
-        <v>4.35</v>
+        <v>4.29</v>
       </c>
       <c r="CD10" t="n">
-        <v>4.99</v>
+        <v>4.88</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="CG10" t="n">
         <v>2.86</v>
@@ -4849,7 +4849,7 @@
         <v>1.89</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CK10" t="n">
         <v>1.71</v>
@@ -4858,10 +4858,10 @@
         <v>2.39</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CO10" t="n">
         <v>1.28</v>
@@ -4870,7 +4870,7 @@
         <v>1.95</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.32</v>
+        <v>3.31</v>
       </c>
       <c r="CR10" t="n">
         <v>1.41</v>
@@ -4909,82 +4909,82 @@
         <v>2.02</v>
       </c>
       <c r="DD10" t="n">
-        <v>3.49</v>
+        <v>3.48</v>
       </c>
       <c r="DE10" t="n">
         <v>0.14</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="DG10" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="DH10" t="n">
-        <v>107.97</v>
+        <v>106.66</v>
       </c>
       <c r="DI10" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.17</v>
+        <v>2.11</v>
       </c>
       <c r="DK10" t="n">
-        <v>3.86</v>
+        <v>3.81</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DM10" t="n">
-        <v>54.32</v>
+        <v>53.47</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="DP10" t="n">
-        <v>13.37</v>
+        <v>13.33</v>
       </c>
       <c r="DQ10" t="n">
-        <v>12.43</v>
+        <v>12.61</v>
       </c>
       <c r="DR10" t="n">
-        <v>8.08</v>
+        <v>8.02</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>48.66</v>
+        <v>48.62</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX10" t="n">
-        <v>12.26</v>
+        <v>12.2</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.4</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.86</v>
+        <v>3.81</v>
       </c>
       <c r="EA10" t="n">
-        <v>22.6</v>
+        <v>22.17</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="11">
@@ -4994,94 +4994,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D11" t="n">
         <v>18</v>
       </c>
       <c r="E11" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="F11" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="G11" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="H11" t="n">
-        <v>105.18</v>
+        <v>102.78</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="K11" t="n">
-        <v>3.76</v>
+        <v>3.67</v>
       </c>
       <c r="L11" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="M11" t="n">
-        <v>54</v>
+        <v>52.72</v>
       </c>
       <c r="N11" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="O11" t="n">
         <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>12</v>
+        <v>12.33</v>
       </c>
       <c r="Q11" t="n">
-        <v>13.12</v>
+        <v>12.89</v>
       </c>
       <c r="R11" t="n">
-        <v>7.65</v>
+        <v>7.67</v>
       </c>
       <c r="S11" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="T11" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="U11" t="n">
-        <v>0.24</v>
+        <v>0.33</v>
       </c>
       <c r="V11" t="n">
-        <v>0.24</v>
+        <v>0.33</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>46.12</v>
+        <v>45.83</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z11" t="n">
-        <v>12.47</v>
+        <v>12.44</v>
       </c>
       <c r="AA11" t="n">
-        <v>8.59</v>
+        <v>8.33</v>
       </c>
       <c r="AB11" t="n">
-        <v>3.88</v>
+        <v>4.11</v>
       </c>
       <c r="AC11" t="n">
-        <v>22.47</v>
+        <v>22.28</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="AF11" t="n">
         <v>0.06</v>
@@ -5165,70 +5165,70 @@
         <v>2.11</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.710000000000001</v>
+        <v>9.58</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.77</v>
+        <v>0.75</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.49</v>
+        <v>0.47</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.23</v>
+        <v>4.17</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.97</v>
+        <v>4.92</v>
       </c>
       <c r="BR11" t="n">
-        <v>94.29000000000001</v>
+        <v>94.44</v>
       </c>
       <c r="BS11" t="n">
-        <v>82.86</v>
+        <v>83.33</v>
       </c>
       <c r="BT11" t="n">
-        <v>48.57</v>
+        <v>47.22</v>
       </c>
       <c r="BU11" t="n">
-        <v>28.57</v>
+        <v>27.78</v>
       </c>
       <c r="BV11" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="BW11" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="BX11" t="n">
-        <v>62.86</v>
+        <v>61.11</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.86</v>
+        <v>2.83</v>
       </c>
       <c r="BZ11" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="CA11" t="n">
         <v>3.44</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.51</v>
+        <v>3.52</v>
       </c>
       <c r="CC11" t="n">
         <v>4.17</v>
@@ -5237,28 +5237,28 @@
         <v>4.89</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="CH11" t="n">
         <v>1.37</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CK11" t="n">
         <v>1.7</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CM11" t="n">
         <v>2.04</v>
@@ -5273,16 +5273,16 @@
         <v>2.03</v>
       </c>
       <c r="CQ11" t="n">
-        <v>3.47</v>
+        <v>3.45</v>
       </c>
       <c r="CR11" t="n">
         <v>1.43</v>
       </c>
       <c r="CS11" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="CT11" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="CU11" t="n">
         <v>1.39</v>
@@ -5294,10 +5294,10 @@
         <v>1.92</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CZ11" t="n">
         <v>2.04</v>
@@ -5312,82 +5312,82 @@
         <v>2.09</v>
       </c>
       <c r="DD11" t="n">
-        <v>3.68</v>
+        <v>3.67</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="DG11" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="DH11" t="n">
-        <v>99.72</v>
+        <v>98.67</v>
       </c>
       <c r="DI11" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="DK11" t="n">
-        <v>3.68</v>
+        <v>3.64</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="DM11" t="n">
-        <v>51.54</v>
+        <v>50.97</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="DP11" t="n">
-        <v>12.48</v>
+        <v>12.64</v>
       </c>
       <c r="DQ11" t="n">
-        <v>12.51</v>
+        <v>12.42</v>
       </c>
       <c r="DR11" t="n">
         <v>8.029999999999999</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>44.83</v>
+        <v>44.72</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DX11" t="n">
-        <v>11.51</v>
+        <v>11.52</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.74</v>
+        <v>7.64</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.77</v>
+        <v>3.89</v>
       </c>
       <c r="EA11" t="n">
-        <v>21.06</v>
+        <v>21</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
     </row>
   </sheetData>
